--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -5,19 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE49ECE-3D90-4E41-83F3-C8B0E95A7864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30496EF-BCB5-40AB-A297-AE3A5608564F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Export!$A$1:$V$117</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -105,6 +102,9 @@
     <t>Pregão</t>
   </si>
   <si>
+    <t>SISLOG 118144 Aquisição de Painéis de LED</t>
+  </si>
+  <si>
     <t>SUTIS</t>
   </si>
   <si>
@@ -837,7 +837,7 @@
     <t>SISLOG 120357 - Aquisição de Workstations - Atender demandas da SES-GO</t>
   </si>
   <si>
-    <t>EM ELABORAÇÃO</t>
+    <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS</t>
   </si>
   <si>
     <t>202600010023321</t>
@@ -849,10 +849,7 @@
     <t>Doação de 105 desktops para o CISCENO</t>
   </si>
   <si>
-    <t>PROCSET</t>
-  </si>
-  <si>
-    <t>PARA PARECER</t>
+    <t>PARA CONTINUIDADE</t>
   </si>
   <si>
     <t>Em Renovação</t>
@@ -942,10 +939,7 @@
     <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
   </si>
   <si>
-    <t>GELIC</t>
-  </si>
-  <si>
-    <t>Comprovante de não entrega de proposta readequada (pós repregoamento)</t>
+    <t>Solicitação de Parecer Técnico</t>
   </si>
   <si>
     <t>SESG</t>
@@ -999,7 +993,7 @@
     <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 9</t>
   </si>
   <si>
-    <t>AGUARDANDO CERTIDÕES</t>
+    <t>AGUARDANDO CERTIDÕES E ACERTOS NAS LICENÇAS. ENVIADA CORRESPONDÊNCIA COBRANDO AGILIDADE</t>
   </si>
   <si>
     <t>09/2026</t>
@@ -1021,7 +1015,7 @@
 / INTERMEDIÁRIO  ADITIVO (12) notebooks /valor R$55.200</t>
   </si>
   <si>
-    <t>PARA PROVIDÊNCIAS APÓS ASSINATURA SECRETÁRIO</t>
+    <t>PARA GESTÃO</t>
   </si>
   <si>
     <t>77/2025</t>
@@ -1115,8 +1109,7 @@
     <t>ACCESS POINT</t>
   </si>
   <si>
-    <t>à Superintendência de Tecnologia, Inovação e Saúde Digital para atendimento das alíneas "c", 
-C) adequação da pesquisa de preços (subitem 7.6);</t>
+    <t>DOCUMENTOS ANEXADOS EM ATENDIMENTO AO  Despacho 242 (91579824)</t>
   </si>
   <si>
     <t>202300010002563</t>
@@ -1218,7 +1211,7 @@
     <t>AQUISIÇÃO DE 40 LICENÇAS AUTODESK AEC DA CS CAD CAM LTDA</t>
   </si>
   <si>
-    <t>Contrato 64 (91152954) EM ELABORAÇÃO</t>
+    <t>PROCSET</t>
   </si>
   <si>
     <t>202600010020471</t>
@@ -1272,6 +1265,9 @@
     <t>Novo Termo de Cooperação entre UFG e SES para realização de capacitação continuada em padrão FHIR.</t>
   </si>
   <si>
+    <t>AGUARDANDO Parecer  Jurídico. 426 (91304192)</t>
+  </si>
+  <si>
     <t>202400005009120</t>
   </si>
   <si>
@@ -1335,7 +1331,7 @@
     <t>FORNECEDOR INDRA. Serviços Técnicos na área de Tecnologia da Informação para suprir as demandas de subscrições Cloudera para atualização do ecossistema Hadoop</t>
   </si>
   <si>
-    <t>ANÁLISE DA MINUTA</t>
+    <t>CERTIDÕES E DOCUMENTOS ANEXADOS</t>
   </si>
   <si>
     <t>58/2022</t>
@@ -1390,7 +1386,10 @@
     <t>FORNECEDOR OTC DOC ORGANIZACAO TECNOLOGIA E CUSTODIA DE DOCUMENTOS. Contratação de empresa especializada em digitalização de documentos</t>
   </si>
   <si>
-    <t>SOLICITAÇÃO DE ORÇAMENTOS A FORNECEDORES. AGUARDAR ATÉ DIA 08/06</t>
+    <t>GEFIN</t>
+  </si>
+  <si>
+    <t>ANEXO II emitido, DAOF E IPOF</t>
   </si>
   <si>
     <t>64/2023</t>
@@ -1457,9 +1456,6 @@
   </si>
   <si>
     <t xml:space="preserve"> SUSPENSO</t>
-  </si>
-  <si>
-    <t>SISLOG 118144 Aquisição de Painéis de LED</t>
   </si>
 </sst>
 </file>
@@ -1467,17 +1463,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="7" formatCode="&quot;R$&quot;\ #,##0.00;\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1509,14 +1500,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1834,17 +1823,13 @@
   <dimension ref="A1:V117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.42578125" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.85546875" customWidth="1"/>
     <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1911,7 +1896,7 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1929,33 +1914,34 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>467</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2">
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
+      <c r="V2" s="4"/>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2">
         <v>45008</v>
@@ -1964,134 +1950,137 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2">
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
+      <c r="V3" s="4"/>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2">
         <v>45383</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2">
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
+      <c r="V4" s="4"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2">
         <v>45784</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2">
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
+      <c r="V5" s="4"/>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>43091</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2">
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1034</v>
+        <v>1043</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M6" s="3"/>
       <c r="O6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P6" s="2">
         <v>45336</v>
@@ -2101,13 +2090,14 @@
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
+      <c r="V6" s="4"/>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2">
         <v>43516</v>
@@ -2116,25 +2106,25 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H7" s="2">
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1035</v>
+        <v>1044</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7" s="2">
         <v>44047</v>
@@ -2143,7 +2133,7 @@
         <v>531</v>
       </c>
       <c r="O7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P7" s="2">
         <v>46023</v>
@@ -2153,13 +2143,14 @@
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
+      <c r="V7" s="4"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="2">
         <v>43770</v>
@@ -2168,25 +2159,25 @@
         <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2">
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>977</v>
+        <v>986</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L8" s="2">
         <v>44176</v>
@@ -2195,7 +2186,7 @@
         <v>406</v>
       </c>
       <c r="O8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P8" s="2">
         <v>45646</v>
@@ -2205,13 +2196,14 @@
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
+      <c r="V8" s="4"/>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>43902</v>
@@ -2220,29 +2212,29 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2">
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="J9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M9" s="3"/>
       <c r="O9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P9" s="2">
         <v>45794</v>
@@ -2252,13 +2244,14 @@
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
+      <c r="V9" s="4"/>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2">
         <v>44176</v>
@@ -2267,29 +2260,29 @@
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" s="2">
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="J10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M10" s="3"/>
       <c r="O10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P10" s="2">
         <v>45505</v>
@@ -2299,44 +2292,45 @@
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
+      <c r="V10" s="4"/>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>44181</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H11" s="2">
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M11" s="3"/>
       <c r="O11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P11" s="2">
         <v>45499</v>
@@ -2346,40 +2340,41 @@
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
+      <c r="V11" s="4"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" s="2">
         <v>44448</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2">
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="J12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L12" s="2">
         <v>44727</v>
@@ -2392,13 +2387,14 @@
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" s="2">
         <v>44628</v>
@@ -2407,25 +2403,25 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H13" s="2">
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L13" s="2">
         <v>45040</v>
@@ -2438,13 +2434,14 @@
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
+      <c r="V13" s="4"/>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" s="2">
         <v>44628</v>
@@ -2453,25 +2450,25 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2">
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1021</v>
+        <v>1030</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L14" s="2">
         <v>45040</v>
@@ -2484,13 +2481,14 @@
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
+      <c r="V14" s="4"/>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" s="2">
         <v>44628</v>
@@ -2499,25 +2497,25 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2">
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="J15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L15" s="2">
         <v>45040</v>
@@ -2530,13 +2528,14 @@
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
+      <c r="V15" s="4"/>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2">
         <v>44628</v>
@@ -2545,25 +2544,25 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2">
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="J16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L16" s="2">
         <v>45040</v>
@@ -2576,13 +2575,14 @@
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="1:21">
+      <c r="V16" s="4"/>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" s="2">
         <v>44628</v>
@@ -2591,25 +2591,25 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2">
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L17" s="2">
         <v>45040</v>
@@ -2622,13 +2622,14 @@
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="V17" s="4"/>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="2">
         <v>44628</v>
@@ -2637,25 +2638,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2">
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="J18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L18" s="2">
         <v>45040</v>
@@ -2668,13 +2669,14 @@
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18" s="4"/>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="2">
         <v>44628</v>
@@ -2683,25 +2685,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H19" s="2">
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L19" s="2">
         <v>45040</v>
@@ -2714,13 +2716,14 @@
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19" s="4"/>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" s="2">
         <v>44713</v>
@@ -2729,33 +2732,34 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H20" s="2">
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1141</v>
+        <v>1150</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20" s="4"/>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2">
         <v>44715</v>
@@ -2764,25 +2768,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H21" s="2">
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1023</v>
+        <v>1032</v>
       </c>
       <c r="J21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L21" s="2">
         <v>45112</v>
@@ -2795,40 +2799,41 @@
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21" s="4"/>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" s="2">
         <v>44721</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2">
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1267</v>
+        <v>1276</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L22" s="2">
         <v>44893</v>
@@ -2841,57 +2846,59 @@
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
-    </row>
-    <row r="23" spans="1:21">
+      <c r="V22" s="4"/>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C23" s="2">
         <v>44741</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H23" s="2">
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="J23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S23" s="2">
         <v>45220</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
-    </row>
-    <row r="24" spans="1:21">
+      <c r="V23" s="4"/>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" s="2">
         <v>44883</v>
@@ -2900,33 +2907,34 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H24" s="2">
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="J24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
-    </row>
-    <row r="25" spans="1:21">
+      <c r="V24" s="4"/>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C25" s="2">
         <v>44911</v>
@@ -2935,25 +2943,25 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25" s="2">
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L25" s="2">
         <v>45217</v>
@@ -2966,13 +2974,14 @@
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
-    </row>
-    <row r="26" spans="1:21">
+      <c r="V25" s="4"/>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C26" s="2">
         <v>44911</v>
@@ -2981,25 +2990,25 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H26" s="2">
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="J26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L26" s="2">
         <v>45217</v>
@@ -3012,13 +3021,14 @@
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
-    </row>
-    <row r="27" spans="1:21">
+      <c r="V26" s="4"/>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27" s="2">
         <v>45229</v>
@@ -3027,25 +3037,25 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H27" s="2">
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="J27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M27" s="3"/>
       <c r="S27" s="2">
@@ -3053,40 +3063,41 @@
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
-    </row>
-    <row r="28" spans="1:21">
+      <c r="V27" s="4"/>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C28" s="2">
         <v>44949</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H28" s="2">
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1041</v>
+        <v>1050</v>
       </c>
       <c r="J28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L28" s="2">
         <v>45112</v>
@@ -3099,48 +3110,50 @@
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
-    </row>
-    <row r="29" spans="1:21">
+      <c r="V28" s="4"/>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C29" s="2">
         <v>44988</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H29" s="2">
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="J29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
-    </row>
-    <row r="30" spans="1:21">
+      <c r="V29" s="4"/>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C30" s="2">
         <v>45015</v>
@@ -3149,33 +3162,34 @@
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H30" s="2">
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="J30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
-    </row>
-    <row r="31" spans="1:21">
+      <c r="V30" s="4"/>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C31" s="2">
         <v>45027</v>
@@ -3184,60 +3198,61 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H31" s="2">
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="J31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M31" s="3"/>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
-    </row>
-    <row r="32" spans="1:21">
+      <c r="V31" s="4"/>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C32" s="2">
         <v>45030</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H32" s="2">
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1000</v>
+        <v>1009</v>
       </c>
       <c r="J32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L32" s="2">
         <v>45161</v>
@@ -3250,13 +3265,14 @@
       </c>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
-    </row>
-    <row r="33" spans="1:21">
+      <c r="V32" s="4"/>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C33" s="2">
         <v>45056</v>
@@ -3265,25 +3281,25 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H33" s="2">
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="J33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L33" s="2">
         <v>45400</v>
@@ -3296,48 +3312,50 @@
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
-    </row>
-    <row r="34" spans="1:21">
+      <c r="V33" s="4"/>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C34" s="2">
         <v>45056</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H34" s="2">
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="J34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
-    </row>
-    <row r="35" spans="1:21">
+      <c r="V34" s="4"/>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C35" s="2">
         <v>45069</v>
@@ -3346,33 +3364,34 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H35" s="2">
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="J35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
-    </row>
-    <row r="36" spans="1:21">
+      <c r="V35" s="4"/>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C36" s="2">
         <v>45063</v>
@@ -3381,60 +3400,61 @@
         <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H36" s="2">
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="J36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
-    </row>
-    <row r="37" spans="1:21">
+      <c r="V36" s="4"/>
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C37" s="2">
         <v>45063</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H37" s="2">
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="J37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L37" s="2">
         <v>45236</v>
@@ -3447,13 +3467,14 @@
       </c>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
-    </row>
-    <row r="38" spans="1:21">
+      <c r="V37" s="4"/>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C38" s="2">
         <v>45065</v>
@@ -3462,33 +3483,34 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H38" s="2">
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="J38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
-    </row>
-    <row r="39" spans="1:21">
+      <c r="V38" s="4"/>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C39" s="2">
         <v>45092</v>
@@ -3497,25 +3519,25 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H39" s="2">
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="J39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L39" s="2">
         <v>45569</v>
@@ -3524,20 +3546,21 @@
         <v>477</v>
       </c>
       <c r="O39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S39" s="2">
         <v>45805</v>
       </c>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="1:21">
+      <c r="V39" s="4"/>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2">
         <v>45106</v>
@@ -3546,60 +3569,61 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H40" s="2">
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="J40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="1:21">
+      <c r="V40" s="4"/>
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C41" s="2">
         <v>45128</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="2">
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="J41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L41" s="2">
         <v>45229</v>
@@ -3612,13 +3636,14 @@
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
-    </row>
-    <row r="42" spans="1:21">
+      <c r="V41" s="4"/>
+    </row>
+    <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C42" s="2">
         <v>45307</v>
@@ -3627,33 +3652,34 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H42" s="2">
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="J42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
-    </row>
-    <row r="43" spans="1:21">
+      <c r="V42" s="4"/>
+    </row>
+    <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C43" s="2">
         <v>45359</v>
@@ -3662,60 +3688,61 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F43" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H43" s="2">
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="J43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
-    </row>
-    <row r="44" spans="1:21">
+      <c r="V43" s="4"/>
+    </row>
+    <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C44" s="2">
         <v>45408</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H44" s="2">
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="J44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L44" s="2">
         <v>45624</v>
@@ -3725,40 +3752,41 @@
       </c>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
-    </row>
-    <row r="45" spans="1:21">
+      <c r="V44" s="4"/>
+    </row>
+    <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C45" s="2">
         <v>45394</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H45" s="2">
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="J45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M45" s="3"/>
       <c r="S45" s="2">
@@ -3766,13 +3794,14 @@
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="V45" s="4"/>
+    </row>
+    <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C46" s="2">
         <v>45456</v>
@@ -3781,25 +3810,25 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H46" s="2">
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="J46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M46" s="3"/>
       <c r="S46" s="2">
@@ -3807,40 +3836,41 @@
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
-    </row>
-    <row r="47" spans="1:21">
+      <c r="V46" s="4"/>
+    </row>
+    <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C47" s="2">
         <v>45395</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H47" s="2">
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="J47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K47" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L47" s="2">
         <v>45548</v>
@@ -3852,43 +3882,44 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1203</v>
+        <v>1194</v>
       </c>
       <c r="U47" s="3"/>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="V47" s="4"/>
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C48" s="2">
         <v>45395</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G48" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H48" s="2">
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="J48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K48" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L48" s="2">
         <v>45530</v>
@@ -3897,47 +3928,48 @@
         <v>135</v>
       </c>
       <c r="N48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="S48" s="2">
         <v>45720</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="V48" s="4"/>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C49" s="2">
         <v>45395</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G49" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H49" s="2">
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="J49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L49" s="2">
         <v>45517</v>
@@ -3949,43 +3981,44 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="U49" s="3"/>
-    </row>
-    <row r="50" spans="1:21">
+      <c r="V49" s="4"/>
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C50" s="2">
         <v>45400</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H50" s="2">
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="J50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L50" s="2">
         <v>45580</v>
@@ -3995,13 +4028,14 @@
       </c>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
-    </row>
-    <row r="51" spans="1:21">
+      <c r="V50" s="4"/>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C51" s="2">
         <v>45553</v>
@@ -4010,130 +4044,133 @@
         <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F51" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H51" s="2">
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="J51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
-    </row>
-    <row r="52" spans="1:21">
+      <c r="V51" s="4"/>
+    </row>
+    <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C52" s="2">
         <v>45516</v>
       </c>
       <c r="D52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G52" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H52" s="2">
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="J52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M52" s="3"/>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
-    </row>
-    <row r="53" spans="1:21">
+      <c r="V52" s="4"/>
+    </row>
+    <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C53" s="2">
         <v>45701</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G53" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H53" s="2">
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="J53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M53" s="3"/>
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
-    </row>
-    <row r="54" spans="1:21">
+      <c r="V53" s="4"/>
+    </row>
+    <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C54" s="2">
         <v>45308</v>
       </c>
       <c r="D54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E54" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G54" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H54" s="2">
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="J54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K54" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L54" s="2">
         <v>45408</v>
@@ -4146,48 +4183,50 @@
       </c>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
-    </row>
-    <row r="55" spans="1:21">
+      <c r="V54" s="4"/>
+    </row>
+    <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C55" s="2">
         <v>45051</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F55" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G55" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H55" s="2">
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="J55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="1:21">
+      <c r="V55" s="4"/>
+    </row>
+    <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2">
         <v>45016</v>
@@ -4196,33 +4235,34 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F56" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G56" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H56" s="2">
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="J56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="1:21">
+      <c r="V56" s="4"/>
+    </row>
+    <row r="57" spans="1:22">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C57" s="2">
         <v>45016</v>
@@ -4231,103 +4271,106 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G57" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H57" s="2">
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="J57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M57" s="3"/>
       <c r="T57" s="3"/>
       <c r="U57" s="3"/>
-    </row>
-    <row r="58" spans="1:21">
+      <c r="V57" s="4"/>
+    </row>
+    <row r="58" spans="1:22">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2">
         <v>45251</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H58" s="2">
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="J58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
-    </row>
-    <row r="59" spans="1:21">
+      <c r="V58" s="4"/>
+    </row>
+    <row r="59" spans="1:22">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C59" s="2">
         <v>45314</v>
       </c>
       <c r="D59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E59" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F59" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G59" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H59" s="2">
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="J59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M59" s="3"/>
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
-    </row>
-    <row r="60" spans="1:21">
+      <c r="V59" s="4"/>
+    </row>
+    <row r="60" spans="1:22">
       <c r="A60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C60" s="2">
         <v>45216</v>
@@ -4336,25 +4379,25 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G60" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H60" s="2">
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="J60" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K60" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L60" s="2">
         <v>45475</v>
@@ -4366,16 +4409,17 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1126</v>
+        <v>1117</v>
       </c>
       <c r="U60" s="3"/>
-    </row>
-    <row r="61" spans="1:21">
+      <c r="V60" s="4"/>
+    </row>
+    <row r="61" spans="1:22">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C61" s="2">
         <v>45742</v>
@@ -4384,68 +4428,70 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F61" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G61" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H61" s="2">
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="J61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M61" s="3"/>
       <c r="T61" s="3"/>
       <c r="U61" s="3"/>
-    </row>
-    <row r="62" spans="1:21">
+      <c r="V61" s="4"/>
+    </row>
+    <row r="62" spans="1:22">
       <c r="A62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C62" s="2">
         <v>45734</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H62" s="2">
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="J62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M62" s="3"/>
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
-    </row>
-    <row r="63" spans="1:21">
+      <c r="V62" s="4"/>
+    </row>
+    <row r="63" spans="1:22">
       <c r="A63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B63" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C63" s="2">
         <v>46162</v>
@@ -4454,54 +4500,55 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H63" s="2">
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="I63" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M63" s="3"/>
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
-    </row>
-    <row r="64" spans="1:21">
+      <c r="V63" s="4"/>
+    </row>
+    <row r="64" spans="1:22">
       <c r="A64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C64" s="2">
         <v>46126</v>
       </c>
       <c r="D64" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E64" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F64" t="s">
-        <v>265</v>
+        <v>67</v>
       </c>
       <c r="G64" t="s">
         <v>266</v>
       </c>
       <c r="H64" s="2">
-        <v>46160</v>
+        <v>46181</v>
       </c>
       <c r="I64" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J64" t="s">
         <v>267</v>
@@ -4509,6 +4556,7 @@
       <c r="M64" s="3"/>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
+      <c r="V64" s="4"/>
     </row>
     <row r="65" spans="1:22">
       <c r="A65" t="s">
@@ -4521,13 +4569,13 @@
         <v>46136</v>
       </c>
       <c r="D65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E65" t="s">
         <v>270</v>
       </c>
       <c r="F65" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G65" t="s">
         <v>271</v>
@@ -4536,15 +4584,15 @@
         <v>46156</v>
       </c>
       <c r="I65" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
       <c r="U65" s="3"/>
-      <c r="V65" s="5">
+      <c r="V65" s="4">
         <v>400</v>
       </c>
     </row>
@@ -4559,13 +4607,13 @@
         <v>46135</v>
       </c>
       <c r="D66" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E66" t="s">
         <v>273</v>
       </c>
       <c r="F66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G66" t="s">
         <v>274</v>
@@ -4574,15 +4622,15 @@
         <v>46155</v>
       </c>
       <c r="I66" s="3">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
-      <c r="V66" s="5">
+      <c r="V66" s="4">
         <v>504</v>
       </c>
     </row>
@@ -4597,13 +4645,13 @@
         <v>46136</v>
       </c>
       <c r="D67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E67" t="s">
         <v>276</v>
       </c>
       <c r="F67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G67" t="s">
         <v>274</v>
@@ -4612,21 +4660,21 @@
         <v>46157</v>
       </c>
       <c r="I67" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-      <c r="V67" s="5">
+      <c r="V67" s="4">
         <v>856</v>
       </c>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B68" t="s">
         <v>277</v>
@@ -4641,7 +4689,7 @@
         <v>278</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G68" t="s">
         <v>279</v>
@@ -4650,21 +4698,21 @@
         <v>45943</v>
       </c>
       <c r="I68" s="3">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="J68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
-      <c r="V68" s="5">
+      <c r="V68" s="4">
         <v>9808.2000000000007</v>
       </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B69" t="s">
         <v>280</v>
@@ -4679,7 +4727,7 @@
         <v>281</v>
       </c>
       <c r="F69" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G69" t="s">
         <v>282</v>
@@ -4688,10 +4736,10 @@
         <v>45715</v>
       </c>
       <c r="I69" s="3">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="J69" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K69" t="s">
         <v>283</v>
@@ -4707,13 +4755,13 @@
       </c>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
-      <c r="V69" s="5">
+      <c r="V69" s="4">
         <v>18900</v>
       </c>
     </row>
     <row r="70" spans="1:22">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B70" t="s">
         <v>284</v>
@@ -4728,7 +4776,7 @@
         <v>285</v>
       </c>
       <c r="F70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G70" t="s">
         <v>286</v>
@@ -4737,10 +4785,10 @@
         <v>45817</v>
       </c>
       <c r="I70" s="3">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="J70" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K70" t="s">
         <v>287</v>
@@ -4755,16 +4803,16 @@
         <v>46909</v>
       </c>
       <c r="T70" s="3">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="U70" s="3"/>
-      <c r="V70" s="5">
+      <c r="V70" s="4">
         <v>23850</v>
       </c>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B71" t="s">
         <v>288</v>
@@ -4773,25 +4821,25 @@
         <v>45492</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E71" t="s">
         <v>289</v>
       </c>
       <c r="F71" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G71" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H71" s="2">
         <v>45911</v>
       </c>
       <c r="I71" s="3">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="J71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K71" t="s">
         <v>290</v>
@@ -4803,20 +4851,20 @@
         <v>54</v>
       </c>
       <c r="O71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P71" s="2">
         <v>45966</v>
       </c>
       <c r="T71" s="3"/>
       <c r="U71" s="3"/>
-      <c r="V71" s="5">
+      <c r="V71" s="4">
         <v>25173.75</v>
       </c>
     </row>
     <row r="72" spans="1:22">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B72" t="s">
         <v>291</v>
@@ -4825,13 +4873,13 @@
         <v>45786</v>
       </c>
       <c r="D72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E72" t="s">
         <v>292</v>
       </c>
       <c r="F72" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G72" t="s">
         <v>293</v>
@@ -4840,21 +4888,21 @@
         <v>45895</v>
       </c>
       <c r="I72" s="3">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="J72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
-      <c r="V72" s="5">
+      <c r="V72" s="4">
         <v>31300</v>
       </c>
     </row>
     <row r="73" spans="1:22">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
         <v>294</v>
@@ -4869,60 +4917,60 @@
         <v>295</v>
       </c>
       <c r="F73" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" t="s">
         <v>296</v>
       </c>
-      <c r="G73" t="s">
-        <v>297</v>
-      </c>
       <c r="H73" s="2">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="I73" s="3">
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M73" s="3"/>
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
-      <c r="V73" s="5">
+      <c r="V73" s="4">
         <v>32983.599999999999</v>
       </c>
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
+        <v>297</v>
+      </c>
+      <c r="B74" t="s">
         <v>298</v>
-      </c>
-      <c r="B74" t="s">
-        <v>299</v>
       </c>
       <c r="C74" s="2">
         <v>45665</v>
       </c>
       <c r="D74" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E74" t="s">
+        <v>299</v>
+      </c>
+      <c r="F74" t="s">
+        <v>297</v>
+      </c>
+      <c r="G74" t="s">
         <v>300</v>
-      </c>
-      <c r="F74" t="s">
-        <v>298</v>
-      </c>
-      <c r="G74" t="s">
-        <v>301</v>
       </c>
       <c r="H74" s="2">
         <v>45838</v>
       </c>
       <c r="I74" s="3">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="J74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L74" s="2">
         <v>46071</v>
@@ -4931,7 +4979,7 @@
         <v>406</v>
       </c>
       <c r="O74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P74" s="2">
         <v>46294</v>
@@ -4940,21 +4988,21 @@
         <v>46202</v>
       </c>
       <c r="T74" s="3">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="U74" s="3">
-        <v>119</v>
-      </c>
-      <c r="V74" s="5">
+        <v>110</v>
+      </c>
+      <c r="V74" s="4">
         <v>51071</v>
       </c>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2">
         <v>43902</v>
@@ -4963,25 +5011,25 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F75" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H75" s="2">
         <v>45790</v>
       </c>
       <c r="I75" s="3">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="J75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K75" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L75" s="2">
         <v>43964</v>
@@ -4990,7 +5038,7 @@
         <v>62</v>
       </c>
       <c r="O75" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P75" s="2">
         <v>46160</v>
@@ -5000,16 +5048,16 @@
       </c>
       <c r="T75" s="3"/>
       <c r="U75" s="3"/>
-      <c r="V75" s="5">
+      <c r="V75" s="4">
         <v>61200</v>
       </c>
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B76" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2">
         <v>45915</v>
@@ -5018,25 +5066,25 @@
         <v>24</v>
       </c>
       <c r="E76" t="s">
+        <v>306</v>
+      </c>
+      <c r="F76" t="s">
+        <v>142</v>
+      </c>
+      <c r="G76" t="s">
         <v>307</v>
-      </c>
-      <c r="F76" t="s">
-        <v>141</v>
-      </c>
-      <c r="G76" t="s">
-        <v>308</v>
       </c>
       <c r="H76" s="2">
         <v>46094</v>
       </c>
       <c r="I76" s="3">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L76" s="2">
         <v>46086</v>
@@ -5048,46 +5096,46 @@
         <v>47181</v>
       </c>
       <c r="T76" s="3">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="U76" s="3"/>
-      <c r="V76" s="5">
+      <c r="V76" s="4">
         <v>71265.600000000006</v>
       </c>
     </row>
     <row r="77" spans="1:22">
       <c r="A77" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C77" s="2">
         <v>45950</v>
       </c>
       <c r="D77" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E77" t="s">
+        <v>310</v>
+      </c>
+      <c r="F77" t="s">
+        <v>43</v>
+      </c>
+      <c r="G77" t="s">
         <v>311</v>
-      </c>
-      <c r="F77" t="s">
-        <v>42</v>
-      </c>
-      <c r="G77" t="s">
-        <v>312</v>
       </c>
       <c r="H77" s="2">
         <v>45975</v>
       </c>
       <c r="I77" s="3">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="J77" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K77" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L77" s="2">
         <v>45978</v>
@@ -5096,7 +5144,7 @@
         <v>28</v>
       </c>
       <c r="O77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P77" s="2">
         <v>46220</v>
@@ -5105,21 +5153,21 @@
         <v>46220</v>
       </c>
       <c r="T77" s="3">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="U77" s="3">
-        <v>45</v>
-      </c>
-      <c r="V77" s="5">
+        <v>36</v>
+      </c>
+      <c r="V77" s="4">
         <v>71722</v>
       </c>
     </row>
     <row r="78" spans="1:22">
       <c r="A78" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C78" s="2">
         <v>45915</v>
@@ -5128,25 +5176,25 @@
         <v>24</v>
       </c>
       <c r="E78" t="s">
+        <v>313</v>
+      </c>
+      <c r="F78" t="s">
+        <v>43</v>
+      </c>
+      <c r="G78" t="s">
         <v>314</v>
       </c>
-      <c r="F78" t="s">
-        <v>42</v>
-      </c>
-      <c r="G78" t="s">
-        <v>315</v>
-      </c>
       <c r="H78" s="2">
-        <v>46161</v>
+        <v>46183</v>
       </c>
       <c r="I78" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J78" t="s">
         <v>267</v>
       </c>
       <c r="K78" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L78" s="2">
         <v>46086</v>
@@ -5158,19 +5206,19 @@
         <v>47181</v>
       </c>
       <c r="T78" s="3">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="U78" s="3"/>
-      <c r="V78" s="5">
+      <c r="V78" s="4">
         <v>73620</v>
       </c>
     </row>
     <row r="79" spans="1:22">
       <c r="A79" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C79" s="2">
         <v>45915</v>
@@ -5179,25 +5227,25 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F79" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G79" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H79" s="2">
         <v>46094</v>
       </c>
       <c r="I79" s="3">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K79" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L79" s="2">
         <v>46086</v>
@@ -5209,19 +5257,19 @@
         <v>47181</v>
       </c>
       <c r="T79" s="3">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="U79" s="3"/>
-      <c r="V79" s="5">
+      <c r="V79" s="4">
         <v>104220</v>
       </c>
     </row>
     <row r="80" spans="1:22">
       <c r="A80" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C80" s="2">
         <v>43902</v>
@@ -5230,25 +5278,25 @@
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F80" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G80" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H80" s="2">
         <v>45790</v>
       </c>
       <c r="I80" s="3">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="J80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K80" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L80" s="2">
         <v>43964</v>
@@ -5257,7 +5305,7 @@
         <v>62</v>
       </c>
       <c r="O80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P80" s="2">
         <v>46160</v>
@@ -5267,43 +5315,43 @@
       </c>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
-      <c r="V80" s="5">
+      <c r="V80" s="4">
         <v>139755.72</v>
       </c>
     </row>
     <row r="81" spans="1:22">
       <c r="A81" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C81" s="2">
         <v>45819</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E81" t="s">
+        <v>320</v>
+      </c>
+      <c r="F81" t="s">
+        <v>43</v>
+      </c>
+      <c r="G81" t="s">
         <v>321</v>
-      </c>
-      <c r="F81" t="s">
-        <v>66</v>
-      </c>
-      <c r="G81" t="s">
-        <v>322</v>
       </c>
       <c r="H81" s="2">
         <v>46170</v>
       </c>
       <c r="I81" s="3">
-        <v>5</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>52</v>
+        <v>14</v>
+      </c>
+      <c r="J81" t="s">
+        <v>53</v>
       </c>
       <c r="K81" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L81" s="2">
         <v>45904</v>
@@ -5315,19 +5363,19 @@
         <v>46273</v>
       </c>
       <c r="T81" s="3">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="U81" s="3"/>
-      <c r="V81" s="5">
+      <c r="V81" s="4">
         <v>230000</v>
       </c>
     </row>
     <row r="82" spans="1:22">
       <c r="A82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B82" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C82" s="2">
         <v>45952</v>
@@ -5336,25 +5384,25 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
+        <v>324</v>
+      </c>
+      <c r="F82" t="s">
         <v>325</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>326</v>
-      </c>
-      <c r="G82" t="s">
-        <v>327</v>
       </c>
       <c r="H82" s="2">
         <v>46087</v>
       </c>
       <c r="I82" s="3">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="J82" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K82" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L82" s="2">
         <v>46086</v>
@@ -5366,46 +5414,46 @@
         <v>47910</v>
       </c>
       <c r="T82" s="3">
-        <v>1735</v>
+        <v>1726</v>
       </c>
       <c r="U82" s="3"/>
-      <c r="V82" s="5">
+      <c r="V82" s="4">
         <v>250977.6</v>
       </c>
     </row>
     <row r="83" spans="1:22">
       <c r="A83" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B83" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2">
         <v>45775</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E83" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F83" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G83" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H83" s="2">
         <v>45861</v>
       </c>
       <c r="I83" s="3">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="J83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K83" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L83" s="2">
         <v>45856</v>
@@ -5417,57 +5465,57 @@
         <v>46225</v>
       </c>
       <c r="T83" s="3">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="U83" s="3"/>
-      <c r="V83" s="5">
+      <c r="V83" s="4">
         <v>288862</v>
       </c>
     </row>
     <row r="84" spans="1:22">
       <c r="A84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C84" s="2">
         <v>45539</v>
       </c>
       <c r="D84" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E84" t="s">
+        <v>330</v>
+      </c>
+      <c r="F84" t="s">
         <v>331</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>332</v>
-      </c>
-      <c r="G84" t="s">
-        <v>333</v>
       </c>
       <c r="H84" s="2">
         <v>45607</v>
       </c>
       <c r="I84" s="3">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="J84" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
-      <c r="V84" s="5">
+      <c r="V84" s="4">
         <v>297600</v>
       </c>
     </row>
     <row r="85" spans="1:22">
       <c r="A85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C85" s="2">
         <v>45840</v>
@@ -5476,25 +5524,25 @@
         <v>24</v>
       </c>
       <c r="E85" t="s">
+        <v>334</v>
+      </c>
+      <c r="F85" t="s">
         <v>335</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>336</v>
-      </c>
-      <c r="G85" t="s">
-        <v>337</v>
       </c>
       <c r="H85" s="2">
         <v>46002</v>
       </c>
       <c r="I85" s="3">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J85" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K85" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L85" s="2">
         <v>46001</v>
@@ -5506,19 +5554,19 @@
         <v>47097</v>
       </c>
       <c r="T85" s="3">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="U85" s="3"/>
-      <c r="V85" s="5">
+      <c r="V85" s="4">
         <v>299821.5</v>
       </c>
     </row>
     <row r="86" spans="1:22">
       <c r="A86" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C86" s="2">
         <v>45868</v>
@@ -5527,25 +5575,25 @@
         <v>24</v>
       </c>
       <c r="E86" t="s">
+        <v>339</v>
+      </c>
+      <c r="F86" t="s">
+        <v>67</v>
+      </c>
+      <c r="G86" t="s">
         <v>340</v>
-      </c>
-      <c r="F86" t="s">
-        <v>66</v>
-      </c>
-      <c r="G86" t="s">
-        <v>341</v>
       </c>
       <c r="H86" s="2">
         <v>46146</v>
       </c>
       <c r="I86" s="3">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J86" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K86" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L86" s="2">
         <v>46077</v>
@@ -5557,19 +5605,19 @@
         <v>47905</v>
       </c>
       <c r="T86" s="3">
-        <v>1730</v>
+        <v>1721</v>
       </c>
       <c r="U86" s="3"/>
-      <c r="V86" s="5">
+      <c r="V86" s="4">
         <v>338580</v>
       </c>
     </row>
     <row r="87" spans="1:22">
       <c r="A87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B87" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C87" s="2">
         <v>44370</v>
@@ -5578,25 +5626,25 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F87" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G87" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H87" s="2">
         <v>45881</v>
       </c>
       <c r="I87" s="3">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="J87" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K87" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L87" s="2">
         <v>44589</v>
@@ -5605,7 +5653,7 @@
         <v>219</v>
       </c>
       <c r="O87" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P87" s="2">
         <v>46419</v>
@@ -5615,45 +5663,45 @@
       </c>
       <c r="T87" s="3"/>
       <c r="U87" s="3">
-        <v>244</v>
-      </c>
-      <c r="V87" s="5">
+        <v>235</v>
+      </c>
+      <c r="V87" s="4">
         <v>374899.96</v>
       </c>
     </row>
     <row r="88" spans="1:22">
       <c r="A88" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C88" s="2">
         <v>45422</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E88" t="s">
+        <v>347</v>
+      </c>
+      <c r="F88" t="s">
+        <v>43</v>
+      </c>
+      <c r="G88" t="s">
         <v>348</v>
-      </c>
-      <c r="F88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G88" t="s">
-        <v>349</v>
       </c>
       <c r="H88" s="2">
         <v>45624</v>
       </c>
       <c r="I88" s="3">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="J88" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K88" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L88" s="2">
         <v>45544</v>
@@ -5666,81 +5714,81 @@
       </c>
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
-      <c r="V88" s="5">
+      <c r="V88" s="4">
         <v>457600</v>
       </c>
     </row>
     <row r="89" spans="1:22">
       <c r="A89" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B89" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C89" s="2">
         <v>46038</v>
       </c>
       <c r="D89" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E89" t="s">
+        <v>351</v>
+      </c>
+      <c r="F89" t="s">
+        <v>142</v>
+      </c>
+      <c r="G89" t="s">
         <v>352</v>
       </c>
-      <c r="F89" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" t="s">
-        <v>353</v>
-      </c>
       <c r="H89" s="2">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="I89" s="3">
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M89" s="3"/>
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
-      <c r="V89" s="5">
+      <c r="V89" s="4">
         <v>687500</v>
       </c>
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C90" s="2">
         <v>44939</v>
       </c>
       <c r="D90" t="s">
+        <v>354</v>
+      </c>
+      <c r="E90" t="s">
         <v>355</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
+        <v>29</v>
+      </c>
+      <c r="G90" t="s">
         <v>356</v>
-      </c>
-      <c r="F90" t="s">
-        <v>28</v>
-      </c>
-      <c r="G90" t="s">
-        <v>357</v>
       </c>
       <c r="H90" s="2">
         <v>45979</v>
       </c>
       <c r="I90" s="3">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="J90" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K90" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L90" s="2">
         <v>45968</v>
@@ -5749,7 +5797,7 @@
         <v>1029</v>
       </c>
       <c r="O90" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P90" s="2">
         <v>46426</v>
@@ -5759,18 +5807,18 @@
       </c>
       <c r="T90" s="3"/>
       <c r="U90" s="3">
-        <v>251</v>
-      </c>
-      <c r="V90" s="5">
+        <v>242</v>
+      </c>
+      <c r="V90" s="4">
         <v>706431.6</v>
       </c>
     </row>
     <row r="91" spans="1:22">
       <c r="A91" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C91" s="2">
         <v>45673</v>
@@ -5779,44 +5827,44 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F91" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G91" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H91" s="2">
         <v>46140</v>
       </c>
       <c r="I91" s="3">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J91" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K91" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M91" s="3"/>
       <c r="S91" s="2">
         <v>46598</v>
       </c>
       <c r="T91" s="3">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="U91" s="3"/>
-      <c r="V91" s="5">
+      <c r="V91" s="4">
         <v>890000</v>
       </c>
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C92" s="2">
         <v>45215</v>
@@ -5825,25 +5873,25 @@
         <v>24</v>
       </c>
       <c r="E92" t="s">
+        <v>362</v>
+      </c>
+      <c r="F92" t="s">
+        <v>170</v>
+      </c>
+      <c r="G92" t="s">
         <v>363</v>
-      </c>
-      <c r="F92" t="s">
-        <v>169</v>
-      </c>
-      <c r="G92" t="s">
-        <v>364</v>
       </c>
       <c r="H92" s="2">
         <v>45687</v>
       </c>
       <c r="I92" s="3">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="J92" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K92" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L92" s="2">
         <v>45685</v>
@@ -5855,46 +5903,46 @@
         <v>46780</v>
       </c>
       <c r="T92" s="3">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="U92" s="3"/>
-      <c r="V92" s="5">
+      <c r="V92" s="4">
         <v>1220266.1399999999</v>
       </c>
     </row>
     <row r="93" spans="1:22">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C93" s="2">
         <v>45366</v>
       </c>
       <c r="D93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E93" t="s">
+        <v>366</v>
+      </c>
+      <c r="F93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" t="s">
         <v>367</v>
-      </c>
-      <c r="F93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G93" t="s">
-        <v>368</v>
       </c>
       <c r="H93" s="2">
         <v>45481</v>
       </c>
       <c r="I93" s="3">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="J93" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K93" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L93" s="2">
         <v>45471</v>
@@ -5906,46 +5954,46 @@
         <v>47301</v>
       </c>
       <c r="T93" s="3">
-        <v>1126</v>
+        <v>1117</v>
       </c>
       <c r="U93" s="3"/>
-      <c r="V93" s="5">
+      <c r="V93" s="4">
         <v>1245414.49</v>
       </c>
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C94" s="2">
         <v>45152</v>
       </c>
       <c r="D94" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E94" t="s">
+        <v>370</v>
+      </c>
+      <c r="F94" t="s">
+        <v>29</v>
+      </c>
+      <c r="G94" t="s">
         <v>371</v>
-      </c>
-      <c r="F94" t="s">
-        <v>28</v>
-      </c>
-      <c r="G94" t="s">
-        <v>372</v>
       </c>
       <c r="H94" s="2">
         <v>45440</v>
       </c>
       <c r="I94" s="3">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="J94" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K94" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L94" s="2">
         <v>45303</v>
@@ -5958,43 +6006,43 @@
       </c>
       <c r="T94" s="3"/>
       <c r="U94" s="3"/>
-      <c r="V94" s="5">
+      <c r="V94" s="4">
         <v>1298031.3600000001</v>
       </c>
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C95" s="2">
         <v>45373</v>
       </c>
       <c r="D95" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E95" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F95" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G95" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H95" s="2">
         <v>45492</v>
       </c>
       <c r="I95" s="3">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="J95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K95" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L95" s="2">
         <v>45492</v>
@@ -6006,19 +6054,19 @@
         <v>46587</v>
       </c>
       <c r="T95" s="3">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="U95" s="3"/>
-      <c r="V95" s="5">
+      <c r="V95" s="4">
         <v>1320176.8799999999</v>
       </c>
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C96" s="2">
         <v>44663</v>
@@ -6027,25 +6075,25 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F96" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G96" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H96" s="2">
         <v>45588</v>
       </c>
       <c r="I96" s="3">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="J96" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K96" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L96" s="2">
         <v>44893</v>
@@ -6054,7 +6102,7 @@
         <v>230</v>
       </c>
       <c r="O96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P96" s="2">
         <v>45996</v>
@@ -6064,16 +6112,16 @@
       </c>
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
-      <c r="V96" s="5">
+      <c r="V96" s="4">
         <v>1416380</v>
       </c>
     </row>
     <row r="97" spans="1:22">
       <c r="A97" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C97" s="2">
         <v>45826</v>
@@ -6082,25 +6130,25 @@
         <v>24</v>
       </c>
       <c r="E97" t="s">
+        <v>380</v>
+      </c>
+      <c r="F97" t="s">
+        <v>67</v>
+      </c>
+      <c r="G97" t="s">
         <v>381</v>
-      </c>
-      <c r="F97" t="s">
-        <v>66</v>
-      </c>
-      <c r="G97" t="s">
-        <v>382</v>
       </c>
       <c r="H97" s="2">
         <v>46079</v>
       </c>
       <c r="I97" s="3">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J97" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K97" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L97" s="2">
         <v>46076</v>
@@ -6112,122 +6160,122 @@
         <v>47903</v>
       </c>
       <c r="T97" s="3">
-        <v>1728</v>
+        <v>1719</v>
       </c>
       <c r="U97" s="3"/>
-      <c r="V97" s="5">
+      <c r="V97" s="4">
         <v>1435000</v>
       </c>
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
+        <v>383</v>
+      </c>
+      <c r="B98" t="s">
         <v>384</v>
-      </c>
-      <c r="B98" t="s">
-        <v>385</v>
       </c>
       <c r="C98" s="2">
         <v>46150</v>
       </c>
       <c r="D98" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E98" t="s">
+        <v>385</v>
+      </c>
+      <c r="F98" t="s">
         <v>386</v>
       </c>
-      <c r="F98" t="s">
-        <v>66</v>
-      </c>
       <c r="G98" t="s">
-        <v>387</v>
+        <v>266</v>
       </c>
       <c r="H98" s="2">
         <v>46168</v>
       </c>
       <c r="I98" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J98" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M98" s="3"/>
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
-      <c r="V98" s="5">
+      <c r="V98" s="4">
         <v>1719174</v>
       </c>
     </row>
     <row r="99" spans="1:22">
       <c r="A99" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C99" s="2">
         <v>46094</v>
       </c>
       <c r="D99" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E99" t="s">
+        <v>388</v>
+      </c>
+      <c r="F99" t="s">
+        <v>386</v>
+      </c>
+      <c r="G99" t="s">
         <v>389</v>
-      </c>
-      <c r="F99" t="s">
-        <v>265</v>
-      </c>
-      <c r="G99" t="s">
-        <v>390</v>
       </c>
       <c r="H99" s="2">
         <v>46170</v>
       </c>
       <c r="I99" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J99" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M99" s="3"/>
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
-      <c r="V99" s="5">
+      <c r="V99" s="4">
         <v>1828126.08</v>
       </c>
     </row>
     <row r="100" spans="1:22">
       <c r="A100" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C100" s="2">
         <v>45950</v>
       </c>
       <c r="D100" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E100" t="s">
+        <v>391</v>
+      </c>
+      <c r="F100" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100" t="s">
         <v>392</v>
-      </c>
-      <c r="F100" t="s">
-        <v>42</v>
-      </c>
-      <c r="G100" t="s">
-        <v>393</v>
       </c>
       <c r="H100" s="2">
         <v>45988</v>
       </c>
       <c r="I100" s="3">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J100" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K100" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L100" s="2">
         <v>45979</v>
@@ -6239,19 +6287,19 @@
         <v>46343</v>
       </c>
       <c r="T100" s="3">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="U100" s="3"/>
-      <c r="V100" s="5">
+      <c r="V100" s="4">
         <v>2075682</v>
       </c>
     </row>
     <row r="101" spans="1:22">
       <c r="A101" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C101" s="2">
         <v>45511</v>
@@ -6260,25 +6308,25 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
+        <v>395</v>
+      </c>
+      <c r="F101" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" t="s">
         <v>396</v>
-      </c>
-      <c r="F101" t="s">
-        <v>25</v>
-      </c>
-      <c r="G101" t="s">
-        <v>397</v>
       </c>
       <c r="H101" s="2">
         <v>45786</v>
       </c>
       <c r="I101" s="3">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="J101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K101" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L101" s="2">
         <v>45794</v>
@@ -6288,43 +6336,43 @@
       </c>
       <c r="T101" s="3"/>
       <c r="U101" s="3"/>
-      <c r="V101" s="5">
+      <c r="V101" s="4">
         <v>2594055</v>
       </c>
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B102" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C102" s="2">
         <v>45848</v>
       </c>
       <c r="D102" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E102" t="s">
+        <v>399</v>
+      </c>
+      <c r="F102" t="s">
+        <v>225</v>
+      </c>
+      <c r="G102" t="s">
         <v>400</v>
-      </c>
-      <c r="F102" t="s">
-        <v>224</v>
-      </c>
-      <c r="G102" t="s">
-        <v>401</v>
       </c>
       <c r="H102" s="2">
         <v>46014</v>
       </c>
       <c r="I102" s="3">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J102" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K102" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L102" s="2">
         <v>46008</v>
@@ -6336,54 +6384,54 @@
         <v>46373</v>
       </c>
       <c r="T102" s="3">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="U102" s="3"/>
-      <c r="V102" s="5">
+      <c r="V102" s="4">
         <v>2641069.35</v>
       </c>
     </row>
     <row r="103" spans="1:22">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B103" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C103" s="2">
         <v>46030</v>
       </c>
       <c r="D103" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E103" t="s">
+        <v>403</v>
+      </c>
+      <c r="F103" t="s">
+        <v>386</v>
+      </c>
+      <c r="G103" t="s">
         <v>404</v>
-      </c>
-      <c r="F103" t="s">
-        <v>265</v>
-      </c>
-      <c r="G103" t="s">
-        <v>266</v>
       </c>
       <c r="H103" s="2">
         <v>46157</v>
       </c>
       <c r="I103" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J103" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M103" s="3"/>
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
-      <c r="V103" s="5">
+      <c r="V103" s="4">
         <v>2652975.2799999998</v>
       </c>
     </row>
     <row r="104" spans="1:22">
       <c r="A104" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B104" t="s">
         <v>405</v>
@@ -6392,7 +6440,7 @@
         <v>45365</v>
       </c>
       <c r="D104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E104" t="s">
         <v>406</v>
@@ -6407,10 +6455,10 @@
         <v>45568</v>
       </c>
       <c r="I104" s="3">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="J104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K104" t="s">
         <v>409</v>
@@ -6425,16 +6473,16 @@
         <v>46479</v>
       </c>
       <c r="T104" s="3">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="U104" s="3"/>
-      <c r="V104" s="5">
+      <c r="V104" s="4">
         <v>2780400.6</v>
       </c>
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B105" t="s">
         <v>410</v>
@@ -6443,7 +6491,7 @@
         <v>45526</v>
       </c>
       <c r="D105" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E105" t="s">
         <v>411</v>
@@ -6458,10 +6506,10 @@
         <v>45932</v>
       </c>
       <c r="I105" s="3">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="J105" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K105" t="s">
         <v>414</v>
@@ -6471,16 +6519,16 @@
         <v>47748</v>
       </c>
       <c r="T105" s="3">
-        <v>1573</v>
+        <v>1564</v>
       </c>
       <c r="U105" s="3"/>
-      <c r="V105" s="5">
+      <c r="V105" s="4">
         <v>4440928.34</v>
       </c>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B106" t="s">
         <v>415</v>
@@ -6495,7 +6543,7 @@
         <v>416</v>
       </c>
       <c r="F106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G106" t="s">
         <v>417</v>
@@ -6504,10 +6552,10 @@
         <v>45958</v>
       </c>
       <c r="I106" s="3">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J106" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K106" t="s">
         <v>418</v>
@@ -6522,16 +6570,16 @@
         <v>46316</v>
       </c>
       <c r="T106" s="3">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="U106" s="3"/>
-      <c r="V106" s="5">
+      <c r="V106" s="4">
         <v>5192424.24</v>
       </c>
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B107" t="s">
         <v>419</v>
@@ -6555,10 +6603,10 @@
         <v>45930</v>
       </c>
       <c r="I107" s="3">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="J107" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K107" t="s">
         <v>423</v>
@@ -6573,10 +6621,10 @@
         <v>46950</v>
       </c>
       <c r="T107" s="3">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="U107" s="3"/>
-      <c r="V107" s="5">
+      <c r="V107" s="4">
         <v>6210000</v>
       </c>
     </row>
@@ -6591,22 +6639,22 @@
         <v>44607</v>
       </c>
       <c r="D108" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E108" t="s">
         <v>425</v>
       </c>
       <c r="F108" t="s">
-        <v>265</v>
+        <v>26</v>
       </c>
       <c r="G108" t="s">
         <v>426</v>
       </c>
       <c r="H108" s="2">
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="I108" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J108" t="s">
         <v>267</v>
@@ -6630,10 +6678,8 @@
         <v>45111</v>
       </c>
       <c r="T108" s="3"/>
-      <c r="U108" s="3">
-        <v>2</v>
-      </c>
-      <c r="V108" s="5">
+      <c r="U108" s="3"/>
+      <c r="V108" s="4">
         <v>6242296.7000000002</v>
       </c>
     </row>
@@ -6648,13 +6694,13 @@
         <v>38661</v>
       </c>
       <c r="D109" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E109" t="s">
         <v>431</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G109" t="s">
         <v>432</v>
@@ -6663,10 +6709,10 @@
         <v>45993</v>
       </c>
       <c r="I109" s="3">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="J109" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K109" t="s">
         <v>433</v>
@@ -6681,16 +6727,16 @@
         <v>46540</v>
       </c>
       <c r="T109" s="3">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="U109" s="3"/>
-      <c r="V109" s="5">
+      <c r="V109" s="4">
         <v>9032000</v>
       </c>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B110" t="s">
         <v>434</v>
@@ -6705,7 +6751,7 @@
         <v>435</v>
       </c>
       <c r="F110" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G110" t="s">
         <v>436</v>
@@ -6714,10 +6760,10 @@
         <v>45797</v>
       </c>
       <c r="I110" s="3">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="J110" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K110" t="s">
         <v>437</v>
@@ -6727,16 +6773,16 @@
         <v>46523</v>
       </c>
       <c r="T110" s="3">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="U110" s="3"/>
-      <c r="V110" s="5">
+      <c r="V110" s="4">
         <v>9152353</v>
       </c>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B111" t="s">
         <v>438</v>
@@ -6751,19 +6797,19 @@
         <v>439</v>
       </c>
       <c r="F111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G111" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H111" s="2">
         <v>45798</v>
       </c>
       <c r="I111" s="3">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="J111" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K111" t="s">
         <v>440</v>
@@ -6775,7 +6821,7 @@
         <v>811</v>
       </c>
       <c r="O111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P111" s="2">
         <v>46313</v>
@@ -6791,15 +6837,15 @@
       </c>
       <c r="T111" s="3"/>
       <c r="U111" s="3">
-        <v>138</v>
-      </c>
-      <c r="V111" s="5">
+        <v>129</v>
+      </c>
+      <c r="V111" s="4">
         <v>10934411.34</v>
       </c>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B112" t="s">
         <v>442</v>
@@ -6808,28 +6854,28 @@
         <v>45014</v>
       </c>
       <c r="D112" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E112" t="s">
         <v>443</v>
       </c>
       <c r="F112" t="s">
-        <v>25</v>
+        <v>444</v>
       </c>
       <c r="G112" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H112" s="2">
-        <v>46163</v>
+        <v>46183</v>
       </c>
       <c r="I112" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J112" t="s">
         <v>267</v>
       </c>
       <c r="K112" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L112" s="2">
         <v>45148</v>
@@ -6838,7 +6884,7 @@
         <v>134</v>
       </c>
       <c r="O112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P112" s="2">
         <v>45878</v>
@@ -6848,16 +6894,16 @@
       </c>
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
-      <c r="V112" s="5">
+      <c r="V112" s="4">
         <v>14412000</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B113" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C113" s="2">
         <v>45666</v>
@@ -6866,27 +6912,27 @@
         <v>24</v>
       </c>
       <c r="E113" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F113" t="s">
         <v>412</v>
       </c>
       <c r="G113" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H113" s="2">
         <v>46174</v>
       </c>
       <c r="I113" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J113" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M113" s="3"/>
       <c r="T113" s="3"/>
       <c r="U113" s="3"/>
-      <c r="V113" s="5">
+      <c r="V113" s="4">
         <v>31106553.600000001</v>
       </c>
     </row>
@@ -6895,34 +6941,34 @@
         <v>412</v>
       </c>
       <c r="B114" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C114" s="2">
         <v>45250</v>
       </c>
       <c r="D114" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E114" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F114" t="s">
         <v>412</v>
       </c>
       <c r="G114" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H114" s="2">
         <v>45400</v>
       </c>
       <c r="I114" s="3">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="J114" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K114" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L114" s="2">
         <v>45401</v>
@@ -6934,19 +6980,19 @@
         <v>47227</v>
       </c>
       <c r="T114" s="3">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="U114" s="3"/>
-      <c r="V114" s="5">
+      <c r="V114" s="4">
         <v>41522909.280000001</v>
       </c>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C115" s="2">
         <v>44238</v>
@@ -6955,25 +7001,25 @@
         <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F115" t="s">
-        <v>265</v>
+        <v>386</v>
       </c>
       <c r="G115" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H115" s="2">
         <v>46170</v>
       </c>
       <c r="I115" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J115" t="s">
         <v>267</v>
       </c>
       <c r="K115" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L115" s="2">
         <v>44969</v>
@@ -6982,7 +7028,7 @@
         <v>731</v>
       </c>
       <c r="O115" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P115" s="2">
         <v>46798</v>
@@ -6992,18 +7038,18 @@
       </c>
       <c r="T115" s="3"/>
       <c r="U115" s="3">
-        <v>623</v>
-      </c>
-      <c r="V115" s="5">
+        <v>614</v>
+      </c>
+      <c r="V115" s="4">
         <v>41936400</v>
       </c>
     </row>
     <row r="116" spans="1:22">
       <c r="A116" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B116" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C116" s="2">
         <v>45607</v>
@@ -7012,25 +7058,25 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F116" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G116" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H116" s="2">
         <v>45798</v>
       </c>
       <c r="I116" s="3">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="J116" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K116" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L116" s="2">
         <v>45798</v>
@@ -7042,19 +7088,19 @@
         <v>46712</v>
       </c>
       <c r="T116" s="3">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="U116" s="3"/>
-      <c r="V116" s="5">
+      <c r="V116" s="4">
         <v>50963796</v>
       </c>
     </row>
     <row r="117" spans="1:22">
       <c r="A117" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C117" s="2">
         <v>45664</v>
@@ -7063,33 +7109,31 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G117" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H117" s="2">
         <v>45958</v>
       </c>
       <c r="I117" s="3">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="J117" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M117" s="3"/>
       <c r="T117" s="3"/>
       <c r="U117" s="3"/>
-      <c r="V117" s="5">
+      <c r="V117" s="4">
         <v>253382919</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V117" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30496EF-BCB5-40AB-A297-AE3A5608564F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D474587F-11FD-4935-9774-53D98BF3E7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="467">
   <si>
     <t>Departamento</t>
   </si>
@@ -1109,9 +1109,6 @@
     <t>ACCESS POINT</t>
   </si>
   <si>
-    <t>DOCUMENTOS ANEXADOS EM ATENDIMENTO AO  Despacho 242 (91579824)</t>
-  </si>
-  <si>
     <t>202300010002563</t>
   </si>
   <si>
@@ -1220,7 +1217,7 @@
     <t>LINKS DE DADOS SD-WAN - PARTÍCIPE ARP 002/2026 – SGG PROCESSO ORIGINAL SEI 202618037001743</t>
   </si>
   <si>
-    <t>Procuradoria Setorial para análise da Minuta do Contrato</t>
+    <t>para análise da Minuta do Contrato</t>
   </si>
   <si>
     <t>202500010083108</t>
@@ -1265,7 +1262,14 @@
     <t>Novo Termo de Cooperação entre UFG e SES para realização de capacitação continuada em padrão FHIR.</t>
   </si>
   <si>
-    <t>AGUARDANDO Parecer  Jurídico. 426 (91304192)</t>
+    <t>SUBPEI GCC</t>
+  </si>
+  <si>
+    <t>juntada de justificativas e dos documentos aptos a afastar a obrigatoriedade de chamamento público (item 3.7);
+b) juntada de justificativas de preço (item 3.8);
+c) adequação do Plano de Trabalho para atendimento do que dispõe o art. 6º do Decreto nº 10.248/23 (itens 5.3 e 5.4);
+d) juntada dos documentos instrutórios da contratação faltantes ou desatualizados e manutenção da regularidade das certidões durante o curso do processo (item 5.4. a 5.7);
+e) adequação da minuta do convênio (item 6.1).</t>
   </si>
   <si>
     <t>202400005009120</t>
@@ -1283,13 +1287,13 @@
     <t>107/2024</t>
   </si>
   <si>
+    <t>SUREG</t>
+  </si>
+  <si>
     <t>202500005026379</t>
   </si>
   <si>
     <t>SISLOG 116096 -Desenvolvimento e operação das integrações entre Sistema MV E SIGO -PROCESSO NO SEI 202500010071925 (CCONT)</t>
-  </si>
-  <si>
-    <t>SUREG</t>
   </si>
   <si>
     <t>Está na SUREG para gestão CONTRATO.   Encaminhem-se os autos à SUPERINTENDÊNCIA DE REGULAÇÃO, CONTROLE E AVALIAÇÃO, tendo em vista que a Contratação SISLOG encontra-se devidamente formalizada.</t>
@@ -1386,10 +1390,7 @@
     <t>FORNECEDOR OTC DOC ORGANIZACAO TECNOLOGIA E CUSTODIA DE DOCUMENTOS. Contratação de empresa especializada em digitalização de documentos</t>
   </si>
   <si>
-    <t>GEFIN</t>
-  </si>
-  <si>
-    <t>ANEXO II emitido, DAOF E IPOF</t>
+    <t>PARA ANÁLISE</t>
   </si>
   <si>
     <t>64/2023</t>
@@ -1404,7 +1405,7 @@
     <t>SISLOG 111945 RUE - REGULAÇÃO DE URGÊNCIA E EMERGENCA - prestação de serviços de solução integrada de regulação médica, comunicação e monitoramento. Processo de autorização para ATA (SEI 202500010001886)</t>
   </si>
   <si>
-    <t>A licitação encontra se devidamente finalizada, conforme previsão legal, estando o mesmo apto para instruções de eventuais procedimentos de compras</t>
+    <t>PUBLICADO PNCP. A licitação encontra se devidamente finalizada, conforme previsão legal, estando o mesmo apto para instruções de eventuais procedimentos de compras</t>
   </si>
   <si>
     <t>202400005000381</t>
@@ -1425,7 +1426,7 @@
     <t>FORNECEDOR INDRA. Prestação de Serviço de Desenvolvimento de software</t>
   </si>
   <si>
-    <t>PARA ANÁLISE</t>
+    <t>PGE</t>
   </si>
   <si>
     <t>15/2023</t>
@@ -1822,15 +1823,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V117"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
@@ -1926,7 +1918,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -1962,7 +1954,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J3" t="s">
         <v>34</v>
@@ -1998,7 +1990,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="J4" t="s">
         <v>39</v>
@@ -2034,7 +2026,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
@@ -2070,7 +2062,7 @@
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="J6" t="s">
         <v>39</v>
@@ -2118,7 +2110,7 @@
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="J7" t="s">
         <v>53</v>
@@ -2171,7 +2163,7 @@
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="J8" t="s">
         <v>53</v>
@@ -2224,7 +2216,7 @@
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -2272,7 +2264,7 @@
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
@@ -2320,7 +2312,7 @@
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -2368,7 +2360,7 @@
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="J12" t="s">
         <v>53</v>
@@ -2415,7 +2407,7 @@
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="J13" t="s">
         <v>53</v>
@@ -2462,7 +2454,7 @@
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="J14" t="s">
         <v>53</v>
@@ -2509,7 +2501,7 @@
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="J15" t="s">
         <v>39</v>
@@ -2556,7 +2548,7 @@
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="J16" t="s">
         <v>53</v>
@@ -2603,7 +2595,7 @@
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
@@ -2650,7 +2642,7 @@
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="J18" t="s">
         <v>53</v>
@@ -2697,7 +2689,7 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="J19" t="s">
         <v>53</v>
@@ -2744,7 +2736,7 @@
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -2780,7 +2772,7 @@
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
@@ -2827,7 +2819,7 @@
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="J22" t="s">
         <v>53</v>
@@ -2874,7 +2866,7 @@
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="J23" t="s">
         <v>39</v>
@@ -2919,7 +2911,7 @@
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -2955,7 +2947,7 @@
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J25" t="s">
         <v>53</v>
@@ -3002,7 +2994,7 @@
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J26" t="s">
         <v>53</v>
@@ -3049,7 +3041,7 @@
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J27" t="s">
         <v>39</v>
@@ -3091,7 +3083,7 @@
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="J28" t="s">
         <v>53</v>
@@ -3138,7 +3130,7 @@
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -3174,7 +3166,7 @@
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="J30" t="s">
         <v>34</v>
@@ -3210,7 +3202,7 @@
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -3246,7 +3238,7 @@
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="J32" t="s">
         <v>39</v>
@@ -3293,7 +3285,7 @@
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -3340,7 +3332,7 @@
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="J34" t="s">
         <v>39</v>
@@ -3376,7 +3368,7 @@
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="J35" t="s">
         <v>34</v>
@@ -3412,7 +3404,7 @@
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -3448,7 +3440,7 @@
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="J37" t="s">
         <v>39</v>
@@ -3495,7 +3487,7 @@
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J38" t="s">
         <v>34</v>
@@ -3531,7 +3523,7 @@
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J39" t="s">
         <v>39</v>
@@ -3581,7 +3573,7 @@
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -3617,7 +3609,7 @@
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="J41" t="s">
         <v>39</v>
@@ -3664,7 +3656,7 @@
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J42" t="s">
         <v>34</v>
@@ -3700,7 +3692,7 @@
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -3736,7 +3728,7 @@
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J44" t="s">
         <v>39</v>
@@ -3780,7 +3772,7 @@
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J45" t="s">
         <v>39</v>
@@ -3822,7 +3814,7 @@
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J46" t="s">
         <v>39</v>
@@ -3864,7 +3856,7 @@
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J47" t="s">
         <v>39</v>
@@ -3882,7 +3874,7 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -3913,7 +3905,7 @@
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J48" t="s">
         <v>39</v>
@@ -3963,7 +3955,7 @@
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J49" t="s">
         <v>39</v>
@@ -3981,7 +3973,7 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
@@ -4012,7 +4004,7 @@
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -4056,7 +4048,7 @@
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J51" t="s">
         <v>34</v>
@@ -4092,7 +4084,7 @@
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -4128,7 +4120,7 @@
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -4164,7 +4156,7 @@
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="J54" t="s">
         <v>53</v>
@@ -4211,7 +4203,7 @@
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J55" t="s">
         <v>39</v>
@@ -4247,7 +4239,7 @@
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="J56" t="s">
         <v>34</v>
@@ -4283,7 +4275,7 @@
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J57" t="s">
         <v>39</v>
@@ -4319,7 +4311,7 @@
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="J58" t="s">
         <v>34</v>
@@ -4355,7 +4347,7 @@
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J59" t="s">
         <v>39</v>
@@ -4391,7 +4383,7 @@
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J60" t="s">
         <v>53</v>
@@ -4409,7 +4401,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4440,7 +4432,7 @@
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J61" t="s">
         <v>34</v>
@@ -4476,7 +4468,7 @@
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -4512,7 +4504,7 @@
         <v>46183</v>
       </c>
       <c r="I63" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="s">
         <v>28</v>
@@ -4548,7 +4540,7 @@
         <v>46181</v>
       </c>
       <c r="I64" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J64" t="s">
         <v>267</v>
@@ -4584,7 +4576,7 @@
         <v>46156</v>
       </c>
       <c r="I65" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J65" t="s">
         <v>39</v>
@@ -4622,7 +4614,7 @@
         <v>46155</v>
       </c>
       <c r="I66" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J66" t="s">
         <v>39</v>
@@ -4660,7 +4652,7 @@
         <v>46157</v>
       </c>
       <c r="I67" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J67" t="s">
         <v>39</v>
@@ -4698,7 +4690,7 @@
         <v>45943</v>
       </c>
       <c r="I68" s="3">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J68" t="s">
         <v>34</v>
@@ -4736,7 +4728,7 @@
         <v>45715</v>
       </c>
       <c r="I69" s="3">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J69" t="s">
         <v>53</v>
@@ -4785,7 +4777,7 @@
         <v>45817</v>
       </c>
       <c r="I70" s="3">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J70" t="s">
         <v>53</v>
@@ -4803,7 +4795,7 @@
         <v>46909</v>
       </c>
       <c r="T70" s="3">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="U70" s="3"/>
       <c r="V70" s="4">
@@ -4836,7 +4828,7 @@
         <v>45911</v>
       </c>
       <c r="I71" s="3">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J71" t="s">
         <v>53</v>
@@ -4888,7 +4880,7 @@
         <v>45895</v>
       </c>
       <c r="I72" s="3">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J72" t="s">
         <v>39</v>
@@ -4926,7 +4918,7 @@
         <v>46183</v>
       </c>
       <c r="I73" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="s">
         <v>28</v>
@@ -4964,7 +4956,7 @@
         <v>45838</v>
       </c>
       <c r="I74" s="3">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J74" t="s">
         <v>53</v>
@@ -4988,10 +4980,10 @@
         <v>46202</v>
       </c>
       <c r="T74" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U74" s="3">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V74" s="4">
         <v>51071</v>
@@ -5023,7 +5015,7 @@
         <v>45790</v>
       </c>
       <c r="I75" s="3">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J75" t="s">
         <v>53</v>
@@ -5078,7 +5070,7 @@
         <v>46094</v>
       </c>
       <c r="I76" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J76" t="s">
         <v>39</v>
@@ -5096,7 +5088,7 @@
         <v>47181</v>
       </c>
       <c r="T76" s="3">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="U76" s="3"/>
       <c r="V76" s="4">
@@ -5129,7 +5121,7 @@
         <v>45975</v>
       </c>
       <c r="I77" s="3">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J77" t="s">
         <v>39</v>
@@ -5153,10 +5145,10 @@
         <v>46220</v>
       </c>
       <c r="T77" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="U77" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V77" s="4">
         <v>71722</v>
@@ -5188,7 +5180,7 @@
         <v>46183</v>
       </c>
       <c r="I78" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="s">
         <v>267</v>
@@ -5206,7 +5198,7 @@
         <v>47181</v>
       </c>
       <c r="T78" s="3">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="U78" s="3"/>
       <c r="V78" s="4">
@@ -5239,7 +5231,7 @@
         <v>46094</v>
       </c>
       <c r="I79" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J79" t="s">
         <v>39</v>
@@ -5257,7 +5249,7 @@
         <v>47181</v>
       </c>
       <c r="T79" s="3">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="U79" s="3"/>
       <c r="V79" s="4">
@@ -5290,7 +5282,7 @@
         <v>45790</v>
       </c>
       <c r="I80" s="3">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J80" t="s">
         <v>53</v>
@@ -5345,7 +5337,7 @@
         <v>46170</v>
       </c>
       <c r="I81" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J81" t="s">
         <v>53</v>
@@ -5363,7 +5355,7 @@
         <v>46273</v>
       </c>
       <c r="T81" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
@@ -5396,7 +5388,7 @@
         <v>46087</v>
       </c>
       <c r="I82" s="3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J82" t="s">
         <v>53</v>
@@ -5414,7 +5406,7 @@
         <v>47910</v>
       </c>
       <c r="T82" s="3">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
@@ -5447,7 +5439,7 @@
         <v>45861</v>
       </c>
       <c r="I83" s="3">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J83" t="s">
         <v>39</v>
@@ -5465,7 +5457,7 @@
         <v>46225</v>
       </c>
       <c r="T83" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
@@ -5498,7 +5490,7 @@
         <v>45607</v>
       </c>
       <c r="I84" s="3">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J84" t="s">
         <v>53</v>
@@ -5536,7 +5528,7 @@
         <v>46002</v>
       </c>
       <c r="I85" s="3">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J85" t="s">
         <v>39</v>
@@ -5554,7 +5546,7 @@
         <v>47097</v>
       </c>
       <c r="T85" s="3">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
@@ -5587,7 +5579,7 @@
         <v>46146</v>
       </c>
       <c r="I86" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J86" t="s">
         <v>53</v>
@@ -5605,7 +5597,7 @@
         <v>47905</v>
       </c>
       <c r="T86" s="3">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
@@ -5638,7 +5630,7 @@
         <v>45881</v>
       </c>
       <c r="I87" s="3">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J87" t="s">
         <v>53</v>
@@ -5663,7 +5655,7 @@
       </c>
       <c r="T87" s="3"/>
       <c r="U87" s="3">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V87" s="4">
         <v>374899.96</v>
@@ -5695,7 +5687,7 @@
         <v>45624</v>
       </c>
       <c r="I88" s="3">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J88" t="s">
         <v>39</v>
@@ -5735,13 +5727,13 @@
         <v>351</v>
       </c>
       <c r="F89" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="G89" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="H89" s="2">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="I89" s="3">
         <v>1</v>
@@ -5761,34 +5753,34 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C90" s="2">
         <v>44939</v>
       </c>
       <c r="D90" t="s">
+        <v>353</v>
+      </c>
+      <c r="E90" t="s">
         <v>354</v>
-      </c>
-      <c r="E90" t="s">
-        <v>355</v>
       </c>
       <c r="F90" t="s">
         <v>29</v>
       </c>
       <c r="G90" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H90" s="2">
         <v>45979</v>
       </c>
       <c r="I90" s="3">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J90" t="s">
         <v>53</v>
       </c>
       <c r="K90" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L90" s="2">
         <v>45968</v>
@@ -5807,7 +5799,7 @@
       </c>
       <c r="T90" s="3"/>
       <c r="U90" s="3">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V90" s="4">
         <v>706431.6</v>
@@ -5818,7 +5810,7 @@
         <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C91" s="2">
         <v>45673</v>
@@ -5827,7 +5819,7 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F91" t="s">
         <v>43</v>
@@ -5839,20 +5831,20 @@
         <v>46140</v>
       </c>
       <c r="I91" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J91" t="s">
         <v>53</v>
       </c>
       <c r="K91" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M91" s="3"/>
       <c r="S91" s="2">
         <v>46598</v>
       </c>
       <c r="T91" s="3">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="U91" s="3"/>
       <c r="V91" s="4">
@@ -5864,7 +5856,7 @@
         <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C92" s="2">
         <v>45215</v>
@@ -5873,25 +5865,25 @@
         <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F92" t="s">
         <v>170</v>
       </c>
       <c r="G92" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H92" s="2">
         <v>45687</v>
       </c>
       <c r="I92" s="3">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J92" t="s">
         <v>39</v>
       </c>
       <c r="K92" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L92" s="2">
         <v>45685</v>
@@ -5903,7 +5895,7 @@
         <v>46780</v>
       </c>
       <c r="T92" s="3">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="U92" s="3"/>
       <c r="V92" s="4">
@@ -5915,7 +5907,7 @@
         <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C93" s="2">
         <v>45366</v>
@@ -5924,25 +5916,25 @@
         <v>45</v>
       </c>
       <c r="E93" t="s">
+        <v>365</v>
+      </c>
+      <c r="F93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" t="s">
         <v>366</v>
-      </c>
-      <c r="F93" t="s">
-        <v>43</v>
-      </c>
-      <c r="G93" t="s">
-        <v>367</v>
       </c>
       <c r="H93" s="2">
         <v>45481</v>
       </c>
       <c r="I93" s="3">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J93" t="s">
         <v>53</v>
       </c>
       <c r="K93" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L93" s="2">
         <v>45471</v>
@@ -5954,7 +5946,7 @@
         <v>47301</v>
       </c>
       <c r="T93" s="3">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="U93" s="3"/>
       <c r="V93" s="4">
@@ -5966,7 +5958,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C94" s="2">
         <v>45152</v>
@@ -5975,25 +5967,25 @@
         <v>264</v>
       </c>
       <c r="E94" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F94" t="s">
         <v>29</v>
       </c>
       <c r="G94" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H94" s="2">
         <v>45440</v>
       </c>
       <c r="I94" s="3">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J94" t="s">
         <v>53</v>
       </c>
       <c r="K94" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L94" s="2">
         <v>45303</v>
@@ -6015,7 +6007,7 @@
         <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C95" s="2">
         <v>45373</v>
@@ -6024,25 +6016,25 @@
         <v>45</v>
       </c>
       <c r="E95" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F95" t="s">
         <v>43</v>
       </c>
       <c r="G95" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H95" s="2">
         <v>45492</v>
       </c>
       <c r="I95" s="3">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J95" t="s">
         <v>53</v>
       </c>
       <c r="K95" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L95" s="2">
         <v>45492</v>
@@ -6054,7 +6046,7 @@
         <v>46587</v>
       </c>
       <c r="T95" s="3">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
@@ -6066,7 +6058,7 @@
         <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C96" s="2">
         <v>44663</v>
@@ -6075,7 +6067,7 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F96" t="s">
         <v>129</v>
@@ -6087,13 +6079,13 @@
         <v>45588</v>
       </c>
       <c r="I96" s="3">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J96" t="s">
         <v>53</v>
       </c>
       <c r="K96" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L96" s="2">
         <v>44893</v>
@@ -6121,7 +6113,7 @@
         <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C97" s="2">
         <v>45826</v>
@@ -6130,25 +6122,25 @@
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F97" t="s">
         <v>67</v>
       </c>
       <c r="G97" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H97" s="2">
         <v>46079</v>
       </c>
       <c r="I97" s="3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J97" t="s">
         <v>53</v>
       </c>
       <c r="K97" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L97" s="2">
         <v>46076</v>
@@ -6160,7 +6152,7 @@
         <v>47903</v>
       </c>
       <c r="T97" s="3">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
@@ -6169,10 +6161,10 @@
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
+        <v>382</v>
+      </c>
+      <c r="B98" t="s">
         <v>383</v>
-      </c>
-      <c r="B98" t="s">
-        <v>384</v>
       </c>
       <c r="C98" s="2">
         <v>46150</v>
@@ -6181,10 +6173,10 @@
         <v>45</v>
       </c>
       <c r="E98" t="s">
+        <v>384</v>
+      </c>
+      <c r="F98" t="s">
         <v>385</v>
-      </c>
-      <c r="F98" t="s">
-        <v>386</v>
       </c>
       <c r="G98" t="s">
         <v>266</v>
@@ -6193,7 +6185,7 @@
         <v>46168</v>
       </c>
       <c r="I98" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J98" t="s">
         <v>28</v>
@@ -6210,7 +6202,7 @@
         <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C99" s="2">
         <v>46094</v>
@@ -6219,19 +6211,19 @@
         <v>45</v>
       </c>
       <c r="E99" t="s">
+        <v>387</v>
+      </c>
+      <c r="F99" t="s">
+        <v>385</v>
+      </c>
+      <c r="G99" t="s">
         <v>388</v>
-      </c>
-      <c r="F99" t="s">
-        <v>386</v>
-      </c>
-      <c r="G99" t="s">
-        <v>389</v>
       </c>
       <c r="H99" s="2">
         <v>46170</v>
       </c>
       <c r="I99" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J99" t="s">
         <v>28</v>
@@ -6248,7 +6240,7 @@
         <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C100" s="2">
         <v>45950</v>
@@ -6257,25 +6249,25 @@
         <v>45</v>
       </c>
       <c r="E100" t="s">
+        <v>390</v>
+      </c>
+      <c r="F100" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100" t="s">
         <v>391</v>
-      </c>
-      <c r="F100" t="s">
-        <v>43</v>
-      </c>
-      <c r="G100" t="s">
-        <v>392</v>
       </c>
       <c r="H100" s="2">
         <v>45988</v>
       </c>
       <c r="I100" s="3">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J100" t="s">
         <v>39</v>
       </c>
       <c r="K100" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L100" s="2">
         <v>45979</v>
@@ -6287,7 +6279,7 @@
         <v>46343</v>
       </c>
       <c r="T100" s="3">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="U100" s="3"/>
       <c r="V100" s="4">
@@ -6299,7 +6291,7 @@
         <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C101" s="2">
         <v>45511</v>
@@ -6308,25 +6300,25 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F101" t="s">
         <v>26</v>
       </c>
       <c r="G101" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H101" s="2">
         <v>45786</v>
       </c>
       <c r="I101" s="3">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J101" t="s">
         <v>39</v>
       </c>
       <c r="K101" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L101" s="2">
         <v>45794</v>
@@ -6345,7 +6337,7 @@
         <v>26</v>
       </c>
       <c r="B102" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C102" s="2">
         <v>45848</v>
@@ -6354,25 +6346,25 @@
         <v>36</v>
       </c>
       <c r="E102" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F102" t="s">
         <v>225</v>
       </c>
       <c r="G102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H102" s="2">
         <v>46014</v>
       </c>
       <c r="I102" s="3">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J102" t="s">
         <v>39</v>
       </c>
       <c r="K102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L102" s="2">
         <v>46008</v>
@@ -6384,7 +6376,7 @@
         <v>46373</v>
       </c>
       <c r="T102" s="3">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
@@ -6396,7 +6388,7 @@
         <v>26</v>
       </c>
       <c r="B103" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C103" s="2">
         <v>46030</v>
@@ -6405,10 +6397,10 @@
         <v>264</v>
       </c>
       <c r="E103" t="s">
+        <v>402</v>
+      </c>
+      <c r="F103" t="s">
         <v>403</v>
-      </c>
-      <c r="F103" t="s">
-        <v>386</v>
       </c>
       <c r="G103" t="s">
         <v>404</v>
@@ -6417,7 +6409,7 @@
         <v>46157</v>
       </c>
       <c r="I103" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J103" t="s">
         <v>28</v>
@@ -6455,7 +6447,7 @@
         <v>45568</v>
       </c>
       <c r="I104" s="3">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="J104" t="s">
         <v>53</v>
@@ -6473,7 +6465,7 @@
         <v>46479</v>
       </c>
       <c r="T104" s="3">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
@@ -6482,10 +6474,10 @@
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
-        <v>29</v>
+        <v>410</v>
       </c>
       <c r="B105" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C105" s="2">
         <v>45526</v>
@@ -6494,10 +6486,10 @@
         <v>36</v>
       </c>
       <c r="E105" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F105" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G105" t="s">
         <v>413</v>
@@ -6506,7 +6498,7 @@
         <v>45932</v>
       </c>
       <c r="I105" s="3">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J105" t="s">
         <v>53</v>
@@ -6519,7 +6511,7 @@
         <v>47748</v>
       </c>
       <c r="T105" s="3">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="U105" s="3"/>
       <c r="V105" s="4">
@@ -6552,7 +6544,7 @@
         <v>45958</v>
       </c>
       <c r="I106" s="3">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J106" t="s">
         <v>53</v>
@@ -6570,7 +6562,7 @@
         <v>46316</v>
       </c>
       <c r="T106" s="3">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
@@ -6603,7 +6595,7 @@
         <v>45930</v>
       </c>
       <c r="I107" s="3">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J107" t="s">
         <v>39</v>
@@ -6621,7 +6613,7 @@
         <v>46950</v>
       </c>
       <c r="T107" s="3">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
@@ -6639,13 +6631,13 @@
         <v>44607</v>
       </c>
       <c r="D108" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E108" t="s">
         <v>425</v>
       </c>
       <c r="F108" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="G108" t="s">
         <v>426</v>
@@ -6654,7 +6646,7 @@
         <v>46183</v>
       </c>
       <c r="I108" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" t="s">
         <v>267</v>
@@ -6709,7 +6701,7 @@
         <v>45993</v>
       </c>
       <c r="I109" s="3">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J109" t="s">
         <v>39</v>
@@ -6727,7 +6719,7 @@
         <v>46540</v>
       </c>
       <c r="T109" s="3">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U109" s="3"/>
       <c r="V109" s="4">
@@ -6760,7 +6752,7 @@
         <v>45797</v>
       </c>
       <c r="I110" s="3">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J110" t="s">
         <v>53</v>
@@ -6773,7 +6765,7 @@
         <v>46523</v>
       </c>
       <c r="T110" s="3">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="U110" s="3"/>
       <c r="V110" s="4">
@@ -6806,7 +6798,7 @@
         <v>45798</v>
       </c>
       <c r="I111" s="3">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J111" t="s">
         <v>53</v>
@@ -6837,7 +6829,7 @@
       </c>
       <c r="T111" s="3"/>
       <c r="U111" s="3">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="V111" s="4">
         <v>10934411.34</v>
@@ -6860,22 +6852,22 @@
         <v>443</v>
       </c>
       <c r="F112" t="s">
+        <v>385</v>
+      </c>
+      <c r="G112" t="s">
         <v>444</v>
-      </c>
-      <c r="G112" t="s">
-        <v>445</v>
       </c>
       <c r="H112" s="2">
         <v>46183</v>
       </c>
       <c r="I112" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" t="s">
         <v>267</v>
       </c>
       <c r="K112" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L112" s="2">
         <v>45148</v>
@@ -6900,31 +6892,31 @@
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
+        <v>446</v>
+      </c>
+      <c r="B113" t="s">
         <v>447</v>
-      </c>
-      <c r="B113" t="s">
-        <v>448</v>
       </c>
       <c r="C113" s="2">
         <v>45666</v>
       </c>
       <c r="D113" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E113" t="s">
+        <v>448</v>
+      </c>
+      <c r="F113" t="s">
+        <v>410</v>
+      </c>
+      <c r="G113" t="s">
         <v>449</v>
-      </c>
-      <c r="F113" t="s">
-        <v>412</v>
-      </c>
-      <c r="G113" t="s">
-        <v>450</v>
       </c>
       <c r="H113" s="2">
         <v>46174</v>
       </c>
       <c r="I113" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J113" t="s">
         <v>28</v>
@@ -6938,10 +6930,10 @@
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B114" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C114" s="2">
         <v>45250</v>
@@ -6950,25 +6942,25 @@
         <v>36</v>
       </c>
       <c r="E114" t="s">
+        <v>451</v>
+      </c>
+      <c r="F114" t="s">
+        <v>410</v>
+      </c>
+      <c r="G114" t="s">
         <v>452</v>
-      </c>
-      <c r="F114" t="s">
-        <v>412</v>
-      </c>
-      <c r="G114" t="s">
-        <v>453</v>
       </c>
       <c r="H114" s="2">
         <v>45400</v>
       </c>
       <c r="I114" s="3">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J114" t="s">
         <v>53</v>
       </c>
       <c r="K114" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L114" s="2">
         <v>45401</v>
@@ -6980,7 +6972,7 @@
         <v>47227</v>
       </c>
       <c r="T114" s="3">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="U114" s="3"/>
       <c r="V114" s="4">
@@ -6992,7 +6984,7 @@
         <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C115" s="2">
         <v>44238</v>
@@ -7001,25 +6993,25 @@
         <v>24</v>
       </c>
       <c r="E115" t="s">
+        <v>455</v>
+      </c>
+      <c r="F115" t="s">
         <v>456</v>
       </c>
-      <c r="F115" t="s">
-        <v>386</v>
-      </c>
       <c r="G115" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="H115" s="2">
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="I115" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J115" t="s">
         <v>267</v>
       </c>
       <c r="K115" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L115" s="2">
         <v>44969</v>
@@ -7028,7 +7020,7 @@
         <v>731</v>
       </c>
       <c r="O115" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P115" s="2">
         <v>46798</v>
@@ -7038,7 +7030,7 @@
       </c>
       <c r="T115" s="3"/>
       <c r="U115" s="3">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="V115" s="4">
         <v>41936400</v>
@@ -7049,7 +7041,7 @@
         <v>43</v>
       </c>
       <c r="B116" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C116" s="2">
         <v>45607</v>
@@ -7058,25 +7050,25 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
+        <v>460</v>
+      </c>
+      <c r="F116" t="s">
         <v>461</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>462</v>
-      </c>
-      <c r="G116" t="s">
-        <v>463</v>
       </c>
       <c r="H116" s="2">
         <v>45798</v>
       </c>
       <c r="I116" s="3">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J116" t="s">
         <v>53</v>
       </c>
       <c r="K116" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L116" s="2">
         <v>45798</v>
@@ -7088,7 +7080,7 @@
         <v>46712</v>
       </c>
       <c r="T116" s="3">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
@@ -7100,7 +7092,7 @@
         <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C117" s="2">
         <v>45664</v>
@@ -7109,19 +7101,19 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F117" t="s">
         <v>225</v>
       </c>
       <c r="G117" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H117" s="2">
         <v>45958</v>
       </c>
       <c r="I117" s="3">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J117" t="s">
         <v>34</v>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D474587F-11FD-4935-9774-53D98BF3E7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22DB8ED-9803-408D-9A3D-052A74BFB4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="469">
   <si>
     <t>Departamento</t>
   </si>
@@ -837,7 +837,7 @@
     <t>SISLOG 120357 - Aquisição de Workstations - Atender demandas da SES-GO</t>
   </si>
   <si>
-    <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS</t>
+    <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS. Existe possiblidade de uma ARP</t>
   </si>
   <si>
     <t>202600010023321</t>
@@ -939,7 +939,10 @@
     <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
   </si>
   <si>
-    <t>Solicitação de Parecer Técnico</t>
+    <t>GELIC</t>
+  </si>
+  <si>
+    <t>houve a apresentação de propostas, as quais foram todas desclassificadas e/ou os licitantes inabilitados, inviabilizando a adjudicação do objeto, declaro o certame FRACASSADO.</t>
   </si>
   <si>
     <t>SESG</t>
@@ -951,7 +954,7 @@
     <t>SISLOG nº 110808 gestão de competências Software GALERA.APP LEME CONSULTORIA EM GESTÃO DE RH LTDA. PROCESSO SEI PARALELO 202500010040069</t>
   </si>
   <si>
-    <t>CONTRATO EM GESTÃO DA SESG</t>
+    <t>PARA RENOVAÇÃO</t>
   </si>
   <si>
     <t>52/2025</t>
@@ -993,7 +996,7 @@
     <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 9</t>
   </si>
   <si>
-    <t>AGUARDANDO CERTIDÕES E ACERTOS NAS LICENÇAS. ENVIADA CORRESPONDÊNCIA COBRANDO AGILIDADE</t>
+    <t>AGUARDANDO CERTIDÕES.  Prints erro licença adobe (92163676). COMUNICADO A CAMALEON AGUARDANDO RETORNO</t>
   </si>
   <si>
     <t>09/2026</t>
@@ -1208,7 +1211,7 @@
     <t>AQUISIÇÃO DE 40 LICENÇAS AUTODESK AEC DA CS CAD CAM LTDA</t>
   </si>
   <si>
-    <t>PROCSET</t>
+    <t>Contrato 64 (91909845) ASSINADO PELO SECRETÁRIO</t>
   </si>
   <si>
     <t>202600010020471</t>
@@ -1217,7 +1220,12 @@
     <t>LINKS DE DADOS SD-WAN - PARTÍCIPE ARP 002/2026 – SGG PROCESSO ORIGINAL SEI 202618037001743</t>
   </si>
   <si>
-    <t>para análise da Minuta do Contrato</t>
+    <t>SUBPEI CCONT</t>
+  </si>
+  <si>
+    <t>a) designação do gestor do contrato por meio de portaria com a consequente publicação (subitem 2.4); SOLICITAR A GETEC INDICAÇÃO.
+b) acompanhamento da execução contratual sob a ótica orçamentária e financeira, em observância ao art. 42 da Lei Complementar nº 101/2000, de modo a assegurar disponibilidade de caixa para eventual pagamento de parcelas no exercício de 2027 (subitens 3.5 a 3.7);
+c) manutenção da regularidade jurídica, fiscal e trabalhista durante toda a execução contratual, bem como renovação das certidões que vencerem no curso do procedimento (subitem 5.4). CERTIDÕES SOLICITADAS E DOCUMENTAÇÃO JURÍDICA.</t>
   </si>
   <si>
     <t>202500010083108</t>
@@ -1262,14 +1270,10 @@
     <t>Novo Termo de Cooperação entre UFG e SES para realização de capacitação continuada em padrão FHIR.</t>
   </si>
   <si>
-    <t>SUBPEI GCC</t>
-  </si>
-  <si>
-    <t>juntada de justificativas e dos documentos aptos a afastar a obrigatoriedade de chamamento público (item 3.7);
-b) juntada de justificativas de preço (item 3.8);
-c) adequação do Plano de Trabalho para atendimento do que dispõe o art. 6º do Decreto nº 10.248/23 (itens 5.3 e 5.4);
-d) juntada dos documentos instrutórios da contratação faltantes ou desatualizados e manutenção da regularidade das certidões durante o curso do processo (item 5.4. a 5.7);
-e) adequação da minuta do convênio (item 6.1).</t>
+    <t>CCONV</t>
+  </si>
+  <si>
+    <t>Convênio 16 (92189244) em elaboração</t>
   </si>
   <si>
     <t>202400005009120</t>
@@ -1335,13 +1339,13 @@
     <t>FORNECEDOR INDRA. Serviços Técnicos na área de Tecnologia da Informação para suprir as demandas de subscrições Cloudera para atualização do ecossistema Hadoop</t>
   </si>
   <si>
-    <t>CERTIDÕES E DOCUMENTOS ANEXADOS</t>
+    <t>Está na GEIN para gestão CONTRATO</t>
   </si>
   <si>
     <t>58/2022</t>
   </si>
   <si>
-    <t>5º</t>
+    <t>6º</t>
   </si>
   <si>
     <t>GEMAE</t>
@@ -1390,7 +1394,7 @@
     <t>FORNECEDOR OTC DOC ORGANIZACAO TECNOLOGIA E CUSTODIA DE DOCUMENTOS. Contratação de empresa especializada em digitalização de documentos</t>
   </si>
   <si>
-    <t>PARA ANÁLISE</t>
+    <t>Nota de Empenho 2026.2850.014.00039. (92365185) INSERIDA NO PROCESSO</t>
   </si>
   <si>
     <t>64/2023</t>
@@ -1426,7 +1430,7 @@
     <t>FORNECEDOR INDRA. Prestação de Serviço de Desenvolvimento de software</t>
   </si>
   <si>
-    <t>PGE</t>
+    <t xml:space="preserve"> AGUARDAR ORIENTAÇÕES DO FILIPE</t>
   </si>
   <si>
     <t>15/2023</t>
@@ -1918,7 +1922,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -1954,7 +1958,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="J3" t="s">
         <v>34</v>
@@ -1990,7 +1994,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="J4" t="s">
         <v>39</v>
@@ -2026,7 +2030,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
@@ -2062,7 +2066,7 @@
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1044</v>
+        <v>1058</v>
       </c>
       <c r="J6" t="s">
         <v>39</v>
@@ -2110,7 +2114,7 @@
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="J7" t="s">
         <v>53</v>
@@ -2163,7 +2167,7 @@
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>987</v>
+        <v>1001</v>
       </c>
       <c r="J8" t="s">
         <v>53</v>
@@ -2216,7 +2220,7 @@
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -2264,7 +2268,7 @@
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
@@ -2312,7 +2316,7 @@
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>732</v>
+        <v>746</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -2360,7 +2364,7 @@
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="J12" t="s">
         <v>53</v>
@@ -2407,7 +2411,7 @@
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1078</v>
+        <v>1092</v>
       </c>
       <c r="J13" t="s">
         <v>53</v>
@@ -2454,7 +2458,7 @@
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1031</v>
+        <v>1045</v>
       </c>
       <c r="J14" t="s">
         <v>53</v>
@@ -2501,7 +2505,7 @@
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>996</v>
+        <v>1010</v>
       </c>
       <c r="J15" t="s">
         <v>39</v>
@@ -2548,7 +2552,7 @@
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="J16" t="s">
         <v>53</v>
@@ -2595,7 +2599,7 @@
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1078</v>
+        <v>1092</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
@@ -2642,7 +2646,7 @@
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>977</v>
+        <v>991</v>
       </c>
       <c r="J18" t="s">
         <v>53</v>
@@ -2689,7 +2693,7 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1078</v>
+        <v>1092</v>
       </c>
       <c r="J19" t="s">
         <v>53</v>
@@ -2736,7 +2740,7 @@
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1151</v>
+        <v>1165</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -2772,7 +2776,7 @@
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
@@ -2819,7 +2823,7 @@
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1277</v>
+        <v>1291</v>
       </c>
       <c r="J22" t="s">
         <v>53</v>
@@ -2866,7 +2870,7 @@
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1178</v>
+        <v>1192</v>
       </c>
       <c r="J23" t="s">
         <v>39</v>
@@ -2911,7 +2915,7 @@
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -2947,7 +2951,7 @@
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>959</v>
+        <v>973</v>
       </c>
       <c r="J25" t="s">
         <v>53</v>
@@ -2994,7 +2998,7 @@
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>961</v>
+        <v>975</v>
       </c>
       <c r="J26" t="s">
         <v>53</v>
@@ -3041,7 +3045,7 @@
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="J27" t="s">
         <v>39</v>
@@ -3083,7 +3087,7 @@
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1051</v>
+        <v>1065</v>
       </c>
       <c r="J28" t="s">
         <v>53</v>
@@ -3130,7 +3134,7 @@
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1142</v>
+        <v>1156</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -3166,7 +3170,7 @@
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="J30" t="s">
         <v>34</v>
@@ -3202,7 +3206,7 @@
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>934</v>
+        <v>948</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -3238,7 +3242,7 @@
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="J32" t="s">
         <v>39</v>
@@ -3285,7 +3289,7 @@
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -3332,7 +3336,7 @@
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="J34" t="s">
         <v>39</v>
@@ -3368,7 +3372,7 @@
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>918</v>
+        <v>932</v>
       </c>
       <c r="J35" t="s">
         <v>34</v>
@@ -3404,7 +3408,7 @@
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -3440,7 +3444,7 @@
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>949</v>
+        <v>963</v>
       </c>
       <c r="J37" t="s">
         <v>39</v>
@@ -3487,7 +3491,7 @@
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="J38" t="s">
         <v>34</v>
@@ -3523,7 +3527,7 @@
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="J39" t="s">
         <v>39</v>
@@ -3573,7 +3577,7 @@
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -3609,7 +3613,7 @@
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>921</v>
+        <v>935</v>
       </c>
       <c r="J41" t="s">
         <v>39</v>
@@ -3656,7 +3660,7 @@
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>759</v>
+        <v>773</v>
       </c>
       <c r="J42" t="s">
         <v>34</v>
@@ -3692,7 +3696,7 @@
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -3728,7 +3732,7 @@
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="J44" t="s">
         <v>39</v>
@@ -3772,7 +3776,7 @@
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="J45" t="s">
         <v>39</v>
@@ -3814,7 +3818,7 @@
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="J46" t="s">
         <v>39</v>
@@ -3856,7 +3860,7 @@
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="J47" t="s">
         <v>39</v>
@@ -3874,7 +3878,7 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1193</v>
+        <v>1179</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -3905,7 +3909,7 @@
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="J48" t="s">
         <v>39</v>
@@ -3955,7 +3959,7 @@
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="J49" t="s">
         <v>39</v>
@@ -3973,7 +3977,7 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1158</v>
+        <v>1144</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
@@ -4004,7 +4008,7 @@
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -4048,7 +4052,7 @@
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="J51" t="s">
         <v>34</v>
@@ -4084,7 +4088,7 @@
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -4120,7 +4124,7 @@
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -4156,7 +4160,7 @@
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="J54" t="s">
         <v>53</v>
@@ -4203,7 +4207,7 @@
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="J55" t="s">
         <v>39</v>
@@ -4239,7 +4243,7 @@
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>966</v>
+        <v>980</v>
       </c>
       <c r="J56" t="s">
         <v>34</v>
@@ -4275,7 +4279,7 @@
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>870</v>
+        <v>884</v>
       </c>
       <c r="J57" t="s">
         <v>39</v>
@@ -4311,7 +4315,7 @@
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="J58" t="s">
         <v>34</v>
@@ -4347,7 +4351,7 @@
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="J59" t="s">
         <v>39</v>
@@ -4383,7 +4387,7 @@
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="J60" t="s">
         <v>53</v>
@@ -4401,7 +4405,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1116</v>
+        <v>1102</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4432,7 +4436,7 @@
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="J61" t="s">
         <v>34</v>
@@ -4468,7 +4472,7 @@
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -4501,7 +4505,7 @@
         <v>262</v>
       </c>
       <c r="H63" s="2">
-        <v>46183</v>
+        <v>46197</v>
       </c>
       <c r="I63" s="3">
         <v>2</v>
@@ -4531,16 +4535,16 @@
         <v>265</v>
       </c>
       <c r="F64" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="G64" t="s">
         <v>266</v>
       </c>
       <c r="H64" s="2">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="I64" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J64" t="s">
         <v>267</v>
@@ -4576,7 +4580,7 @@
         <v>46156</v>
       </c>
       <c r="I65" s="3">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J65" t="s">
         <v>39</v>
@@ -4614,7 +4618,7 @@
         <v>46155</v>
       </c>
       <c r="I66" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="J66" t="s">
         <v>39</v>
@@ -4652,7 +4656,7 @@
         <v>46157</v>
       </c>
       <c r="I67" s="3">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J67" t="s">
         <v>39</v>
@@ -4690,7 +4694,7 @@
         <v>45943</v>
       </c>
       <c r="I68" s="3">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="J68" t="s">
         <v>34</v>
@@ -4728,7 +4732,7 @@
         <v>45715</v>
       </c>
       <c r="I69" s="3">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="J69" t="s">
         <v>53</v>
@@ -4777,7 +4781,7 @@
         <v>45817</v>
       </c>
       <c r="I70" s="3">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="J70" t="s">
         <v>53</v>
@@ -4795,7 +4799,7 @@
         <v>46909</v>
       </c>
       <c r="T70" s="3">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="U70" s="3"/>
       <c r="V70" s="4">
@@ -4828,7 +4832,7 @@
         <v>45911</v>
       </c>
       <c r="I71" s="3">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="J71" t="s">
         <v>53</v>
@@ -4880,7 +4884,7 @@
         <v>45895</v>
       </c>
       <c r="I72" s="3">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="J72" t="s">
         <v>39</v>
@@ -4909,19 +4913,19 @@
         <v>295</v>
       </c>
       <c r="F73" t="s">
-        <v>26</v>
+        <v>296</v>
       </c>
       <c r="G73" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H73" s="2">
-        <v>46183</v>
+        <v>46196</v>
       </c>
       <c r="I73" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J73" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M73" s="3"/>
       <c r="T73" s="3"/>
@@ -4932,10 +4936,10 @@
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C74" s="2">
         <v>45665</v>
@@ -4944,25 +4948,25 @@
         <v>36</v>
       </c>
       <c r="E74" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F74" t="s">
-        <v>297</v>
+        <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H74" s="2">
-        <v>45838</v>
+        <v>46198</v>
       </c>
       <c r="I74" s="3">
-        <v>347</v>
+        <v>1</v>
       </c>
       <c r="J74" t="s">
-        <v>53</v>
+        <v>267</v>
       </c>
       <c r="K74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L74" s="2">
         <v>46071</v>
@@ -4971,7 +4975,7 @@
         <v>406</v>
       </c>
       <c r="O74" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P74" s="2">
         <v>46294</v>
@@ -4980,10 +4984,10 @@
         <v>46202</v>
       </c>
       <c r="T74" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U74" s="3">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="V74" s="4">
         <v>51071</v>
@@ -5003,7 +5007,7 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F75" t="s">
         <v>43</v>
@@ -5015,13 +5019,13 @@
         <v>45790</v>
       </c>
       <c r="I75" s="3">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="J75" t="s">
         <v>53</v>
       </c>
       <c r="K75" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L75" s="2">
         <v>43964</v>
@@ -5049,7 +5053,7 @@
         <v>43</v>
       </c>
       <c r="B76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C76" s="2">
         <v>45915</v>
@@ -5058,25 +5062,25 @@
         <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F76" t="s">
         <v>142</v>
       </c>
       <c r="G76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H76" s="2">
         <v>46094</v>
       </c>
       <c r="I76" s="3">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J76" t="s">
         <v>39</v>
       </c>
       <c r="K76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L76" s="2">
         <v>46086</v>
@@ -5088,7 +5092,7 @@
         <v>47181</v>
       </c>
       <c r="T76" s="3">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="U76" s="3"/>
       <c r="V76" s="4">
@@ -5100,7 +5104,7 @@
         <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C77" s="2">
         <v>45950</v>
@@ -5109,25 +5113,25 @@
         <v>45</v>
       </c>
       <c r="E77" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F77" t="s">
         <v>43</v>
       </c>
       <c r="G77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H77" s="2">
         <v>45975</v>
       </c>
       <c r="I77" s="3">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="J77" t="s">
         <v>39</v>
       </c>
       <c r="K77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L77" s="2">
         <v>45978</v>
@@ -5145,10 +5149,10 @@
         <v>46220</v>
       </c>
       <c r="T77" s="3">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="U77" s="3">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="V77" s="4">
         <v>71722</v>
@@ -5159,7 +5163,7 @@
         <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C78" s="2">
         <v>45915</v>
@@ -5168,25 +5172,25 @@
         <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F78" t="s">
         <v>43</v>
       </c>
       <c r="G78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H78" s="2">
-        <v>46183</v>
+        <v>46198</v>
       </c>
       <c r="I78" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="s">
         <v>267</v>
       </c>
       <c r="K78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L78" s="2">
         <v>46086</v>
@@ -5198,7 +5202,7 @@
         <v>47181</v>
       </c>
       <c r="T78" s="3">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="U78" s="3"/>
       <c r="V78" s="4">
@@ -5210,7 +5214,7 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C79" s="2">
         <v>45915</v>
@@ -5219,25 +5223,25 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F79" t="s">
         <v>142</v>
       </c>
       <c r="G79" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H79" s="2">
         <v>46094</v>
       </c>
       <c r="I79" s="3">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J79" t="s">
         <v>39</v>
       </c>
       <c r="K79" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L79" s="2">
         <v>46086</v>
@@ -5249,7 +5253,7 @@
         <v>47181</v>
       </c>
       <c r="T79" s="3">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="U79" s="3"/>
       <c r="V79" s="4">
@@ -5282,13 +5286,13 @@
         <v>45790</v>
       </c>
       <c r="I80" s="3">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="J80" t="s">
         <v>53</v>
       </c>
       <c r="K80" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L80" s="2">
         <v>43964</v>
@@ -5316,7 +5320,7 @@
         <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C81" s="2">
         <v>45819</v>
@@ -5325,25 +5329,25 @@
         <v>45</v>
       </c>
       <c r="E81" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F81" t="s">
         <v>43</v>
       </c>
       <c r="G81" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H81" s="2">
         <v>46170</v>
       </c>
       <c r="I81" s="3">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J81" t="s">
         <v>53</v>
       </c>
       <c r="K81" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L81" s="2">
         <v>45904</v>
@@ -5355,7 +5359,7 @@
         <v>46273</v>
       </c>
       <c r="T81" s="3">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
@@ -5367,7 +5371,7 @@
         <v>43</v>
       </c>
       <c r="B82" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C82" s="2">
         <v>45952</v>
@@ -5376,25 +5380,25 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F82" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G82" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H82" s="2">
         <v>46087</v>
       </c>
       <c r="I82" s="3">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="J82" t="s">
         <v>53</v>
       </c>
       <c r="K82" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L82" s="2">
         <v>46086</v>
@@ -5406,7 +5410,7 @@
         <v>47910</v>
       </c>
       <c r="T82" s="3">
-        <v>1725</v>
+        <v>1711</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
@@ -5418,7 +5422,7 @@
         <v>43</v>
       </c>
       <c r="B83" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C83" s="2">
         <v>45775</v>
@@ -5427,7 +5431,7 @@
         <v>45</v>
       </c>
       <c r="E83" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F83" t="s">
         <v>43</v>
@@ -5439,13 +5443,13 @@
         <v>45861</v>
       </c>
       <c r="I83" s="3">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="J83" t="s">
         <v>39</v>
       </c>
       <c r="K83" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L83" s="2">
         <v>45856</v>
@@ -5457,7 +5461,7 @@
         <v>46225</v>
       </c>
       <c r="T83" s="3">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
@@ -5469,7 +5473,7 @@
         <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C84" s="2">
         <v>45539</v>
@@ -5478,19 +5482,19 @@
         <v>45</v>
       </c>
       <c r="E84" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F84" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G84" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H84" s="2">
         <v>45607</v>
       </c>
       <c r="I84" s="3">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="J84" t="s">
         <v>53</v>
@@ -5507,7 +5511,7 @@
         <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C85" s="2">
         <v>45840</v>
@@ -5516,25 +5520,25 @@
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F85" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G85" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H85" s="2">
         <v>46002</v>
       </c>
       <c r="I85" s="3">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J85" t="s">
         <v>39</v>
       </c>
       <c r="K85" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L85" s="2">
         <v>46001</v>
@@ -5546,7 +5550,7 @@
         <v>47097</v>
       </c>
       <c r="T85" s="3">
-        <v>912</v>
+        <v>898</v>
       </c>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
@@ -5558,7 +5562,7 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C86" s="2">
         <v>45868</v>
@@ -5567,25 +5571,25 @@
         <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F86" t="s">
         <v>67</v>
       </c>
       <c r="G86" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H86" s="2">
         <v>46146</v>
       </c>
       <c r="I86" s="3">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J86" t="s">
         <v>53</v>
       </c>
       <c r="K86" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L86" s="2">
         <v>46077</v>
@@ -5597,7 +5601,7 @@
         <v>47905</v>
       </c>
       <c r="T86" s="3">
-        <v>1720</v>
+        <v>1706</v>
       </c>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
@@ -5609,7 +5613,7 @@
         <v>43</v>
       </c>
       <c r="B87" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C87" s="2">
         <v>44370</v>
@@ -5618,7 +5622,7 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F87" t="s">
         <v>43</v>
@@ -5630,13 +5634,13 @@
         <v>45881</v>
       </c>
       <c r="I87" s="3">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="J87" t="s">
         <v>53</v>
       </c>
       <c r="K87" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L87" s="2">
         <v>44589</v>
@@ -5645,7 +5649,7 @@
         <v>219</v>
       </c>
       <c r="O87" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P87" s="2">
         <v>46419</v>
@@ -5655,7 +5659,7 @@
       </c>
       <c r="T87" s="3"/>
       <c r="U87" s="3">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="V87" s="4">
         <v>374899.96</v>
@@ -5666,7 +5670,7 @@
         <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C88" s="2">
         <v>45422</v>
@@ -5675,25 +5679,25 @@
         <v>45</v>
       </c>
       <c r="E88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F88" t="s">
         <v>43</v>
       </c>
       <c r="G88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H88" s="2">
         <v>45624</v>
       </c>
       <c r="I88" s="3">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="J88" t="s">
         <v>39</v>
       </c>
       <c r="K88" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L88" s="2">
         <v>45544</v>
@@ -5715,7 +5719,7 @@
         <v>26</v>
       </c>
       <c r="B89" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C89" s="2">
         <v>46038</v>
@@ -5724,7 +5728,7 @@
         <v>45</v>
       </c>
       <c r="E89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F89" t="s">
         <v>170</v>
@@ -5733,10 +5737,10 @@
         <v>271</v>
       </c>
       <c r="H89" s="2">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="I89" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J89" t="s">
         <v>28</v>
@@ -5753,34 +5757,34 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C90" s="2">
         <v>44939</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E90" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F90" t="s">
         <v>29</v>
       </c>
       <c r="G90" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H90" s="2">
         <v>45979</v>
       </c>
       <c r="I90" s="3">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="J90" t="s">
         <v>53</v>
       </c>
       <c r="K90" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L90" s="2">
         <v>45968</v>
@@ -5789,7 +5793,7 @@
         <v>1029</v>
       </c>
       <c r="O90" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P90" s="2">
         <v>46426</v>
@@ -5799,7 +5803,7 @@
       </c>
       <c r="T90" s="3"/>
       <c r="U90" s="3">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="V90" s="4">
         <v>706431.6</v>
@@ -5810,7 +5814,7 @@
         <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C91" s="2">
         <v>45673</v>
@@ -5819,7 +5823,7 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F91" t="s">
         <v>43</v>
@@ -5831,20 +5835,20 @@
         <v>46140</v>
       </c>
       <c r="I91" s="3">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J91" t="s">
         <v>53</v>
       </c>
       <c r="K91" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M91" s="3"/>
       <c r="S91" s="2">
         <v>46598</v>
       </c>
       <c r="T91" s="3">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="U91" s="3"/>
       <c r="V91" s="4">
@@ -5856,7 +5860,7 @@
         <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C92" s="2">
         <v>45215</v>
@@ -5865,25 +5869,25 @@
         <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F92" t="s">
         <v>170</v>
       </c>
       <c r="G92" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H92" s="2">
         <v>45687</v>
       </c>
       <c r="I92" s="3">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="J92" t="s">
         <v>39</v>
       </c>
       <c r="K92" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L92" s="2">
         <v>45685</v>
@@ -5895,7 +5899,7 @@
         <v>46780</v>
       </c>
       <c r="T92" s="3">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="U92" s="3"/>
       <c r="V92" s="4">
@@ -5907,7 +5911,7 @@
         <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C93" s="2">
         <v>45366</v>
@@ -5916,25 +5920,25 @@
         <v>45</v>
       </c>
       <c r="E93" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F93" t="s">
         <v>43</v>
       </c>
       <c r="G93" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H93" s="2">
         <v>45481</v>
       </c>
       <c r="I93" s="3">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="J93" t="s">
         <v>53</v>
       </c>
       <c r="K93" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L93" s="2">
         <v>45471</v>
@@ -5946,7 +5950,7 @@
         <v>47301</v>
       </c>
       <c r="T93" s="3">
-        <v>1116</v>
+        <v>1102</v>
       </c>
       <c r="U93" s="3"/>
       <c r="V93" s="4">
@@ -5958,7 +5962,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C94" s="2">
         <v>45152</v>
@@ -5967,25 +5971,25 @@
         <v>264</v>
       </c>
       <c r="E94" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F94" t="s">
         <v>29</v>
       </c>
       <c r="G94" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H94" s="2">
         <v>45440</v>
       </c>
       <c r="I94" s="3">
-        <v>745</v>
+        <v>759</v>
       </c>
       <c r="J94" t="s">
         <v>53</v>
       </c>
       <c r="K94" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L94" s="2">
         <v>45303</v>
@@ -6007,7 +6011,7 @@
         <v>43</v>
       </c>
       <c r="B95" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C95" s="2">
         <v>45373</v>
@@ -6016,25 +6020,25 @@
         <v>45</v>
       </c>
       <c r="E95" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F95" t="s">
         <v>43</v>
       </c>
       <c r="G95" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H95" s="2">
         <v>45492</v>
       </c>
       <c r="I95" s="3">
-        <v>693</v>
+        <v>707</v>
       </c>
       <c r="J95" t="s">
         <v>53</v>
       </c>
       <c r="K95" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L95" s="2">
         <v>45492</v>
@@ -6046,7 +6050,7 @@
         <v>46587</v>
       </c>
       <c r="T95" s="3">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
@@ -6058,7 +6062,7 @@
         <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C96" s="2">
         <v>44663</v>
@@ -6067,7 +6071,7 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F96" t="s">
         <v>129</v>
@@ -6079,13 +6083,13 @@
         <v>45588</v>
       </c>
       <c r="I96" s="3">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="J96" t="s">
         <v>53</v>
       </c>
       <c r="K96" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L96" s="2">
         <v>44893</v>
@@ -6113,7 +6117,7 @@
         <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C97" s="2">
         <v>45826</v>
@@ -6122,25 +6126,25 @@
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F97" t="s">
         <v>67</v>
       </c>
       <c r="G97" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H97" s="2">
         <v>46079</v>
       </c>
       <c r="I97" s="3">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="J97" t="s">
         <v>53</v>
       </c>
       <c r="K97" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L97" s="2">
         <v>46076</v>
@@ -6152,7 +6156,7 @@
         <v>47903</v>
       </c>
       <c r="T97" s="3">
-        <v>1718</v>
+        <v>1704</v>
       </c>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
@@ -6161,10 +6165,10 @@
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B98" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C98" s="2">
         <v>46150</v>
@@ -6173,19 +6177,19 @@
         <v>45</v>
       </c>
       <c r="E98" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F98" t="s">
-        <v>385</v>
+        <v>67</v>
       </c>
       <c r="G98" t="s">
-        <v>266</v>
+        <v>386</v>
       </c>
       <c r="H98" s="2">
-        <v>46168</v>
+        <v>46199</v>
       </c>
       <c r="I98" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J98" t="s">
         <v>28</v>
@@ -6202,7 +6206,7 @@
         <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C99" s="2">
         <v>46094</v>
@@ -6211,19 +6215,19 @@
         <v>45</v>
       </c>
       <c r="E99" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F99" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G99" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H99" s="2">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="I99" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J99" t="s">
         <v>28</v>
@@ -6240,7 +6244,7 @@
         <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C100" s="2">
         <v>45950</v>
@@ -6249,25 +6253,25 @@
         <v>45</v>
       </c>
       <c r="E100" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F100" t="s">
         <v>43</v>
       </c>
       <c r="G100" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H100" s="2">
         <v>45988</v>
       </c>
       <c r="I100" s="3">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="J100" t="s">
         <v>39</v>
       </c>
       <c r="K100" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L100" s="2">
         <v>45979</v>
@@ -6279,7 +6283,7 @@
         <v>46343</v>
       </c>
       <c r="T100" s="3">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="U100" s="3"/>
       <c r="V100" s="4">
@@ -6291,7 +6295,7 @@
         <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C101" s="2">
         <v>45511</v>
@@ -6300,25 +6304,25 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F101" t="s">
         <v>26</v>
       </c>
       <c r="G101" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H101" s="2">
         <v>45786</v>
       </c>
       <c r="I101" s="3">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="J101" t="s">
         <v>39</v>
       </c>
       <c r="K101" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L101" s="2">
         <v>45794</v>
@@ -6337,7 +6341,7 @@
         <v>26</v>
       </c>
       <c r="B102" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C102" s="2">
         <v>45848</v>
@@ -6346,25 +6350,25 @@
         <v>36</v>
       </c>
       <c r="E102" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F102" t="s">
         <v>225</v>
       </c>
       <c r="G102" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H102" s="2">
         <v>46014</v>
       </c>
       <c r="I102" s="3">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="J102" t="s">
         <v>39</v>
       </c>
       <c r="K102" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L102" s="2">
         <v>46008</v>
@@ -6376,7 +6380,7 @@
         <v>46373</v>
       </c>
       <c r="T102" s="3">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
@@ -6388,7 +6392,7 @@
         <v>26</v>
       </c>
       <c r="B103" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C103" s="2">
         <v>46030</v>
@@ -6397,19 +6401,19 @@
         <v>264</v>
       </c>
       <c r="E103" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F103" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G103" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H103" s="2">
-        <v>46157</v>
+        <v>46198</v>
       </c>
       <c r="I103" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J103" t="s">
         <v>28</v>
@@ -6426,7 +6430,7 @@
         <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C104" s="2">
         <v>45365</v>
@@ -6435,25 +6439,25 @@
         <v>36</v>
       </c>
       <c r="E104" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F104" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G104" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H104" s="2">
         <v>45568</v>
       </c>
       <c r="I104" s="3">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="J104" t="s">
         <v>53</v>
       </c>
       <c r="K104" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L104" s="2">
         <v>45567</v>
@@ -6465,7 +6469,7 @@
         <v>46479</v>
       </c>
       <c r="T104" s="3">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
@@ -6474,10 +6478,10 @@
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B105" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C105" s="2">
         <v>45526</v>
@@ -6486,32 +6490,32 @@
         <v>36</v>
       </c>
       <c r="E105" t="s">
+        <v>414</v>
+      </c>
+      <c r="F105" t="s">
         <v>412</v>
       </c>
-      <c r="F105" t="s">
-        <v>410</v>
-      </c>
       <c r="G105" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H105" s="2">
         <v>45932</v>
       </c>
       <c r="I105" s="3">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="J105" t="s">
         <v>53</v>
       </c>
       <c r="K105" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M105" s="3"/>
       <c r="S105" s="2">
         <v>47748</v>
       </c>
       <c r="T105" s="3">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="U105" s="3"/>
       <c r="V105" s="4">
@@ -6523,7 +6527,7 @@
         <v>26</v>
       </c>
       <c r="B106" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C106" s="2">
         <v>45824</v>
@@ -6532,25 +6536,25 @@
         <v>24</v>
       </c>
       <c r="E106" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F106" t="s">
         <v>26</v>
       </c>
       <c r="G106" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H106" s="2">
         <v>45958</v>
       </c>
       <c r="I106" s="3">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="J106" t="s">
         <v>53</v>
       </c>
       <c r="K106" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L106" s="2">
         <v>45951</v>
@@ -6562,7 +6566,7 @@
         <v>46316</v>
       </c>
       <c r="T106" s="3">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
@@ -6574,7 +6578,7 @@
         <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C107" s="2">
         <v>45560</v>
@@ -6583,25 +6587,25 @@
         <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F107" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G107" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H107" s="2">
         <v>45930</v>
       </c>
       <c r="I107" s="3">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="J107" t="s">
         <v>39</v>
       </c>
       <c r="K107" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L107" s="2">
         <v>45854</v>
@@ -6613,7 +6617,7 @@
         <v>46950</v>
       </c>
       <c r="T107" s="3">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
@@ -6625,34 +6629,34 @@
         <v>268</v>
       </c>
       <c r="B108" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C108" s="2">
         <v>44607</v>
       </c>
       <c r="D108" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E108" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F108" t="s">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="G108" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H108" s="2">
-        <v>46183</v>
+        <v>46196</v>
       </c>
       <c r="I108" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J108" t="s">
-        <v>267</v>
+        <v>53</v>
       </c>
       <c r="K108" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L108" s="2">
         <v>44747</v>
@@ -6661,26 +6665,28 @@
         <v>140</v>
       </c>
       <c r="O108" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P108" s="2">
-        <v>46177</v>
+        <v>46573</v>
       </c>
       <c r="S108" s="2">
         <v>45111</v>
       </c>
       <c r="T108" s="3"/>
-      <c r="U108" s="3"/>
+      <c r="U108" s="3">
+        <v>374</v>
+      </c>
       <c r="V108" s="4">
-        <v>6242296.7000000002</v>
+        <v>6571898.25</v>
       </c>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B109" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C109" s="2">
         <v>38661</v>
@@ -6689,25 +6695,25 @@
         <v>36</v>
       </c>
       <c r="E109" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F109" t="s">
         <v>26</v>
       </c>
       <c r="G109" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H109" s="2">
         <v>45993</v>
       </c>
       <c r="I109" s="3">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="J109" t="s">
         <v>39</v>
       </c>
       <c r="K109" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L109" s="2">
         <v>45993</v>
@@ -6719,7 +6725,7 @@
         <v>46540</v>
       </c>
       <c r="T109" s="3">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="U109" s="3"/>
       <c r="V109" s="4">
@@ -6731,7 +6737,7 @@
         <v>225</v>
       </c>
       <c r="B110" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C110" s="2">
         <v>45560</v>
@@ -6740,32 +6746,32 @@
         <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F110" t="s">
         <v>225</v>
       </c>
       <c r="G110" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H110" s="2">
         <v>45797</v>
       </c>
       <c r="I110" s="3">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="J110" t="s">
         <v>53</v>
       </c>
       <c r="K110" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M110" s="3"/>
       <c r="S110" s="2">
         <v>46523</v>
       </c>
       <c r="T110" s="3">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="U110" s="3"/>
       <c r="V110" s="4">
@@ -6777,7 +6783,7 @@
         <v>43</v>
       </c>
       <c r="B111" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C111" s="2">
         <v>44763</v>
@@ -6786,7 +6792,7 @@
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F111" t="s">
         <v>43</v>
@@ -6798,13 +6804,13 @@
         <v>45798</v>
       </c>
       <c r="I111" s="3">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="J111" t="s">
         <v>53</v>
       </c>
       <c r="K111" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L111" s="2">
         <v>45574</v>
@@ -6819,7 +6825,7 @@
         <v>46313</v>
       </c>
       <c r="Q111" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="R111" s="2">
         <v>45786</v>
@@ -6829,7 +6835,7 @@
       </c>
       <c r="T111" s="3"/>
       <c r="U111" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="V111" s="4">
         <v>10934411.34</v>
@@ -6840,7 +6846,7 @@
         <v>26</v>
       </c>
       <c r="B112" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C112" s="2">
         <v>45014</v>
@@ -6849,25 +6855,25 @@
         <v>45</v>
       </c>
       <c r="E112" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F112" t="s">
-        <v>385</v>
+        <v>157</v>
       </c>
       <c r="G112" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H112" s="2">
-        <v>46183</v>
+        <v>46198</v>
       </c>
       <c r="I112" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J112" t="s">
         <v>267</v>
       </c>
       <c r="K112" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L112" s="2">
         <v>45148</v>
@@ -6876,26 +6882,28 @@
         <v>134</v>
       </c>
       <c r="O112" t="s">
-        <v>60</v>
+        <v>346</v>
       </c>
       <c r="P112" s="2">
-        <v>45878</v>
+        <v>46609</v>
       </c>
       <c r="S112" s="2">
         <v>45518</v>
       </c>
       <c r="T112" s="3"/>
-      <c r="U112" s="3"/>
+      <c r="U112" s="3">
+        <v>410</v>
+      </c>
       <c r="V112" s="4">
-        <v>14412000</v>
+        <v>17946403.739999998</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B113" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C113" s="2">
         <v>45666</v>
@@ -6904,19 +6912,19 @@
         <v>45</v>
       </c>
       <c r="E113" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F113" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G113" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H113" s="2">
         <v>46174</v>
       </c>
       <c r="I113" s="3">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J113" t="s">
         <v>28</v>
@@ -6930,10 +6938,10 @@
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B114" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C114" s="2">
         <v>45250</v>
@@ -6942,25 +6950,25 @@
         <v>36</v>
       </c>
       <c r="E114" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F114" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G114" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H114" s="2">
         <v>45400</v>
       </c>
       <c r="I114" s="3">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="J114" t="s">
         <v>53</v>
       </c>
       <c r="K114" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L114" s="2">
         <v>45401</v>
@@ -6972,7 +6980,7 @@
         <v>47227</v>
       </c>
       <c r="T114" s="3">
-        <v>1042</v>
+        <v>1028</v>
       </c>
       <c r="U114" s="3"/>
       <c r="V114" s="4">
@@ -6984,7 +6992,7 @@
         <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C115" s="2">
         <v>44238</v>
@@ -6993,16 +7001,16 @@
         <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F115" t="s">
-        <v>456</v>
+        <v>43</v>
       </c>
       <c r="G115" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="H115" s="2">
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="I115" s="3">
         <v>1</v>
@@ -7011,7 +7019,7 @@
         <v>267</v>
       </c>
       <c r="K115" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L115" s="2">
         <v>44969</v>
@@ -7020,7 +7028,7 @@
         <v>731</v>
       </c>
       <c r="O115" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P115" s="2">
         <v>46798</v>
@@ -7030,7 +7038,7 @@
       </c>
       <c r="T115" s="3"/>
       <c r="U115" s="3">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="V115" s="4">
         <v>41936400</v>
@@ -7041,7 +7049,7 @@
         <v>43</v>
       </c>
       <c r="B116" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C116" s="2">
         <v>45607</v>
@@ -7050,25 +7058,25 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F116" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G116" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H116" s="2">
         <v>45798</v>
       </c>
       <c r="I116" s="3">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="J116" t="s">
         <v>53</v>
       </c>
       <c r="K116" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L116" s="2">
         <v>45798</v>
@@ -7080,7 +7088,7 @@
         <v>46712</v>
       </c>
       <c r="T116" s="3">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
@@ -7092,7 +7100,7 @@
         <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C117" s="2">
         <v>45664</v>
@@ -7101,19 +7109,19 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F117" t="s">
         <v>225</v>
       </c>
       <c r="G117" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H117" s="2">
         <v>45958</v>
       </c>
       <c r="I117" s="3">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="J117" t="s">
         <v>34</v>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22DB8ED-9803-408D-9A3D-052A74BFB4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1072F13-856F-4150-9CFE-86612A94D12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="475">
   <si>
     <t>Departamento</t>
   </si>
@@ -840,6 +840,15 @@
     <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS. Existe possiblidade de uma ARP</t>
   </si>
   <si>
+    <t>202600005022365</t>
+  </si>
+  <si>
+    <t>SISLOG 121388 GALERA APP</t>
+  </si>
+  <si>
+    <t>ELABORAÇÃO DE DOD E ETP</t>
+  </si>
+  <si>
     <t>202600010023321</t>
   </si>
   <si>
@@ -996,7 +1005,11 @@
     <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 9</t>
   </si>
   <si>
-    <t>AGUARDANDO CERTIDÕES.  Prints erro licença adobe (92163676). COMUNICADO A CAMALEON AGUARDANDO RETORNO</t>
+    <t>GETEC SUBPEI</t>
+  </si>
+  <si>
+    <t>AGUARDANDO CERTIDÕES.  Prints erro licença adobe (92163676). COMUNICADO A CAMALEON AGUARDANDO RETORNO.
+Despacho 1911 (92656380) AGUARDANDO CONCLUSÃO</t>
   </si>
   <si>
     <t>09/2026</t>
@@ -1112,6 +1125,9 @@
     <t>ACCESS POINT</t>
   </si>
   <si>
+    <t>Instrumento de Planejamento, Orçamento e Finanças - IPOF 2026285002954 (92853984)</t>
+  </si>
+  <si>
     <t>202300010002563</t>
   </si>
   <si>
@@ -1211,7 +1227,7 @@
     <t>AQUISIÇÃO DE 40 LICENÇAS AUTODESK AEC DA CS CAD CAM LTDA</t>
   </si>
   <si>
-    <t>Contrato 64 (91909845) ASSINADO PELO SECRETÁRIO</t>
+    <t>Para gestão do contrato</t>
   </si>
   <si>
     <t>202600010020471</t>
@@ -1220,12 +1236,10 @@
     <t>LINKS DE DADOS SD-WAN - PARTÍCIPE ARP 002/2026 – SGG PROCESSO ORIGINAL SEI 202618037001743</t>
   </si>
   <si>
-    <t>SUBPEI CCONT</t>
-  </si>
-  <si>
-    <t>a) designação do gestor do contrato por meio de portaria com a consequente publicação (subitem 2.4); SOLICITAR A GETEC INDICAÇÃO.
-b) acompanhamento da execução contratual sob a ótica orçamentária e financeira, em observância ao art. 42 da Lei Complementar nº 101/2000, de modo a assegurar disponibilidade de caixa para eventual pagamento de parcelas no exercício de 2027 (subitens 3.5 a 3.7);
-c) manutenção da regularidade jurídica, fiscal e trabalhista durante toda a execução contratual, bem como renovação das certidões que vencerem no curso do procedimento (subitem 5.4). CERTIDÕES SOLICITADAS E DOCUMENTAÇÃO JURÍDICA.</t>
+    <t>GAB SGI</t>
+  </si>
+  <si>
+    <t>CONTRATO ASSINADO PELO SECRETÁRIO</t>
   </si>
   <si>
     <t>202500010083108</t>
@@ -1273,7 +1287,7 @@
     <t>CCONV</t>
   </si>
   <si>
-    <t>Convênio 16 (92189244) em elaboração</t>
+    <t>Convênio 16 (92189244) E Portaria Numeração Automática 2071 (92517731) EM ELABORAÇÃO</t>
   </si>
   <si>
     <t>202400005009120</t>
@@ -1394,7 +1408,10 @@
     <t>FORNECEDOR OTC DOC ORGANIZACAO TECNOLOGIA E CUSTODIA DE DOCUMENTOS. Contratação de empresa especializada em digitalização de documentos</t>
   </si>
   <si>
-    <t>Nota de Empenho 2026.2850.014.00039. (92365185) INSERIDA NO PROCESSO</t>
+    <t>PGE</t>
+  </si>
+  <si>
+    <t>PGE manifestando-se pela regularidade jurídica da celebração do 4º Termo Aditivo</t>
   </si>
   <si>
     <t>64/2023</t>
@@ -1409,7 +1426,7 @@
     <t>SISLOG 111945 RUE - REGULAÇÃO DE URGÊNCIA E EMERGENCA - prestação de serviços de solução integrada de regulação médica, comunicação e monitoramento. Processo de autorização para ATA (SEI 202500010001886)</t>
   </si>
   <si>
-    <t>PUBLICADO PNCP. A licitação encontra se devidamente finalizada, conforme previsão legal, estando o mesmo apto para instruções de eventuais procedimentos de compras</t>
+    <t>PARA GESTÃO DA SUREG</t>
   </si>
   <si>
     <t>202400005000381</t>
@@ -1430,7 +1447,7 @@
     <t>FORNECEDOR INDRA. Prestação de Serviço de Desenvolvimento de software</t>
   </si>
   <si>
-    <t xml:space="preserve"> AGUARDAR ORIENTAÇÕES DO FILIPE</t>
+    <t xml:space="preserve"> Termo Aditivo assinado pelo Secretário.</t>
   </si>
   <si>
     <t>15/2023</t>
@@ -1825,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V117"/>
+  <dimension ref="A1:V118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1922,7 +1939,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -1958,7 +1975,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="J3" t="s">
         <v>34</v>
@@ -1994,7 +2011,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>792</v>
+        <v>805</v>
       </c>
       <c r="J4" t="s">
         <v>39</v>
@@ -2030,7 +2047,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
@@ -2066,7 +2083,7 @@
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1058</v>
+        <v>1071</v>
       </c>
       <c r="J6" t="s">
         <v>39</v>
@@ -2114,7 +2131,7 @@
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="J7" t="s">
         <v>53</v>
@@ -2167,7 +2184,7 @@
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>1001</v>
+        <v>1014</v>
       </c>
       <c r="J8" t="s">
         <v>53</v>
@@ -2220,7 +2237,7 @@
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -2268,7 +2285,7 @@
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>827</v>
+        <v>840</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
@@ -2316,7 +2333,7 @@
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>746</v>
+        <v>759</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -2364,7 +2381,7 @@
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="J12" t="s">
         <v>53</v>
@@ -2411,7 +2428,7 @@
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="J13" t="s">
         <v>53</v>
@@ -2458,7 +2475,7 @@
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="J14" t="s">
         <v>53</v>
@@ -2505,7 +2522,7 @@
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="J15" t="s">
         <v>39</v>
@@ -2552,7 +2569,7 @@
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1054</v>
+        <v>1067</v>
       </c>
       <c r="J16" t="s">
         <v>53</v>
@@ -2599,7 +2616,7 @@
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
@@ -2646,7 +2663,7 @@
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="J18" t="s">
         <v>53</v>
@@ -2693,7 +2710,7 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="J19" t="s">
         <v>53</v>
@@ -2740,7 +2757,7 @@
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -2776,7 +2793,7 @@
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
@@ -2823,7 +2840,7 @@
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1291</v>
+        <v>1304</v>
       </c>
       <c r="J22" t="s">
         <v>53</v>
@@ -2870,7 +2887,7 @@
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="J23" t="s">
         <v>39</v>
@@ -2915,7 +2932,7 @@
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -2951,7 +2968,7 @@
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>973</v>
+        <v>986</v>
       </c>
       <c r="J25" t="s">
         <v>53</v>
@@ -2998,7 +3015,7 @@
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>975</v>
+        <v>988</v>
       </c>
       <c r="J26" t="s">
         <v>53</v>
@@ -3045,7 +3062,7 @@
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="J27" t="s">
         <v>39</v>
@@ -3087,7 +3104,7 @@
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1065</v>
+        <v>1078</v>
       </c>
       <c r="J28" t="s">
         <v>53</v>
@@ -3134,7 +3151,7 @@
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -3170,7 +3187,7 @@
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>804</v>
+        <v>817</v>
       </c>
       <c r="J30" t="s">
         <v>34</v>
@@ -3206,7 +3223,7 @@
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -3242,7 +3259,7 @@
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="J32" t="s">
         <v>39</v>
@@ -3289,7 +3306,7 @@
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -3336,7 +3353,7 @@
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>947</v>
+        <v>960</v>
       </c>
       <c r="J34" t="s">
         <v>39</v>
@@ -3372,7 +3389,7 @@
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="J35" t="s">
         <v>34</v>
@@ -3408,7 +3425,7 @@
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -3444,7 +3461,7 @@
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>963</v>
+        <v>976</v>
       </c>
       <c r="J37" t="s">
         <v>39</v>
@@ -3491,7 +3508,7 @@
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="J38" t="s">
         <v>34</v>
@@ -3527,7 +3544,7 @@
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="J39" t="s">
         <v>39</v>
@@ -3577,7 +3594,7 @@
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -3613,7 +3630,7 @@
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>935</v>
+        <v>948</v>
       </c>
       <c r="J41" t="s">
         <v>39</v>
@@ -3660,7 +3677,7 @@
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="J42" t="s">
         <v>34</v>
@@ -3696,7 +3713,7 @@
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -3732,7 +3749,7 @@
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="J44" t="s">
         <v>39</v>
@@ -3776,7 +3793,7 @@
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="J45" t="s">
         <v>39</v>
@@ -3818,7 +3835,7 @@
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="J46" t="s">
         <v>39</v>
@@ -3860,7 +3877,7 @@
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="J47" t="s">
         <v>39</v>
@@ -3878,7 +3895,7 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1179</v>
+        <v>1166</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -3909,7 +3926,7 @@
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="J48" t="s">
         <v>39</v>
@@ -3959,7 +3976,7 @@
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="J49" t="s">
         <v>39</v>
@@ -3977,7 +3994,7 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1144</v>
+        <v>1131</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
@@ -4008,7 +4025,7 @@
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -4052,7 +4069,7 @@
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>632</v>
+        <v>645</v>
       </c>
       <c r="J51" t="s">
         <v>34</v>
@@ -4088,7 +4105,7 @@
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -4124,7 +4141,7 @@
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -4160,7 +4177,7 @@
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="J54" t="s">
         <v>53</v>
@@ -4207,7 +4224,7 @@
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="J55" t="s">
         <v>39</v>
@@ -4243,7 +4260,7 @@
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>980</v>
+        <v>993</v>
       </c>
       <c r="J56" t="s">
         <v>34</v>
@@ -4279,7 +4296,7 @@
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="J57" t="s">
         <v>39</v>
@@ -4315,7 +4332,7 @@
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>900</v>
+        <v>913</v>
       </c>
       <c r="J58" t="s">
         <v>34</v>
@@ -4351,7 +4368,7 @@
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="J59" t="s">
         <v>39</v>
@@ -4387,7 +4404,7 @@
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="J60" t="s">
         <v>53</v>
@@ -4405,7 +4422,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1102</v>
+        <v>1089</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4436,7 +4453,7 @@
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="J61" t="s">
         <v>34</v>
@@ -4472,7 +4489,7 @@
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -4508,7 +4525,7 @@
         <v>46197</v>
       </c>
       <c r="I63" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J63" t="s">
         <v>28</v>
@@ -4526,28 +4543,25 @@
         <v>263</v>
       </c>
       <c r="C64" s="2">
-        <v>46126</v>
-      </c>
-      <c r="D64" t="s">
+        <v>46210</v>
+      </c>
+      <c r="E64" t="s">
         <v>264</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" t="s">
         <v>265</v>
       </c>
-      <c r="F64" t="s">
-        <v>129</v>
-      </c>
-      <c r="G64" t="s">
-        <v>266</v>
-      </c>
       <c r="H64" s="2">
-        <v>46182</v>
+        <v>46210</v>
       </c>
       <c r="I64" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J64" t="s">
-        <v>267</v>
+        <v>28</v>
       </c>
       <c r="M64" s="3"/>
       <c r="T64" s="3"/>
@@ -4556,51 +4570,49 @@
     </row>
     <row r="65" spans="1:22">
       <c r="A65" t="s">
+        <v>26</v>
+      </c>
+      <c r="B65" t="s">
+        <v>266</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D65" t="s">
+        <v>267</v>
+      </c>
+      <c r="E65" t="s">
         <v>268</v>
       </c>
-      <c r="B65" t="s">
+      <c r="F65" t="s">
+        <v>129</v>
+      </c>
+      <c r="G65" t="s">
         <v>269</v>
       </c>
-      <c r="C65" s="2">
-        <v>46136</v>
-      </c>
-      <c r="D65" t="s">
-        <v>36</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="H65" s="2">
+        <v>46182</v>
+      </c>
+      <c r="I65" s="3">
+        <v>30</v>
+      </c>
+      <c r="J65" t="s">
         <v>270</v>
-      </c>
-      <c r="F65" t="s">
-        <v>170</v>
-      </c>
-      <c r="G65" t="s">
-        <v>271</v>
-      </c>
-      <c r="H65" s="2">
-        <v>46156</v>
-      </c>
-      <c r="I65" s="3">
-        <v>43</v>
-      </c>
-      <c r="J65" t="s">
-        <v>39</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
       <c r="U65" s="3"/>
-      <c r="V65" s="4">
-        <v>400</v>
-      </c>
+      <c r="V65" s="4"/>
     </row>
     <row r="66" spans="1:22">
       <c r="A66" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B66" t="s">
         <v>272</v>
       </c>
       <c r="C66" s="2">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="D66" t="s">
         <v>36</v>
@@ -4609,16 +4621,16 @@
         <v>273</v>
       </c>
       <c r="F66" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="G66" t="s">
         <v>274</v>
       </c>
       <c r="H66" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I66" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="J66" t="s">
         <v>39</v>
@@ -4627,18 +4639,18 @@
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="4">
-        <v>504</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B67" t="s">
         <v>275</v>
       </c>
       <c r="C67" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="D67" t="s">
         <v>36</v>
@@ -4650,13 +4662,13 @@
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H67" s="2">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="I67" s="3">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J67" t="s">
         <v>39</v>
@@ -4665,45 +4677,45 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="4">
-        <v>856</v>
+        <v>504</v>
       </c>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>271</v>
       </c>
       <c r="B68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C68" s="2">
-        <v>45804</v>
+        <v>46136</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H68" s="2">
-        <v>45943</v>
+        <v>46157</v>
       </c>
       <c r="I68" s="3">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="J68" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="4">
-        <v>9808.2000000000007</v>
+        <v>856</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -4714,7 +4726,7 @@
         <v>280</v>
       </c>
       <c r="C69" s="2">
-        <v>45513</v>
+        <v>45804</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
@@ -4723,36 +4735,25 @@
         <v>281</v>
       </c>
       <c r="F69" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="G69" t="s">
         <v>282</v>
       </c>
       <c r="H69" s="2">
-        <v>45715</v>
+        <v>45943</v>
       </c>
       <c r="I69" s="3">
-        <v>484</v>
+        <v>269</v>
       </c>
       <c r="J69" t="s">
-        <v>53</v>
-      </c>
-      <c r="K69" t="s">
-        <v>283</v>
-      </c>
-      <c r="L69" s="2">
-        <v>45712</v>
-      </c>
-      <c r="M69" s="3">
-        <v>199</v>
-      </c>
-      <c r="S69" s="2">
-        <v>46077</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M69" s="3"/>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
       <c r="V69" s="4">
-        <v>18900</v>
+        <v>9808.2000000000007</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -4760,50 +4761,48 @@
         <v>43</v>
       </c>
       <c r="B70" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2">
-        <v>45659</v>
+        <v>45513</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
       </c>
       <c r="E70" t="s">
+        <v>284</v>
+      </c>
+      <c r="F70" t="s">
+        <v>129</v>
+      </c>
+      <c r="G70" t="s">
         <v>285</v>
       </c>
-      <c r="F70" t="s">
-        <v>67</v>
-      </c>
-      <c r="G70" t="s">
-        <v>286</v>
-      </c>
       <c r="H70" s="2">
-        <v>45817</v>
+        <v>45715</v>
       </c>
       <c r="I70" s="3">
-        <v>382</v>
+        <v>497</v>
       </c>
       <c r="J70" t="s">
         <v>53</v>
       </c>
       <c r="K70" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L70" s="2">
-        <v>45812</v>
+        <v>45712</v>
       </c>
       <c r="M70" s="3">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="S70" s="2">
-        <v>46909</v>
-      </c>
-      <c r="T70" s="3">
-        <v>710</v>
-      </c>
+        <v>46077</v>
+      </c>
+      <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="4">
-        <v>23850</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -4811,28 +4810,28 @@
         <v>43</v>
       </c>
       <c r="B71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C71" s="2">
+        <v>45659</v>
+      </c>
+      <c r="D71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" t="s">
         <v>288</v>
       </c>
-      <c r="C71" s="2">
-        <v>45492</v>
-      </c>
-      <c r="D71" t="s">
-        <v>45</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>67</v>
+      </c>
+      <c r="G71" t="s">
         <v>289</v>
       </c>
-      <c r="F71" t="s">
-        <v>43</v>
-      </c>
-      <c r="G71" t="s">
-        <v>52</v>
-      </c>
       <c r="H71" s="2">
-        <v>45911</v>
+        <v>45817</v>
       </c>
       <c r="I71" s="3">
-        <v>288</v>
+        <v>395</v>
       </c>
       <c r="J71" t="s">
         <v>53</v>
@@ -4841,32 +4840,31 @@
         <v>290</v>
       </c>
       <c r="L71" s="2">
-        <v>45546</v>
+        <v>45812</v>
       </c>
       <c r="M71" s="3">
-        <v>54</v>
-      </c>
-      <c r="O71" t="s">
-        <v>60</v>
-      </c>
-      <c r="P71" s="2">
-        <v>45966</v>
-      </c>
-      <c r="T71" s="3"/>
+        <v>153</v>
+      </c>
+      <c r="S71" s="2">
+        <v>46909</v>
+      </c>
+      <c r="T71" s="3">
+        <v>697</v>
+      </c>
       <c r="U71" s="3"/>
       <c r="V71" s="4">
-        <v>25173.75</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="72" spans="1:22">
       <c r="A72" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s">
         <v>291</v>
       </c>
       <c r="C72" s="2">
-        <v>45786</v>
+        <v>45492</v>
       </c>
       <c r="D72" t="s">
         <v>45</v>
@@ -4875,177 +4873,172 @@
         <v>292</v>
       </c>
       <c r="F72" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="G72" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="2">
+        <v>45911</v>
+      </c>
+      <c r="I72" s="3">
+        <v>301</v>
+      </c>
+      <c r="J72" t="s">
+        <v>53</v>
+      </c>
+      <c r="K72" t="s">
         <v>293</v>
       </c>
-      <c r="H72" s="2">
-        <v>45895</v>
-      </c>
-      <c r="I72" s="3">
-        <v>304</v>
-      </c>
-      <c r="J72" t="s">
-        <v>39</v>
-      </c>
-      <c r="M72" s="3"/>
+      <c r="L72" s="2">
+        <v>45546</v>
+      </c>
+      <c r="M72" s="3">
+        <v>54</v>
+      </c>
+      <c r="O72" t="s">
+        <v>60</v>
+      </c>
+      <c r="P72" s="2">
+        <v>45966</v>
+      </c>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="4">
-        <v>31300</v>
+        <v>25173.75</v>
       </c>
     </row>
     <row r="73" spans="1:22">
       <c r="A73" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B73" t="s">
         <v>294</v>
       </c>
       <c r="C73" s="2">
-        <v>45946</v>
+        <v>45786</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E73" t="s">
         <v>295</v>
       </c>
       <c r="F73" t="s">
+        <v>142</v>
+      </c>
+      <c r="G73" t="s">
         <v>296</v>
       </c>
-      <c r="G73" t="s">
-        <v>297</v>
-      </c>
       <c r="H73" s="2">
-        <v>46196</v>
+        <v>45895</v>
       </c>
       <c r="I73" s="3">
-        <v>3</v>
+        <v>317</v>
       </c>
       <c r="J73" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M73" s="3"/>
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
       <c r="V73" s="4">
-        <v>32983.599999999999</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" t="s">
+        <v>297</v>
+      </c>
+      <c r="C74" s="2">
+        <v>45946</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" t="s">
         <v>298</v>
       </c>
-      <c r="B74" t="s">
+      <c r="F74" t="s">
         <v>299</v>
       </c>
-      <c r="C74" s="2">
-        <v>45665</v>
-      </c>
-      <c r="D74" t="s">
-        <v>36</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>300</v>
       </c>
-      <c r="F74" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" t="s">
-        <v>301</v>
-      </c>
       <c r="H74" s="2">
-        <v>46198</v>
+        <v>46196</v>
       </c>
       <c r="I74" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J74" t="s">
-        <v>267</v>
-      </c>
-      <c r="K74" t="s">
-        <v>302</v>
-      </c>
-      <c r="L74" s="2">
-        <v>46071</v>
-      </c>
-      <c r="M74" s="3">
-        <v>406</v>
-      </c>
-      <c r="O74" t="s">
-        <v>303</v>
-      </c>
-      <c r="P74" s="2">
-        <v>46294</v>
-      </c>
-      <c r="S74" s="2">
-        <v>46202</v>
-      </c>
-      <c r="T74" s="3">
-        <v>3</v>
-      </c>
-      <c r="U74" s="3">
-        <v>95</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
       <c r="V74" s="4">
-        <v>51071</v>
+        <v>32983.599999999999</v>
       </c>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" t="s">
-        <v>43</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s">
-        <v>61</v>
+        <v>302</v>
       </c>
       <c r="C75" s="2">
-        <v>43902</v>
+        <v>45665</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E75" t="s">
+        <v>303</v>
+      </c>
+      <c r="F75" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" t="s">
         <v>304</v>
       </c>
-      <c r="F75" t="s">
-        <v>43</v>
-      </c>
-      <c r="G75" t="s">
-        <v>149</v>
-      </c>
       <c r="H75" s="2">
-        <v>45790</v>
+        <v>46198</v>
       </c>
       <c r="I75" s="3">
-        <v>409</v>
+        <v>14</v>
       </c>
       <c r="J75" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K75" t="s">
         <v>305</v>
       </c>
       <c r="L75" s="2">
-        <v>43964</v>
+        <v>46071</v>
       </c>
       <c r="M75" s="3">
-        <v>62</v>
+        <v>406</v>
       </c>
       <c r="O75" t="s">
-        <v>70</v>
+        <v>306</v>
       </c>
       <c r="P75" s="2">
-        <v>46160</v>
+        <v>46294</v>
       </c>
       <c r="S75" s="2">
-        <v>44917</v>
+        <v>46202</v>
       </c>
       <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
+      <c r="U75" s="3">
+        <v>82</v>
+      </c>
       <c r="V75" s="4">
-        <v>61200</v>
+        <v>51071</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -5053,10 +5046,10 @@
         <v>43</v>
       </c>
       <c r="B76" t="s">
-        <v>306</v>
+        <v>61</v>
       </c>
       <c r="C76" s="2">
-        <v>45915</v>
+        <v>43902</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -5065,38 +5058,42 @@
         <v>307</v>
       </c>
       <c r="F76" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="G76" t="s">
+        <v>149</v>
+      </c>
+      <c r="H76" s="2">
+        <v>45790</v>
+      </c>
+      <c r="I76" s="3">
+        <v>422</v>
+      </c>
+      <c r="J76" t="s">
+        <v>53</v>
+      </c>
+      <c r="K76" t="s">
         <v>308</v>
       </c>
-      <c r="H76" s="2">
-        <v>46094</v>
-      </c>
-      <c r="I76" s="3">
-        <v>105</v>
-      </c>
-      <c r="J76" t="s">
-        <v>39</v>
-      </c>
-      <c r="K76" t="s">
-        <v>309</v>
-      </c>
       <c r="L76" s="2">
-        <v>46086</v>
+        <v>43964</v>
       </c>
       <c r="M76" s="3">
-        <v>171</v>
+        <v>62</v>
+      </c>
+      <c r="O76" t="s">
+        <v>70</v>
+      </c>
+      <c r="P76" s="2">
+        <v>46160</v>
       </c>
       <c r="S76" s="2">
-        <v>47181</v>
-      </c>
-      <c r="T76" s="3">
-        <v>982</v>
-      </c>
+        <v>44917</v>
+      </c>
+      <c r="T76" s="3"/>
       <c r="U76" s="3"/>
       <c r="V76" s="4">
-        <v>71265.600000000006</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5104,58 +5101,50 @@
         <v>43</v>
       </c>
       <c r="B77" t="s">
+        <v>309</v>
+      </c>
+      <c r="C77" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" t="s">
         <v>310</v>
       </c>
-      <c r="C77" s="2">
-        <v>45950</v>
-      </c>
-      <c r="D77" t="s">
-        <v>45</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
+        <v>142</v>
+      </c>
+      <c r="G77" t="s">
         <v>311</v>
       </c>
-      <c r="F77" t="s">
-        <v>43</v>
-      </c>
-      <c r="G77" t="s">
-        <v>312</v>
-      </c>
       <c r="H77" s="2">
-        <v>45975</v>
+        <v>46094</v>
       </c>
       <c r="I77" s="3">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="J77" t="s">
         <v>39</v>
       </c>
       <c r="K77" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L77" s="2">
-        <v>45978</v>
+        <v>46086</v>
       </c>
       <c r="M77" s="3">
-        <v>28</v>
-      </c>
-      <c r="O77" t="s">
-        <v>60</v>
-      </c>
-      <c r="P77" s="2">
-        <v>46220</v>
+        <v>171</v>
       </c>
       <c r="S77" s="2">
-        <v>46220</v>
+        <v>47181</v>
       </c>
       <c r="T77" s="3">
-        <v>21</v>
-      </c>
-      <c r="U77" s="3">
-        <v>21</v>
-      </c>
+        <v>969</v>
+      </c>
+      <c r="U77" s="3"/>
       <c r="V77" s="4">
-        <v>71722</v>
+        <v>71265.600000000006</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5163,13 +5152,13 @@
         <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C78" s="2">
-        <v>45915</v>
+        <v>45950</v>
       </c>
       <c r="D78" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E78" t="s">
         <v>314</v>
@@ -5181,32 +5170,40 @@
         <v>315</v>
       </c>
       <c r="H78" s="2">
-        <v>46198</v>
+        <v>45975</v>
       </c>
       <c r="I78" s="3">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="J78" t="s">
-        <v>267</v>
+        <v>39</v>
       </c>
       <c r="K78" t="s">
         <v>316</v>
       </c>
       <c r="L78" s="2">
-        <v>46086</v>
+        <v>45978</v>
       </c>
       <c r="M78" s="3">
-        <v>171</v>
+        <v>28</v>
+      </c>
+      <c r="O78" t="s">
+        <v>60</v>
+      </c>
+      <c r="P78" s="2">
+        <v>46220</v>
       </c>
       <c r="S78" s="2">
-        <v>47181</v>
+        <v>46220</v>
       </c>
       <c r="T78" s="3">
-        <v>982</v>
-      </c>
-      <c r="U78" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="U78" s="3">
+        <v>8</v>
+      </c>
       <c r="V78" s="4">
-        <v>73620</v>
+        <v>71722</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5214,7 +5211,7 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C79" s="2">
         <v>45915</v>
@@ -5226,22 +5223,22 @@
         <v>317</v>
       </c>
       <c r="F79" t="s">
-        <v>142</v>
+        <v>318</v>
       </c>
       <c r="G79" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="H79" s="2">
-        <v>46094</v>
+        <v>46205</v>
       </c>
       <c r="I79" s="3">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="J79" t="s">
-        <v>39</v>
+        <v>270</v>
       </c>
       <c r="K79" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L79" s="2">
         <v>46086</v>
@@ -5253,11 +5250,11 @@
         <v>47181</v>
       </c>
       <c r="T79" s="3">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="U79" s="3"/>
       <c r="V79" s="4">
-        <v>104220</v>
+        <v>73620</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -5265,54 +5262,50 @@
         <v>43</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>309</v>
       </c>
       <c r="C80" s="2">
-        <v>43902</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>62</v>
+        <v>321</v>
       </c>
       <c r="F80" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="G80" t="s">
-        <v>149</v>
+        <v>311</v>
       </c>
       <c r="H80" s="2">
-        <v>45790</v>
+        <v>46094</v>
       </c>
       <c r="I80" s="3">
-        <v>409</v>
+        <v>118</v>
       </c>
       <c r="J80" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K80" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="L80" s="2">
-        <v>43964</v>
+        <v>46086</v>
       </c>
       <c r="M80" s="3">
-        <v>62</v>
-      </c>
-      <c r="O80" t="s">
-        <v>70</v>
-      </c>
-      <c r="P80" s="2">
-        <v>46160</v>
+        <v>171</v>
       </c>
       <c r="S80" s="2">
-        <v>44917</v>
-      </c>
-      <c r="T80" s="3"/>
+        <v>47181</v>
+      </c>
+      <c r="T80" s="3">
+        <v>969</v>
+      </c>
       <c r="U80" s="3"/>
       <c r="V80" s="4">
-        <v>139755.72</v>
+        <v>104220</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -5320,28 +5313,28 @@
         <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>320</v>
+        <v>61</v>
       </c>
       <c r="C81" s="2">
-        <v>45819</v>
+        <v>43902</v>
       </c>
       <c r="D81" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>321</v>
+        <v>62</v>
       </c>
       <c r="F81" t="s">
         <v>43</v>
       </c>
       <c r="G81" t="s">
-        <v>322</v>
+        <v>149</v>
       </c>
       <c r="H81" s="2">
-        <v>46170</v>
+        <v>45790</v>
       </c>
       <c r="I81" s="3">
-        <v>29</v>
+        <v>422</v>
       </c>
       <c r="J81" t="s">
         <v>53</v>
@@ -5350,20 +5343,24 @@
         <v>323</v>
       </c>
       <c r="L81" s="2">
-        <v>45904</v>
+        <v>43964</v>
       </c>
       <c r="M81" s="3">
-        <v>85</v>
+        <v>62</v>
+      </c>
+      <c r="O81" t="s">
+        <v>70</v>
+      </c>
+      <c r="P81" s="2">
+        <v>46160</v>
       </c>
       <c r="S81" s="2">
-        <v>46273</v>
-      </c>
-      <c r="T81" s="3">
-        <v>74</v>
-      </c>
+        <v>44917</v>
+      </c>
+      <c r="T81" s="3"/>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
-        <v>230000</v>
+        <v>139755.72</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -5374,47 +5371,47 @@
         <v>324</v>
       </c>
       <c r="C82" s="2">
-        <v>45952</v>
+        <v>45819</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E82" t="s">
         <v>325</v>
       </c>
       <c r="F82" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82" t="s">
         <v>326</v>
       </c>
-      <c r="G82" t="s">
-        <v>327</v>
-      </c>
       <c r="H82" s="2">
-        <v>46087</v>
+        <v>46170</v>
       </c>
       <c r="I82" s="3">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="J82" t="s">
         <v>53</v>
       </c>
       <c r="K82" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L82" s="2">
-        <v>46086</v>
+        <v>45904</v>
       </c>
       <c r="M82" s="3">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="S82" s="2">
-        <v>47910</v>
+        <v>46273</v>
       </c>
       <c r="T82" s="3">
-        <v>1711</v>
+        <v>61</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
-        <v>250977.6</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -5422,50 +5419,50 @@
         <v>43</v>
       </c>
       <c r="B83" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C83" s="2">
-        <v>45775</v>
+        <v>45952</v>
       </c>
       <c r="D83" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
         <v>329</v>
       </c>
       <c r="F83" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="G83" t="s">
-        <v>52</v>
+        <v>331</v>
       </c>
       <c r="H83" s="2">
-        <v>45861</v>
+        <v>46087</v>
       </c>
       <c r="I83" s="3">
-        <v>338</v>
+        <v>125</v>
       </c>
       <c r="J83" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K83" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="L83" s="2">
-        <v>45856</v>
+        <v>46086</v>
       </c>
       <c r="M83" s="3">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="S83" s="2">
-        <v>46225</v>
+        <v>47910</v>
       </c>
       <c r="T83" s="3">
-        <v>26</v>
+        <v>1698</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
-        <v>288862</v>
+        <v>250977.6</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -5473,37 +5470,50 @@
         <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C84" s="2">
-        <v>45539</v>
+        <v>45775</v>
       </c>
       <c r="D84" t="s">
         <v>45</v>
       </c>
       <c r="E84" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F84" t="s">
-        <v>332</v>
+        <v>43</v>
       </c>
       <c r="G84" t="s">
-        <v>333</v>
+        <v>52</v>
       </c>
       <c r="H84" s="2">
-        <v>45607</v>
+        <v>45861</v>
       </c>
       <c r="I84" s="3">
-        <v>592</v>
+        <v>351</v>
       </c>
       <c r="J84" t="s">
-        <v>53</v>
-      </c>
-      <c r="M84" s="3"/>
-      <c r="T84" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="K84" t="s">
+        <v>316</v>
+      </c>
+      <c r="L84" s="2">
+        <v>45856</v>
+      </c>
+      <c r="M84" s="3">
+        <v>81</v>
+      </c>
+      <c r="S84" s="2">
+        <v>46225</v>
+      </c>
+      <c r="T84" s="3">
+        <v>13</v>
+      </c>
       <c r="U84" s="3"/>
       <c r="V84" s="4">
-        <v>297600</v>
+        <v>288862</v>
       </c>
     </row>
     <row r="85" spans="1:22">
@@ -5514,10 +5524,10 @@
         <v>334</v>
       </c>
       <c r="C85" s="2">
-        <v>45840</v>
+        <v>45539</v>
       </c>
       <c r="D85" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E85" t="s">
         <v>335</v>
@@ -5529,32 +5539,19 @@
         <v>337</v>
       </c>
       <c r="H85" s="2">
-        <v>46002</v>
+        <v>45607</v>
       </c>
       <c r="I85" s="3">
-        <v>197</v>
+        <v>605</v>
       </c>
       <c r="J85" t="s">
-        <v>39</v>
-      </c>
-      <c r="K85" t="s">
-        <v>338</v>
-      </c>
-      <c r="L85" s="2">
-        <v>46001</v>
-      </c>
-      <c r="M85" s="3">
-        <v>161</v>
-      </c>
-      <c r="S85" s="2">
-        <v>47097</v>
-      </c>
-      <c r="T85" s="3">
-        <v>898</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="T85" s="3"/>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
-        <v>299821.5</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -5562,50 +5559,50 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C86" s="2">
-        <v>45868</v>
+        <v>45840</v>
       </c>
       <c r="D86" t="s">
         <v>24</v>
       </c>
       <c r="E86" t="s">
+        <v>339</v>
+      </c>
+      <c r="F86" t="s">
         <v>340</v>
-      </c>
-      <c r="F86" t="s">
-        <v>67</v>
       </c>
       <c r="G86" t="s">
         <v>341</v>
       </c>
       <c r="H86" s="2">
-        <v>46146</v>
+        <v>46002</v>
       </c>
       <c r="I86" s="3">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="J86" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K86" t="s">
         <v>342</v>
       </c>
       <c r="L86" s="2">
-        <v>46077</v>
+        <v>46001</v>
       </c>
       <c r="M86" s="3">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="S86" s="2">
-        <v>47905</v>
+        <v>47097</v>
       </c>
       <c r="T86" s="3">
-        <v>1706</v>
+        <v>885</v>
       </c>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
-        <v>338580</v>
+        <v>299821.5</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -5616,7 +5613,7 @@
         <v>343</v>
       </c>
       <c r="C87" s="2">
-        <v>44370</v>
+        <v>45868</v>
       </c>
       <c r="D87" t="s">
         <v>24</v>
@@ -5625,44 +5622,38 @@
         <v>344</v>
       </c>
       <c r="F87" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="G87" t="s">
-        <v>149</v>
+        <v>345</v>
       </c>
       <c r="H87" s="2">
-        <v>45881</v>
+        <v>46146</v>
       </c>
       <c r="I87" s="3">
-        <v>318</v>
+        <v>66</v>
       </c>
       <c r="J87" t="s">
         <v>53</v>
       </c>
       <c r="K87" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L87" s="2">
-        <v>44589</v>
+        <v>46077</v>
       </c>
       <c r="M87" s="3">
-        <v>219</v>
-      </c>
-      <c r="O87" t="s">
-        <v>346</v>
-      </c>
-      <c r="P87" s="2">
-        <v>46419</v>
+        <v>209</v>
       </c>
       <c r="S87" s="2">
-        <v>44593</v>
-      </c>
-      <c r="T87" s="3"/>
-      <c r="U87" s="3">
-        <v>220</v>
-      </c>
+        <v>47905</v>
+      </c>
+      <c r="T87" s="3">
+        <v>1693</v>
+      </c>
+      <c r="U87" s="3"/>
       <c r="V87" s="4">
-        <v>374899.96</v>
+        <v>338580</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -5673,10 +5664,10 @@
         <v>347</v>
       </c>
       <c r="C88" s="2">
-        <v>45422</v>
+        <v>44370</v>
       </c>
       <c r="D88" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E88" t="s">
         <v>348</v>
@@ -5685,44 +5676,52 @@
         <v>43</v>
       </c>
       <c r="G88" t="s">
+        <v>149</v>
+      </c>
+      <c r="H88" s="2">
+        <v>45881</v>
+      </c>
+      <c r="I88" s="3">
+        <v>331</v>
+      </c>
+      <c r="J88" t="s">
+        <v>53</v>
+      </c>
+      <c r="K88" t="s">
         <v>349</v>
       </c>
-      <c r="H88" s="2">
-        <v>45624</v>
-      </c>
-      <c r="I88" s="3">
-        <v>575</v>
-      </c>
-      <c r="J88" t="s">
-        <v>39</v>
-      </c>
-      <c r="K88" t="s">
+      <c r="L88" s="2">
+        <v>44589</v>
+      </c>
+      <c r="M88" s="3">
+        <v>219</v>
+      </c>
+      <c r="O88" t="s">
         <v>350</v>
       </c>
-      <c r="L88" s="2">
-        <v>45544</v>
-      </c>
-      <c r="M88" s="3">
-        <v>122</v>
+      <c r="P88" s="2">
+        <v>46419</v>
       </c>
       <c r="S88" s="2">
-        <v>45911</v>
+        <v>44593</v>
       </c>
       <c r="T88" s="3"/>
-      <c r="U88" s="3"/>
+      <c r="U88" s="3">
+        <v>207</v>
+      </c>
       <c r="V88" s="4">
-        <v>457600</v>
+        <v>374899.96</v>
       </c>
     </row>
     <row r="89" spans="1:22">
       <c r="A89" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B89" t="s">
         <v>351</v>
       </c>
       <c r="C89" s="2">
-        <v>46038</v>
+        <v>45422</v>
       </c>
       <c r="D89" t="s">
         <v>45</v>
@@ -5731,128 +5730,131 @@
         <v>352</v>
       </c>
       <c r="F89" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="G89" t="s">
-        <v>271</v>
+        <v>353</v>
       </c>
       <c r="H89" s="2">
-        <v>46196</v>
+        <v>45624</v>
       </c>
       <c r="I89" s="3">
-        <v>3</v>
+        <v>588</v>
       </c>
       <c r="J89" t="s">
-        <v>28</v>
-      </c>
-      <c r="M89" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="K89" t="s">
+        <v>354</v>
+      </c>
+      <c r="L89" s="2">
+        <v>45544</v>
+      </c>
+      <c r="M89" s="3">
+        <v>122</v>
+      </c>
+      <c r="S89" s="2">
+        <v>45911</v>
+      </c>
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
       <c r="V89" s="4">
-        <v>687500</v>
+        <v>457600</v>
       </c>
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C90" s="2">
-        <v>44939</v>
+        <v>46038</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>45</v>
       </c>
       <c r="E90" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F90" t="s">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="G90" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H90" s="2">
-        <v>45979</v>
+        <v>46210</v>
       </c>
       <c r="I90" s="3">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="J90" t="s">
-        <v>53</v>
-      </c>
-      <c r="K90" t="s">
-        <v>357</v>
-      </c>
-      <c r="L90" s="2">
-        <v>45968</v>
-      </c>
-      <c r="M90" s="3">
-        <v>1029</v>
-      </c>
-      <c r="O90" t="s">
-        <v>346</v>
-      </c>
-      <c r="P90" s="2">
-        <v>46426</v>
-      </c>
-      <c r="S90" s="2">
-        <v>45334</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3">
-        <v>227</v>
-      </c>
+      <c r="U90" s="3"/>
       <c r="V90" s="4">
-        <v>706431.6</v>
+        <v>687500</v>
       </c>
     </row>
     <row r="91" spans="1:22">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B91" t="s">
         <v>358</v>
       </c>
       <c r="C91" s="2">
-        <v>45673</v>
+        <v>44939</v>
       </c>
       <c r="D91" t="s">
-        <v>24</v>
+        <v>359</v>
       </c>
       <c r="E91" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G91" t="s">
-        <v>52</v>
+        <v>361</v>
       </c>
       <c r="H91" s="2">
-        <v>46140</v>
+        <v>45979</v>
       </c>
       <c r="I91" s="3">
-        <v>59</v>
+        <v>233</v>
       </c>
       <c r="J91" t="s">
         <v>53</v>
       </c>
       <c r="K91" t="s">
-        <v>360</v>
-      </c>
-      <c r="M91" s="3"/>
+        <v>362</v>
+      </c>
+      <c r="L91" s="2">
+        <v>45968</v>
+      </c>
+      <c r="M91" s="3">
+        <v>1029</v>
+      </c>
+      <c r="O91" t="s">
+        <v>350</v>
+      </c>
+      <c r="P91" s="2">
+        <v>46426</v>
+      </c>
       <c r="S91" s="2">
-        <v>46598</v>
-      </c>
-      <c r="T91" s="3">
-        <v>399</v>
-      </c>
-      <c r="U91" s="3"/>
+        <v>45334</v>
+      </c>
+      <c r="T91" s="3"/>
+      <c r="U91" s="3">
+        <v>214</v>
+      </c>
       <c r="V91" s="4">
-        <v>890000</v>
+        <v>706431.6</v>
       </c>
     </row>
     <row r="92" spans="1:22">
@@ -5860,50 +5862,45 @@
         <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C92" s="2">
-        <v>45215</v>
+        <v>45673</v>
       </c>
       <c r="D92" t="s">
         <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F92" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="G92" t="s">
-        <v>363</v>
+        <v>52</v>
       </c>
       <c r="H92" s="2">
-        <v>45687</v>
+        <v>46140</v>
       </c>
       <c r="I92" s="3">
-        <v>512</v>
+        <v>72</v>
       </c>
       <c r="J92" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K92" t="s">
-        <v>364</v>
-      </c>
-      <c r="L92" s="2">
-        <v>45685</v>
-      </c>
-      <c r="M92" s="3">
-        <v>470</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="M92" s="3"/>
       <c r="S92" s="2">
-        <v>46780</v>
+        <v>46598</v>
       </c>
       <c r="T92" s="3">
-        <v>581</v>
+        <v>386</v>
       </c>
       <c r="U92" s="3"/>
       <c r="V92" s="4">
-        <v>1220266.1399999999</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="93" spans="1:22">
@@ -5911,150 +5908,150 @@
         <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C93" s="2">
-        <v>45366</v>
+        <v>45215</v>
       </c>
       <c r="D93" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F93" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G93" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H93" s="2">
-        <v>45481</v>
+        <v>45687</v>
       </c>
       <c r="I93" s="3">
-        <v>718</v>
+        <v>525</v>
       </c>
       <c r="J93" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K93" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L93" s="2">
-        <v>45471</v>
+        <v>45685</v>
       </c>
       <c r="M93" s="3">
-        <v>105</v>
+        <v>470</v>
       </c>
       <c r="S93" s="2">
-        <v>47301</v>
+        <v>46780</v>
       </c>
       <c r="T93" s="3">
-        <v>1102</v>
+        <v>568</v>
       </c>
       <c r="U93" s="3"/>
       <c r="V93" s="4">
-        <v>1245414.49</v>
+        <v>1220266.1399999999</v>
       </c>
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B94" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C94" s="2">
-        <v>45152</v>
+        <v>45366</v>
       </c>
       <c r="D94" t="s">
-        <v>264</v>
+        <v>45</v>
       </c>
       <c r="E94" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F94" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G94" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H94" s="2">
-        <v>45440</v>
+        <v>45481</v>
       </c>
       <c r="I94" s="3">
-        <v>759</v>
+        <v>731</v>
       </c>
       <c r="J94" t="s">
         <v>53</v>
       </c>
       <c r="K94" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L94" s="2">
-        <v>45303</v>
+        <v>45471</v>
       </c>
       <c r="M94" s="3">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="S94" s="2">
-        <v>45992</v>
-      </c>
-      <c r="T94" s="3"/>
+        <v>47301</v>
+      </c>
+      <c r="T94" s="3">
+        <v>1089</v>
+      </c>
       <c r="U94" s="3"/>
       <c r="V94" s="4">
-        <v>1298031.3600000001</v>
+        <v>1245414.49</v>
       </c>
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B95" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C95" s="2">
-        <v>45373</v>
+        <v>45152</v>
       </c>
       <c r="D95" t="s">
-        <v>45</v>
+        <v>267</v>
       </c>
       <c r="E95" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F95" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G95" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="H95" s="2">
-        <v>45492</v>
+        <v>45440</v>
       </c>
       <c r="I95" s="3">
-        <v>707</v>
+        <v>772</v>
       </c>
       <c r="J95" t="s">
         <v>53</v>
       </c>
       <c r="K95" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L95" s="2">
-        <v>45492</v>
+        <v>45303</v>
       </c>
       <c r="M95" s="3">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="S95" s="2">
-        <v>46587</v>
-      </c>
-      <c r="T95" s="3">
-        <v>388</v>
-      </c>
+        <v>45992</v>
+      </c>
+      <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
-        <v>1320176.8799999999</v>
+        <v>1298031.3600000001</v>
       </c>
     </row>
     <row r="96" spans="1:22">
@@ -6062,54 +6059,50 @@
         <v>43</v>
       </c>
       <c r="B96" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C96" s="2">
-        <v>44663</v>
+        <v>45373</v>
       </c>
       <c r="D96" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E96" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F96" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="G96" t="s">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="H96" s="2">
-        <v>45588</v>
+        <v>45492</v>
       </c>
       <c r="I96" s="3">
-        <v>611</v>
+        <v>720</v>
       </c>
       <c r="J96" t="s">
         <v>53</v>
       </c>
       <c r="K96" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L96" s="2">
-        <v>44893</v>
+        <v>45492</v>
       </c>
       <c r="M96" s="3">
-        <v>230</v>
-      </c>
-      <c r="O96" t="s">
-        <v>60</v>
-      </c>
-      <c r="P96" s="2">
-        <v>45996</v>
+        <v>119</v>
       </c>
       <c r="S96" s="2">
-        <v>45624</v>
-      </c>
-      <c r="T96" s="3"/>
+        <v>46587</v>
+      </c>
+      <c r="T96" s="3">
+        <v>375</v>
+      </c>
       <c r="U96" s="3"/>
       <c r="V96" s="4">
-        <v>1416380</v>
+        <v>1320176.8799999999</v>
       </c>
     </row>
     <row r="97" spans="1:22">
@@ -6117,64 +6110,68 @@
         <v>43</v>
       </c>
       <c r="B97" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C97" s="2">
-        <v>45826</v>
+        <v>44663</v>
       </c>
       <c r="D97" t="s">
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F97" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="G97" t="s">
-        <v>381</v>
+        <v>201</v>
       </c>
       <c r="H97" s="2">
-        <v>46079</v>
+        <v>45588</v>
       </c>
       <c r="I97" s="3">
-        <v>120</v>
+        <v>624</v>
       </c>
       <c r="J97" t="s">
         <v>53</v>
       </c>
       <c r="K97" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L97" s="2">
-        <v>46076</v>
+        <v>44893</v>
       </c>
       <c r="M97" s="3">
-        <v>250</v>
+        <v>230</v>
+      </c>
+      <c r="O97" t="s">
+        <v>60</v>
+      </c>
+      <c r="P97" s="2">
+        <v>45996</v>
       </c>
       <c r="S97" s="2">
-        <v>47903</v>
-      </c>
-      <c r="T97" s="3">
-        <v>1704</v>
-      </c>
+        <v>45624</v>
+      </c>
+      <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
-        <v>1435000</v>
+        <v>1416380</v>
       </c>
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
-        <v>383</v>
+        <v>43</v>
       </c>
       <c r="B98" t="s">
         <v>384</v>
       </c>
       <c r="C98" s="2">
-        <v>46150</v>
+        <v>45826</v>
       </c>
       <c r="D98" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E98" t="s">
         <v>385</v>
@@ -6186,57 +6183,70 @@
         <v>386</v>
       </c>
       <c r="H98" s="2">
-        <v>46199</v>
+        <v>46079</v>
       </c>
       <c r="I98" s="3">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="J98" t="s">
-        <v>28</v>
-      </c>
-      <c r="M98" s="3"/>
-      <c r="T98" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="K98" t="s">
+        <v>387</v>
+      </c>
+      <c r="L98" s="2">
+        <v>46076</v>
+      </c>
+      <c r="M98" s="3">
+        <v>250</v>
+      </c>
+      <c r="S98" s="2">
+        <v>47903</v>
+      </c>
+      <c r="T98" s="3">
+        <v>1691</v>
+      </c>
       <c r="U98" s="3"/>
       <c r="V98" s="4">
-        <v>1719174</v>
+        <v>1435000</v>
       </c>
     </row>
     <row r="99" spans="1:22">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>388</v>
       </c>
       <c r="B99" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C99" s="2">
-        <v>46094</v>
+        <v>46150</v>
       </c>
       <c r="D99" t="s">
         <v>45</v>
       </c>
       <c r="E99" t="s">
+        <v>390</v>
+      </c>
+      <c r="F99" t="s">
         <v>388</v>
       </c>
-      <c r="F99" t="s">
-        <v>389</v>
-      </c>
       <c r="G99" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H99" s="2">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="I99" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J99" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="M99" s="3"/>
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
-        <v>1828126.08</v>
+        <v>1719174</v>
       </c>
     </row>
     <row r="100" spans="1:22">
@@ -6244,50 +6254,37 @@
         <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C100" s="2">
-        <v>45950</v>
+        <v>46094</v>
       </c>
       <c r="D100" t="s">
         <v>45</v>
       </c>
       <c r="E100" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F100" t="s">
-        <v>43</v>
+        <v>394</v>
       </c>
       <c r="G100" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H100" s="2">
-        <v>45988</v>
+        <v>46199</v>
       </c>
       <c r="I100" s="3">
-        <v>211</v>
+        <v>13</v>
       </c>
       <c r="J100" t="s">
-        <v>39</v>
-      </c>
-      <c r="K100" t="s">
-        <v>394</v>
-      </c>
-      <c r="L100" s="2">
-        <v>45979</v>
-      </c>
-      <c r="M100" s="3">
-        <v>29</v>
-      </c>
-      <c r="S100" s="2">
-        <v>46343</v>
-      </c>
-      <c r="T100" s="3">
-        <v>144</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M100" s="3"/>
+      <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="4">
-        <v>2075682</v>
+        <v>1828126.08</v>
       </c>
     </row>
     <row r="101" spans="1:22">
@@ -6295,96 +6292,96 @@
         <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C101" s="2">
-        <v>45511</v>
+        <v>45950</v>
       </c>
       <c r="D101" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E101" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F101" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G101" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H101" s="2">
-        <v>45786</v>
+        <v>45988</v>
       </c>
       <c r="I101" s="3">
-        <v>413</v>
+        <v>224</v>
       </c>
       <c r="J101" t="s">
         <v>39</v>
       </c>
       <c r="K101" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L101" s="2">
-        <v>45794</v>
+        <v>45979</v>
       </c>
       <c r="M101" s="3">
-        <v>283</v>
-      </c>
-      <c r="T101" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="S101" s="2">
+        <v>46343</v>
+      </c>
+      <c r="T101" s="3">
+        <v>131</v>
+      </c>
       <c r="U101" s="3"/>
       <c r="V101" s="4">
-        <v>2594055</v>
+        <v>2075682</v>
       </c>
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
+        <v>43</v>
+      </c>
+      <c r="B102" t="s">
+        <v>400</v>
+      </c>
+      <c r="C102" s="2">
+        <v>45511</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102" t="s">
+        <v>401</v>
+      </c>
+      <c r="F102" t="s">
         <v>26</v>
       </c>
-      <c r="B102" t="s">
-        <v>399</v>
-      </c>
-      <c r="C102" s="2">
-        <v>45848</v>
-      </c>
-      <c r="D102" t="s">
-        <v>36</v>
-      </c>
-      <c r="E102" t="s">
-        <v>400</v>
-      </c>
-      <c r="F102" t="s">
-        <v>225</v>
-      </c>
       <c r="G102" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H102" s="2">
-        <v>46014</v>
+        <v>45786</v>
       </c>
       <c r="I102" s="3">
-        <v>185</v>
+        <v>426</v>
       </c>
       <c r="J102" t="s">
         <v>39</v>
       </c>
       <c r="K102" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L102" s="2">
-        <v>46008</v>
+        <v>45794</v>
       </c>
       <c r="M102" s="3">
-        <v>160</v>
-      </c>
-      <c r="S102" s="2">
-        <v>46373</v>
-      </c>
-      <c r="T102" s="3">
-        <v>174</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="T102" s="3"/>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
-        <v>2641069.35</v>
+        <v>2594055</v>
       </c>
     </row>
     <row r="103" spans="1:22">
@@ -6392,117 +6389,117 @@
         <v>26</v>
       </c>
       <c r="B103" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C103" s="2">
-        <v>46030</v>
+        <v>45848</v>
       </c>
       <c r="D103" t="s">
-        <v>264</v>
+        <v>36</v>
       </c>
       <c r="E103" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F103" t="s">
-        <v>405</v>
+        <v>225</v>
       </c>
       <c r="G103" t="s">
         <v>406</v>
       </c>
       <c r="H103" s="2">
-        <v>46198</v>
+        <v>46014</v>
       </c>
       <c r="I103" s="3">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="J103" t="s">
-        <v>28</v>
-      </c>
-      <c r="M103" s="3"/>
-      <c r="T103" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="K103" t="s">
+        <v>407</v>
+      </c>
+      <c r="L103" s="2">
+        <v>46008</v>
+      </c>
+      <c r="M103" s="3">
+        <v>160</v>
+      </c>
+      <c r="S103" s="2">
+        <v>46373</v>
+      </c>
+      <c r="T103" s="3">
+        <v>161</v>
+      </c>
       <c r="U103" s="3"/>
       <c r="V103" s="4">
-        <v>2652975.2799999998</v>
+        <v>2641069.35</v>
       </c>
     </row>
     <row r="104" spans="1:22">
       <c r="A104" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B104" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C104" s="2">
-        <v>45365</v>
+        <v>46030</v>
       </c>
       <c r="D104" t="s">
-        <v>36</v>
+        <v>267</v>
       </c>
       <c r="E104" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F104" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G104" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H104" s="2">
-        <v>45568</v>
+        <v>46198</v>
       </c>
       <c r="I104" s="3">
-        <v>631</v>
+        <v>14</v>
       </c>
       <c r="J104" t="s">
-        <v>53</v>
-      </c>
-      <c r="K104" t="s">
-        <v>411</v>
-      </c>
-      <c r="L104" s="2">
-        <v>45567</v>
-      </c>
-      <c r="M104" s="3">
-        <v>202</v>
-      </c>
-      <c r="S104" s="2">
-        <v>46479</v>
-      </c>
-      <c r="T104" s="3">
-        <v>280</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M104" s="3"/>
+      <c r="T104" s="3"/>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
-        <v>2780400.6</v>
+        <v>2652975.2799999998</v>
       </c>
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
+        <v>43</v>
+      </c>
+      <c r="B105" t="s">
         <v>412</v>
       </c>
-      <c r="B105" t="s">
-        <v>413</v>
-      </c>
       <c r="C105" s="2">
-        <v>45526</v>
+        <v>45365</v>
       </c>
       <c r="D105" t="s">
         <v>36</v>
       </c>
       <c r="E105" t="s">
+        <v>413</v>
+      </c>
+      <c r="F105" t="s">
         <v>414</v>
-      </c>
-      <c r="F105" t="s">
-        <v>412</v>
       </c>
       <c r="G105" t="s">
         <v>415</v>
       </c>
       <c r="H105" s="2">
-        <v>45932</v>
+        <v>45568</v>
       </c>
       <c r="I105" s="3">
-        <v>267</v>
+        <v>644</v>
       </c>
       <c r="J105" t="s">
         <v>53</v>
@@ -6510,67 +6507,67 @@
       <c r="K105" t="s">
         <v>416</v>
       </c>
-      <c r="M105" s="3"/>
+      <c r="L105" s="2">
+        <v>45567</v>
+      </c>
+      <c r="M105" s="3">
+        <v>202</v>
+      </c>
       <c r="S105" s="2">
-        <v>47748</v>
+        <v>46479</v>
       </c>
       <c r="T105" s="3">
-        <v>1549</v>
+        <v>267</v>
       </c>
       <c r="U105" s="3"/>
       <c r="V105" s="4">
-        <v>4440928.34</v>
+        <v>2780400.6</v>
       </c>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>417</v>
       </c>
       <c r="B106" t="s">
+        <v>418</v>
+      </c>
+      <c r="C106" s="2">
+        <v>45526</v>
+      </c>
+      <c r="D106" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106" t="s">
+        <v>419</v>
+      </c>
+      <c r="F106" t="s">
         <v>417</v>
       </c>
-      <c r="C106" s="2">
-        <v>45824</v>
-      </c>
-      <c r="D106" t="s">
-        <v>24</v>
-      </c>
-      <c r="E106" t="s">
-        <v>418</v>
-      </c>
-      <c r="F106" t="s">
-        <v>26</v>
-      </c>
       <c r="G106" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H106" s="2">
-        <v>45958</v>
+        <v>45932</v>
       </c>
       <c r="I106" s="3">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="J106" t="s">
         <v>53</v>
       </c>
       <c r="K106" t="s">
-        <v>420</v>
-      </c>
-      <c r="L106" s="2">
-        <v>45951</v>
-      </c>
-      <c r="M106" s="3">
-        <v>127</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="M106" s="3"/>
       <c r="S106" s="2">
-        <v>46316</v>
+        <v>47748</v>
       </c>
       <c r="T106" s="3">
-        <v>117</v>
+        <v>1536</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
-        <v>5192424.24</v>
+        <v>4440928.34</v>
       </c>
     </row>
     <row r="107" spans="1:22">
@@ -6578,335 +6575,329 @@
         <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C107" s="2">
-        <v>45560</v>
+        <v>45824</v>
       </c>
       <c r="D107" t="s">
         <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F107" t="s">
-        <v>423</v>
+        <v>26</v>
       </c>
       <c r="G107" t="s">
         <v>424</v>
       </c>
       <c r="H107" s="2">
-        <v>45930</v>
+        <v>45958</v>
       </c>
       <c r="I107" s="3">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="J107" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K107" t="s">
         <v>425</v>
       </c>
       <c r="L107" s="2">
-        <v>45854</v>
+        <v>45951</v>
       </c>
       <c r="M107" s="3">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="S107" s="2">
-        <v>46950</v>
+        <v>46316</v>
       </c>
       <c r="T107" s="3">
-        <v>751</v>
+        <v>104</v>
       </c>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
-        <v>6210000</v>
+        <v>5192424.24</v>
       </c>
     </row>
     <row r="108" spans="1:22">
       <c r="A108" t="s">
-        <v>268</v>
+        <v>26</v>
       </c>
       <c r="B108" t="s">
         <v>426</v>
       </c>
       <c r="C108" s="2">
-        <v>44607</v>
+        <v>45560</v>
       </c>
       <c r="D108" t="s">
-        <v>354</v>
+        <v>24</v>
       </c>
       <c r="E108" t="s">
         <v>427</v>
       </c>
       <c r="F108" t="s">
-        <v>268</v>
+        <v>428</v>
       </c>
       <c r="G108" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H108" s="2">
-        <v>46196</v>
+        <v>45930</v>
       </c>
       <c r="I108" s="3">
-        <v>3</v>
+        <v>282</v>
       </c>
       <c r="J108" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K108" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L108" s="2">
-        <v>44747</v>
+        <v>45854</v>
       </c>
       <c r="M108" s="3">
-        <v>140</v>
-      </c>
-      <c r="O108" t="s">
-        <v>430</v>
-      </c>
-      <c r="P108" s="2">
-        <v>46573</v>
+        <v>294</v>
       </c>
       <c r="S108" s="2">
-        <v>45111</v>
-      </c>
-      <c r="T108" s="3"/>
-      <c r="U108" s="3">
-        <v>374</v>
-      </c>
+        <v>46950</v>
+      </c>
+      <c r="T108" s="3">
+        <v>738</v>
+      </c>
+      <c r="U108" s="3"/>
       <c r="V108" s="4">
-        <v>6571898.25</v>
+        <v>6210000</v>
       </c>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
+        <v>271</v>
+      </c>
+      <c r="B109" t="s">
         <v>431</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" s="2">
+        <v>44607</v>
+      </c>
+      <c r="D109" t="s">
+        <v>359</v>
+      </c>
+      <c r="E109" t="s">
         <v>432</v>
       </c>
-      <c r="C109" s="2">
-        <v>38661</v>
-      </c>
-      <c r="D109" t="s">
-        <v>36</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
+        <v>271</v>
+      </c>
+      <c r="G109" t="s">
         <v>433</v>
       </c>
-      <c r="F109" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" t="s">
+      <c r="H109" s="2">
+        <v>46196</v>
+      </c>
+      <c r="I109" s="3">
+        <v>16</v>
+      </c>
+      <c r="J109" t="s">
+        <v>53</v>
+      </c>
+      <c r="K109" t="s">
         <v>434</v>
       </c>
-      <c r="H109" s="2">
-        <v>45993</v>
-      </c>
-      <c r="I109" s="3">
-        <v>206</v>
-      </c>
-      <c r="J109" t="s">
-        <v>39</v>
-      </c>
-      <c r="K109" t="s">
+      <c r="L109" s="2">
+        <v>44747</v>
+      </c>
+      <c r="M109" s="3">
+        <v>140</v>
+      </c>
+      <c r="O109" t="s">
         <v>435</v>
       </c>
-      <c r="L109" s="2">
-        <v>45993</v>
-      </c>
-      <c r="M109" s="3">
-        <v>7332</v>
+      <c r="P109" s="2">
+        <v>46573</v>
       </c>
       <c r="S109" s="2">
-        <v>46540</v>
-      </c>
-      <c r="T109" s="3">
-        <v>341</v>
-      </c>
-      <c r="U109" s="3"/>
+        <v>45111</v>
+      </c>
+      <c r="T109" s="3"/>
+      <c r="U109" s="3">
+        <v>361</v>
+      </c>
       <c r="V109" s="4">
-        <v>9032000</v>
+        <v>6571898.25</v>
       </c>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
-        <v>225</v>
+        <v>436</v>
       </c>
       <c r="B110" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C110" s="2">
-        <v>45560</v>
+        <v>38661</v>
       </c>
       <c r="D110" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E110" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F110" t="s">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="G110" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H110" s="2">
-        <v>45797</v>
+        <v>45993</v>
       </c>
       <c r="I110" s="3">
-        <v>402</v>
+        <v>219</v>
       </c>
       <c r="J110" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K110" t="s">
-        <v>439</v>
-      </c>
-      <c r="M110" s="3"/>
+        <v>440</v>
+      </c>
+      <c r="L110" s="2">
+        <v>45993</v>
+      </c>
+      <c r="M110" s="3">
+        <v>7332</v>
+      </c>
       <c r="S110" s="2">
-        <v>46523</v>
+        <v>46540</v>
       </c>
       <c r="T110" s="3">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="U110" s="3"/>
       <c r="V110" s="4">
-        <v>9152353</v>
+        <v>9032000</v>
       </c>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="B111" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C111" s="2">
-        <v>44763</v>
+        <v>45560</v>
       </c>
       <c r="D111" t="s">
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F111" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="G111" t="s">
-        <v>52</v>
+        <v>443</v>
       </c>
       <c r="H111" s="2">
-        <v>45798</v>
+        <v>45797</v>
       </c>
       <c r="I111" s="3">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="J111" t="s">
         <v>53</v>
       </c>
       <c r="K111" t="s">
-        <v>442</v>
-      </c>
-      <c r="L111" s="2">
-        <v>45574</v>
-      </c>
-      <c r="M111" s="3">
-        <v>811</v>
-      </c>
-      <c r="O111" t="s">
-        <v>60</v>
-      </c>
-      <c r="P111" s="2">
-        <v>46313</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>443</v>
-      </c>
-      <c r="R111" s="2">
-        <v>45786</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="M111" s="3"/>
       <c r="S111" s="2">
-        <v>45218</v>
-      </c>
-      <c r="T111" s="3"/>
-      <c r="U111" s="3">
-        <v>114</v>
-      </c>
+        <v>46523</v>
+      </c>
+      <c r="T111" s="3">
+        <v>311</v>
+      </c>
+      <c r="U111" s="3"/>
       <c r="V111" s="4">
-        <v>10934411.34</v>
+        <v>9152353</v>
       </c>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B112" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C112" s="2">
-        <v>45014</v>
+        <v>44763</v>
       </c>
       <c r="D112" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E112" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F112" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="G112" t="s">
-        <v>446</v>
+        <v>52</v>
       </c>
       <c r="H112" s="2">
-        <v>46198</v>
+        <v>45798</v>
       </c>
       <c r="I112" s="3">
-        <v>1</v>
+        <v>414</v>
       </c>
       <c r="J112" t="s">
-        <v>267</v>
+        <v>53</v>
       </c>
       <c r="K112" t="s">
         <v>447</v>
       </c>
       <c r="L112" s="2">
-        <v>45148</v>
+        <v>45574</v>
       </c>
       <c r="M112" s="3">
-        <v>134</v>
+        <v>811</v>
       </c>
       <c r="O112" t="s">
-        <v>346</v>
+        <v>60</v>
       </c>
       <c r="P112" s="2">
-        <v>46609</v>
+        <v>46313</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>448</v>
+      </c>
+      <c r="R112" s="2">
+        <v>45786</v>
       </c>
       <c r="S112" s="2">
-        <v>45518</v>
+        <v>45218</v>
       </c>
       <c r="T112" s="3"/>
       <c r="U112" s="3">
-        <v>410</v>
+        <v>101</v>
       </c>
       <c r="V112" s="4">
-        <v>17946403.739999998</v>
+        <v>10934411.34</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>448</v>
+        <v>26</v>
       </c>
       <c r="B113" t="s">
         <v>449</v>
       </c>
       <c r="C113" s="2">
-        <v>45666</v>
+        <v>45014</v>
       </c>
       <c r="D113" t="s">
         <v>45</v>
@@ -6915,133 +6906,133 @@
         <v>450</v>
       </c>
       <c r="F113" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="G113" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H113" s="2">
-        <v>46174</v>
+        <v>46211</v>
       </c>
       <c r="I113" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>28</v>
-      </c>
-      <c r="M113" s="3"/>
+        <v>270</v>
+      </c>
+      <c r="K113" t="s">
+        <v>453</v>
+      </c>
+      <c r="L113" s="2">
+        <v>45148</v>
+      </c>
+      <c r="M113" s="3">
+        <v>134</v>
+      </c>
+      <c r="O113" t="s">
+        <v>350</v>
+      </c>
+      <c r="P113" s="2">
+        <v>46609</v>
+      </c>
+      <c r="S113" s="2">
+        <v>45518</v>
+      </c>
       <c r="T113" s="3"/>
-      <c r="U113" s="3"/>
+      <c r="U113" s="3">
+        <v>397</v>
+      </c>
       <c r="V113" s="4">
-        <v>31106553.600000001</v>
+        <v>17946403.739999998</v>
       </c>
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="B114" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C114" s="2">
-        <v>45250</v>
+        <v>45666</v>
       </c>
       <c r="D114" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E114" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F114" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="G114" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="H114" s="2">
-        <v>45400</v>
+        <v>46174</v>
       </c>
       <c r="I114" s="3">
-        <v>799</v>
+        <v>38</v>
       </c>
       <c r="J114" t="s">
         <v>53</v>
       </c>
-      <c r="K114" t="s">
-        <v>455</v>
-      </c>
-      <c r="L114" s="2">
-        <v>45401</v>
-      </c>
-      <c r="M114" s="3">
-        <v>151</v>
-      </c>
-      <c r="S114" s="2">
-        <v>47227</v>
-      </c>
-      <c r="T114" s="3">
-        <v>1028</v>
-      </c>
+      <c r="M114" s="3"/>
+      <c r="T114" s="3"/>
       <c r="U114" s="3"/>
       <c r="V114" s="4">
-        <v>41522909.280000001</v>
+        <v>31106553.600000001</v>
       </c>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>43</v>
+        <v>417</v>
       </c>
       <c r="B115" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C115" s="2">
-        <v>44238</v>
+        <v>45250</v>
       </c>
       <c r="D115" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E115" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F115" t="s">
-        <v>43</v>
+        <v>417</v>
       </c>
       <c r="G115" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H115" s="2">
-        <v>46198</v>
+        <v>45400</v>
       </c>
       <c r="I115" s="3">
-        <v>1</v>
+        <v>812</v>
       </c>
       <c r="J115" t="s">
-        <v>267</v>
+        <v>53</v>
       </c>
       <c r="K115" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L115" s="2">
-        <v>44969</v>
+        <v>45401</v>
       </c>
       <c r="M115" s="3">
-        <v>731</v>
-      </c>
-      <c r="O115" t="s">
-        <v>460</v>
-      </c>
-      <c r="P115" s="2">
-        <v>46798</v>
+        <v>151</v>
       </c>
       <c r="S115" s="2">
-        <v>45886</v>
-      </c>
-      <c r="T115" s="3"/>
-      <c r="U115" s="3">
-        <v>599</v>
-      </c>
+        <v>47227</v>
+      </c>
+      <c r="T115" s="3">
+        <v>1015</v>
+      </c>
+      <c r="U115" s="3"/>
       <c r="V115" s="4">
-        <v>41936400</v>
+        <v>41522909.280000001</v>
       </c>
     </row>
     <row r="116" spans="1:22">
@@ -7049,50 +7040,56 @@
         <v>43</v>
       </c>
       <c r="B116" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C116" s="2">
-        <v>45607</v>
+        <v>44238</v>
       </c>
       <c r="D116" t="s">
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F116" t="s">
-        <v>463</v>
+        <v>67</v>
       </c>
       <c r="G116" t="s">
         <v>464</v>
       </c>
       <c r="H116" s="2">
-        <v>45798</v>
+        <v>46211</v>
       </c>
       <c r="I116" s="3">
-        <v>401</v>
+        <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>53</v>
+        <v>270</v>
       </c>
       <c r="K116" t="s">
         <v>465</v>
       </c>
       <c r="L116" s="2">
-        <v>45798</v>
+        <v>44969</v>
       </c>
       <c r="M116" s="3">
-        <v>191</v>
+        <v>731</v>
+      </c>
+      <c r="O116" t="s">
+        <v>466</v>
+      </c>
+      <c r="P116" s="2">
+        <v>46798</v>
       </c>
       <c r="S116" s="2">
-        <v>46712</v>
-      </c>
-      <c r="T116" s="3">
-        <v>513</v>
-      </c>
-      <c r="U116" s="3"/>
+        <v>45886</v>
+      </c>
+      <c r="T116" s="3"/>
+      <c r="U116" s="3">
+        <v>586</v>
+      </c>
       <c r="V116" s="4">
-        <v>50963796</v>
+        <v>41936400</v>
       </c>
     </row>
     <row r="117" spans="1:22">
@@ -7100,36 +7097,87 @@
         <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C117" s="2">
-        <v>45664</v>
+        <v>45607</v>
       </c>
       <c r="D117" t="s">
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F117" t="s">
-        <v>225</v>
+        <v>469</v>
       </c>
       <c r="G117" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H117" s="2">
-        <v>45958</v>
+        <v>45798</v>
       </c>
       <c r="I117" s="3">
-        <v>241</v>
+        <v>414</v>
       </c>
       <c r="J117" t="s">
-        <v>34</v>
-      </c>
-      <c r="M117" s="3"/>
-      <c r="T117" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="K117" t="s">
+        <v>471</v>
+      </c>
+      <c r="L117" s="2">
+        <v>45798</v>
+      </c>
+      <c r="M117" s="3">
+        <v>191</v>
+      </c>
+      <c r="S117" s="2">
+        <v>46712</v>
+      </c>
+      <c r="T117" s="3">
+        <v>500</v>
+      </c>
       <c r="U117" s="3"/>
       <c r="V117" s="4">
+        <v>50963796</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22">
+      <c r="A118" t="s">
+        <v>43</v>
+      </c>
+      <c r="B118" t="s">
+        <v>472</v>
+      </c>
+      <c r="C118" s="2">
+        <v>45664</v>
+      </c>
+      <c r="D118" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118" t="s">
+        <v>473</v>
+      </c>
+      <c r="F118" t="s">
+        <v>225</v>
+      </c>
+      <c r="G118" t="s">
+        <v>474</v>
+      </c>
+      <c r="H118" s="2">
+        <v>45958</v>
+      </c>
+      <c r="I118" s="3">
+        <v>254</v>
+      </c>
+      <c r="J118" t="s">
+        <v>34</v>
+      </c>
+      <c r="M118" s="3"/>
+      <c r="T118" s="3"/>
+      <c r="U118" s="3"/>
+      <c r="V118" s="4">
         <v>253382919</v>
       </c>
     </row>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1072F13-856F-4150-9CFE-86612A94D12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3431EDF-0E43-4347-AF98-CEB0129A2087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="476">
   <si>
     <t>Departamento</t>
   </si>
@@ -837,7 +837,7 @@
     <t>SISLOG 120357 - Aquisição de Workstations - Atender demandas da SES-GO</t>
   </si>
   <si>
-    <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS. Existe possiblidade de uma ARP</t>
+    <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS.</t>
   </si>
   <si>
     <t>202600005022365</t>
@@ -847,6 +847,12 @@
   </si>
   <si>
     <t>ELABORAÇÃO DE DOD E ETP</t>
+  </si>
+  <si>
+    <t>202600005022653</t>
+  </si>
+  <si>
+    <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
   </si>
   <si>
     <t>202600010023321</t>
@@ -1125,7 +1131,7 @@
     <t>ACCESS POINT</t>
   </si>
   <si>
-    <t>Instrumento de Planejamento, Orçamento e Finanças - IPOF 2026285002954 (92853984)</t>
+    <t>AGUARDANDO CONCLUSÃO Termo de Adesão 92947741</t>
   </si>
   <si>
     <t>202300010002563</t>
@@ -1236,7 +1242,7 @@
     <t>LINKS DE DADOS SD-WAN - PARTÍCIPE ARP 002/2026 – SGG PROCESSO ORIGINAL SEI 202618037001743</t>
   </si>
   <si>
-    <t>GAB SGI</t>
+    <t>SGI</t>
   </si>
   <si>
     <t>CONTRATO ASSINADO PELO SECRETÁRIO</t>
@@ -1284,10 +1290,7 @@
     <t>Novo Termo de Cooperação entre UFG e SES para realização de capacitação continuada em padrão FHIR.</t>
   </si>
   <si>
-    <t>CCONV</t>
-  </si>
-  <si>
-    <t>Convênio 16 (92189244) E Portaria Numeração Automática 2071 (92517731) EM ELABORAÇÃO</t>
+    <t>Despacho 92 (92970915) AGUARDANDO CONCLUSÃO</t>
   </si>
   <si>
     <t>202400005009120</t>
@@ -1408,10 +1411,11 @@
     <t>FORNECEDOR OTC DOC ORGANIZACAO TECNOLOGIA E CUSTODIA DE DOCUMENTOS. Contratação de empresa especializada em digitalização de documentos</t>
   </si>
   <si>
-    <t>PGE</t>
-  </si>
-  <si>
-    <t>PGE manifestando-se pela regularidade jurídica da celebração do 4º Termo Aditivo</t>
+    <t>PROCSET</t>
+  </si>
+  <si>
+    <t>PGE manifestando-se pela regularidade jurídica da celebração do 4º Termo Aditivo 
+Despacho 1372 (92975869) aguardando conclusão</t>
   </si>
   <si>
     <t>64/2023</t>
@@ -1842,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V118"/>
+  <dimension ref="A1:V119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1939,7 +1943,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -1975,7 +1979,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J3" t="s">
         <v>34</v>
@@ -2011,7 +2015,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J4" t="s">
         <v>39</v>
@@ -2047,7 +2051,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
@@ -2083,7 +2087,7 @@
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="J6" t="s">
         <v>39</v>
@@ -2131,7 +2135,7 @@
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="J7" t="s">
         <v>53</v>
@@ -2184,7 +2188,7 @@
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="J8" t="s">
         <v>53</v>
@@ -2237,7 +2241,7 @@
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J9" t="s">
         <v>34</v>
@@ -2285,7 +2289,7 @@
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
@@ -2333,7 +2337,7 @@
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -2381,7 +2385,7 @@
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="J12" t="s">
         <v>53</v>
@@ -2428,7 +2432,7 @@
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="J13" t="s">
         <v>53</v>
@@ -2475,7 +2479,7 @@
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="J14" t="s">
         <v>53</v>
@@ -2522,7 +2526,7 @@
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J15" t="s">
         <v>39</v>
@@ -2569,7 +2573,7 @@
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="J16" t="s">
         <v>53</v>
@@ -2616,7 +2620,7 @@
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
@@ -2663,7 +2667,7 @@
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="J18" t="s">
         <v>53</v>
@@ -2710,7 +2714,7 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="J19" t="s">
         <v>53</v>
@@ -2757,7 +2761,7 @@
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="J20" t="s">
         <v>34</v>
@@ -2793,7 +2797,7 @@
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
@@ -2840,7 +2844,7 @@
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="J22" t="s">
         <v>53</v>
@@ -2887,7 +2891,7 @@
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="J23" t="s">
         <v>39</v>
@@ -2932,7 +2936,7 @@
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="J24" t="s">
         <v>34</v>
@@ -2968,7 +2972,7 @@
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="J25" t="s">
         <v>53</v>
@@ -3015,7 +3019,7 @@
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="J26" t="s">
         <v>53</v>
@@ -3062,7 +3066,7 @@
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J27" t="s">
         <v>39</v>
@@ -3104,7 +3108,7 @@
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="J28" t="s">
         <v>53</v>
@@ -3151,7 +3155,7 @@
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J29" t="s">
         <v>34</v>
@@ -3187,7 +3191,7 @@
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="J30" t="s">
         <v>34</v>
@@ -3223,7 +3227,7 @@
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
@@ -3259,7 +3263,7 @@
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J32" t="s">
         <v>39</v>
@@ -3306,7 +3310,7 @@
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -3353,7 +3357,7 @@
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J34" t="s">
         <v>39</v>
@@ -3389,7 +3393,7 @@
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J35" t="s">
         <v>34</v>
@@ -3425,7 +3429,7 @@
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J36" t="s">
         <v>34</v>
@@ -3461,7 +3465,7 @@
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="J37" t="s">
         <v>39</v>
@@ -3508,7 +3512,7 @@
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="J38" t="s">
         <v>34</v>
@@ -3544,7 +3548,7 @@
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J39" t="s">
         <v>39</v>
@@ -3594,7 +3598,7 @@
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="J40" t="s">
         <v>34</v>
@@ -3630,7 +3634,7 @@
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="J41" t="s">
         <v>39</v>
@@ -3677,7 +3681,7 @@
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J42" t="s">
         <v>34</v>
@@ -3713,7 +3717,7 @@
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J43" t="s">
         <v>34</v>
@@ -3749,7 +3753,7 @@
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="J44" t="s">
         <v>39</v>
@@ -3793,7 +3797,7 @@
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J45" t="s">
         <v>39</v>
@@ -3835,7 +3839,7 @@
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J46" t="s">
         <v>39</v>
@@ -3877,7 +3881,7 @@
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J47" t="s">
         <v>39</v>
@@ -3895,7 +3899,7 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -3926,7 +3930,7 @@
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J48" t="s">
         <v>39</v>
@@ -3976,7 +3980,7 @@
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J49" t="s">
         <v>39</v>
@@ -3994,7 +3998,7 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
@@ -4025,7 +4029,7 @@
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J50" t="s">
         <v>34</v>
@@ -4069,7 +4073,7 @@
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J51" t="s">
         <v>34</v>
@@ -4105,7 +4109,7 @@
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J52" t="s">
         <v>34</v>
@@ -4141,7 +4145,7 @@
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J53" t="s">
         <v>34</v>
@@ -4177,7 +4181,7 @@
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J54" t="s">
         <v>53</v>
@@ -4224,7 +4228,7 @@
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J55" t="s">
         <v>39</v>
@@ -4260,7 +4264,7 @@
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J56" t="s">
         <v>34</v>
@@ -4296,7 +4300,7 @@
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="J57" t="s">
         <v>39</v>
@@ -4332,7 +4336,7 @@
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J58" t="s">
         <v>34</v>
@@ -4368,7 +4372,7 @@
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="J59" t="s">
         <v>39</v>
@@ -4404,7 +4408,7 @@
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J60" t="s">
         <v>53</v>
@@ -4422,7 +4426,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4453,7 +4457,7 @@
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J61" t="s">
         <v>34</v>
@@ -4489,7 +4493,7 @@
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J62" t="s">
         <v>34</v>
@@ -4525,7 +4529,7 @@
         <v>46197</v>
       </c>
       <c r="I63" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J63" t="s">
         <v>28</v>
@@ -4545,6 +4549,9 @@
       <c r="C64" s="2">
         <v>46210</v>
       </c>
+      <c r="D64" t="s">
+        <v>36</v>
+      </c>
       <c r="E64" t="s">
         <v>264</v>
       </c>
@@ -4558,7 +4565,7 @@
         <v>46210</v>
       </c>
       <c r="I64" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J64" t="s">
         <v>28</v>
@@ -4576,28 +4583,28 @@
         <v>266</v>
       </c>
       <c r="C65" s="2">
-        <v>46126</v>
+        <v>46211</v>
       </c>
       <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" t="s">
         <v>267</v>
       </c>
-      <c r="E65" t="s">
-        <v>268</v>
-      </c>
       <c r="F65" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H65" s="2">
-        <v>46182</v>
+        <v>46211</v>
       </c>
       <c r="I65" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J65" t="s">
-        <v>270</v>
+        <v>28</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
@@ -4606,66 +4613,64 @@
     </row>
     <row r="66" spans="1:22">
       <c r="A66" t="s">
+        <v>26</v>
+      </c>
+      <c r="B66" t="s">
+        <v>268</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D66" t="s">
+        <v>269</v>
+      </c>
+      <c r="E66" t="s">
+        <v>270</v>
+      </c>
+      <c r="F66" t="s">
+        <v>129</v>
+      </c>
+      <c r="G66" t="s">
         <v>271</v>
       </c>
-      <c r="B66" t="s">
+      <c r="H66" s="2">
+        <v>46182</v>
+      </c>
+      <c r="I66" s="3">
+        <v>31</v>
+      </c>
+      <c r="J66" t="s">
         <v>272</v>
-      </c>
-      <c r="C66" s="2">
-        <v>46136</v>
-      </c>
-      <c r="D66" t="s">
-        <v>36</v>
-      </c>
-      <c r="E66" t="s">
-        <v>273</v>
-      </c>
-      <c r="F66" t="s">
-        <v>170</v>
-      </c>
-      <c r="G66" t="s">
-        <v>274</v>
-      </c>
-      <c r="H66" s="2">
-        <v>46156</v>
-      </c>
-      <c r="I66" s="3">
-        <v>56</v>
-      </c>
-      <c r="J66" t="s">
-        <v>39</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
-      <c r="V66" s="4">
-        <v>400</v>
-      </c>
+      <c r="V66" s="4"/>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B67" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C67" s="2">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="D67" t="s">
         <v>36</v>
       </c>
       <c r="E67" t="s">
+        <v>275</v>
+      </c>
+      <c r="F67" t="s">
+        <v>170</v>
+      </c>
+      <c r="G67" t="s">
         <v>276</v>
       </c>
-      <c r="F67" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" t="s">
-        <v>277</v>
-      </c>
       <c r="H67" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I67" s="3">
         <v>57</v>
@@ -4677,36 +4682,36 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="4">
-        <v>504</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="D68" t="s">
         <v>36</v>
       </c>
       <c r="E68" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H68" s="2">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="I68" s="3">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J68" t="s">
         <v>39</v>
@@ -4715,21 +4720,21 @@
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="4">
-        <v>856</v>
+        <v>504</v>
       </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>273</v>
       </c>
       <c r="B69" t="s">
         <v>280</v>
       </c>
       <c r="C69" s="2">
-        <v>45804</v>
+        <v>46136</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E69" t="s">
         <v>281</v>
@@ -4738,22 +4743,22 @@
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H69" s="2">
-        <v>45943</v>
+        <v>46157</v>
       </c>
       <c r="I69" s="3">
-        <v>269</v>
+        <v>56</v>
       </c>
       <c r="J69" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M69" s="3"/>
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
       <c r="V69" s="4">
-        <v>9808.2000000000007</v>
+        <v>856</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -4761,48 +4766,37 @@
         <v>43</v>
       </c>
       <c r="B70" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2">
-        <v>45513</v>
+        <v>45804</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
       </c>
       <c r="E70" t="s">
+        <v>283</v>
+      </c>
+      <c r="F70" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" t="s">
         <v>284</v>
       </c>
-      <c r="F70" t="s">
-        <v>129</v>
-      </c>
-      <c r="G70" t="s">
-        <v>285</v>
-      </c>
       <c r="H70" s="2">
-        <v>45715</v>
+        <v>45943</v>
       </c>
       <c r="I70" s="3">
-        <v>497</v>
+        <v>270</v>
       </c>
       <c r="J70" t="s">
-        <v>53</v>
-      </c>
-      <c r="K70" t="s">
-        <v>286</v>
-      </c>
-      <c r="L70" s="2">
-        <v>45712</v>
-      </c>
-      <c r="M70" s="3">
-        <v>199</v>
-      </c>
-      <c r="S70" s="2">
-        <v>46077</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M70" s="3"/>
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="4">
-        <v>18900</v>
+        <v>9808.2000000000007</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -4810,50 +4804,48 @@
         <v>43</v>
       </c>
       <c r="B71" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C71" s="2">
-        <v>45659</v>
+        <v>45513</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F71" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="G71" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H71" s="2">
-        <v>45817</v>
+        <v>45715</v>
       </c>
       <c r="I71" s="3">
-        <v>395</v>
+        <v>498</v>
       </c>
       <c r="J71" t="s">
         <v>53</v>
       </c>
       <c r="K71" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L71" s="2">
-        <v>45812</v>
+        <v>45712</v>
       </c>
       <c r="M71" s="3">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="S71" s="2">
-        <v>46909</v>
-      </c>
-      <c r="T71" s="3">
-        <v>697</v>
-      </c>
+        <v>46077</v>
+      </c>
+      <c r="T71" s="3"/>
       <c r="U71" s="3"/>
       <c r="V71" s="4">
-        <v>23850</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -4861,239 +4853,235 @@
         <v>43</v>
       </c>
       <c r="B72" t="s">
+        <v>289</v>
+      </c>
+      <c r="C72" s="2">
+        <v>45659</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" t="s">
+        <v>290</v>
+      </c>
+      <c r="F72" t="s">
+        <v>67</v>
+      </c>
+      <c r="G72" t="s">
         <v>291</v>
       </c>
-      <c r="C72" s="2">
-        <v>45492</v>
-      </c>
-      <c r="D72" t="s">
-        <v>45</v>
-      </c>
-      <c r="E72" t="s">
-        <v>292</v>
-      </c>
-      <c r="F72" t="s">
-        <v>43</v>
-      </c>
-      <c r="G72" t="s">
-        <v>52</v>
-      </c>
       <c r="H72" s="2">
-        <v>45911</v>
+        <v>45817</v>
       </c>
       <c r="I72" s="3">
-        <v>301</v>
+        <v>396</v>
       </c>
       <c r="J72" t="s">
         <v>53</v>
       </c>
       <c r="K72" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L72" s="2">
-        <v>45546</v>
+        <v>45812</v>
       </c>
       <c r="M72" s="3">
-        <v>54</v>
-      </c>
-      <c r="O72" t="s">
-        <v>60</v>
-      </c>
-      <c r="P72" s="2">
-        <v>45966</v>
-      </c>
-      <c r="T72" s="3"/>
+        <v>153</v>
+      </c>
+      <c r="S72" s="2">
+        <v>46909</v>
+      </c>
+      <c r="T72" s="3">
+        <v>696</v>
+      </c>
       <c r="U72" s="3"/>
       <c r="V72" s="4">
-        <v>25173.75</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="73" spans="1:22">
       <c r="A73" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C73" s="2">
-        <v>45786</v>
+        <v>45492</v>
       </c>
       <c r="D73" t="s">
         <v>45</v>
       </c>
       <c r="E73" t="s">
+        <v>294</v>
+      </c>
+      <c r="F73" t="s">
+        <v>43</v>
+      </c>
+      <c r="G73" t="s">
+        <v>52</v>
+      </c>
+      <c r="H73" s="2">
+        <v>45911</v>
+      </c>
+      <c r="I73" s="3">
+        <v>302</v>
+      </c>
+      <c r="J73" t="s">
+        <v>53</v>
+      </c>
+      <c r="K73" t="s">
         <v>295</v>
       </c>
-      <c r="F73" t="s">
-        <v>142</v>
-      </c>
-      <c r="G73" t="s">
-        <v>296</v>
-      </c>
-      <c r="H73" s="2">
-        <v>45895</v>
-      </c>
-      <c r="I73" s="3">
-        <v>317</v>
-      </c>
-      <c r="J73" t="s">
-        <v>39</v>
-      </c>
-      <c r="M73" s="3"/>
+      <c r="L73" s="2">
+        <v>45546</v>
+      </c>
+      <c r="M73" s="3">
+        <v>54</v>
+      </c>
+      <c r="O73" t="s">
+        <v>60</v>
+      </c>
+      <c r="P73" s="2">
+        <v>45966</v>
+      </c>
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
       <c r="V73" s="4">
-        <v>31300</v>
+        <v>25173.75</v>
       </c>
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B74" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74" s="2">
+        <v>45786</v>
+      </c>
+      <c r="D74" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" t="s">
         <v>297</v>
       </c>
-      <c r="C74" s="2">
-        <v>45946</v>
-      </c>
-      <c r="D74" t="s">
-        <v>24</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
+        <v>142</v>
+      </c>
+      <c r="G74" t="s">
         <v>298</v>
       </c>
-      <c r="F74" t="s">
-        <v>299</v>
-      </c>
-      <c r="G74" t="s">
-        <v>300</v>
-      </c>
       <c r="H74" s="2">
-        <v>46196</v>
+        <v>45895</v>
       </c>
       <c r="I74" s="3">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="J74" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M74" s="3"/>
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="4">
-        <v>32983.599999999999</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B75" t="s">
+        <v>299</v>
+      </c>
+      <c r="C75" s="2">
+        <v>45946</v>
+      </c>
+      <c r="D75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" t="s">
+        <v>300</v>
+      </c>
+      <c r="F75" t="s">
         <v>301</v>
       </c>
-      <c r="B75" t="s">
+      <c r="G75" t="s">
         <v>302</v>
       </c>
-      <c r="C75" s="2">
-        <v>45665</v>
-      </c>
-      <c r="D75" t="s">
-        <v>36</v>
-      </c>
-      <c r="E75" t="s">
-        <v>303</v>
-      </c>
-      <c r="F75" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" t="s">
-        <v>304</v>
-      </c>
       <c r="H75" s="2">
-        <v>46198</v>
+        <v>46196</v>
       </c>
       <c r="I75" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J75" t="s">
-        <v>39</v>
-      </c>
-      <c r="K75" t="s">
-        <v>305</v>
-      </c>
-      <c r="L75" s="2">
-        <v>46071</v>
-      </c>
-      <c r="M75" s="3">
-        <v>406</v>
-      </c>
-      <c r="O75" t="s">
-        <v>306</v>
-      </c>
-      <c r="P75" s="2">
-        <v>46294</v>
-      </c>
-      <c r="S75" s="2">
-        <v>46202</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M75" s="3"/>
       <c r="T75" s="3"/>
-      <c r="U75" s="3">
-        <v>82</v>
-      </c>
+      <c r="U75" s="3"/>
       <c r="V75" s="4">
-        <v>51071</v>
+        <v>32983.599999999999</v>
       </c>
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
-        <v>43</v>
+        <v>303</v>
       </c>
       <c r="B76" t="s">
-        <v>61</v>
+        <v>304</v>
       </c>
       <c r="C76" s="2">
-        <v>43902</v>
+        <v>45665</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E76" t="s">
+        <v>305</v>
+      </c>
+      <c r="F76" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" t="s">
+        <v>306</v>
+      </c>
+      <c r="H76" s="2">
+        <v>46198</v>
+      </c>
+      <c r="I76" s="3">
+        <v>15</v>
+      </c>
+      <c r="J76" t="s">
+        <v>39</v>
+      </c>
+      <c r="K76" t="s">
         <v>307</v>
       </c>
-      <c r="F76" t="s">
-        <v>43</v>
-      </c>
-      <c r="G76" t="s">
-        <v>149</v>
-      </c>
-      <c r="H76" s="2">
-        <v>45790</v>
-      </c>
-      <c r="I76" s="3">
-        <v>422</v>
-      </c>
-      <c r="J76" t="s">
-        <v>53</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="L76" s="2">
+        <v>46071</v>
+      </c>
+      <c r="M76" s="3">
+        <v>406</v>
+      </c>
+      <c r="O76" t="s">
         <v>308</v>
       </c>
-      <c r="L76" s="2">
-        <v>43964</v>
-      </c>
-      <c r="M76" s="3">
-        <v>62</v>
-      </c>
-      <c r="O76" t="s">
-        <v>70</v>
-      </c>
       <c r="P76" s="2">
-        <v>46160</v>
+        <v>46294</v>
       </c>
       <c r="S76" s="2">
-        <v>44917</v>
+        <v>46202</v>
       </c>
       <c r="T76" s="3"/>
-      <c r="U76" s="3"/>
+      <c r="U76" s="3">
+        <v>81</v>
+      </c>
       <c r="V76" s="4">
-        <v>61200</v>
+        <v>51071</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -5101,50 +5089,54 @@
         <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>309</v>
+        <v>61</v>
       </c>
       <c r="C77" s="2">
-        <v>45915</v>
+        <v>43902</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
       </c>
       <c r="E77" t="s">
+        <v>309</v>
+      </c>
+      <c r="F77" t="s">
+        <v>43</v>
+      </c>
+      <c r="G77" t="s">
+        <v>149</v>
+      </c>
+      <c r="H77" s="2">
+        <v>45790</v>
+      </c>
+      <c r="I77" s="3">
+        <v>423</v>
+      </c>
+      <c r="J77" t="s">
+        <v>53</v>
+      </c>
+      <c r="K77" t="s">
         <v>310</v>
       </c>
-      <c r="F77" t="s">
-        <v>142</v>
-      </c>
-      <c r="G77" t="s">
-        <v>311</v>
-      </c>
-      <c r="H77" s="2">
-        <v>46094</v>
-      </c>
-      <c r="I77" s="3">
-        <v>118</v>
-      </c>
-      <c r="J77" t="s">
-        <v>39</v>
-      </c>
-      <c r="K77" t="s">
-        <v>312</v>
-      </c>
       <c r="L77" s="2">
-        <v>46086</v>
+        <v>43964</v>
       </c>
       <c r="M77" s="3">
-        <v>171</v>
+        <v>62</v>
+      </c>
+      <c r="O77" t="s">
+        <v>70</v>
+      </c>
+      <c r="P77" s="2">
+        <v>46160</v>
       </c>
       <c r="S77" s="2">
-        <v>47181</v>
-      </c>
-      <c r="T77" s="3">
-        <v>969</v>
-      </c>
+        <v>44917</v>
+      </c>
+      <c r="T77" s="3"/>
       <c r="U77" s="3"/>
       <c r="V77" s="4">
-        <v>71265.600000000006</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5152,58 +5144,50 @@
         <v>43</v>
       </c>
       <c r="B78" t="s">
+        <v>311</v>
+      </c>
+      <c r="C78" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D78" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" t="s">
+        <v>312</v>
+      </c>
+      <c r="F78" t="s">
+        <v>142</v>
+      </c>
+      <c r="G78" t="s">
         <v>313</v>
       </c>
-      <c r="C78" s="2">
-        <v>45950</v>
-      </c>
-      <c r="D78" t="s">
-        <v>45</v>
-      </c>
-      <c r="E78" t="s">
-        <v>314</v>
-      </c>
-      <c r="F78" t="s">
-        <v>43</v>
-      </c>
-      <c r="G78" t="s">
-        <v>315</v>
-      </c>
       <c r="H78" s="2">
-        <v>45975</v>
+        <v>46094</v>
       </c>
       <c r="I78" s="3">
-        <v>237</v>
+        <v>119</v>
       </c>
       <c r="J78" t="s">
         <v>39</v>
       </c>
       <c r="K78" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L78" s="2">
-        <v>45978</v>
+        <v>46086</v>
       </c>
       <c r="M78" s="3">
-        <v>28</v>
-      </c>
-      <c r="O78" t="s">
-        <v>60</v>
-      </c>
-      <c r="P78" s="2">
-        <v>46220</v>
+        <v>171</v>
       </c>
       <c r="S78" s="2">
-        <v>46220</v>
+        <v>47181</v>
       </c>
       <c r="T78" s="3">
-        <v>8</v>
-      </c>
-      <c r="U78" s="3">
-        <v>8</v>
-      </c>
+        <v>968</v>
+      </c>
+      <c r="U78" s="3"/>
       <c r="V78" s="4">
-        <v>71722</v>
+        <v>71265.600000000006</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5211,50 +5195,58 @@
         <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C79" s="2">
-        <v>45915</v>
+        <v>45950</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E79" t="s">
+        <v>316</v>
+      </c>
+      <c r="F79" t="s">
+        <v>43</v>
+      </c>
+      <c r="G79" t="s">
         <v>317</v>
       </c>
-      <c r="F79" t="s">
+      <c r="H79" s="2">
+        <v>45975</v>
+      </c>
+      <c r="I79" s="3">
+        <v>238</v>
+      </c>
+      <c r="J79" t="s">
+        <v>39</v>
+      </c>
+      <c r="K79" t="s">
         <v>318</v>
       </c>
-      <c r="G79" t="s">
-        <v>319</v>
-      </c>
-      <c r="H79" s="2">
-        <v>46205</v>
-      </c>
-      <c r="I79" s="3">
+      <c r="L79" s="2">
+        <v>45978</v>
+      </c>
+      <c r="M79" s="3">
+        <v>28</v>
+      </c>
+      <c r="O79" t="s">
+        <v>60</v>
+      </c>
+      <c r="P79" s="2">
+        <v>46220</v>
+      </c>
+      <c r="S79" s="2">
+        <v>46220</v>
+      </c>
+      <c r="T79" s="3">
         <v>7</v>
       </c>
-      <c r="J79" t="s">
-        <v>270</v>
-      </c>
-      <c r="K79" t="s">
-        <v>320</v>
-      </c>
-      <c r="L79" s="2">
-        <v>46086</v>
-      </c>
-      <c r="M79" s="3">
-        <v>171</v>
-      </c>
-      <c r="S79" s="2">
-        <v>47181</v>
-      </c>
-      <c r="T79" s="3">
-        <v>969</v>
-      </c>
-      <c r="U79" s="3"/>
+      <c r="U79" s="3">
+        <v>7</v>
+      </c>
       <c r="V79" s="4">
-        <v>73620</v>
+        <v>71722</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -5262,7 +5254,7 @@
         <v>43</v>
       </c>
       <c r="B80" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C80" s="2">
         <v>45915</v>
@@ -5271,22 +5263,22 @@
         <v>24</v>
       </c>
       <c r="E80" t="s">
+        <v>319</v>
+      </c>
+      <c r="F80" t="s">
+        <v>320</v>
+      </c>
+      <c r="G80" t="s">
         <v>321</v>
       </c>
-      <c r="F80" t="s">
-        <v>142</v>
-      </c>
-      <c r="G80" t="s">
-        <v>311</v>
-      </c>
       <c r="H80" s="2">
-        <v>46094</v>
+        <v>46205</v>
       </c>
       <c r="I80" s="3">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="J80" t="s">
-        <v>39</v>
+        <v>272</v>
       </c>
       <c r="K80" t="s">
         <v>322</v>
@@ -5301,11 +5293,11 @@
         <v>47181</v>
       </c>
       <c r="T80" s="3">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="U80" s="3"/>
       <c r="V80" s="4">
-        <v>104220</v>
+        <v>73620</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -5313,54 +5305,50 @@
         <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>61</v>
+        <v>311</v>
       </c>
       <c r="C81" s="2">
-        <v>43902</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>62</v>
+        <v>323</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="G81" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="H81" s="2">
-        <v>45790</v>
+        <v>46094</v>
       </c>
       <c r="I81" s="3">
-        <v>422</v>
+        <v>119</v>
       </c>
       <c r="J81" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K81" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L81" s="2">
-        <v>43964</v>
+        <v>46086</v>
       </c>
       <c r="M81" s="3">
-        <v>62</v>
-      </c>
-      <c r="O81" t="s">
-        <v>70</v>
-      </c>
-      <c r="P81" s="2">
-        <v>46160</v>
+        <v>171</v>
       </c>
       <c r="S81" s="2">
-        <v>44917</v>
-      </c>
-      <c r="T81" s="3"/>
+        <v>47181</v>
+      </c>
+      <c r="T81" s="3">
+        <v>968</v>
+      </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
-        <v>139755.72</v>
+        <v>104220</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -5368,50 +5356,54 @@
         <v>43</v>
       </c>
       <c r="B82" t="s">
-        <v>324</v>
+        <v>61</v>
       </c>
       <c r="C82" s="2">
-        <v>45819</v>
+        <v>43902</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>325</v>
+        <v>62</v>
       </c>
       <c r="F82" t="s">
         <v>43</v>
       </c>
       <c r="G82" t="s">
-        <v>326</v>
+        <v>149</v>
       </c>
       <c r="H82" s="2">
-        <v>46170</v>
+        <v>45790</v>
       </c>
       <c r="I82" s="3">
-        <v>42</v>
+        <v>423</v>
       </c>
       <c r="J82" t="s">
         <v>53</v>
       </c>
       <c r="K82" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L82" s="2">
-        <v>45904</v>
+        <v>43964</v>
       </c>
       <c r="M82" s="3">
-        <v>85</v>
+        <v>62</v>
+      </c>
+      <c r="O82" t="s">
+        <v>70</v>
+      </c>
+      <c r="P82" s="2">
+        <v>46160</v>
       </c>
       <c r="S82" s="2">
-        <v>46273</v>
-      </c>
-      <c r="T82" s="3">
-        <v>61</v>
-      </c>
+        <v>44917</v>
+      </c>
+      <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
-        <v>230000</v>
+        <v>139755.72</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -5419,50 +5411,50 @@
         <v>43</v>
       </c>
       <c r="B83" t="s">
+        <v>326</v>
+      </c>
+      <c r="C83" s="2">
+        <v>45819</v>
+      </c>
+      <c r="D83" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" t="s">
+        <v>327</v>
+      </c>
+      <c r="F83" t="s">
+        <v>43</v>
+      </c>
+      <c r="G83" t="s">
         <v>328</v>
       </c>
-      <c r="C83" s="2">
-        <v>45952</v>
-      </c>
-      <c r="D83" t="s">
-        <v>24</v>
-      </c>
-      <c r="E83" t="s">
-        <v>329</v>
-      </c>
-      <c r="F83" t="s">
-        <v>330</v>
-      </c>
-      <c r="G83" t="s">
-        <v>331</v>
-      </c>
       <c r="H83" s="2">
-        <v>46087</v>
+        <v>46170</v>
       </c>
       <c r="I83" s="3">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="J83" t="s">
         <v>53</v>
       </c>
       <c r="K83" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L83" s="2">
-        <v>46086</v>
+        <v>45904</v>
       </c>
       <c r="M83" s="3">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="S83" s="2">
-        <v>47910</v>
+        <v>46273</v>
       </c>
       <c r="T83" s="3">
-        <v>1698</v>
+        <v>60</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
-        <v>250977.6</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -5470,50 +5462,50 @@
         <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="C84" s="2">
-        <v>45775</v>
+        <v>45952</v>
       </c>
       <c r="D84" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E84" t="s">
+        <v>331</v>
+      </c>
+      <c r="F84" t="s">
+        <v>332</v>
+      </c>
+      <c r="G84" t="s">
         <v>333</v>
       </c>
-      <c r="F84" t="s">
-        <v>43</v>
-      </c>
-      <c r="G84" t="s">
-        <v>52</v>
-      </c>
       <c r="H84" s="2">
-        <v>45861</v>
+        <v>46087</v>
       </c>
       <c r="I84" s="3">
-        <v>351</v>
+        <v>126</v>
       </c>
       <c r="J84" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K84" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="L84" s="2">
-        <v>45856</v>
+        <v>46086</v>
       </c>
       <c r="M84" s="3">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="S84" s="2">
-        <v>46225</v>
+        <v>47910</v>
       </c>
       <c r="T84" s="3">
-        <v>13</v>
+        <v>1697</v>
       </c>
       <c r="U84" s="3"/>
       <c r="V84" s="4">
-        <v>288862</v>
+        <v>250977.6</v>
       </c>
     </row>
     <row r="85" spans="1:22">
@@ -5521,10 +5513,10 @@
         <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="C85" s="2">
-        <v>45539</v>
+        <v>45775</v>
       </c>
       <c r="D85" t="s">
         <v>45</v>
@@ -5533,25 +5525,38 @@
         <v>335</v>
       </c>
       <c r="F85" t="s">
-        <v>336</v>
+        <v>43</v>
       </c>
       <c r="G85" t="s">
-        <v>337</v>
+        <v>52</v>
       </c>
       <c r="H85" s="2">
-        <v>45607</v>
+        <v>45861</v>
       </c>
       <c r="I85" s="3">
-        <v>605</v>
+        <v>352</v>
       </c>
       <c r="J85" t="s">
-        <v>53</v>
-      </c>
-      <c r="M85" s="3"/>
-      <c r="T85" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="K85" t="s">
+        <v>318</v>
+      </c>
+      <c r="L85" s="2">
+        <v>45856</v>
+      </c>
+      <c r="M85" s="3">
+        <v>81</v>
+      </c>
+      <c r="S85" s="2">
+        <v>46225</v>
+      </c>
+      <c r="T85" s="3">
+        <v>12</v>
+      </c>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
-        <v>297600</v>
+        <v>288862</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -5559,50 +5564,37 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
+        <v>336</v>
+      </c>
+      <c r="C86" s="2">
+        <v>45539</v>
+      </c>
+      <c r="D86" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" t="s">
+        <v>337</v>
+      </c>
+      <c r="F86" t="s">
         <v>338</v>
       </c>
-      <c r="C86" s="2">
-        <v>45840</v>
-      </c>
-      <c r="D86" t="s">
-        <v>24</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="G86" t="s">
         <v>339</v>
       </c>
-      <c r="F86" t="s">
-        <v>340</v>
-      </c>
-      <c r="G86" t="s">
-        <v>341</v>
-      </c>
       <c r="H86" s="2">
-        <v>46002</v>
+        <v>45607</v>
       </c>
       <c r="I86" s="3">
-        <v>210</v>
+        <v>606</v>
       </c>
       <c r="J86" t="s">
-        <v>39</v>
-      </c>
-      <c r="K86" t="s">
-        <v>342</v>
-      </c>
-      <c r="L86" s="2">
-        <v>46001</v>
-      </c>
-      <c r="M86" s="3">
-        <v>161</v>
-      </c>
-      <c r="S86" s="2">
-        <v>47097</v>
-      </c>
-      <c r="T86" s="3">
-        <v>885</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
-        <v>299821.5</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -5610,50 +5602,50 @@
         <v>43</v>
       </c>
       <c r="B87" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C87" s="2">
-        <v>45868</v>
+        <v>45840</v>
       </c>
       <c r="D87" t="s">
         <v>24</v>
       </c>
       <c r="E87" t="s">
+        <v>341</v>
+      </c>
+      <c r="F87" t="s">
+        <v>342</v>
+      </c>
+      <c r="G87" t="s">
+        <v>343</v>
+      </c>
+      <c r="H87" s="2">
+        <v>46002</v>
+      </c>
+      <c r="I87" s="3">
+        <v>211</v>
+      </c>
+      <c r="J87" t="s">
+        <v>39</v>
+      </c>
+      <c r="K87" t="s">
         <v>344</v>
       </c>
-      <c r="F87" t="s">
-        <v>67</v>
-      </c>
-      <c r="G87" t="s">
-        <v>345</v>
-      </c>
-      <c r="H87" s="2">
-        <v>46146</v>
-      </c>
-      <c r="I87" s="3">
-        <v>66</v>
-      </c>
-      <c r="J87" t="s">
-        <v>53</v>
-      </c>
-      <c r="K87" t="s">
-        <v>346</v>
-      </c>
       <c r="L87" s="2">
-        <v>46077</v>
+        <v>46001</v>
       </c>
       <c r="M87" s="3">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="S87" s="2">
-        <v>47905</v>
+        <v>47097</v>
       </c>
       <c r="T87" s="3">
-        <v>1693</v>
+        <v>884</v>
       </c>
       <c r="U87" s="3"/>
       <c r="V87" s="4">
-        <v>338580</v>
+        <v>299821.5</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -5661,56 +5653,50 @@
         <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C88" s="2">
-        <v>44370</v>
+        <v>45868</v>
       </c>
       <c r="D88" t="s">
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F88" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="G88" t="s">
-        <v>149</v>
+        <v>347</v>
       </c>
       <c r="H88" s="2">
-        <v>45881</v>
+        <v>46146</v>
       </c>
       <c r="I88" s="3">
-        <v>331</v>
+        <v>67</v>
       </c>
       <c r="J88" t="s">
         <v>53</v>
       </c>
       <c r="K88" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L88" s="2">
-        <v>44589</v>
+        <v>46077</v>
       </c>
       <c r="M88" s="3">
-        <v>219</v>
-      </c>
-      <c r="O88" t="s">
-        <v>350</v>
-      </c>
-      <c r="P88" s="2">
-        <v>46419</v>
+        <v>209</v>
       </c>
       <c r="S88" s="2">
-        <v>44593</v>
-      </c>
-      <c r="T88" s="3"/>
-      <c r="U88" s="3">
-        <v>207</v>
-      </c>
+        <v>47905</v>
+      </c>
+      <c r="T88" s="3">
+        <v>1692</v>
+      </c>
+      <c r="U88" s="3"/>
       <c r="V88" s="4">
-        <v>374899.96</v>
+        <v>338580</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -5718,189 +5704,200 @@
         <v>43</v>
       </c>
       <c r="B89" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="2">
+        <v>44370</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" t="s">
+        <v>350</v>
+      </c>
+      <c r="F89" t="s">
+        <v>43</v>
+      </c>
+      <c r="G89" t="s">
+        <v>149</v>
+      </c>
+      <c r="H89" s="2">
+        <v>45881</v>
+      </c>
+      <c r="I89" s="3">
+        <v>332</v>
+      </c>
+      <c r="J89" t="s">
+        <v>53</v>
+      </c>
+      <c r="K89" t="s">
         <v>351</v>
       </c>
-      <c r="C89" s="2">
-        <v>45422</v>
-      </c>
-      <c r="D89" t="s">
-        <v>45</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="L89" s="2">
+        <v>44589</v>
+      </c>
+      <c r="M89" s="3">
+        <v>219</v>
+      </c>
+      <c r="O89" t="s">
         <v>352</v>
       </c>
-      <c r="F89" t="s">
-        <v>43</v>
-      </c>
-      <c r="G89" t="s">
-        <v>353</v>
-      </c>
-      <c r="H89" s="2">
-        <v>45624</v>
-      </c>
-      <c r="I89" s="3">
-        <v>588</v>
-      </c>
-      <c r="J89" t="s">
-        <v>39</v>
-      </c>
-      <c r="K89" t="s">
-        <v>354</v>
-      </c>
-      <c r="L89" s="2">
-        <v>45544</v>
-      </c>
-      <c r="M89" s="3">
-        <v>122</v>
+      <c r="P89" s="2">
+        <v>46419</v>
       </c>
       <c r="S89" s="2">
-        <v>45911</v>
+        <v>44593</v>
       </c>
       <c r="T89" s="3"/>
-      <c r="U89" s="3"/>
+      <c r="U89" s="3">
+        <v>206</v>
+      </c>
       <c r="V89" s="4">
-        <v>457600</v>
+        <v>374899.96</v>
       </c>
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B90" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C90" s="2">
-        <v>46038</v>
+        <v>45422</v>
       </c>
       <c r="D90" t="s">
         <v>45</v>
       </c>
       <c r="E90" t="s">
+        <v>354</v>
+      </c>
+      <c r="F90" t="s">
+        <v>43</v>
+      </c>
+      <c r="G90" t="s">
+        <v>355</v>
+      </c>
+      <c r="H90" s="2">
+        <v>45624</v>
+      </c>
+      <c r="I90" s="3">
+        <v>589</v>
+      </c>
+      <c r="J90" t="s">
+        <v>39</v>
+      </c>
+      <c r="K90" t="s">
         <v>356</v>
       </c>
-      <c r="F90" t="s">
-        <v>299</v>
-      </c>
-      <c r="G90" t="s">
-        <v>357</v>
-      </c>
-      <c r="H90" s="2">
-        <v>46210</v>
-      </c>
-      <c r="I90" s="3">
-        <v>2</v>
-      </c>
-      <c r="J90" t="s">
-        <v>28</v>
-      </c>
-      <c r="M90" s="3"/>
+      <c r="L90" s="2">
+        <v>45544</v>
+      </c>
+      <c r="M90" s="3">
+        <v>122</v>
+      </c>
+      <c r="S90" s="2">
+        <v>45911</v>
+      </c>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="4">
-        <v>687500</v>
+        <v>457600</v>
       </c>
     </row>
     <row r="91" spans="1:22">
       <c r="A91" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B91" t="s">
+        <v>357</v>
+      </c>
+      <c r="C91" s="2">
+        <v>46038</v>
+      </c>
+      <c r="D91" t="s">
+        <v>45</v>
+      </c>
+      <c r="E91" t="s">
         <v>358</v>
       </c>
-      <c r="C91" s="2">
-        <v>44939</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
+        <v>103</v>
+      </c>
+      <c r="G91" t="s">
         <v>359</v>
       </c>
-      <c r="E91" t="s">
-        <v>360</v>
-      </c>
-      <c r="F91" t="s">
-        <v>29</v>
-      </c>
-      <c r="G91" t="s">
-        <v>361</v>
-      </c>
       <c r="H91" s="2">
-        <v>45979</v>
+        <v>46210</v>
       </c>
       <c r="I91" s="3">
-        <v>233</v>
+        <v>3</v>
       </c>
       <c r="J91" t="s">
-        <v>53</v>
-      </c>
-      <c r="K91" t="s">
-        <v>362</v>
-      </c>
-      <c r="L91" s="2">
-        <v>45968</v>
-      </c>
-      <c r="M91" s="3">
-        <v>1029</v>
-      </c>
-      <c r="O91" t="s">
-        <v>350</v>
-      </c>
-      <c r="P91" s="2">
-        <v>46426</v>
-      </c>
-      <c r="S91" s="2">
-        <v>45334</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M91" s="3"/>
       <c r="T91" s="3"/>
-      <c r="U91" s="3">
-        <v>214</v>
-      </c>
+      <c r="U91" s="3"/>
       <c r="V91" s="4">
-        <v>706431.6</v>
+        <v>687500</v>
       </c>
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B92" t="s">
+        <v>360</v>
+      </c>
+      <c r="C92" s="2">
+        <v>44939</v>
+      </c>
+      <c r="D92" t="s">
+        <v>361</v>
+      </c>
+      <c r="E92" t="s">
+        <v>362</v>
+      </c>
+      <c r="F92" t="s">
+        <v>29</v>
+      </c>
+      <c r="G92" t="s">
         <v>363</v>
       </c>
-      <c r="C92" s="2">
-        <v>45673</v>
-      </c>
-      <c r="D92" t="s">
-        <v>24</v>
-      </c>
-      <c r="E92" t="s">
-        <v>364</v>
-      </c>
-      <c r="F92" t="s">
-        <v>43</v>
-      </c>
-      <c r="G92" t="s">
-        <v>52</v>
-      </c>
       <c r="H92" s="2">
-        <v>46140</v>
+        <v>45979</v>
       </c>
       <c r="I92" s="3">
-        <v>72</v>
+        <v>234</v>
       </c>
       <c r="J92" t="s">
         <v>53</v>
       </c>
       <c r="K92" t="s">
-        <v>365</v>
-      </c>
-      <c r="M92" s="3"/>
+        <v>364</v>
+      </c>
+      <c r="L92" s="2">
+        <v>45968</v>
+      </c>
+      <c r="M92" s="3">
+        <v>1029</v>
+      </c>
+      <c r="O92" t="s">
+        <v>352</v>
+      </c>
+      <c r="P92" s="2">
+        <v>46426</v>
+      </c>
       <c r="S92" s="2">
-        <v>46598</v>
-      </c>
-      <c r="T92" s="3">
-        <v>386</v>
-      </c>
-      <c r="U92" s="3"/>
+        <v>45334</v>
+      </c>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3">
+        <v>213</v>
+      </c>
       <c r="V92" s="4">
-        <v>890000</v>
+        <v>706431.6</v>
       </c>
     </row>
     <row r="93" spans="1:22">
@@ -5908,50 +5905,45 @@
         <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C93" s="2">
-        <v>45215</v>
+        <v>45673</v>
       </c>
       <c r="D93" t="s">
         <v>24</v>
       </c>
       <c r="E93" t="s">
+        <v>366</v>
+      </c>
+      <c r="F93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" t="s">
+        <v>52</v>
+      </c>
+      <c r="H93" s="2">
+        <v>46140</v>
+      </c>
+      <c r="I93" s="3">
+        <v>73</v>
+      </c>
+      <c r="J93" t="s">
+        <v>53</v>
+      </c>
+      <c r="K93" t="s">
         <v>367</v>
       </c>
-      <c r="F93" t="s">
-        <v>170</v>
-      </c>
-      <c r="G93" t="s">
-        <v>368</v>
-      </c>
-      <c r="H93" s="2">
-        <v>45687</v>
-      </c>
-      <c r="I93" s="3">
-        <v>525</v>
-      </c>
-      <c r="J93" t="s">
-        <v>39</v>
-      </c>
-      <c r="K93" t="s">
-        <v>369</v>
-      </c>
-      <c r="L93" s="2">
-        <v>45685</v>
-      </c>
-      <c r="M93" s="3">
-        <v>470</v>
-      </c>
+      <c r="M93" s="3"/>
       <c r="S93" s="2">
-        <v>46780</v>
+        <v>46598</v>
       </c>
       <c r="T93" s="3">
-        <v>568</v>
+        <v>385</v>
       </c>
       <c r="U93" s="3"/>
       <c r="V93" s="4">
-        <v>1220266.1399999999</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="94" spans="1:22">
@@ -5959,150 +5951,150 @@
         <v>43</v>
       </c>
       <c r="B94" t="s">
+        <v>368</v>
+      </c>
+      <c r="C94" s="2">
+        <v>45215</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" t="s">
+        <v>369</v>
+      </c>
+      <c r="F94" t="s">
+        <v>170</v>
+      </c>
+      <c r="G94" t="s">
         <v>370</v>
       </c>
-      <c r="C94" s="2">
-        <v>45366</v>
-      </c>
-      <c r="D94" t="s">
-        <v>45</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="H94" s="2">
+        <v>45687</v>
+      </c>
+      <c r="I94" s="3">
+        <v>526</v>
+      </c>
+      <c r="J94" t="s">
+        <v>39</v>
+      </c>
+      <c r="K94" t="s">
         <v>371</v>
       </c>
-      <c r="F94" t="s">
-        <v>43</v>
-      </c>
-      <c r="G94" t="s">
-        <v>372</v>
-      </c>
-      <c r="H94" s="2">
-        <v>45481</v>
-      </c>
-      <c r="I94" s="3">
-        <v>731</v>
-      </c>
-      <c r="J94" t="s">
-        <v>53</v>
-      </c>
-      <c r="K94" t="s">
-        <v>373</v>
-      </c>
       <c r="L94" s="2">
-        <v>45471</v>
+        <v>45685</v>
       </c>
       <c r="M94" s="3">
-        <v>105</v>
+        <v>470</v>
       </c>
       <c r="S94" s="2">
-        <v>47301</v>
+        <v>46780</v>
       </c>
       <c r="T94" s="3">
-        <v>1089</v>
+        <v>567</v>
       </c>
       <c r="U94" s="3"/>
       <c r="V94" s="4">
-        <v>1245414.49</v>
+        <v>1220266.1399999999</v>
       </c>
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B95" t="s">
+        <v>372</v>
+      </c>
+      <c r="C95" s="2">
+        <v>45366</v>
+      </c>
+      <c r="D95" t="s">
+        <v>45</v>
+      </c>
+      <c r="E95" t="s">
+        <v>373</v>
+      </c>
+      <c r="F95" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95" t="s">
         <v>374</v>
       </c>
-      <c r="C95" s="2">
-        <v>45152</v>
-      </c>
-      <c r="D95" t="s">
-        <v>267</v>
-      </c>
-      <c r="E95" t="s">
-        <v>375</v>
-      </c>
-      <c r="F95" t="s">
-        <v>29</v>
-      </c>
-      <c r="G95" t="s">
-        <v>376</v>
-      </c>
       <c r="H95" s="2">
-        <v>45440</v>
+        <v>45481</v>
       </c>
       <c r="I95" s="3">
-        <v>772</v>
+        <v>732</v>
       </c>
       <c r="J95" t="s">
         <v>53</v>
       </c>
       <c r="K95" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L95" s="2">
-        <v>45303</v>
+        <v>45471</v>
       </c>
       <c r="M95" s="3">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="S95" s="2">
-        <v>45992</v>
-      </c>
-      <c r="T95" s="3"/>
+        <v>47301</v>
+      </c>
+      <c r="T95" s="3">
+        <v>1088</v>
+      </c>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
-        <v>1298031.3600000001</v>
+        <v>1245414.49</v>
       </c>
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B96" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" s="2">
+        <v>45152</v>
+      </c>
+      <c r="D96" t="s">
+        <v>269</v>
+      </c>
+      <c r="E96" t="s">
+        <v>377</v>
+      </c>
+      <c r="F96" t="s">
+        <v>29</v>
+      </c>
+      <c r="G96" t="s">
         <v>378</v>
       </c>
-      <c r="C96" s="2">
-        <v>45373</v>
-      </c>
-      <c r="D96" t="s">
-        <v>45</v>
-      </c>
-      <c r="E96" t="s">
-        <v>379</v>
-      </c>
-      <c r="F96" t="s">
-        <v>43</v>
-      </c>
-      <c r="G96" t="s">
-        <v>372</v>
-      </c>
       <c r="H96" s="2">
-        <v>45492</v>
+        <v>45440</v>
       </c>
       <c r="I96" s="3">
-        <v>720</v>
+        <v>773</v>
       </c>
       <c r="J96" t="s">
         <v>53</v>
       </c>
       <c r="K96" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L96" s="2">
-        <v>45492</v>
+        <v>45303</v>
       </c>
       <c r="M96" s="3">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="S96" s="2">
-        <v>46587</v>
-      </c>
-      <c r="T96" s="3">
-        <v>375</v>
-      </c>
+        <v>45992</v>
+      </c>
+      <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="4">
-        <v>1320176.8799999999</v>
+        <v>1298031.3600000001</v>
       </c>
     </row>
     <row r="97" spans="1:22">
@@ -6110,54 +6102,50 @@
         <v>43</v>
       </c>
       <c r="B97" t="s">
+        <v>380</v>
+      </c>
+      <c r="C97" s="2">
+        <v>45373</v>
+      </c>
+      <c r="D97" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" t="s">
         <v>381</v>
       </c>
-      <c r="C97" s="2">
-        <v>44663</v>
-      </c>
-      <c r="D97" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" t="s">
-        <v>382</v>
-      </c>
       <c r="F97" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="G97" t="s">
-        <v>201</v>
+        <v>374</v>
       </c>
       <c r="H97" s="2">
-        <v>45588</v>
+        <v>45492</v>
       </c>
       <c r="I97" s="3">
-        <v>624</v>
+        <v>721</v>
       </c>
       <c r="J97" t="s">
         <v>53</v>
       </c>
       <c r="K97" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L97" s="2">
-        <v>44893</v>
+        <v>45492</v>
       </c>
       <c r="M97" s="3">
-        <v>230</v>
-      </c>
-      <c r="O97" t="s">
-        <v>60</v>
-      </c>
-      <c r="P97" s="2">
-        <v>45996</v>
+        <v>119</v>
       </c>
       <c r="S97" s="2">
-        <v>45624</v>
-      </c>
-      <c r="T97" s="3"/>
+        <v>46587</v>
+      </c>
+      <c r="T97" s="3">
+        <v>374</v>
+      </c>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
-        <v>1416380</v>
+        <v>1320176.8799999999</v>
       </c>
     </row>
     <row r="98" spans="1:22">
@@ -6165,126 +6153,143 @@
         <v>43</v>
       </c>
       <c r="B98" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C98" s="2">
-        <v>45826</v>
+        <v>44663</v>
       </c>
       <c r="D98" t="s">
         <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F98" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="G98" t="s">
-        <v>386</v>
+        <v>201</v>
       </c>
       <c r="H98" s="2">
-        <v>46079</v>
+        <v>45588</v>
       </c>
       <c r="I98" s="3">
-        <v>133</v>
+        <v>625</v>
       </c>
       <c r="J98" t="s">
         <v>53</v>
       </c>
       <c r="K98" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="L98" s="2">
-        <v>46076</v>
+        <v>44893</v>
       </c>
       <c r="M98" s="3">
-        <v>250</v>
+        <v>230</v>
+      </c>
+      <c r="O98" t="s">
+        <v>60</v>
+      </c>
+      <c r="P98" s="2">
+        <v>45996</v>
       </c>
       <c r="S98" s="2">
-        <v>47903</v>
-      </c>
-      <c r="T98" s="3">
-        <v>1691</v>
-      </c>
+        <v>45624</v>
+      </c>
+      <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="4">
-        <v>1435000</v>
+        <v>1416380</v>
       </c>
     </row>
     <row r="99" spans="1:22">
       <c r="A99" t="s">
+        <v>43</v>
+      </c>
+      <c r="B99" t="s">
+        <v>386</v>
+      </c>
+      <c r="C99" s="2">
+        <v>45826</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" t="s">
+        <v>387</v>
+      </c>
+      <c r="F99" t="s">
+        <v>67</v>
+      </c>
+      <c r="G99" t="s">
         <v>388</v>
       </c>
-      <c r="B99" t="s">
-        <v>389</v>
-      </c>
-      <c r="C99" s="2">
-        <v>46150</v>
-      </c>
-      <c r="D99" t="s">
-        <v>45</v>
-      </c>
-      <c r="E99" t="s">
-        <v>390</v>
-      </c>
-      <c r="F99" t="s">
-        <v>388</v>
-      </c>
-      <c r="G99" t="s">
-        <v>391</v>
-      </c>
       <c r="H99" s="2">
-        <v>46206</v>
+        <v>46079</v>
       </c>
       <c r="I99" s="3">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="J99" t="s">
         <v>53</v>
       </c>
-      <c r="M99" s="3"/>
-      <c r="T99" s="3"/>
+      <c r="K99" t="s">
+        <v>389</v>
+      </c>
+      <c r="L99" s="2">
+        <v>46076</v>
+      </c>
+      <c r="M99" s="3">
+        <v>250</v>
+      </c>
+      <c r="S99" s="2">
+        <v>47903</v>
+      </c>
+      <c r="T99" s="3">
+        <v>1690</v>
+      </c>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
-        <v>1719174</v>
+        <v>1435000</v>
       </c>
     </row>
     <row r="100" spans="1:22">
       <c r="A100" t="s">
-        <v>43</v>
+        <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C100" s="2">
-        <v>46094</v>
+        <v>46150</v>
       </c>
       <c r="D100" t="s">
         <v>45</v>
       </c>
       <c r="E100" t="s">
+        <v>392</v>
+      </c>
+      <c r="F100" t="s">
+        <v>390</v>
+      </c>
+      <c r="G100" t="s">
         <v>393</v>
       </c>
-      <c r="F100" t="s">
-        <v>394</v>
-      </c>
-      <c r="G100" t="s">
-        <v>395</v>
-      </c>
       <c r="H100" s="2">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="I100" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J100" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="M100" s="3"/>
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="4">
-        <v>1828126.08</v>
+        <v>1719174</v>
       </c>
     </row>
     <row r="101" spans="1:22">
@@ -6292,50 +6297,37 @@
         <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C101" s="2">
-        <v>45950</v>
+        <v>46094</v>
       </c>
       <c r="D101" t="s">
         <v>45</v>
       </c>
       <c r="E101" t="s">
+        <v>395</v>
+      </c>
+      <c r="F101" t="s">
+        <v>396</v>
+      </c>
+      <c r="G101" t="s">
         <v>397</v>
       </c>
-      <c r="F101" t="s">
-        <v>43</v>
-      </c>
-      <c r="G101" t="s">
-        <v>398</v>
-      </c>
       <c r="H101" s="2">
-        <v>45988</v>
+        <v>46199</v>
       </c>
       <c r="I101" s="3">
-        <v>224</v>
+        <v>14</v>
       </c>
       <c r="J101" t="s">
-        <v>39</v>
-      </c>
-      <c r="K101" t="s">
-        <v>399</v>
-      </c>
-      <c r="L101" s="2">
-        <v>45979</v>
-      </c>
-      <c r="M101" s="3">
-        <v>29</v>
-      </c>
-      <c r="S101" s="2">
-        <v>46343</v>
-      </c>
-      <c r="T101" s="3">
-        <v>131</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M101" s="3"/>
+      <c r="T101" s="3"/>
       <c r="U101" s="3"/>
       <c r="V101" s="4">
-        <v>2075682</v>
+        <v>1828126.08</v>
       </c>
     </row>
     <row r="102" spans="1:22">
@@ -6343,96 +6335,96 @@
         <v>43</v>
       </c>
       <c r="B102" t="s">
+        <v>398</v>
+      </c>
+      <c r="C102" s="2">
+        <v>45950</v>
+      </c>
+      <c r="D102" t="s">
+        <v>45</v>
+      </c>
+      <c r="E102" t="s">
+        <v>399</v>
+      </c>
+      <c r="F102" t="s">
+        <v>43</v>
+      </c>
+      <c r="G102" t="s">
         <v>400</v>
       </c>
-      <c r="C102" s="2">
-        <v>45511</v>
-      </c>
-      <c r="D102" t="s">
-        <v>24</v>
-      </c>
-      <c r="E102" t="s">
-        <v>401</v>
-      </c>
-      <c r="F102" t="s">
-        <v>26</v>
-      </c>
-      <c r="G102" t="s">
-        <v>402</v>
-      </c>
       <c r="H102" s="2">
-        <v>45786</v>
+        <v>45988</v>
       </c>
       <c r="I102" s="3">
-        <v>426</v>
+        <v>225</v>
       </c>
       <c r="J102" t="s">
         <v>39</v>
       </c>
       <c r="K102" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L102" s="2">
-        <v>45794</v>
+        <v>45979</v>
       </c>
       <c r="M102" s="3">
-        <v>283</v>
-      </c>
-      <c r="T102" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="S102" s="2">
+        <v>46343</v>
+      </c>
+      <c r="T102" s="3">
+        <v>130</v>
+      </c>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
-        <v>2594055</v>
+        <v>2075682</v>
       </c>
     </row>
     <row r="103" spans="1:22">
       <c r="A103" t="s">
+        <v>43</v>
+      </c>
+      <c r="B103" t="s">
+        <v>402</v>
+      </c>
+      <c r="C103" s="2">
+        <v>45511</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" t="s">
+        <v>403</v>
+      </c>
+      <c r="F103" t="s">
         <v>26</v>
       </c>
-      <c r="B103" t="s">
+      <c r="G103" t="s">
         <v>404</v>
       </c>
-      <c r="C103" s="2">
-        <v>45848</v>
-      </c>
-      <c r="D103" t="s">
-        <v>36</v>
-      </c>
-      <c r="E103" t="s">
-        <v>405</v>
-      </c>
-      <c r="F103" t="s">
-        <v>225</v>
-      </c>
-      <c r="G103" t="s">
-        <v>406</v>
-      </c>
       <c r="H103" s="2">
-        <v>46014</v>
+        <v>45786</v>
       </c>
       <c r="I103" s="3">
-        <v>198</v>
+        <v>427</v>
       </c>
       <c r="J103" t="s">
         <v>39</v>
       </c>
       <c r="K103" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L103" s="2">
-        <v>46008</v>
+        <v>45794</v>
       </c>
       <c r="M103" s="3">
-        <v>160</v>
-      </c>
-      <c r="S103" s="2">
-        <v>46373</v>
-      </c>
-      <c r="T103" s="3">
-        <v>161</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="T103" s="3"/>
       <c r="U103" s="3"/>
       <c r="V103" s="4">
-        <v>2641069.35</v>
+        <v>2594055</v>
       </c>
     </row>
     <row r="104" spans="1:22">
@@ -6440,185 +6432,185 @@
         <v>26</v>
       </c>
       <c r="B104" t="s">
+        <v>406</v>
+      </c>
+      <c r="C104" s="2">
+        <v>45848</v>
+      </c>
+      <c r="D104" t="s">
+        <v>36</v>
+      </c>
+      <c r="E104" t="s">
+        <v>407</v>
+      </c>
+      <c r="F104" t="s">
+        <v>225</v>
+      </c>
+      <c r="G104" t="s">
         <v>408</v>
       </c>
-      <c r="C104" s="2">
-        <v>46030</v>
-      </c>
-      <c r="D104" t="s">
-        <v>267</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="H104" s="2">
+        <v>46014</v>
+      </c>
+      <c r="I104" s="3">
+        <v>199</v>
+      </c>
+      <c r="J104" t="s">
+        <v>39</v>
+      </c>
+      <c r="K104" t="s">
         <v>409</v>
       </c>
-      <c r="F104" t="s">
-        <v>410</v>
-      </c>
-      <c r="G104" t="s">
-        <v>411</v>
-      </c>
-      <c r="H104" s="2">
-        <v>46198</v>
-      </c>
-      <c r="I104" s="3">
-        <v>14</v>
-      </c>
-      <c r="J104" t="s">
-        <v>28</v>
-      </c>
-      <c r="M104" s="3"/>
-      <c r="T104" s="3"/>
+      <c r="L104" s="2">
+        <v>46008</v>
+      </c>
+      <c r="M104" s="3">
+        <v>160</v>
+      </c>
+      <c r="S104" s="2">
+        <v>46373</v>
+      </c>
+      <c r="T104" s="3">
+        <v>160</v>
+      </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
-        <v>2652975.2799999998</v>
+        <v>2641069.35</v>
       </c>
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B105" t="s">
+        <v>410</v>
+      </c>
+      <c r="C105" s="2">
+        <v>46030</v>
+      </c>
+      <c r="D105" t="s">
+        <v>269</v>
+      </c>
+      <c r="E105" t="s">
+        <v>411</v>
+      </c>
+      <c r="F105" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" t="s">
         <v>412</v>
       </c>
-      <c r="C105" s="2">
-        <v>45365</v>
-      </c>
-      <c r="D105" t="s">
-        <v>36</v>
-      </c>
-      <c r="E105" t="s">
-        <v>413</v>
-      </c>
-      <c r="F105" t="s">
-        <v>414</v>
-      </c>
-      <c r="G105" t="s">
-        <v>415</v>
-      </c>
       <c r="H105" s="2">
-        <v>45568</v>
+        <v>46211</v>
       </c>
       <c r="I105" s="3">
-        <v>644</v>
+        <v>2</v>
       </c>
       <c r="J105" t="s">
-        <v>53</v>
-      </c>
-      <c r="K105" t="s">
-        <v>416</v>
-      </c>
-      <c r="L105" s="2">
-        <v>45567</v>
-      </c>
-      <c r="M105" s="3">
-        <v>202</v>
-      </c>
-      <c r="S105" s="2">
-        <v>46479</v>
-      </c>
-      <c r="T105" s="3">
-        <v>267</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M105" s="3"/>
+      <c r="T105" s="3"/>
       <c r="U105" s="3"/>
       <c r="V105" s="4">
-        <v>2780400.6</v>
+        <v>2652975.2799999998</v>
       </c>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>417</v>
+        <v>43</v>
       </c>
       <c r="B106" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C106" s="2">
-        <v>45526</v>
+        <v>45365</v>
       </c>
       <c r="D106" t="s">
         <v>36</v>
       </c>
       <c r="E106" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F106" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G106" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H106" s="2">
-        <v>45932</v>
+        <v>45568</v>
       </c>
       <c r="I106" s="3">
-        <v>280</v>
+        <v>645</v>
       </c>
       <c r="J106" t="s">
         <v>53</v>
       </c>
       <c r="K106" t="s">
-        <v>421</v>
-      </c>
-      <c r="M106" s="3"/>
+        <v>417</v>
+      </c>
+      <c r="L106" s="2">
+        <v>45567</v>
+      </c>
+      <c r="M106" s="3">
+        <v>202</v>
+      </c>
       <c r="S106" s="2">
-        <v>47748</v>
+        <v>46479</v>
       </c>
       <c r="T106" s="3">
-        <v>1536</v>
+        <v>266</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
-        <v>4440928.34</v>
+        <v>2780400.6</v>
       </c>
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
-        <v>26</v>
+        <v>418</v>
       </c>
       <c r="B107" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C107" s="2">
-        <v>45824</v>
+        <v>45526</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E107" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F107" t="s">
-        <v>26</v>
+        <v>418</v>
       </c>
       <c r="G107" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H107" s="2">
-        <v>45958</v>
+        <v>45932</v>
       </c>
       <c r="I107" s="3">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="J107" t="s">
         <v>53</v>
       </c>
       <c r="K107" t="s">
-        <v>425</v>
-      </c>
-      <c r="L107" s="2">
-        <v>45951</v>
-      </c>
-      <c r="M107" s="3">
-        <v>127</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="M107" s="3"/>
       <c r="S107" s="2">
-        <v>46316</v>
+        <v>47748</v>
       </c>
       <c r="T107" s="3">
-        <v>104</v>
+        <v>1535</v>
       </c>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
-        <v>5192424.24</v>
+        <v>4440928.34</v>
       </c>
     </row>
     <row r="108" spans="1:22">
@@ -6626,470 +6618,464 @@
         <v>26</v>
       </c>
       <c r="B108" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C108" s="2">
-        <v>45560</v>
+        <v>45824</v>
       </c>
       <c r="D108" t="s">
         <v>24</v>
       </c>
       <c r="E108" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F108" t="s">
-        <v>428</v>
+        <v>26</v>
       </c>
       <c r="G108" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="H108" s="2">
-        <v>45930</v>
+        <v>45958</v>
       </c>
       <c r="I108" s="3">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="J108" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K108" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="L108" s="2">
-        <v>45854</v>
+        <v>45951</v>
       </c>
       <c r="M108" s="3">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="S108" s="2">
-        <v>46950</v>
+        <v>46316</v>
       </c>
       <c r="T108" s="3">
-        <v>738</v>
+        <v>103</v>
       </c>
       <c r="U108" s="3"/>
       <c r="V108" s="4">
-        <v>6210000</v>
+        <v>5192424.24</v>
       </c>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
-        <v>271</v>
+        <v>26</v>
       </c>
       <c r="B109" t="s">
+        <v>427</v>
+      </c>
+      <c r="C109" s="2">
+        <v>45560</v>
+      </c>
+      <c r="D109" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109" t="s">
+        <v>428</v>
+      </c>
+      <c r="F109" t="s">
+        <v>429</v>
+      </c>
+      <c r="G109" t="s">
+        <v>430</v>
+      </c>
+      <c r="H109" s="2">
+        <v>45930</v>
+      </c>
+      <c r="I109" s="3">
+        <v>283</v>
+      </c>
+      <c r="J109" t="s">
+        <v>39</v>
+      </c>
+      <c r="K109" t="s">
         <v>431</v>
       </c>
-      <c r="C109" s="2">
-        <v>44607</v>
-      </c>
-      <c r="D109" t="s">
-        <v>359</v>
-      </c>
-      <c r="E109" t="s">
-        <v>432</v>
-      </c>
-      <c r="F109" t="s">
-        <v>271</v>
-      </c>
-      <c r="G109" t="s">
-        <v>433</v>
-      </c>
-      <c r="H109" s="2">
-        <v>46196</v>
-      </c>
-      <c r="I109" s="3">
-        <v>16</v>
-      </c>
-      <c r="J109" t="s">
-        <v>53</v>
-      </c>
-      <c r="K109" t="s">
-        <v>434</v>
-      </c>
       <c r="L109" s="2">
-        <v>44747</v>
+        <v>45854</v>
       </c>
       <c r="M109" s="3">
-        <v>140</v>
-      </c>
-      <c r="O109" t="s">
-        <v>435</v>
-      </c>
-      <c r="P109" s="2">
-        <v>46573</v>
+        <v>294</v>
       </c>
       <c r="S109" s="2">
-        <v>45111</v>
-      </c>
-      <c r="T109" s="3"/>
-      <c r="U109" s="3">
-        <v>361</v>
-      </c>
+        <v>46950</v>
+      </c>
+      <c r="T109" s="3">
+        <v>737</v>
+      </c>
+      <c r="U109" s="3"/>
       <c r="V109" s="4">
-        <v>6571898.25</v>
+        <v>6210000</v>
       </c>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
+        <v>273</v>
+      </c>
+      <c r="B110" t="s">
+        <v>432</v>
+      </c>
+      <c r="C110" s="2">
+        <v>44607</v>
+      </c>
+      <c r="D110" t="s">
+        <v>361</v>
+      </c>
+      <c r="E110" t="s">
+        <v>433</v>
+      </c>
+      <c r="F110" t="s">
+        <v>273</v>
+      </c>
+      <c r="G110" t="s">
+        <v>434</v>
+      </c>
+      <c r="H110" s="2">
+        <v>46196</v>
+      </c>
+      <c r="I110" s="3">
+        <v>17</v>
+      </c>
+      <c r="J110" t="s">
+        <v>53</v>
+      </c>
+      <c r="K110" t="s">
+        <v>435</v>
+      </c>
+      <c r="L110" s="2">
+        <v>44747</v>
+      </c>
+      <c r="M110" s="3">
+        <v>140</v>
+      </c>
+      <c r="O110" t="s">
         <v>436</v>
       </c>
-      <c r="B110" t="s">
-        <v>437</v>
-      </c>
-      <c r="C110" s="2">
-        <v>38661</v>
-      </c>
-      <c r="D110" t="s">
-        <v>36</v>
-      </c>
-      <c r="E110" t="s">
-        <v>438</v>
-      </c>
-      <c r="F110" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" t="s">
-        <v>439</v>
-      </c>
-      <c r="H110" s="2">
-        <v>45993</v>
-      </c>
-      <c r="I110" s="3">
-        <v>219</v>
-      </c>
-      <c r="J110" t="s">
-        <v>39</v>
-      </c>
-      <c r="K110" t="s">
-        <v>440</v>
-      </c>
-      <c r="L110" s="2">
-        <v>45993</v>
-      </c>
-      <c r="M110" s="3">
-        <v>7332</v>
+      <c r="P110" s="2">
+        <v>46573</v>
       </c>
       <c r="S110" s="2">
-        <v>46540</v>
-      </c>
-      <c r="T110" s="3">
-        <v>328</v>
-      </c>
-      <c r="U110" s="3"/>
+        <v>45111</v>
+      </c>
+      <c r="T110" s="3"/>
+      <c r="U110" s="3">
+        <v>360</v>
+      </c>
       <c r="V110" s="4">
-        <v>9032000</v>
+        <v>6571898.25</v>
       </c>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
-        <v>225</v>
+        <v>437</v>
       </c>
       <c r="B111" t="s">
+        <v>438</v>
+      </c>
+      <c r="C111" s="2">
+        <v>38661</v>
+      </c>
+      <c r="D111" t="s">
+        <v>36</v>
+      </c>
+      <c r="E111" t="s">
+        <v>439</v>
+      </c>
+      <c r="F111" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" t="s">
+        <v>440</v>
+      </c>
+      <c r="H111" s="2">
+        <v>45993</v>
+      </c>
+      <c r="I111" s="3">
+        <v>220</v>
+      </c>
+      <c r="J111" t="s">
+        <v>39</v>
+      </c>
+      <c r="K111" t="s">
         <v>441</v>
       </c>
-      <c r="C111" s="2">
-        <v>45560</v>
-      </c>
-      <c r="D111" t="s">
-        <v>24</v>
-      </c>
-      <c r="E111" t="s">
-        <v>442</v>
-      </c>
-      <c r="F111" t="s">
-        <v>225</v>
-      </c>
-      <c r="G111" t="s">
-        <v>443</v>
-      </c>
-      <c r="H111" s="2">
-        <v>45797</v>
-      </c>
-      <c r="I111" s="3">
-        <v>415</v>
-      </c>
-      <c r="J111" t="s">
-        <v>53</v>
-      </c>
-      <c r="K111" t="s">
-        <v>444</v>
-      </c>
-      <c r="M111" s="3"/>
+      <c r="L111" s="2">
+        <v>45993</v>
+      </c>
+      <c r="M111" s="3">
+        <v>7332</v>
+      </c>
       <c r="S111" s="2">
-        <v>46523</v>
+        <v>46540</v>
       </c>
       <c r="T111" s="3">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="U111" s="3"/>
       <c r="V111" s="4">
-        <v>9152353</v>
+        <v>9032000</v>
       </c>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="B112" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C112" s="2">
-        <v>44763</v>
+        <v>45560</v>
       </c>
       <c r="D112" t="s">
         <v>24</v>
       </c>
       <c r="E112" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F112" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="G112" t="s">
-        <v>52</v>
+        <v>444</v>
       </c>
       <c r="H112" s="2">
-        <v>45798</v>
+        <v>45797</v>
       </c>
       <c r="I112" s="3">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J112" t="s">
         <v>53</v>
       </c>
       <c r="K112" t="s">
-        <v>447</v>
-      </c>
-      <c r="L112" s="2">
-        <v>45574</v>
-      </c>
-      <c r="M112" s="3">
-        <v>811</v>
-      </c>
-      <c r="O112" t="s">
-        <v>60</v>
-      </c>
-      <c r="P112" s="2">
-        <v>46313</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>448</v>
-      </c>
-      <c r="R112" s="2">
-        <v>45786</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="M112" s="3"/>
       <c r="S112" s="2">
-        <v>45218</v>
-      </c>
-      <c r="T112" s="3"/>
-      <c r="U112" s="3">
-        <v>101</v>
-      </c>
+        <v>46523</v>
+      </c>
+      <c r="T112" s="3">
+        <v>310</v>
+      </c>
+      <c r="U112" s="3"/>
       <c r="V112" s="4">
-        <v>10934411.34</v>
+        <v>9152353</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B113" t="s">
+        <v>446</v>
+      </c>
+      <c r="C113" s="2">
+        <v>44763</v>
+      </c>
+      <c r="D113" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113" t="s">
+        <v>447</v>
+      </c>
+      <c r="F113" t="s">
+        <v>43</v>
+      </c>
+      <c r="G113" t="s">
+        <v>52</v>
+      </c>
+      <c r="H113" s="2">
+        <v>45798</v>
+      </c>
+      <c r="I113" s="3">
+        <v>415</v>
+      </c>
+      <c r="J113" t="s">
+        <v>53</v>
+      </c>
+      <c r="K113" t="s">
+        <v>448</v>
+      </c>
+      <c r="L113" s="2">
+        <v>45574</v>
+      </c>
+      <c r="M113" s="3">
+        <v>811</v>
+      </c>
+      <c r="O113" t="s">
+        <v>60</v>
+      </c>
+      <c r="P113" s="2">
+        <v>46313</v>
+      </c>
+      <c r="Q113" t="s">
         <v>449</v>
       </c>
-      <c r="C113" s="2">
-        <v>45014</v>
-      </c>
-      <c r="D113" t="s">
-        <v>45</v>
-      </c>
-      <c r="E113" t="s">
-        <v>450</v>
-      </c>
-      <c r="F113" t="s">
-        <v>451</v>
-      </c>
-      <c r="G113" t="s">
-        <v>452</v>
-      </c>
-      <c r="H113" s="2">
-        <v>46211</v>
-      </c>
-      <c r="I113" s="3">
-        <v>1</v>
-      </c>
-      <c r="J113" t="s">
-        <v>270</v>
-      </c>
-      <c r="K113" t="s">
-        <v>453</v>
-      </c>
-      <c r="L113" s="2">
-        <v>45148</v>
-      </c>
-      <c r="M113" s="3">
-        <v>134</v>
-      </c>
-      <c r="O113" t="s">
-        <v>350</v>
-      </c>
-      <c r="P113" s="2">
-        <v>46609</v>
+      <c r="R113" s="2">
+        <v>45786</v>
       </c>
       <c r="S113" s="2">
-        <v>45518</v>
+        <v>45218</v>
       </c>
       <c r="T113" s="3"/>
       <c r="U113" s="3">
-        <v>397</v>
+        <v>100</v>
       </c>
       <c r="V113" s="4">
-        <v>17946403.739999998</v>
+        <v>10934411.34</v>
       </c>
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>454</v>
+        <v>26</v>
       </c>
       <c r="B114" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C114" s="2">
-        <v>45666</v>
+        <v>45014</v>
       </c>
       <c r="D114" t="s">
         <v>45</v>
       </c>
       <c r="E114" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F114" t="s">
-        <v>417</v>
+        <v>452</v>
       </c>
       <c r="G114" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H114" s="2">
-        <v>46174</v>
+        <v>46211</v>
       </c>
       <c r="I114" s="3">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J114" t="s">
-        <v>53</v>
-      </c>
-      <c r="M114" s="3"/>
+        <v>272</v>
+      </c>
+      <c r="K114" t="s">
+        <v>454</v>
+      </c>
+      <c r="L114" s="2">
+        <v>45148</v>
+      </c>
+      <c r="M114" s="3">
+        <v>134</v>
+      </c>
+      <c r="O114" t="s">
+        <v>352</v>
+      </c>
+      <c r="P114" s="2">
+        <v>46609</v>
+      </c>
+      <c r="S114" s="2">
+        <v>45518</v>
+      </c>
       <c r="T114" s="3"/>
-      <c r="U114" s="3"/>
+      <c r="U114" s="3">
+        <v>396</v>
+      </c>
       <c r="V114" s="4">
-        <v>31106553.600000001</v>
+        <v>17946403.739999998</v>
       </c>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="B115" t="s">
+        <v>456</v>
+      </c>
+      <c r="C115" s="2">
+        <v>45666</v>
+      </c>
+      <c r="D115" t="s">
+        <v>45</v>
+      </c>
+      <c r="E115" t="s">
+        <v>457</v>
+      </c>
+      <c r="F115" t="s">
+        <v>418</v>
+      </c>
+      <c r="G115" t="s">
         <v>458</v>
       </c>
-      <c r="C115" s="2">
-        <v>45250</v>
-      </c>
-      <c r="D115" t="s">
-        <v>36</v>
-      </c>
-      <c r="E115" t="s">
-        <v>459</v>
-      </c>
-      <c r="F115" t="s">
-        <v>417</v>
-      </c>
-      <c r="G115" t="s">
-        <v>460</v>
-      </c>
       <c r="H115" s="2">
-        <v>45400</v>
+        <v>46174</v>
       </c>
       <c r="I115" s="3">
-        <v>812</v>
+        <v>39</v>
       </c>
       <c r="J115" t="s">
         <v>53</v>
       </c>
-      <c r="K115" t="s">
-        <v>461</v>
-      </c>
-      <c r="L115" s="2">
-        <v>45401</v>
-      </c>
-      <c r="M115" s="3">
-        <v>151</v>
-      </c>
-      <c r="S115" s="2">
-        <v>47227</v>
-      </c>
-      <c r="T115" s="3">
-        <v>1015</v>
-      </c>
+      <c r="M115" s="3"/>
+      <c r="T115" s="3"/>
       <c r="U115" s="3"/>
       <c r="V115" s="4">
-        <v>41522909.280000001</v>
+        <v>31106553.600000001</v>
       </c>
     </row>
     <row r="116" spans="1:22">
       <c r="A116" t="s">
-        <v>43</v>
+        <v>418</v>
       </c>
       <c r="B116" t="s">
+        <v>459</v>
+      </c>
+      <c r="C116" s="2">
+        <v>45250</v>
+      </c>
+      <c r="D116" t="s">
+        <v>36</v>
+      </c>
+      <c r="E116" t="s">
+        <v>460</v>
+      </c>
+      <c r="F116" t="s">
+        <v>418</v>
+      </c>
+      <c r="G116" t="s">
+        <v>461</v>
+      </c>
+      <c r="H116" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I116" s="3">
+        <v>813</v>
+      </c>
+      <c r="J116" t="s">
+        <v>53</v>
+      </c>
+      <c r="K116" t="s">
         <v>462</v>
       </c>
-      <c r="C116" s="2">
-        <v>44238</v>
-      </c>
-      <c r="D116" t="s">
-        <v>24</v>
-      </c>
-      <c r="E116" t="s">
-        <v>463</v>
-      </c>
-      <c r="F116" t="s">
-        <v>67</v>
-      </c>
-      <c r="G116" t="s">
-        <v>464</v>
-      </c>
-      <c r="H116" s="2">
-        <v>46211</v>
-      </c>
-      <c r="I116" s="3">
-        <v>1</v>
-      </c>
-      <c r="J116" t="s">
-        <v>270</v>
-      </c>
-      <c r="K116" t="s">
-        <v>465</v>
-      </c>
       <c r="L116" s="2">
-        <v>44969</v>
+        <v>45401</v>
       </c>
       <c r="M116" s="3">
-        <v>731</v>
-      </c>
-      <c r="O116" t="s">
-        <v>466</v>
-      </c>
-      <c r="P116" s="2">
-        <v>46798</v>
+        <v>151</v>
       </c>
       <c r="S116" s="2">
-        <v>45886</v>
-      </c>
-      <c r="T116" s="3"/>
-      <c r="U116" s="3">
-        <v>586</v>
-      </c>
+        <v>47227</v>
+      </c>
+      <c r="T116" s="3">
+        <v>1014</v>
+      </c>
+      <c r="U116" s="3"/>
       <c r="V116" s="4">
-        <v>41936400</v>
+        <v>41522909.280000001</v>
       </c>
     </row>
     <row r="117" spans="1:22">
@@ -7097,50 +7083,56 @@
         <v>43</v>
       </c>
       <c r="B117" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C117" s="2">
-        <v>45607</v>
+        <v>44238</v>
       </c>
       <c r="D117" t="s">
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F117" t="s">
-        <v>469</v>
+        <v>67</v>
       </c>
       <c r="G117" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="H117" s="2">
-        <v>45798</v>
+        <v>46211</v>
       </c>
       <c r="I117" s="3">
-        <v>414</v>
+        <v>2</v>
       </c>
       <c r="J117" t="s">
-        <v>53</v>
+        <v>272</v>
       </c>
       <c r="K117" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="L117" s="2">
-        <v>45798</v>
+        <v>44969</v>
       </c>
       <c r="M117" s="3">
-        <v>191</v>
+        <v>731</v>
+      </c>
+      <c r="O117" t="s">
+        <v>467</v>
+      </c>
+      <c r="P117" s="2">
+        <v>46798</v>
       </c>
       <c r="S117" s="2">
-        <v>46712</v>
-      </c>
-      <c r="T117" s="3">
-        <v>500</v>
-      </c>
-      <c r="U117" s="3"/>
+        <v>45886</v>
+      </c>
+      <c r="T117" s="3"/>
+      <c r="U117" s="3">
+        <v>585</v>
+      </c>
       <c r="V117" s="4">
-        <v>50963796</v>
+        <v>41936400</v>
       </c>
     </row>
     <row r="118" spans="1:22">
@@ -7148,36 +7140,87 @@
         <v>43</v>
       </c>
       <c r="B118" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C118" s="2">
-        <v>45664</v>
+        <v>45607</v>
       </c>
       <c r="D118" t="s">
         <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F118" t="s">
-        <v>225</v>
+        <v>470</v>
       </c>
       <c r="G118" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H118" s="2">
-        <v>45958</v>
+        <v>45798</v>
       </c>
       <c r="I118" s="3">
-        <v>254</v>
+        <v>415</v>
       </c>
       <c r="J118" t="s">
-        <v>34</v>
-      </c>
-      <c r="M118" s="3"/>
-      <c r="T118" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="K118" t="s">
+        <v>472</v>
+      </c>
+      <c r="L118" s="2">
+        <v>45798</v>
+      </c>
+      <c r="M118" s="3">
+        <v>191</v>
+      </c>
+      <c r="S118" s="2">
+        <v>46712</v>
+      </c>
+      <c r="T118" s="3">
+        <v>499</v>
+      </c>
       <c r="U118" s="3"/>
       <c r="V118" s="4">
+        <v>50963796</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22">
+      <c r="A119" t="s">
+        <v>43</v>
+      </c>
+      <c r="B119" t="s">
+        <v>473</v>
+      </c>
+      <c r="C119" s="2">
+        <v>45664</v>
+      </c>
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+      <c r="E119" t="s">
+        <v>474</v>
+      </c>
+      <c r="F119" t="s">
+        <v>225</v>
+      </c>
+      <c r="G119" t="s">
+        <v>475</v>
+      </c>
+      <c r="H119" s="2">
+        <v>45958</v>
+      </c>
+      <c r="I119" s="3">
+        <v>255</v>
+      </c>
+      <c r="J119" t="s">
+        <v>34</v>
+      </c>
+      <c r="M119" s="3"/>
+      <c r="T119" s="3"/>
+      <c r="U119" s="3"/>
+      <c r="V119" s="4">
         <v>253382919</v>
       </c>
     </row>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3431EDF-0E43-4347-AF98-CEB0129A2087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE397E0A-729B-4D5A-9985-11C2302166EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="476">
   <si>
     <t>Departamento</t>
   </si>
@@ -111,7 +111,7 @@
     <t>SUSPENSO ATÉ A MUDANÇA DE PRÉDIO</t>
   </si>
   <si>
-    <t>Aquisição</t>
+    <t>Cancelado</t>
   </si>
   <si>
     <t>GESAD</t>
@@ -128,9 +128,6 @@
   <si>
     <t>GRUPO DE TRABALHO :Com base na análise detalhada dos quatro sistemas de gestão hospitalar avaliados, o Sistema AGHUse Bahia é o mais recomendado para a Secretaria de Estado da Saúde de Goiás (SES GO). Dessa forma, a transição para o AGHUse Bahia ocorrerá de forma estruturada, preservando os benefícios conquistados com o Sistema MV e garantindo a continuidade da qualidade administrativa e assistencial em todas as unidades de saúde estaduais.
 Diante do exposto, declaro concluídas as atividades do Grupo de Trabalho. EM 25/11/2024   PROCESSO AQUISIÇÃO PARADO DESDE 13/04/2023</t>
-  </si>
-  <si>
-    <t>Cancelado</t>
   </si>
   <si>
     <t>202400005010660</t>
@@ -840,21 +837,27 @@
     <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS.</t>
   </si>
   <si>
+    <t>Aquisição</t>
+  </si>
+  <si>
     <t>202600005022365</t>
   </si>
   <si>
     <t>SISLOG 121388 GALERA APP</t>
   </si>
   <si>
+    <t>Documentos feitos para nova Contratação galera app falta comprovação de preços praticados e declaração de exclusividade</t>
+  </si>
+  <si>
+    <t>202600005022653</t>
+  </si>
+  <si>
+    <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
+  </si>
+  <si>
     <t>ELABORAÇÃO DE DOD E ETP</t>
   </si>
   <si>
-    <t>202600005022653</t>
-  </si>
-  <si>
-    <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
-  </si>
-  <si>
     <t>202600010023321</t>
   </si>
   <si>
@@ -1011,11 +1014,10 @@
     <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 9</t>
   </si>
   <si>
-    <t>GETEC SUBPEI</t>
-  </si>
-  <si>
-    <t>AGUARDANDO CERTIDÕES.  Prints erro licença adobe (92163676). COMUNICADO A CAMALEON AGUARDANDO RETORNO.
-Despacho 1911 (92656380) AGUARDANDO CONCLUSÃO</t>
+    <t>GAB</t>
+  </si>
+  <si>
+    <t>com vistas à apuração de eventual inexecução contratual, bem como à possível responsabilização da empresa contratada.</t>
   </si>
   <si>
     <t>09/2026</t>
@@ -1131,7 +1133,7 @@
     <t>ACCESS POINT</t>
   </si>
   <si>
-    <t>AGUARDANDO CONCLUSÃO Termo de Adesão 92947741</t>
+    <t>PARA GESTÃO DO CONTRATO</t>
   </si>
   <si>
     <t>202300010002563</t>
@@ -1233,9 +1235,6 @@
     <t>AQUISIÇÃO DE 40 LICENÇAS AUTODESK AEC DA CS CAD CAM LTDA</t>
   </si>
   <si>
-    <t>Para gestão do contrato</t>
-  </si>
-  <si>
     <t>202600010020471</t>
   </si>
   <si>
@@ -1245,7 +1244,7 @@
     <t>SGI</t>
   </si>
   <si>
-    <t>CONTRATO ASSINADO PELO SECRETÁRIO</t>
+    <t>PARA GESTÃO DA GETEC</t>
   </si>
   <si>
     <t>202500010083108</t>
@@ -1290,9 +1289,6 @@
     <t>Novo Termo de Cooperação entre UFG e SES para realização de capacitação continuada em padrão FHIR.</t>
   </si>
   <si>
-    <t>Despacho 92 (92970915) AGUARDANDO CONCLUSÃO</t>
-  </si>
-  <si>
     <t>202400005009120</t>
   </si>
   <si>
@@ -1308,6 +1304,27 @@
     <t>107/2024</t>
   </si>
   <si>
+    <t>202600010062463</t>
+  </si>
+  <si>
+    <t>Ata de Registro de Preços nº 001/2026, gerenciada por esse Egrégio Tribunal de Justiça do Estado de Goiás, cujo objeto contempla o fornecimento de microcomputadores e acessórios.</t>
+  </si>
+  <si>
+    <t>AGUARDANDO RETORNO DE OFICIOS DE SOLICITAÇÃO DE AUTORIZAÇÃO A ADESÃO</t>
+  </si>
+  <si>
+    <t>202500005011774</t>
+  </si>
+  <si>
+    <t>SISLOG 113930 -GLOBAL TI Contratação de solução de Inteligência Artificial (IA). Processo 202500010079078 paralelo CCONT</t>
+  </si>
+  <si>
+    <t>PARA ANÁLISE</t>
+  </si>
+  <si>
+    <t>93/2025</t>
+  </si>
+  <si>
     <t>SUREG</t>
   </si>
   <si>
@@ -1321,18 +1338,6 @@
   </si>
   <si>
     <t>Contrato 84/2025</t>
-  </si>
-  <si>
-    <t>202500005011774</t>
-  </si>
-  <si>
-    <t>SISLOG 113930 - Contratação de solução de Inteligência Artificial (IA). Processo 202500010079078 paralelo CCONT</t>
-  </si>
-  <si>
-    <t>ESTÁ NA SUTIS PARA GESTÃO DO CONTRATO -Contratada: GLOBAL TI+RH SOLUTIONS LTDA.</t>
-  </si>
-  <si>
-    <t>93/2025</t>
   </si>
   <si>
     <t>202400005034261</t>
@@ -1411,13 +1416,6 @@
     <t>FORNECEDOR OTC DOC ORGANIZACAO TECNOLOGIA E CUSTODIA DE DOCUMENTOS. Contratação de empresa especializada em digitalização de documentos</t>
   </si>
   <si>
-    <t>PROCSET</t>
-  </si>
-  <si>
-    <t>PGE manifestando-se pela regularidade jurídica da celebração do 4º Termo Aditivo 
-Despacho 1372 (92975869) aguardando conclusão</t>
-  </si>
-  <si>
     <t>64/2023</t>
   </si>
   <si>
@@ -1451,7 +1449,7 @@
     <t>FORNECEDOR INDRA. Prestação de Serviço de Desenvolvimento de software</t>
   </si>
   <si>
-    <t xml:space="preserve"> Termo Aditivo assinado pelo Secretário.</t>
+    <t>GESTÃO DA GETEC</t>
   </si>
   <si>
     <t>15/2023</t>
@@ -1846,8 +1844,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V119"/>
+  <dimension ref="A1:V120"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
@@ -1943,7 +1949,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -1979,10 +1985,10 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M3" s="3"/>
       <c r="T3" s="3"/>
@@ -1994,31 +2000,31 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2">
         <v>45383</v>
       </c>
       <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2">
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M4" s="3"/>
       <c r="T4" s="3"/>
@@ -2030,31 +2036,31 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2">
         <v>45784</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="2">
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M5" s="3"/>
       <c r="T5" s="3"/>
@@ -2063,41 +2069,41 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
         <v>43</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>43091</v>
       </c>
       <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
         <v>45</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" t="s">
         <v>46</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" t="s">
-        <v>47</v>
       </c>
       <c r="H6" s="2">
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1072</v>
+        <v>1097</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M6" s="3"/>
       <c r="O6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P6" s="2">
         <v>45336</v>
@@ -2111,10 +2117,10 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2">
         <v>43516</v>
@@ -2123,25 +2129,25 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
         <v>51</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>52</v>
       </c>
       <c r="H7" s="2">
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1073</v>
+        <v>1098</v>
       </c>
       <c r="J7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" t="s">
         <v>53</v>
-      </c>
-      <c r="K7" t="s">
-        <v>54</v>
       </c>
       <c r="L7" s="2">
         <v>44047</v>
@@ -2150,7 +2156,7 @@
         <v>531</v>
       </c>
       <c r="O7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7" s="2">
         <v>46023</v>
@@ -2164,10 +2170,10 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2">
         <v>43770</v>
@@ -2176,25 +2182,25 @@
         <v>24</v>
       </c>
       <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
         <v>57</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
-        <v>58</v>
       </c>
       <c r="H8" s="2">
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>1015</v>
+        <v>1040</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L8" s="2">
         <v>44176</v>
@@ -2203,7 +2209,7 @@
         <v>406</v>
       </c>
       <c r="O8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P8" s="2">
         <v>45646</v>
@@ -2217,10 +2223,10 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2">
         <v>43902</v>
@@ -2229,29 +2235,29 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
         <v>62</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" t="s">
-        <v>63</v>
       </c>
       <c r="H9" s="2">
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M9" s="3"/>
       <c r="O9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P9" s="2">
         <v>45794</v>
@@ -2265,10 +2271,10 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2">
         <v>44176</v>
@@ -2277,29 +2283,29 @@
         <v>24</v>
       </c>
       <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
         <v>66</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>67</v>
-      </c>
-      <c r="G10" t="s">
-        <v>68</v>
       </c>
       <c r="H10" s="2">
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>841</v>
+        <v>866</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M10" s="3"/>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P10" s="2">
         <v>45505</v>
@@ -2313,41 +2319,41 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="2">
         <v>44181</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
         <v>72</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" t="s">
-        <v>73</v>
       </c>
       <c r="H11" s="2">
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M11" s="3"/>
       <c r="O11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P11" s="2">
         <v>45499</v>
@@ -2361,37 +2367,37 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="2">
         <v>44448</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12" s="2">
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1233</v>
+        <v>1258</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L12" s="2">
         <v>44727</v>
@@ -2408,10 +2414,10 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="2">
         <v>44628</v>
@@ -2420,25 +2426,25 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
         <v>79</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" t="s">
-        <v>80</v>
       </c>
       <c r="H13" s="2">
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1106</v>
+        <v>1131</v>
       </c>
       <c r="J13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L13" s="2">
         <v>45040</v>
@@ -2455,10 +2461,10 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" s="2">
         <v>44628</v>
@@ -2467,25 +2473,25 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
         <v>82</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" t="s">
-        <v>83</v>
       </c>
       <c r="H14" s="2">
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1059</v>
+        <v>1084</v>
       </c>
       <c r="J14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L14" s="2">
         <v>45040</v>
@@ -2502,10 +2508,10 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2">
         <v>44628</v>
@@ -2514,25 +2520,25 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" t="s">
         <v>85</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" t="s">
-        <v>86</v>
       </c>
       <c r="H15" s="2">
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>1024</v>
+        <v>1049</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L15" s="2">
         <v>45040</v>
@@ -2549,10 +2555,10 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="2">
         <v>44628</v>
@@ -2561,25 +2567,25 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
         <v>88</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" t="s">
-        <v>89</v>
       </c>
       <c r="H16" s="2">
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1068</v>
+        <v>1093</v>
       </c>
       <c r="J16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L16" s="2">
         <v>45040</v>
@@ -2596,10 +2602,10 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="2">
         <v>44628</v>
@@ -2608,25 +2614,25 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
         <v>91</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" t="s">
-        <v>92</v>
       </c>
       <c r="H17" s="2">
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1106</v>
+        <v>1131</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L17" s="2">
         <v>45040</v>
@@ -2643,10 +2649,10 @@
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2">
         <v>44628</v>
@@ -2655,25 +2661,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" t="s">
         <v>94</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>95</v>
-      </c>
-      <c r="G18" t="s">
-        <v>96</v>
       </c>
       <c r="H18" s="2">
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>1005</v>
+        <v>1030</v>
       </c>
       <c r="J18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L18" s="2">
         <v>45040</v>
@@ -2690,10 +2696,10 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2">
         <v>44628</v>
@@ -2702,25 +2708,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" t="s">
         <v>98</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" t="s">
-        <v>99</v>
       </c>
       <c r="H19" s="2">
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1106</v>
+        <v>1131</v>
       </c>
       <c r="J19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L19" s="2">
         <v>45040</v>
@@ -2737,10 +2743,10 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="2">
         <v>44713</v>
@@ -2749,22 +2755,22 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" t="s">
         <v>102</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>103</v>
-      </c>
-      <c r="G20" t="s">
-        <v>104</v>
       </c>
       <c r="H20" s="2">
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1179</v>
+        <v>1204</v>
       </c>
       <c r="J20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M20" s="3"/>
       <c r="T20" s="3"/>
@@ -2773,10 +2779,10 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2">
         <v>44715</v>
@@ -2785,25 +2791,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" t="s">
         <v>106</v>
-      </c>
-      <c r="F21" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" t="s">
-        <v>107</v>
       </c>
       <c r="H21" s="2">
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1061</v>
+        <v>1086</v>
       </c>
       <c r="J21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L21" s="2">
         <v>45112</v>
@@ -2820,37 +2826,37 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2">
         <v>44721</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
         <v>110</v>
-      </c>
-      <c r="F22" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" t="s">
-        <v>111</v>
       </c>
       <c r="H22" s="2">
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1305</v>
+        <v>1330</v>
       </c>
       <c r="J22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L22" s="2">
         <v>44893</v>
@@ -2867,41 +2873,41 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C23" s="2">
         <v>44741</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" t="s">
         <v>114</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>115</v>
-      </c>
-      <c r="G23" t="s">
-        <v>116</v>
       </c>
       <c r="H23" s="2">
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1206</v>
+        <v>1231</v>
       </c>
       <c r="J23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S23" s="2">
         <v>45220</v>
@@ -2912,10 +2918,10 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C24" s="2">
         <v>44883</v>
@@ -2924,22 +2930,22 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" t="s">
         <v>120</v>
-      </c>
-      <c r="F24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" t="s">
-        <v>121</v>
       </c>
       <c r="H24" s="2">
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>1011</v>
+        <v>1036</v>
       </c>
       <c r="J24" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M24" s="3"/>
       <c r="T24" s="3"/>
@@ -2948,10 +2954,10 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" s="2">
         <v>44911</v>
@@ -2960,25 +2966,25 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H25" s="2">
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>987</v>
+        <v>1012</v>
       </c>
       <c r="J25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L25" s="2">
         <v>45217</v>
@@ -2995,10 +3001,10 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C26" s="2">
         <v>44911</v>
@@ -3007,25 +3013,25 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H26" s="2">
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>989</v>
+        <v>1014</v>
       </c>
       <c r="J26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L26" s="2">
         <v>45217</v>
@@ -3042,10 +3048,10 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C27" s="2">
         <v>45229</v>
@@ -3054,25 +3060,25 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" t="s">
         <v>128</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>129</v>
-      </c>
-      <c r="G27" t="s">
-        <v>130</v>
       </c>
       <c r="H27" s="2">
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M27" s="3"/>
       <c r="S27" s="2">
@@ -3084,37 +3090,37 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C28" s="2">
         <v>44949</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" t="s">
         <v>133</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>134</v>
-      </c>
-      <c r="G28" t="s">
-        <v>135</v>
       </c>
       <c r="H28" s="2">
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="J28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L28" s="2">
         <v>45112</v>
@@ -3131,34 +3137,34 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C29" s="2">
         <v>44988</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" t="s">
         <v>138</v>
-      </c>
-      <c r="F29" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" t="s">
-        <v>139</v>
       </c>
       <c r="H29" s="2">
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1170</v>
+        <v>1195</v>
       </c>
       <c r="J29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M29" s="3"/>
       <c r="T29" s="3"/>
@@ -3167,10 +3173,10 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C30" s="2">
         <v>45015</v>
@@ -3179,22 +3185,22 @@
         <v>24</v>
       </c>
       <c r="E30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" t="s">
         <v>141</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>142</v>
-      </c>
-      <c r="G30" t="s">
-        <v>143</v>
       </c>
       <c r="H30" s="2">
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>818</v>
+        <v>843</v>
       </c>
       <c r="J30" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M30" s="3"/>
       <c r="T30" s="3"/>
@@ -3203,10 +3209,10 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C31" s="2">
         <v>45027</v>
@@ -3215,22 +3221,22 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" t="s">
         <v>145</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
-      </c>
-      <c r="G31" t="s">
-        <v>146</v>
       </c>
       <c r="H31" s="2">
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>962</v>
+        <v>987</v>
       </c>
       <c r="J31" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M31" s="3"/>
       <c r="T31" s="3"/>
@@ -3239,37 +3245,37 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C32" s="2">
         <v>45030</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
+        <v>147</v>
+      </c>
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" t="s">
         <v>148</v>
-      </c>
-      <c r="F32" t="s">
-        <v>43</v>
-      </c>
-      <c r="G32" t="s">
-        <v>149</v>
       </c>
       <c r="H32" s="2">
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1038</v>
+        <v>1063</v>
       </c>
       <c r="J32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L32" s="2">
         <v>45161</v>
@@ -3286,10 +3292,10 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C33" s="2">
         <v>45056</v>
@@ -3298,25 +3304,25 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" t="s">
         <v>152</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33" t="s">
-        <v>153</v>
       </c>
       <c r="H33" s="2">
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="J33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L33" s="2">
         <v>45400</v>
@@ -3333,34 +3339,34 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" s="2">
         <v>45056</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s">
         <v>156</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>157</v>
-      </c>
-      <c r="G34" t="s">
-        <v>158</v>
       </c>
       <c r="H34" s="2">
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>961</v>
+        <v>986</v>
       </c>
       <c r="J34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M34" s="3"/>
       <c r="T34" s="3"/>
@@ -3369,10 +3375,10 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C35" s="2">
         <v>45069</v>
@@ -3381,22 +3387,22 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" t="s">
         <v>160</v>
-      </c>
-      <c r="F35" t="s">
-        <v>43</v>
-      </c>
-      <c r="G35" t="s">
-        <v>161</v>
       </c>
       <c r="H35" s="2">
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>946</v>
+        <v>971</v>
       </c>
       <c r="J35" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M35" s="3"/>
       <c r="T35" s="3"/>
@@ -3405,10 +3411,10 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C36" s="2">
         <v>45063</v>
@@ -3417,22 +3423,22 @@
         <v>24</v>
       </c>
       <c r="E36" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" t="s">
         <v>163</v>
-      </c>
-      <c r="F36" t="s">
-        <v>43</v>
-      </c>
-      <c r="G36" t="s">
-        <v>164</v>
       </c>
       <c r="H36" s="2">
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="J36" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M36" s="3"/>
       <c r="T36" s="3"/>
@@ -3441,37 +3447,37 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C37" s="2">
         <v>45063</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H37" s="2">
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>977</v>
+        <v>1002</v>
       </c>
       <c r="J37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L37" s="2">
         <v>45236</v>
@@ -3488,10 +3494,10 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C38" s="2">
         <v>45065</v>
@@ -3500,22 +3506,22 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" t="s">
         <v>169</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>170</v>
-      </c>
-      <c r="G38" t="s">
-        <v>171</v>
       </c>
       <c r="H38" s="2">
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>1004</v>
+        <v>1029</v>
       </c>
       <c r="J38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M38" s="3"/>
       <c r="T38" s="3"/>
@@ -3524,10 +3530,10 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C39" s="2">
         <v>45092</v>
@@ -3536,25 +3542,25 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" t="s">
+        <v>114</v>
+      </c>
+      <c r="G39" t="s">
         <v>173</v>
-      </c>
-      <c r="F39" t="s">
-        <v>115</v>
-      </c>
-      <c r="G39" t="s">
-        <v>174</v>
       </c>
       <c r="H39" s="2">
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="J39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L39" s="2">
         <v>45569</v>
@@ -3563,7 +3569,7 @@
         <v>477</v>
       </c>
       <c r="O39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S39" s="2">
         <v>45805</v>
@@ -3574,10 +3580,10 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C40" s="2">
         <v>45106</v>
@@ -3586,22 +3592,22 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
+        <v>176</v>
+      </c>
+      <c r="F40" t="s">
         <v>177</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>178</v>
-      </c>
-      <c r="G40" t="s">
-        <v>179</v>
       </c>
       <c r="H40" s="2">
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>907</v>
+        <v>932</v>
       </c>
       <c r="J40" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M40" s="3"/>
       <c r="T40" s="3"/>
@@ -3610,37 +3616,37 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C41" s="2">
         <v>45128</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H41" s="2">
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>949</v>
+        <v>974</v>
       </c>
       <c r="J41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L41" s="2">
         <v>45229</v>
@@ -3657,10 +3663,10 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2">
         <v>45307</v>
@@ -3669,22 +3675,22 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" t="s">
+        <v>42</v>
+      </c>
+      <c r="G42" t="s">
         <v>184</v>
-      </c>
-      <c r="F42" t="s">
-        <v>43</v>
-      </c>
-      <c r="G42" t="s">
-        <v>185</v>
       </c>
       <c r="H42" s="2">
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>787</v>
+        <v>812</v>
       </c>
       <c r="J42" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M42" s="3"/>
       <c r="T42" s="3"/>
@@ -3693,10 +3699,10 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C43" s="2">
         <v>45359</v>
@@ -3705,22 +3711,22 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
+        <v>186</v>
+      </c>
+      <c r="F43" t="s">
+        <v>177</v>
+      </c>
+      <c r="G43" t="s">
         <v>187</v>
-      </c>
-      <c r="F43" t="s">
-        <v>178</v>
-      </c>
-      <c r="G43" t="s">
-        <v>188</v>
       </c>
       <c r="H43" s="2">
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>854</v>
+        <v>879</v>
       </c>
       <c r="J43" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M43" s="3"/>
       <c r="T43" s="3"/>
@@ -3729,37 +3735,37 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C44" s="2">
         <v>45408</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E44" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" t="s">
+        <v>42</v>
+      </c>
+      <c r="G44" t="s">
         <v>190</v>
-      </c>
-      <c r="F44" t="s">
-        <v>43</v>
-      </c>
-      <c r="G44" t="s">
-        <v>191</v>
       </c>
       <c r="H44" s="2">
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="J44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L44" s="2">
         <v>45624</v>
@@ -3773,37 +3779,37 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C45" s="2">
         <v>45394</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G45" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H45" s="2">
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="J45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M45" s="3"/>
       <c r="S45" s="2">
@@ -3815,10 +3821,10 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C46" s="2">
         <v>45456</v>
@@ -3827,25 +3833,25 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H46" s="2">
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="J46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M46" s="3"/>
       <c r="S46" s="2">
@@ -3857,37 +3863,37 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C47" s="2">
         <v>45395</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
+        <v>199</v>
+      </c>
+      <c r="F47" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" t="s">
         <v>200</v>
-      </c>
-      <c r="F47" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" t="s">
-        <v>201</v>
       </c>
       <c r="H47" s="2">
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="J47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L47" s="2">
         <v>45548</v>
@@ -3899,44 +3905,44 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1165</v>
+        <v>1140</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C48" s="2">
         <v>45395</v>
       </c>
       <c r="D48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G48" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H48" s="2">
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="J48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L48" s="2">
         <v>45530</v>
@@ -3945,7 +3951,7 @@
         <v>135</v>
       </c>
       <c r="N48" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S48" s="2">
         <v>45720</v>
@@ -3956,37 +3962,37 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C49" s="2">
         <v>45395</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H49" s="2">
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="J49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K49" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L49" s="2">
         <v>45517</v>
@@ -3998,44 +4004,44 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1130</v>
+        <v>1105</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C50" s="2">
         <v>45400</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H50" s="2">
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="J50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L50" s="2">
         <v>45580</v>
@@ -4049,10 +4055,10 @@
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C51" s="2">
         <v>45553</v>
@@ -4061,22 +4067,22 @@
         <v>24</v>
       </c>
       <c r="E51" t="s">
+        <v>214</v>
+      </c>
+      <c r="F51" t="s">
         <v>215</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>216</v>
-      </c>
-      <c r="G51" t="s">
-        <v>217</v>
       </c>
       <c r="H51" s="2">
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="J51" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M51" s="3"/>
       <c r="T51" s="3"/>
@@ -4085,34 +4091,34 @@
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C52" s="2">
         <v>45516</v>
       </c>
       <c r="D52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E52" t="s">
+        <v>218</v>
+      </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" t="s">
         <v>219</v>
-      </c>
-      <c r="F52" t="s">
-        <v>43</v>
-      </c>
-      <c r="G52" t="s">
-        <v>220</v>
       </c>
       <c r="H52" s="2">
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="J52" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M52" s="3"/>
       <c r="T52" s="3"/>
@@ -4121,34 +4127,34 @@
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C53" s="2">
         <v>45701</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E53" t="s">
+        <v>221</v>
+      </c>
+      <c r="F53" t="s">
         <v>222</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>223</v>
-      </c>
-      <c r="G53" t="s">
-        <v>224</v>
       </c>
       <c r="H53" s="2">
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="J53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M53" s="3"/>
       <c r="T53" s="3"/>
@@ -4157,37 +4163,37 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" t="s">
         <v>225</v>
-      </c>
-      <c r="B54" t="s">
-        <v>226</v>
       </c>
       <c r="C54" s="2">
         <v>45308</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" t="s">
+        <v>226</v>
+      </c>
+      <c r="F54" t="s">
+        <v>224</v>
+      </c>
+      <c r="G54" t="s">
         <v>227</v>
-      </c>
-      <c r="F54" t="s">
-        <v>225</v>
-      </c>
-      <c r="G54" t="s">
-        <v>228</v>
       </c>
       <c r="H54" s="2">
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="J54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L54" s="2">
         <v>45408</v>
@@ -4207,31 +4213,31 @@
         <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C55" s="2">
         <v>45051</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" t="s">
+        <v>230</v>
+      </c>
+      <c r="F55" t="s">
         <v>231</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>232</v>
-      </c>
-      <c r="G55" t="s">
-        <v>233</v>
       </c>
       <c r="H55" s="2">
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="J55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M55" s="3"/>
       <c r="T55" s="3"/>
@@ -4243,7 +4249,7 @@
         <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C56" s="2">
         <v>45016</v>
@@ -4252,22 +4258,22 @@
         <v>24</v>
       </c>
       <c r="E56" t="s">
+        <v>234</v>
+      </c>
+      <c r="F56" t="s">
         <v>235</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>236</v>
-      </c>
-      <c r="G56" t="s">
-        <v>237</v>
       </c>
       <c r="H56" s="2">
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>994</v>
+        <v>1019</v>
       </c>
       <c r="J56" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M56" s="3"/>
       <c r="T56" s="3"/>
@@ -4279,7 +4285,7 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C57" s="2">
         <v>45016</v>
@@ -4288,22 +4294,22 @@
         <v>24</v>
       </c>
       <c r="E57" t="s">
+        <v>238</v>
+      </c>
+      <c r="F57" t="s">
+        <v>133</v>
+      </c>
+      <c r="G57" t="s">
         <v>239</v>
-      </c>
-      <c r="F57" t="s">
-        <v>134</v>
-      </c>
-      <c r="G57" t="s">
-        <v>240</v>
       </c>
       <c r="H57" s="2">
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>898</v>
+        <v>923</v>
       </c>
       <c r="J57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M57" s="3"/>
       <c r="T57" s="3"/>
@@ -4315,31 +4321,31 @@
         <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C58" s="2">
         <v>45251</v>
       </c>
       <c r="D58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E58" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H58" s="2">
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>914</v>
+        <v>939</v>
       </c>
       <c r="J58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M58" s="3"/>
       <c r="T58" s="3"/>
@@ -4351,31 +4357,31 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C59" s="2">
         <v>45314</v>
       </c>
       <c r="D59" t="s">
+        <v>244</v>
+      </c>
+      <c r="E59" t="s">
         <v>245</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>246</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>247</v>
-      </c>
-      <c r="G59" t="s">
-        <v>248</v>
       </c>
       <c r="H59" s="2">
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>751</v>
+        <v>776</v>
       </c>
       <c r="J59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M59" s="3"/>
       <c r="T59" s="3"/>
@@ -4387,7 +4393,7 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C60" s="2">
         <v>45216</v>
@@ -4396,25 +4402,25 @@
         <v>24</v>
       </c>
       <c r="E60" t="s">
+        <v>249</v>
+      </c>
+      <c r="F60" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" t="s">
         <v>250</v>
-      </c>
-      <c r="F60" t="s">
-        <v>43</v>
-      </c>
-      <c r="G60" t="s">
-        <v>251</v>
       </c>
       <c r="H60" s="2">
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="J60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K60" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L60" s="2">
         <v>45475</v>
@@ -4426,7 +4432,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1088</v>
+        <v>1063</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4436,7 +4442,7 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C61" s="2">
         <v>45742</v>
@@ -4445,22 +4451,22 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
+        <v>253</v>
+      </c>
+      <c r="F61" t="s">
         <v>254</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>255</v>
-      </c>
-      <c r="G61" t="s">
-        <v>256</v>
       </c>
       <c r="H61" s="2">
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="J61" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M61" s="3"/>
       <c r="T61" s="3"/>
@@ -4472,31 +4478,31 @@
         <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C62" s="2">
         <v>45734</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E62" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H62" s="2">
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="J62" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M62" s="3"/>
       <c r="T62" s="3"/>
@@ -4508,7 +4514,7 @@
         <v>26</v>
       </c>
       <c r="B63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C63" s="2">
         <v>46162</v>
@@ -4517,22 +4523,22 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H63" s="2">
         <v>46197</v>
       </c>
       <c r="I63" s="3">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="J63" t="s">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="M63" s="3"/>
       <c r="T63" s="3"/>
@@ -4550,7 +4556,7 @@
         <v>46210</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E64" t="s">
         <v>264</v>
@@ -4562,13 +4568,13 @@
         <v>265</v>
       </c>
       <c r="H64" s="2">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="I64" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="J64" t="s">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="M64" s="3"/>
       <c r="T64" s="3"/>
@@ -4595,16 +4601,16 @@
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H65" s="2">
         <v>46211</v>
       </c>
       <c r="I65" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="J65" t="s">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
@@ -4616,31 +4622,31 @@
         <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C66" s="2">
         <v>46126</v>
       </c>
       <c r="D66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F66" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H66" s="2">
         <v>46182</v>
       </c>
       <c r="I66" s="3">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="J66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
@@ -4649,34 +4655,34 @@
     </row>
     <row r="67" spans="1:22">
       <c r="A67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2">
         <v>46136</v>
       </c>
       <c r="D67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E67" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H67" s="2">
         <v>46156</v>
       </c>
       <c r="I67" s="3">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M67" s="3"/>
       <c r="T67" s="3"/>
@@ -4687,34 +4693,34 @@
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C68" s="2">
         <v>46135</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H68" s="2">
         <v>46155</v>
       </c>
       <c r="I68" s="3">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="J68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M68" s="3"/>
       <c r="T68" s="3"/>
@@ -4725,34 +4731,34 @@
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C69" s="2">
         <v>46136</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E69" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H69" s="2">
         <v>46157</v>
       </c>
       <c r="I69" s="3">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="J69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M69" s="3"/>
       <c r="T69" s="3"/>
@@ -4763,10 +4769,10 @@
     </row>
     <row r="70" spans="1:22">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2">
         <v>45804</v>
@@ -4775,22 +4781,22 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H70" s="2">
         <v>45943</v>
       </c>
       <c r="I70" s="3">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="J70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M70" s="3"/>
       <c r="T70" s="3"/>
@@ -4801,10 +4807,10 @@
     </row>
     <row r="71" spans="1:22">
       <c r="A71" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C71" s="2">
         <v>45513</v>
@@ -4813,25 +4819,25 @@
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F71" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G71" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H71" s="2">
         <v>45715</v>
       </c>
       <c r="I71" s="3">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="J71" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L71" s="2">
         <v>45712</v>
@@ -4850,10 +4856,10 @@
     </row>
     <row r="72" spans="1:22">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C72" s="2">
         <v>45659</v>
@@ -4862,25 +4868,25 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F72" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H72" s="2">
         <v>45817</v>
       </c>
       <c r="I72" s="3">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="J72" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L72" s="2">
         <v>45812</v>
@@ -4892,7 +4898,7 @@
         <v>46909</v>
       </c>
       <c r="T72" s="3">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="U72" s="3"/>
       <c r="V72" s="4">
@@ -4901,37 +4907,37 @@
     </row>
     <row r="73" spans="1:22">
       <c r="A73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C73" s="2">
         <v>45492</v>
       </c>
       <c r="D73" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G73" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H73" s="2">
         <v>45911</v>
       </c>
       <c r="I73" s="3">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="J73" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K73" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L73" s="2">
         <v>45546</v>
@@ -4940,7 +4946,7 @@
         <v>54</v>
       </c>
       <c r="O73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P73" s="2">
         <v>45966</v>
@@ -4956,31 +4962,31 @@
         <v>26</v>
       </c>
       <c r="B74" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C74" s="2">
         <v>45786</v>
       </c>
       <c r="D74" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F74" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H74" s="2">
         <v>45895</v>
       </c>
       <c r="I74" s="3">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="J74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M74" s="3"/>
       <c r="T74" s="3"/>
@@ -4991,10 +4997,10 @@
     </row>
     <row r="75" spans="1:22">
       <c r="A75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C75" s="2">
         <v>45946</v>
@@ -5003,22 +5009,22 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F75" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H75" s="2">
         <v>46196</v>
       </c>
       <c r="I75" s="3">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J75" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M75" s="3"/>
       <c r="T75" s="3"/>
@@ -5029,37 +5035,37 @@
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B76" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2">
         <v>45665</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H76" s="2">
         <v>46198</v>
       </c>
       <c r="I76" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L76" s="2">
         <v>46071</v>
@@ -5068,7 +5074,7 @@
         <v>406</v>
       </c>
       <c r="O76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P76" s="2">
         <v>46294</v>
@@ -5078,7 +5084,7 @@
       </c>
       <c r="T76" s="3"/>
       <c r="U76" s="3">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="V76" s="4">
         <v>51071</v>
@@ -5086,10 +5092,10 @@
     </row>
     <row r="77" spans="1:22">
       <c r="A77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C77" s="2">
         <v>43902</v>
@@ -5098,25 +5104,25 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H77" s="2">
         <v>45790</v>
       </c>
       <c r="I77" s="3">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="J77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K77" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L77" s="2">
         <v>43964</v>
@@ -5125,7 +5131,7 @@
         <v>62</v>
       </c>
       <c r="O77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P77" s="2">
         <v>46160</v>
@@ -5141,10 +5147,10 @@
     </row>
     <row r="78" spans="1:22">
       <c r="A78" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C78" s="2">
         <v>45915</v>
@@ -5153,25 +5159,25 @@
         <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H78" s="2">
         <v>46094</v>
       </c>
       <c r="I78" s="3">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="J78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L78" s="2">
         <v>46086</v>
@@ -5183,7 +5189,7 @@
         <v>47181</v>
       </c>
       <c r="T78" s="3">
-        <v>968</v>
+        <v>943</v>
       </c>
       <c r="U78" s="3"/>
       <c r="V78" s="4">
@@ -5192,37 +5198,37 @@
     </row>
     <row r="79" spans="1:22">
       <c r="A79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C79" s="2">
         <v>45950</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E79" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G79" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H79" s="2">
         <v>45975</v>
       </c>
       <c r="I79" s="3">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="J79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L79" s="2">
         <v>45978</v>
@@ -5231,7 +5237,7 @@
         <v>28</v>
       </c>
       <c r="O79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P79" s="2">
         <v>46220</v>
@@ -5239,22 +5245,18 @@
       <c r="S79" s="2">
         <v>46220</v>
       </c>
-      <c r="T79" s="3">
-        <v>7</v>
-      </c>
-      <c r="U79" s="3">
-        <v>7</v>
-      </c>
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
       <c r="V79" s="4">
         <v>71722</v>
       </c>
     </row>
     <row r="80" spans="1:22">
       <c r="A80" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C80" s="2">
         <v>45915</v>
@@ -5263,25 +5265,25 @@
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F80" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H80" s="2">
-        <v>46205</v>
+        <v>46237</v>
       </c>
       <c r="I80" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L80" s="2">
         <v>46086</v>
@@ -5293,7 +5295,7 @@
         <v>47181</v>
       </c>
       <c r="T80" s="3">
-        <v>968</v>
+        <v>943</v>
       </c>
       <c r="U80" s="3"/>
       <c r="V80" s="4">
@@ -5302,10 +5304,10 @@
     </row>
     <row r="81" spans="1:22">
       <c r="A81" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C81" s="2">
         <v>45915</v>
@@ -5314,25 +5316,25 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F81" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H81" s="2">
         <v>46094</v>
       </c>
       <c r="I81" s="3">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="J81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L81" s="2">
         <v>46086</v>
@@ -5344,7 +5346,7 @@
         <v>47181</v>
       </c>
       <c r="T81" s="3">
-        <v>968</v>
+        <v>943</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
@@ -5353,10 +5355,10 @@
     </row>
     <row r="82" spans="1:22">
       <c r="A82" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C82" s="2">
         <v>43902</v>
@@ -5365,25 +5367,25 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F82" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G82" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H82" s="2">
         <v>45790</v>
       </c>
       <c r="I82" s="3">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="J82" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K82" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L82" s="2">
         <v>43964</v>
@@ -5392,7 +5394,7 @@
         <v>62</v>
       </c>
       <c r="O82" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P82" s="2">
         <v>46160</v>
@@ -5408,37 +5410,37 @@
     </row>
     <row r="83" spans="1:22">
       <c r="A83" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B83" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C83" s="2">
         <v>45819</v>
       </c>
       <c r="D83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E83" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F83" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G83" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H83" s="2">
         <v>46170</v>
       </c>
       <c r="I83" s="3">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="J83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K83" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L83" s="2">
         <v>45904</v>
@@ -5450,7 +5452,7 @@
         <v>46273</v>
       </c>
       <c r="T83" s="3">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
@@ -5459,10 +5461,10 @@
     </row>
     <row r="84" spans="1:22">
       <c r="A84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C84" s="2">
         <v>45952</v>
@@ -5471,25 +5473,25 @@
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F84" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G84" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H84" s="2">
         <v>46087</v>
       </c>
       <c r="I84" s="3">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="J84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K84" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L84" s="2">
         <v>46086</v>
@@ -5501,7 +5503,7 @@
         <v>47910</v>
       </c>
       <c r="T84" s="3">
-        <v>1697</v>
+        <v>1672</v>
       </c>
       <c r="U84" s="3"/>
       <c r="V84" s="4">
@@ -5510,37 +5512,37 @@
     </row>
     <row r="85" spans="1:22">
       <c r="A85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B85" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C85" s="2">
         <v>45775</v>
       </c>
       <c r="D85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E85" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G85" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H85" s="2">
         <v>45861</v>
       </c>
       <c r="I85" s="3">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="J85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K85" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L85" s="2">
         <v>45856</v>
@@ -5551,9 +5553,7 @@
       <c r="S85" s="2">
         <v>46225</v>
       </c>
-      <c r="T85" s="3">
-        <v>12</v>
-      </c>
+      <c r="T85" s="3"/>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
         <v>288862</v>
@@ -5561,34 +5561,34 @@
     </row>
     <row r="86" spans="1:22">
       <c r="A86" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B86" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C86" s="2">
         <v>45539</v>
       </c>
       <c r="D86" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F86" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G86" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H86" s="2">
         <v>45607</v>
       </c>
       <c r="I86" s="3">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="J86" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M86" s="3"/>
       <c r="T86" s="3"/>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="87" spans="1:22">
       <c r="A87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C87" s="2">
         <v>45840</v>
@@ -5611,25 +5611,25 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F87" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G87" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H87" s="2">
         <v>46002</v>
       </c>
       <c r="I87" s="3">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="J87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K87" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L87" s="2">
         <v>46001</v>
@@ -5641,7 +5641,7 @@
         <v>47097</v>
       </c>
       <c r="T87" s="3">
-        <v>884</v>
+        <v>859</v>
       </c>
       <c r="U87" s="3"/>
       <c r="V87" s="4">
@@ -5650,10 +5650,10 @@
     </row>
     <row r="88" spans="1:22">
       <c r="A88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C88" s="2">
         <v>45868</v>
@@ -5662,25 +5662,25 @@
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H88" s="2">
         <v>46146</v>
       </c>
       <c r="I88" s="3">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="J88" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L88" s="2">
         <v>46077</v>
@@ -5692,7 +5692,7 @@
         <v>47905</v>
       </c>
       <c r="T88" s="3">
-        <v>1692</v>
+        <v>1667</v>
       </c>
       <c r="U88" s="3"/>
       <c r="V88" s="4">
@@ -5701,10 +5701,10 @@
     </row>
     <row r="89" spans="1:22">
       <c r="A89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C89" s="2">
         <v>44370</v>
@@ -5713,25 +5713,25 @@
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G89" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H89" s="2">
         <v>45881</v>
       </c>
       <c r="I89" s="3">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="J89" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L89" s="2">
         <v>44589</v>
@@ -5740,7 +5740,7 @@
         <v>219</v>
       </c>
       <c r="O89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P89" s="2">
         <v>46419</v>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="T89" s="3"/>
       <c r="U89" s="3">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="V89" s="4">
         <v>374899.96</v>
@@ -5758,37 +5758,37 @@
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C90" s="2">
         <v>45422</v>
       </c>
       <c r="D90" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E90" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G90" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H90" s="2">
         <v>45624</v>
       </c>
       <c r="I90" s="3">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="J90" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K90" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L90" s="2">
         <v>45544</v>
@@ -5810,31 +5810,31 @@
         <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C91" s="2">
         <v>46038</v>
       </c>
       <c r="D91" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E91" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F91" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="G91" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H91" s="2">
-        <v>46210</v>
+        <v>46237</v>
       </c>
       <c r="I91" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="M91" s="3"/>
       <c r="T91" s="3"/>
@@ -5848,34 +5848,34 @@
         <v>29</v>
       </c>
       <c r="B92" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C92" s="2">
         <v>44939</v>
       </c>
       <c r="D92" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E92" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F92" t="s">
         <v>29</v>
       </c>
       <c r="G92" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H92" s="2">
         <v>45979</v>
       </c>
       <c r="I92" s="3">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="J92" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K92" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L92" s="2">
         <v>45968</v>
@@ -5884,7 +5884,7 @@
         <v>1029</v>
       </c>
       <c r="O92" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P92" s="2">
         <v>46426</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="T92" s="3"/>
       <c r="U92" s="3">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="V92" s="4">
         <v>706431.6</v>
@@ -5902,10 +5902,10 @@
     </row>
     <row r="93" spans="1:22">
       <c r="A93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C93" s="2">
         <v>45673</v>
@@ -5914,32 +5914,32 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F93" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G93" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H93" s="2">
         <v>46140</v>
       </c>
       <c r="I93" s="3">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="J93" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K93" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M93" s="3"/>
       <c r="S93" s="2">
         <v>46598</v>
       </c>
       <c r="T93" s="3">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="U93" s="3"/>
       <c r="V93" s="4">
@@ -5948,10 +5948,10 @@
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C94" s="2">
         <v>45215</v>
@@ -5960,25 +5960,25 @@
         <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F94" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G94" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H94" s="2">
         <v>45687</v>
       </c>
       <c r="I94" s="3">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="J94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K94" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L94" s="2">
         <v>45685</v>
@@ -5990,7 +5990,7 @@
         <v>46780</v>
       </c>
       <c r="T94" s="3">
-        <v>567</v>
+        <v>542</v>
       </c>
       <c r="U94" s="3"/>
       <c r="V94" s="4">
@@ -5999,37 +5999,37 @@
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C95" s="2">
         <v>45366</v>
       </c>
       <c r="D95" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E95" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G95" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H95" s="2">
         <v>45481</v>
       </c>
       <c r="I95" s="3">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="J95" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K95" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L95" s="2">
         <v>45471</v>
@@ -6041,7 +6041,7 @@
         <v>47301</v>
       </c>
       <c r="T95" s="3">
-        <v>1088</v>
+        <v>1063</v>
       </c>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
@@ -6053,34 +6053,34 @@
         <v>26</v>
       </c>
       <c r="B96" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C96" s="2">
         <v>45152</v>
       </c>
       <c r="D96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E96" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F96" t="s">
         <v>29</v>
       </c>
       <c r="G96" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H96" s="2">
         <v>45440</v>
       </c>
       <c r="I96" s="3">
-        <v>773</v>
+        <v>798</v>
       </c>
       <c r="J96" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K96" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L96" s="2">
         <v>45303</v>
@@ -6099,37 +6099,37 @@
     </row>
     <row r="97" spans="1:22">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C97" s="2">
         <v>45373</v>
       </c>
       <c r="D97" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E97" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F97" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G97" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H97" s="2">
         <v>45492</v>
       </c>
       <c r="I97" s="3">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="J97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K97" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L97" s="2">
         <v>45492</v>
@@ -6141,7 +6141,7 @@
         <v>46587</v>
       </c>
       <c r="T97" s="3">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
@@ -6150,10 +6150,10 @@
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C98" s="2">
         <v>44663</v>
@@ -6162,25 +6162,25 @@
         <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G98" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H98" s="2">
         <v>45588</v>
       </c>
       <c r="I98" s="3">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="J98" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K98" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L98" s="2">
         <v>44893</v>
@@ -6189,7 +6189,7 @@
         <v>230</v>
       </c>
       <c r="O98" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P98" s="2">
         <v>45996</v>
@@ -6205,10 +6205,10 @@
     </row>
     <row r="99" spans="1:22">
       <c r="A99" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C99" s="2">
         <v>45826</v>
@@ -6217,25 +6217,25 @@
         <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F99" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G99" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H99" s="2">
         <v>46079</v>
       </c>
       <c r="I99" s="3">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="J99" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K99" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L99" s="2">
         <v>46076</v>
@@ -6247,7 +6247,7 @@
         <v>47903</v>
       </c>
       <c r="T99" s="3">
-        <v>1690</v>
+        <v>1665</v>
       </c>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
@@ -6256,34 +6256,34 @@
     </row>
     <row r="100" spans="1:22">
       <c r="A100" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C100" s="2">
         <v>46150</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E100" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F100" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G100" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="H100" s="2">
         <v>46206</v>
       </c>
       <c r="I100" s="3">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J100" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M100" s="3"/>
       <c r="T100" s="3"/>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="101" spans="1:22">
       <c r="A101" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B101" t="s">
         <v>394</v>
@@ -6303,7 +6303,7 @@
         <v>46094</v>
       </c>
       <c r="D101" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E101" t="s">
         <v>395</v>
@@ -6315,13 +6315,13 @@
         <v>397</v>
       </c>
       <c r="H101" s="2">
-        <v>46199</v>
+        <v>46211</v>
       </c>
       <c r="I101" s="3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J101" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="M101" s="3"/>
       <c r="T101" s="3"/>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B102" t="s">
         <v>398</v>
@@ -6341,13 +6341,13 @@
         <v>45950</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E102" t="s">
         <v>399</v>
       </c>
       <c r="F102" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G102" t="s">
         <v>400</v>
@@ -6356,10 +6356,10 @@
         <v>45988</v>
       </c>
       <c r="I102" s="3">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="J102" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K102" t="s">
         <v>401</v>
@@ -6374,7 +6374,7 @@
         <v>46343</v>
       </c>
       <c r="T102" s="3">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
@@ -6383,7 +6383,7 @@
     </row>
     <row r="103" spans="1:22">
       <c r="A103" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B103" t="s">
         <v>402</v>
@@ -6407,10 +6407,10 @@
         <v>45786</v>
       </c>
       <c r="I103" s="3">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="J103" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K103" t="s">
         <v>405</v>
@@ -6438,13 +6438,13 @@
         <v>45848</v>
       </c>
       <c r="D104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E104" t="s">
         <v>407</v>
       </c>
       <c r="F104" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G104" t="s">
         <v>408</v>
@@ -6453,10 +6453,10 @@
         <v>46014</v>
       </c>
       <c r="I104" s="3">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="J104" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K104" t="s">
         <v>409</v>
@@ -6471,7 +6471,7 @@
         <v>46373</v>
       </c>
       <c r="T104" s="3">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
@@ -6489,25 +6489,25 @@
         <v>46030</v>
       </c>
       <c r="D105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E105" t="s">
         <v>411</v>
       </c>
       <c r="F105" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G105" t="s">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="H105" s="2">
-        <v>46211</v>
+        <v>46237</v>
       </c>
       <c r="I105" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="M105" s="3"/>
       <c r="T105" s="3"/>
@@ -6518,37 +6518,37 @@
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C106" s="2">
         <v>45365</v>
       </c>
       <c r="D106" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E106" t="s">
+        <v>413</v>
+      </c>
+      <c r="F106" t="s">
         <v>414</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>415</v>
-      </c>
-      <c r="G106" t="s">
-        <v>416</v>
       </c>
       <c r="H106" s="2">
         <v>45568</v>
       </c>
       <c r="I106" s="3">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="J106" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L106" s="2">
         <v>45567</v>
@@ -6560,7 +6560,7 @@
         <v>46479</v>
       </c>
       <c r="T106" s="3">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
@@ -6569,48 +6569,40 @@
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
+        <v>42</v>
+      </c>
+      <c r="B107" t="s">
+        <v>417</v>
+      </c>
+      <c r="C107" s="2">
+        <v>46232</v>
+      </c>
+      <c r="D107" t="s">
+        <v>44</v>
+      </c>
+      <c r="E107" t="s">
         <v>418</v>
       </c>
-      <c r="B107" t="s">
+      <c r="F107" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" t="s">
         <v>419</v>
       </c>
-      <c r="C107" s="2">
-        <v>45526</v>
-      </c>
-      <c r="D107" t="s">
-        <v>36</v>
-      </c>
-      <c r="E107" t="s">
-        <v>420</v>
-      </c>
-      <c r="F107" t="s">
-        <v>418</v>
-      </c>
-      <c r="G107" t="s">
-        <v>421</v>
-      </c>
       <c r="H107" s="2">
-        <v>45932</v>
+        <v>46237</v>
       </c>
       <c r="I107" s="3">
-        <v>281</v>
+        <v>1</v>
       </c>
       <c r="J107" t="s">
-        <v>53</v>
-      </c>
-      <c r="K107" t="s">
-        <v>422</v>
+        <v>262</v>
       </c>
       <c r="M107" s="3"/>
-      <c r="S107" s="2">
-        <v>47748</v>
-      </c>
-      <c r="T107" s="3">
-        <v>1535</v>
-      </c>
+      <c r="T107" s="3"/>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
-        <v>4440928.34</v>
+        <v>3446570</v>
       </c>
     </row>
     <row r="108" spans="1:22">
@@ -6618,7 +6610,7 @@
         <v>26</v>
       </c>
       <c r="B108" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C108" s="2">
         <v>45824</v>
@@ -6627,25 +6619,25 @@
         <v>24</v>
       </c>
       <c r="E108" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F108" t="s">
-        <v>26</v>
+        <v>222</v>
       </c>
       <c r="G108" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H108" s="2">
-        <v>45958</v>
+        <v>46237</v>
       </c>
       <c r="I108" s="3">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>53</v>
+        <v>273</v>
       </c>
       <c r="K108" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="L108" s="2">
         <v>45951</v>
@@ -6657,570 +6649,616 @@
         <v>46316</v>
       </c>
       <c r="T108" s="3">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="U108" s="3"/>
       <c r="V108" s="4">
-        <v>5192424.24</v>
+        <v>4130258.58</v>
       </c>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
-        <v>26</v>
+        <v>424</v>
       </c>
       <c r="B109" t="s">
+        <v>425</v>
+      </c>
+      <c r="C109" s="2">
+        <v>45526</v>
+      </c>
+      <c r="D109" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" t="s">
+        <v>426</v>
+      </c>
+      <c r="F109" t="s">
+        <v>424</v>
+      </c>
+      <c r="G109" t="s">
         <v>427</v>
       </c>
-      <c r="C109" s="2">
-        <v>45560</v>
-      </c>
-      <c r="D109" t="s">
-        <v>24</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="H109" s="2">
+        <v>45932</v>
+      </c>
+      <c r="I109" s="3">
+        <v>306</v>
+      </c>
+      <c r="J109" t="s">
+        <v>52</v>
+      </c>
+      <c r="K109" t="s">
         <v>428</v>
       </c>
-      <c r="F109" t="s">
-        <v>429</v>
-      </c>
-      <c r="G109" t="s">
-        <v>430</v>
-      </c>
-      <c r="H109" s="2">
-        <v>45930</v>
-      </c>
-      <c r="I109" s="3">
-        <v>283</v>
-      </c>
-      <c r="J109" t="s">
-        <v>39</v>
-      </c>
-      <c r="K109" t="s">
-        <v>431</v>
-      </c>
-      <c r="L109" s="2">
-        <v>45854</v>
-      </c>
-      <c r="M109" s="3">
-        <v>294</v>
-      </c>
+      <c r="M109" s="3"/>
       <c r="S109" s="2">
-        <v>46950</v>
+        <v>47748</v>
       </c>
       <c r="T109" s="3">
-        <v>737</v>
+        <v>1510</v>
       </c>
       <c r="U109" s="3"/>
       <c r="V109" s="4">
-        <v>6210000</v>
+        <v>4440928.34</v>
       </c>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
-        <v>273</v>
+        <v>26</v>
       </c>
       <c r="B110" t="s">
+        <v>429</v>
+      </c>
+      <c r="C110" s="2">
+        <v>45560</v>
+      </c>
+      <c r="D110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110" t="s">
+        <v>430</v>
+      </c>
+      <c r="F110" t="s">
+        <v>431</v>
+      </c>
+      <c r="G110" t="s">
         <v>432</v>
       </c>
-      <c r="C110" s="2">
-        <v>44607</v>
-      </c>
-      <c r="D110" t="s">
-        <v>361</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="H110" s="2">
+        <v>45930</v>
+      </c>
+      <c r="I110" s="3">
+        <v>308</v>
+      </c>
+      <c r="J110" t="s">
+        <v>38</v>
+      </c>
+      <c r="K110" t="s">
         <v>433</v>
       </c>
-      <c r="F110" t="s">
-        <v>273</v>
-      </c>
-      <c r="G110" t="s">
-        <v>434</v>
-      </c>
-      <c r="H110" s="2">
-        <v>46196</v>
-      </c>
-      <c r="I110" s="3">
-        <v>17</v>
-      </c>
-      <c r="J110" t="s">
-        <v>53</v>
-      </c>
-      <c r="K110" t="s">
-        <v>435</v>
-      </c>
       <c r="L110" s="2">
-        <v>44747</v>
+        <v>45854</v>
       </c>
       <c r="M110" s="3">
-        <v>140</v>
-      </c>
-      <c r="O110" t="s">
-        <v>436</v>
-      </c>
-      <c r="P110" s="2">
-        <v>46573</v>
+        <v>294</v>
       </c>
       <c r="S110" s="2">
-        <v>45111</v>
-      </c>
-      <c r="T110" s="3"/>
-      <c r="U110" s="3">
-        <v>360</v>
-      </c>
+        <v>46950</v>
+      </c>
+      <c r="T110" s="3">
+        <v>712</v>
+      </c>
+      <c r="U110" s="3"/>
       <c r="V110" s="4">
-        <v>6571898.25</v>
+        <v>6210000</v>
       </c>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
+        <v>274</v>
+      </c>
+      <c r="B111" t="s">
+        <v>434</v>
+      </c>
+      <c r="C111" s="2">
+        <v>44607</v>
+      </c>
+      <c r="D111" t="s">
+        <v>362</v>
+      </c>
+      <c r="E111" t="s">
+        <v>435</v>
+      </c>
+      <c r="F111" t="s">
+        <v>274</v>
+      </c>
+      <c r="G111" t="s">
+        <v>436</v>
+      </c>
+      <c r="H111" s="2">
+        <v>46196</v>
+      </c>
+      <c r="I111" s="3">
+        <v>42</v>
+      </c>
+      <c r="J111" t="s">
+        <v>52</v>
+      </c>
+      <c r="K111" t="s">
         <v>437</v>
       </c>
-      <c r="B111" t="s">
+      <c r="L111" s="2">
+        <v>44747</v>
+      </c>
+      <c r="M111" s="3">
+        <v>140</v>
+      </c>
+      <c r="O111" t="s">
         <v>438</v>
       </c>
-      <c r="C111" s="2">
-        <v>38661</v>
-      </c>
-      <c r="D111" t="s">
-        <v>36</v>
-      </c>
-      <c r="E111" t="s">
-        <v>439</v>
-      </c>
-      <c r="F111" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" t="s">
-        <v>440</v>
-      </c>
-      <c r="H111" s="2">
-        <v>45993</v>
-      </c>
-      <c r="I111" s="3">
-        <v>220</v>
-      </c>
-      <c r="J111" t="s">
-        <v>39</v>
-      </c>
-      <c r="K111" t="s">
-        <v>441</v>
-      </c>
-      <c r="L111" s="2">
-        <v>45993</v>
-      </c>
-      <c r="M111" s="3">
-        <v>7332</v>
+      <c r="P111" s="2">
+        <v>46573</v>
       </c>
       <c r="S111" s="2">
-        <v>46540</v>
-      </c>
-      <c r="T111" s="3">
-        <v>327</v>
-      </c>
-      <c r="U111" s="3"/>
+        <v>45111</v>
+      </c>
+      <c r="T111" s="3"/>
+      <c r="U111" s="3">
+        <v>335</v>
+      </c>
       <c r="V111" s="4">
-        <v>9032000</v>
+        <v>6571898.25</v>
       </c>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
-        <v>225</v>
+        <v>439</v>
       </c>
       <c r="B112" t="s">
+        <v>440</v>
+      </c>
+      <c r="C112" s="2">
+        <v>38661</v>
+      </c>
+      <c r="D112" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" t="s">
+        <v>441</v>
+      </c>
+      <c r="F112" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" t="s">
         <v>442</v>
       </c>
-      <c r="C112" s="2">
-        <v>45560</v>
-      </c>
-      <c r="D112" t="s">
-        <v>24</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="H112" s="2">
+        <v>45993</v>
+      </c>
+      <c r="I112" s="3">
+        <v>245</v>
+      </c>
+      <c r="J112" t="s">
+        <v>38</v>
+      </c>
+      <c r="K112" t="s">
         <v>443</v>
       </c>
-      <c r="F112" t="s">
-        <v>225</v>
-      </c>
-      <c r="G112" t="s">
-        <v>444</v>
-      </c>
-      <c r="H112" s="2">
-        <v>45797</v>
-      </c>
-      <c r="I112" s="3">
-        <v>416</v>
-      </c>
-      <c r="J112" t="s">
-        <v>53</v>
-      </c>
-      <c r="K112" t="s">
-        <v>445</v>
-      </c>
-      <c r="M112" s="3"/>
+      <c r="L112" s="2">
+        <v>45993</v>
+      </c>
+      <c r="M112" s="3">
+        <v>7332</v>
+      </c>
       <c r="S112" s="2">
-        <v>46523</v>
+        <v>46540</v>
       </c>
       <c r="T112" s="3">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="U112" s="3"/>
       <c r="V112" s="4">
-        <v>9152353</v>
+        <v>9032000</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>43</v>
+        <v>224</v>
       </c>
       <c r="B113" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C113" s="2">
-        <v>44763</v>
+        <v>45560</v>
       </c>
       <c r="D113" t="s">
         <v>24</v>
       </c>
       <c r="E113" t="s">
+        <v>445</v>
+      </c>
+      <c r="F113" t="s">
+        <v>224</v>
+      </c>
+      <c r="G113" t="s">
+        <v>446</v>
+      </c>
+      <c r="H113" s="2">
+        <v>45797</v>
+      </c>
+      <c r="I113" s="3">
+        <v>441</v>
+      </c>
+      <c r="J113" t="s">
+        <v>52</v>
+      </c>
+      <c r="K113" t="s">
         <v>447</v>
       </c>
-      <c r="F113" t="s">
-        <v>43</v>
-      </c>
-      <c r="G113" t="s">
-        <v>52</v>
-      </c>
-      <c r="H113" s="2">
-        <v>45798</v>
-      </c>
-      <c r="I113" s="3">
-        <v>415</v>
-      </c>
-      <c r="J113" t="s">
-        <v>53</v>
-      </c>
-      <c r="K113" t="s">
-        <v>448</v>
-      </c>
-      <c r="L113" s="2">
-        <v>45574</v>
-      </c>
-      <c r="M113" s="3">
-        <v>811</v>
-      </c>
-      <c r="O113" t="s">
-        <v>60</v>
-      </c>
-      <c r="P113" s="2">
-        <v>46313</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>449</v>
-      </c>
-      <c r="R113" s="2">
-        <v>45786</v>
-      </c>
+      <c r="M113" s="3"/>
       <c r="S113" s="2">
-        <v>45218</v>
-      </c>
-      <c r="T113" s="3"/>
-      <c r="U113" s="3">
-        <v>100</v>
-      </c>
+        <v>46523</v>
+      </c>
+      <c r="T113" s="3">
+        <v>285</v>
+      </c>
+      <c r="U113" s="3"/>
       <c r="V113" s="4">
-        <v>10934411.34</v>
+        <v>9152353</v>
       </c>
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B114" t="s">
+        <v>448</v>
+      </c>
+      <c r="C114" s="2">
+        <v>44763</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" t="s">
+        <v>449</v>
+      </c>
+      <c r="F114" t="s">
+        <v>222</v>
+      </c>
+      <c r="G114" t="s">
+        <v>422</v>
+      </c>
+      <c r="H114" s="2">
+        <v>46237</v>
+      </c>
+      <c r="I114" s="3">
+        <v>1</v>
+      </c>
+      <c r="J114" t="s">
+        <v>273</v>
+      </c>
+      <c r="K114" t="s">
         <v>450</v>
       </c>
-      <c r="C114" s="2">
-        <v>45014</v>
-      </c>
-      <c r="D114" t="s">
-        <v>45</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="L114" s="2">
+        <v>45574</v>
+      </c>
+      <c r="M114" s="3">
+        <v>811</v>
+      </c>
+      <c r="O114" t="s">
+        <v>59</v>
+      </c>
+      <c r="P114" s="2">
+        <v>46313</v>
+      </c>
+      <c r="Q114" t="s">
         <v>451</v>
       </c>
-      <c r="F114" t="s">
-        <v>452</v>
-      </c>
-      <c r="G114" t="s">
-        <v>453</v>
-      </c>
-      <c r="H114" s="2">
-        <v>46211</v>
-      </c>
-      <c r="I114" s="3">
-        <v>2</v>
-      </c>
-      <c r="J114" t="s">
-        <v>272</v>
-      </c>
-      <c r="K114" t="s">
-        <v>454</v>
-      </c>
-      <c r="L114" s="2">
-        <v>45148</v>
-      </c>
-      <c r="M114" s="3">
-        <v>134</v>
-      </c>
-      <c r="O114" t="s">
-        <v>352</v>
-      </c>
-      <c r="P114" s="2">
-        <v>46609</v>
+      <c r="R114" s="2">
+        <v>45786</v>
       </c>
       <c r="S114" s="2">
-        <v>45518</v>
+        <v>45218</v>
       </c>
       <c r="T114" s="3"/>
       <c r="U114" s="3">
-        <v>396</v>
+        <v>75</v>
       </c>
       <c r="V114" s="4">
-        <v>17946403.739999998</v>
+        <v>10934411.34</v>
       </c>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>455</v>
+        <v>26</v>
       </c>
       <c r="B115" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C115" s="2">
-        <v>45666</v>
+        <v>45014</v>
       </c>
       <c r="D115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E115" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F115" t="s">
-        <v>418</v>
+        <v>26</v>
       </c>
       <c r="G115" t="s">
-        <v>458</v>
+        <v>360</v>
       </c>
       <c r="H115" s="2">
-        <v>46174</v>
+        <v>46219</v>
       </c>
       <c r="I115" s="3">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s">
-        <v>53</v>
-      </c>
-      <c r="M115" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="K115" t="s">
+        <v>454</v>
+      </c>
+      <c r="L115" s="2">
+        <v>45148</v>
+      </c>
+      <c r="M115" s="3">
+        <v>134</v>
+      </c>
+      <c r="O115" t="s">
+        <v>353</v>
+      </c>
+      <c r="P115" s="2">
+        <v>46609</v>
+      </c>
+      <c r="S115" s="2">
+        <v>45518</v>
+      </c>
       <c r="T115" s="3"/>
-      <c r="U115" s="3"/>
+      <c r="U115" s="3">
+        <v>371</v>
+      </c>
       <c r="V115" s="4">
-        <v>31106553.600000001</v>
+        <v>17946403.739999998</v>
       </c>
     </row>
     <row r="116" spans="1:22">
       <c r="A116" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="B116" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C116" s="2">
-        <v>45250</v>
+        <v>45666</v>
       </c>
       <c r="D116" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E116" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F116" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G116" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H116" s="2">
-        <v>45400</v>
+        <v>46174</v>
       </c>
       <c r="I116" s="3">
-        <v>813</v>
+        <v>64</v>
       </c>
       <c r="J116" t="s">
-        <v>53</v>
-      </c>
-      <c r="K116" t="s">
-        <v>462</v>
-      </c>
-      <c r="L116" s="2">
-        <v>45401</v>
-      </c>
-      <c r="M116" s="3">
-        <v>151</v>
-      </c>
-      <c r="S116" s="2">
-        <v>47227</v>
-      </c>
-      <c r="T116" s="3">
-        <v>1014</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M116" s="3"/>
+      <c r="T116" s="3"/>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
-        <v>41522909.280000001</v>
+        <v>31106553.600000001</v>
       </c>
     </row>
     <row r="117" spans="1:22">
       <c r="A117" t="s">
-        <v>43</v>
+        <v>424</v>
       </c>
       <c r="B117" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C117" s="2">
-        <v>44238</v>
+        <v>45250</v>
       </c>
       <c r="D117" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E117" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F117" t="s">
-        <v>67</v>
+        <v>424</v>
       </c>
       <c r="G117" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H117" s="2">
-        <v>46211</v>
+        <v>45400</v>
       </c>
       <c r="I117" s="3">
-        <v>2</v>
+        <v>838</v>
       </c>
       <c r="J117" t="s">
-        <v>272</v>
+        <v>52</v>
       </c>
       <c r="K117" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="L117" s="2">
-        <v>44969</v>
+        <v>45401</v>
       </c>
       <c r="M117" s="3">
-        <v>731</v>
-      </c>
-      <c r="O117" t="s">
-        <v>467</v>
-      </c>
-      <c r="P117" s="2">
-        <v>46798</v>
+        <v>151</v>
       </c>
       <c r="S117" s="2">
-        <v>45886</v>
-      </c>
-      <c r="T117" s="3"/>
-      <c r="U117" s="3">
-        <v>585</v>
-      </c>
+        <v>47227</v>
+      </c>
+      <c r="T117" s="3">
+        <v>989</v>
+      </c>
+      <c r="U117" s="3"/>
       <c r="V117" s="4">
-        <v>41936400</v>
+        <v>41522909.280000001</v>
       </c>
     </row>
     <row r="118" spans="1:22">
       <c r="A118" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B118" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C118" s="2">
-        <v>45607</v>
+        <v>44238</v>
       </c>
       <c r="D118" t="s">
         <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F118" t="s">
-        <v>470</v>
+        <v>66</v>
       </c>
       <c r="G118" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="H118" s="2">
-        <v>45798</v>
+        <v>46211</v>
       </c>
       <c r="I118" s="3">
-        <v>415</v>
+        <v>27</v>
       </c>
       <c r="J118" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K118" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="L118" s="2">
-        <v>45798</v>
+        <v>44969</v>
       </c>
       <c r="M118" s="3">
-        <v>191</v>
+        <v>731</v>
+      </c>
+      <c r="O118" t="s">
+        <v>467</v>
+      </c>
+      <c r="P118" s="2">
+        <v>46798</v>
       </c>
       <c r="S118" s="2">
-        <v>46712</v>
-      </c>
-      <c r="T118" s="3">
-        <v>499</v>
-      </c>
-      <c r="U118" s="3"/>
+        <v>45886</v>
+      </c>
+      <c r="T118" s="3"/>
+      <c r="U118" s="3">
+        <v>560</v>
+      </c>
       <c r="V118" s="4">
-        <v>50963796</v>
+        <v>41936400</v>
       </c>
     </row>
     <row r="119" spans="1:22">
       <c r="A119" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B119" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C119" s="2">
-        <v>45664</v>
+        <v>45607</v>
       </c>
       <c r="D119" t="s">
         <v>24</v>
       </c>
       <c r="E119" t="s">
+        <v>469</v>
+      </c>
+      <c r="F119" t="s">
+        <v>470</v>
+      </c>
+      <c r="G119" t="s">
+        <v>471</v>
+      </c>
+      <c r="H119" s="2">
+        <v>45798</v>
+      </c>
+      <c r="I119" s="3">
+        <v>440</v>
+      </c>
+      <c r="J119" t="s">
+        <v>52</v>
+      </c>
+      <c r="K119" t="s">
+        <v>472</v>
+      </c>
+      <c r="L119" s="2">
+        <v>45798</v>
+      </c>
+      <c r="M119" s="3">
+        <v>191</v>
+      </c>
+      <c r="S119" s="2">
+        <v>46712</v>
+      </c>
+      <c r="T119" s="3">
         <v>474</v>
       </c>
-      <c r="F119" t="s">
-        <v>225</v>
-      </c>
-      <c r="G119" t="s">
-        <v>475</v>
-      </c>
-      <c r="H119" s="2">
-        <v>45958</v>
-      </c>
-      <c r="I119" s="3">
-        <v>255</v>
-      </c>
-      <c r="J119" t="s">
-        <v>34</v>
-      </c>
-      <c r="M119" s="3"/>
-      <c r="T119" s="3"/>
       <c r="U119" s="3"/>
       <c r="V119" s="4">
+        <v>50963796</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22">
+      <c r="A120" t="s">
+        <v>42</v>
+      </c>
+      <c r="B120" t="s">
+        <v>473</v>
+      </c>
+      <c r="C120" s="2">
+        <v>45664</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" t="s">
+        <v>474</v>
+      </c>
+      <c r="F120" t="s">
+        <v>224</v>
+      </c>
+      <c r="G120" t="s">
+        <v>475</v>
+      </c>
+      <c r="H120" s="2">
+        <v>45958</v>
+      </c>
+      <c r="I120" s="3">
+        <v>280</v>
+      </c>
+      <c r="J120" t="s">
+        <v>28</v>
+      </c>
+      <c r="M120" s="3"/>
+      <c r="T120" s="3"/>
+      <c r="U120" s="3"/>
+      <c r="V120" s="4">
         <v>253382919</v>
       </c>
     </row>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE397E0A-729B-4D5A-9985-11C2302166EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E91F9A-158D-40C9-8E04-B146FA219FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="485">
   <si>
     <t>Departamento</t>
   </si>
@@ -834,157 +834,163 @@
     <t>SISLOG 120357 - Aquisição de Workstations - Atender demandas da SES-GO</t>
   </si>
   <si>
-    <t>ETP CONCLUÍDO AGUARDANDO ORÇAMENTOS.</t>
+    <t>SOLICITAR NOVOS ORÇAMENTOS</t>
   </si>
   <si>
     <t>Aquisição</t>
   </si>
   <si>
+    <t>SISLOG 120357 - Aquisição de Workstations</t>
+  </si>
+  <si>
+    <t>ELABORAÇÃO DOD ETP</t>
+  </si>
+  <si>
+    <t>202600010023321</t>
+  </si>
+  <si>
+    <t>Convênio</t>
+  </si>
+  <si>
+    <t>Doação de 105 desktops para o CISCENO</t>
+  </si>
+  <si>
+    <t>PARA CONTINUIDADE</t>
+  </si>
+  <si>
+    <t>Em Renovação</t>
+  </si>
+  <si>
+    <t>202600005022653</t>
+  </si>
+  <si>
+    <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
+  </si>
+  <si>
+    <t>TERMO DE REFERÊNCIA</t>
+  </si>
+  <si>
+    <t>GEIN</t>
+  </si>
+  <si>
+    <t>202600010030662</t>
+  </si>
+  <si>
+    <t>Sislog 120082 -Ingressos do CONSAD-feito pelo GECG</t>
+  </si>
+  <si>
+    <t>ANEXO II</t>
+  </si>
+  <si>
+    <t>202600005015076</t>
+  </si>
+  <si>
+    <t>119902 Ingresso participação no Simpósio SBCAS 2026</t>
+  </si>
+  <si>
+    <t>Emitida a nota de empenho, encaminhem-se os autos à SUTIS para conhecimento e demais providências cabíveis.</t>
+  </si>
+  <si>
+    <t>202600005015052</t>
+  </si>
+  <si>
+    <t>119899 - Aquisição de ingresso para a participação no Simpósio Brasileiro de Sistemas de Informação (SBSI)</t>
+  </si>
+  <si>
+    <t>202500005019071</t>
+  </si>
+  <si>
+    <t>SISLOG 114940  - Kits Mouse &amp; teclado com fio/sem fio</t>
+  </si>
+  <si>
+    <t>Comunicamos que o julgamento do Pregão Eletrônico 173/2025, objeto em epígrafe, realizar-se-á dia 14/10/2025 (terça-feira) às 09:00 h,</t>
+  </si>
+  <si>
+    <t>202400005028451</t>
+  </si>
+  <si>
+    <t>SISLOG 108212 estabilizador de tensão, potência mínima de 500 va, tensão de 220 v, capacidade mínima para 4 tomada - SEI nº 202500010009280 - Digitalizado e encaminhado a GCC</t>
+  </si>
+  <si>
+    <t>Extrato de Publicação - Contrato 13 (71284812). E-mail 71304720 ao fornecedor.contato@brasillprodutos.com.br. Aguardando a publicação no PNCP para o início da contagem da vigência, conforme a Cláusula Quarta.</t>
+  </si>
+  <si>
+    <t>13/2025</t>
+  </si>
+  <si>
+    <t>202500005000064</t>
+  </si>
+  <si>
+    <t>SISLOG 111806 CERTIFICADOS DIGITAIS PROCESSO PRÉVIO  202400010046932. Processo paralelo da contratação: SEI 202500010039434.</t>
+  </si>
+  <si>
+    <t>CONTRATO EM GESTÃO DA GETEC</t>
+  </si>
+  <si>
+    <t>50/2025</t>
+  </si>
+  <si>
+    <t>202400010051978</t>
+  </si>
+  <si>
+    <t>Aquisição de Suprimentos de Informática diversos, Estabilizador ,Pen drive - 32 GBHeadset (Fone de ouvido) derivado da Ata de Registro de Preços nº 004/2024 - SEAD/GECC resultante do Pregão Eletrônico 'SRP' nº 001/2023 (processo SEI nº 202100005019301). Aditivo ao Contrato nº 113/2024/SES no percentual de 25% (vinte e cinco por cento) – BRASLYNC</t>
+  </si>
+  <si>
+    <t>113/2024</t>
+  </si>
+  <si>
+    <t>202500010034499</t>
+  </si>
+  <si>
+    <t>ADESÃO A ARP PARA AQUISIÇÃO DE WORKSTATION PARA O LACEN</t>
+  </si>
+  <si>
+    <t>Está no LACEN para gestão CONTRATO</t>
+  </si>
+  <si>
+    <t>202500005035836</t>
+  </si>
+  <si>
+    <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
+  </si>
+  <si>
+    <t>GELIC</t>
+  </si>
+  <si>
+    <t>houve a apresentação de propostas, as quais foram todas desclassificadas e/ou os licitantes inabilitados, inviabilizando a adjudicação do objeto, declaro o certame FRACASSADO.</t>
+  </si>
+  <si>
+    <t>SESG</t>
+  </si>
+  <si>
+    <t>202400005045335</t>
+  </si>
+  <si>
+    <t>SISLOG nº 110808 gestão de competências Software GALERA.APP LEME CONSULTORIA EM GESTÃO DE RH LTDA. PROCESSO SEI PARALELO 202500010040069</t>
+  </si>
+  <si>
+    <t>PARA RENOVAÇÃO</t>
+  </si>
+  <si>
+    <t>52/2025</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>FORNECEDOR VOGEL ALGAR. PROC - Serviços de telecomunicações para tráfego de dados</t>
+  </si>
+  <si>
+    <t>22/2020</t>
+  </si>
+  <si>
     <t>202600005022365</t>
   </si>
   <si>
     <t>SISLOG 121388 GALERA APP</t>
   </si>
   <si>
-    <t>Documentos feitos para nova Contratação galera app falta comprovação de preços praticados e declaração de exclusividade</t>
-  </si>
-  <si>
-    <t>202600005022653</t>
-  </si>
-  <si>
-    <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
-  </si>
-  <si>
-    <t>ELABORAÇÃO DE DOD E ETP</t>
-  </si>
-  <si>
-    <t>202600010023321</t>
-  </si>
-  <si>
-    <t>Convênio</t>
-  </si>
-  <si>
-    <t>Doação de 105 desktops para o CISCENO</t>
-  </si>
-  <si>
-    <t>PARA CONTINUIDADE</t>
-  </si>
-  <si>
-    <t>Em Renovação</t>
-  </si>
-  <si>
-    <t>GEIN</t>
-  </si>
-  <si>
-    <t>202600010030662</t>
-  </si>
-  <si>
-    <t>Sislog 120082 -Ingressos do CONSAD-feito pelo GECG</t>
-  </si>
-  <si>
-    <t>ANEXO II</t>
-  </si>
-  <si>
-    <t>202600005015076</t>
-  </si>
-  <si>
-    <t>119902 Ingresso participação no Simpósio SBCAS 2026</t>
-  </si>
-  <si>
-    <t>Emitida a nota de empenho, encaminhem-se os autos à SUTIS para conhecimento e demais providências cabíveis.</t>
-  </si>
-  <si>
-    <t>202600005015052</t>
-  </si>
-  <si>
-    <t>119899 - Aquisição de ingresso para a participação no Simpósio Brasileiro de Sistemas de Informação (SBSI)</t>
-  </si>
-  <si>
-    <t>202500005019071</t>
-  </si>
-  <si>
-    <t>SISLOG 114940  - Kits Mouse &amp; teclado com fio/sem fio</t>
-  </si>
-  <si>
-    <t>Comunicamos que o julgamento do Pregão Eletrônico 173/2025, objeto em epígrafe, realizar-se-á dia 14/10/2025 (terça-feira) às 09:00 h,</t>
-  </si>
-  <si>
-    <t>202400005028451</t>
-  </si>
-  <si>
-    <t>SISLOG 108212 estabilizador de tensão, potência mínima de 500 va, tensão de 220 v, capacidade mínima para 4 tomada - SEI nº 202500010009280 - Digitalizado e encaminhado a GCC</t>
-  </si>
-  <si>
-    <t>Extrato de Publicação - Contrato 13 (71284812). E-mail 71304720 ao fornecedor.contato@brasillprodutos.com.br. Aguardando a publicação no PNCP para o início da contagem da vigência, conforme a Cláusula Quarta.</t>
-  </si>
-  <si>
-    <t>13/2025</t>
-  </si>
-  <si>
-    <t>202500005000064</t>
-  </si>
-  <si>
-    <t>SISLOG 111806 CERTIFICADOS DIGITAIS PROCESSO PRÉVIO  202400010046932. Processo paralelo da contratação: SEI 202500010039434.</t>
-  </si>
-  <si>
-    <t>CONTRATO EM GESTÃO DA GETEC</t>
-  </si>
-  <si>
-    <t>50/2025</t>
-  </si>
-  <si>
-    <t>202400010051978</t>
-  </si>
-  <si>
-    <t>Aquisição de Suprimentos de Informática diversos, Estabilizador ,Pen drive - 32 GBHeadset (Fone de ouvido) derivado da Ata de Registro de Preços nº 004/2024 - SEAD/GECC resultante do Pregão Eletrônico 'SRP' nº 001/2023 (processo SEI nº 202100005019301). Aditivo ao Contrato nº 113/2024/SES no percentual de 25% (vinte e cinco por cento) – BRASLYNC</t>
-  </si>
-  <si>
-    <t>113/2024</t>
-  </si>
-  <si>
-    <t>202500010034499</t>
-  </si>
-  <si>
-    <t>ADESÃO A ARP PARA AQUISIÇÃO DE WORKSTATION PARA O LACEN</t>
-  </si>
-  <si>
-    <t>Está no LACEN para gestão CONTRATO</t>
-  </si>
-  <si>
-    <t>202500005035836</t>
-  </si>
-  <si>
-    <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
-  </si>
-  <si>
-    <t>GELIC</t>
-  </si>
-  <si>
-    <t>houve a apresentação de propostas, as quais foram todas desclassificadas e/ou os licitantes inabilitados, inviabilizando a adjudicação do objeto, declaro o certame FRACASSADO.</t>
-  </si>
-  <si>
-    <t>SESG</t>
-  </si>
-  <si>
-    <t>202400005045335</t>
-  </si>
-  <si>
-    <t>SISLOG nº 110808 gestão de competências Software GALERA.APP LEME CONSULTORIA EM GESTÃO DE RH LTDA. PROCESSO SEI PARALELO 202500010040069</t>
-  </si>
-  <si>
-    <t>PARA RENOVAÇÃO</t>
-  </si>
-  <si>
-    <t>52/2025</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>FORNECEDOR VOGEL ALGAR. PROC - Serviços de telecomunicações para tráfego de dados</t>
-  </si>
-  <si>
-    <t>22/2020</t>
+    <t>Documentos feitos para nova Contratação</t>
   </si>
   <si>
     <t>202500005030582</t>
@@ -1014,10 +1020,10 @@
     <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 9</t>
   </si>
   <si>
-    <t>GAB</t>
-  </si>
-  <si>
-    <t>com vistas à apuração de eventual inexecução contratual, bem como à possível responsabilização da empresa contratada.</t>
+    <t>GECORSET</t>
+  </si>
+  <si>
+    <t>para conhecimento e providências que julgar cabíveis.</t>
   </si>
   <si>
     <t>09/2026</t>
@@ -1030,6 +1036,12 @@
   </si>
   <si>
     <t>21/2020</t>
+  </si>
+  <si>
+    <t>202600005026702</t>
+  </si>
+  <si>
+    <t>SISLOG 121994- Aquisição Webcam e Headset</t>
   </si>
   <si>
     <t>202500010044120</t>
@@ -1304,6 +1316,12 @@
     <t>107/2024</t>
   </si>
   <si>
+    <t>202600005026003</t>
+  </si>
+  <si>
+    <t>SISLOG 121821 ARP nº 001/2026 do TJ-GO - 500 micromputadores</t>
+  </si>
+  <si>
     <t>202600010062463</t>
   </si>
   <si>
@@ -1319,7 +1337,10 @@
     <t>SISLOG 113930 -GLOBAL TI Contratação de solução de Inteligência Artificial (IA). Processo 202500010079078 paralelo CCONT</t>
   </si>
   <si>
-    <t>PARA ANÁLISE</t>
+    <t>SUTIS GEFIN</t>
+  </si>
+  <si>
+    <t>ATENDER DILIGÊNCIA 14 DA CACTIC</t>
   </si>
   <si>
     <t>93/2025</t>
@@ -1402,6 +1423,12 @@
   </si>
   <si>
     <t>FORNECEDOR MEMORA. Contratação de mão de obra de infra e banco.</t>
+  </si>
+  <si>
+    <t>GEPO CACTIC SGI</t>
+  </si>
+  <si>
+    <t>ANEXO II E ATENDER DILIGÊNCIA 15 DA CACTIC SUGESTÃO DE ENVIO A CONTABILIDADE E PROCSET</t>
   </si>
   <si>
     <t>83/2023</t>
@@ -1844,13 +1871,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V120"/>
+  <dimension ref="A1:V123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1949,7 +1977,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -1985,7 +2013,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -2021,7 +2049,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -2057,7 +2085,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
@@ -2093,7 +2121,7 @@
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="J6" t="s">
         <v>38</v>
@@ -2141,7 +2169,7 @@
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1098</v>
+        <v>1107</v>
       </c>
       <c r="J7" t="s">
         <v>52</v>
@@ -2194,7 +2222,7 @@
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J8" t="s">
         <v>52</v>
@@ -2247,7 +2275,7 @@
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="J9" t="s">
         <v>28</v>
@@ -2295,7 +2323,7 @@
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
@@ -2343,7 +2371,7 @@
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="J11" t="s">
         <v>28</v>
@@ -2391,7 +2419,7 @@
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1258</v>
+        <v>1267</v>
       </c>
       <c r="J12" t="s">
         <v>52</v>
@@ -2438,7 +2466,7 @@
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="J13" t="s">
         <v>52</v>
@@ -2485,7 +2513,7 @@
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="J14" t="s">
         <v>52</v>
@@ -2532,7 +2560,7 @@
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>1049</v>
+        <v>1058</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -2579,7 +2607,7 @@
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="J16" t="s">
         <v>52</v>
@@ -2626,7 +2654,7 @@
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -2673,7 +2701,7 @@
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="J18" t="s">
         <v>52</v>
@@ -2720,7 +2748,7 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="J19" t="s">
         <v>52</v>
@@ -2767,7 +2795,7 @@
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="J20" t="s">
         <v>28</v>
@@ -2803,7 +2831,7 @@
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
@@ -2850,7 +2878,7 @@
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1330</v>
+        <v>1339</v>
       </c>
       <c r="J22" t="s">
         <v>52</v>
@@ -2897,7 +2925,7 @@
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="J23" t="s">
         <v>38</v>
@@ -2942,7 +2970,7 @@
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="J24" t="s">
         <v>28</v>
@@ -2978,7 +3006,7 @@
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
@@ -3025,7 +3053,7 @@
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>1014</v>
+        <v>1023</v>
       </c>
       <c r="J26" t="s">
         <v>52</v>
@@ -3072,7 +3100,7 @@
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
@@ -3114,7 +3142,7 @@
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="J28" t="s">
         <v>52</v>
@@ -3161,7 +3189,7 @@
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="J29" t="s">
         <v>28</v>
@@ -3197,7 +3225,7 @@
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="J30" t="s">
         <v>28</v>
@@ -3233,7 +3261,7 @@
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="J31" t="s">
         <v>28</v>
@@ -3269,7 +3297,7 @@
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="J32" t="s">
         <v>38</v>
@@ -3316,7 +3344,7 @@
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="J33" t="s">
         <v>38</v>
@@ -3363,7 +3391,7 @@
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
@@ -3399,7 +3427,7 @@
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>971</v>
+        <v>980</v>
       </c>
       <c r="J35" t="s">
         <v>28</v>
@@ -3435,7 +3463,7 @@
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="J36" t="s">
         <v>28</v>
@@ -3471,7 +3499,7 @@
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="J37" t="s">
         <v>38</v>
@@ -3518,7 +3546,7 @@
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="J38" t="s">
         <v>28</v>
@@ -3554,7 +3582,7 @@
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
@@ -3604,7 +3632,7 @@
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>932</v>
+        <v>941</v>
       </c>
       <c r="J40" t="s">
         <v>28</v>
@@ -3640,7 +3668,7 @@
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -3687,7 +3715,7 @@
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="J42" t="s">
         <v>28</v>
@@ -3723,7 +3751,7 @@
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="J43" t="s">
         <v>28</v>
@@ -3759,7 +3787,7 @@
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="J44" t="s">
         <v>38</v>
@@ -3803,7 +3831,7 @@
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="J45" t="s">
         <v>38</v>
@@ -3845,7 +3873,7 @@
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="J46" t="s">
         <v>38</v>
@@ -3887,7 +3915,7 @@
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="J47" t="s">
         <v>38</v>
@@ -3905,7 +3933,7 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -3936,7 +3964,7 @@
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="J48" t="s">
         <v>38</v>
@@ -3986,7 +4014,7 @@
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="J49" t="s">
         <v>38</v>
@@ -4004,7 +4032,7 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
@@ -4035,7 +4063,7 @@
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="J50" t="s">
         <v>28</v>
@@ -4079,7 +4107,7 @@
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="J51" t="s">
         <v>28</v>
@@ -4115,7 +4143,7 @@
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="J52" t="s">
         <v>28</v>
@@ -4151,7 +4179,7 @@
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="J53" t="s">
         <v>28</v>
@@ -4187,7 +4215,7 @@
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="J54" t="s">
         <v>52</v>
@@ -4234,7 +4262,7 @@
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="J55" t="s">
         <v>38</v>
@@ -4270,7 +4298,7 @@
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>1019</v>
+        <v>1028</v>
       </c>
       <c r="J56" t="s">
         <v>28</v>
@@ -4306,7 +4334,7 @@
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="J57" t="s">
         <v>38</v>
@@ -4342,7 +4370,7 @@
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="J58" t="s">
         <v>28</v>
@@ -4378,7 +4406,7 @@
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="J59" t="s">
         <v>38</v>
@@ -4414,7 +4442,7 @@
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="J60" t="s">
         <v>52</v>
@@ -4432,7 +4460,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4463,7 +4491,7 @@
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="J61" t="s">
         <v>28</v>
@@ -4499,7 +4527,7 @@
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="J62" t="s">
         <v>28</v>
@@ -4532,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="H63" s="2">
-        <v>46197</v>
+        <v>46246</v>
       </c>
       <c r="I63" s="3">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J63" t="s">
         <v>262</v>
@@ -4550,28 +4578,28 @@
         <v>26</v>
       </c>
       <c r="B64" t="s">
+        <v>259</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46245</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" t="s">
         <v>263</v>
-      </c>
-      <c r="C64" s="2">
-        <v>46210</v>
-      </c>
-      <c r="D64" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" t="s">
-        <v>264</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H64" s="2">
-        <v>46216</v>
+        <v>46246</v>
       </c>
       <c r="I64" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J64" t="s">
         <v>262</v>
@@ -4586,31 +4614,31 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
+        <v>265</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D65" t="s">
         <v>266</v>
-      </c>
-      <c r="C65" s="2">
-        <v>46211</v>
-      </c>
-      <c r="D65" t="s">
-        <v>24</v>
       </c>
       <c r="E65" t="s">
         <v>267</v>
       </c>
       <c r="F65" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="G65" t="s">
         <v>268</v>
       </c>
       <c r="H65" s="2">
-        <v>46211</v>
+        <v>46182</v>
       </c>
       <c r="I65" s="3">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="J65" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
@@ -4622,43 +4650,45 @@
         <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C66" s="2">
-        <v>46126</v>
+        <v>46211</v>
       </c>
       <c r="D66" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
         <v>271</v>
       </c>
       <c r="F66" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="G66" t="s">
         <v>272</v>
       </c>
       <c r="H66" s="2">
-        <v>46182</v>
+        <v>46241</v>
       </c>
       <c r="I66" s="3">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="J66" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
-      <c r="V66" s="4"/>
+      <c r="V66" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" t="s">
+        <v>273</v>
+      </c>
+      <c r="B67" t="s">
         <v>274</v>
-      </c>
-      <c r="B67" t="s">
-        <v>275</v>
       </c>
       <c r="C67" s="2">
         <v>46136</v>
@@ -4667,19 +4697,19 @@
         <v>35</v>
       </c>
       <c r="E67" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F67" t="s">
         <v>169</v>
       </c>
       <c r="G67" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H67" s="2">
         <v>46156</v>
       </c>
       <c r="I67" s="3">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J67" t="s">
         <v>38</v>
@@ -4693,10 +4723,10 @@
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2">
         <v>46135</v>
@@ -4705,19 +4735,19 @@
         <v>35</v>
       </c>
       <c r="E68" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H68" s="2">
         <v>46155</v>
       </c>
       <c r="I68" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J68" t="s">
         <v>38</v>
@@ -4731,10 +4761,10 @@
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B69" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2">
         <v>46136</v>
@@ -4743,19 +4773,19 @@
         <v>35</v>
       </c>
       <c r="E69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H69" s="2">
         <v>46157</v>
       </c>
       <c r="I69" s="3">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -4772,7 +4802,7 @@
         <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2">
         <v>45804</v>
@@ -4781,19 +4811,19 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H70" s="2">
         <v>45943</v>
       </c>
       <c r="I70" s="3">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="J70" t="s">
         <v>28</v>
@@ -4810,7 +4840,7 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C71" s="2">
         <v>45513</v>
@@ -4819,25 +4849,25 @@
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F71" t="s">
         <v>128</v>
       </c>
       <c r="G71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H71" s="2">
         <v>45715</v>
       </c>
       <c r="I71" s="3">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="J71" t="s">
         <v>52</v>
       </c>
       <c r="K71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L71" s="2">
         <v>45712</v>
@@ -4859,7 +4889,7 @@
         <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C72" s="2">
         <v>45659</v>
@@ -4868,25 +4898,25 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F72" t="s">
         <v>66</v>
       </c>
       <c r="G72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H72" s="2">
         <v>45817</v>
       </c>
       <c r="I72" s="3">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="J72" t="s">
         <v>52</v>
       </c>
       <c r="K72" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L72" s="2">
         <v>45812</v>
@@ -4898,7 +4928,7 @@
         <v>46909</v>
       </c>
       <c r="T72" s="3">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="U72" s="3"/>
       <c r="V72" s="4">
@@ -4910,7 +4940,7 @@
         <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C73" s="2">
         <v>45492</v>
@@ -4919,7 +4949,7 @@
         <v>44</v>
       </c>
       <c r="E73" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F73" t="s">
         <v>42</v>
@@ -4931,13 +4961,13 @@
         <v>45911</v>
       </c>
       <c r="I73" s="3">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="J73" t="s">
         <v>52</v>
       </c>
       <c r="K73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L73" s="2">
         <v>45546</v>
@@ -4962,7 +4992,7 @@
         <v>26</v>
       </c>
       <c r="B74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C74" s="2">
         <v>45786</v>
@@ -4971,19 +5001,19 @@
         <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F74" t="s">
         <v>141</v>
       </c>
       <c r="G74" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H74" s="2">
         <v>45895</v>
       </c>
       <c r="I74" s="3">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="J74" t="s">
         <v>38</v>
@@ -5000,7 +5030,7 @@
         <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C75" s="2">
         <v>45946</v>
@@ -5009,19 +5039,19 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
+        <v>300</v>
+      </c>
+      <c r="F75" t="s">
         <v>301</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>302</v>
-      </c>
-      <c r="G75" t="s">
-        <v>303</v>
       </c>
       <c r="H75" s="2">
         <v>46196</v>
       </c>
       <c r="I75" s="3">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J75" t="s">
         <v>28</v>
@@ -5035,10 +5065,10 @@
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
+        <v>303</v>
+      </c>
+      <c r="B76" t="s">
         <v>304</v>
-      </c>
-      <c r="B76" t="s">
-        <v>305</v>
       </c>
       <c r="C76" s="2">
         <v>45665</v>
@@ -5047,25 +5077,25 @@
         <v>35</v>
       </c>
       <c r="E76" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H76" s="2">
         <v>46198</v>
       </c>
       <c r="I76" s="3">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J76" t="s">
         <v>38</v>
       </c>
       <c r="K76" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L76" s="2">
         <v>46071</v>
@@ -5074,7 +5104,7 @@
         <v>406</v>
       </c>
       <c r="O76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P76" s="2">
         <v>46294</v>
@@ -5084,7 +5114,7 @@
       </c>
       <c r="T76" s="3"/>
       <c r="U76" s="3">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="V76" s="4">
         <v>51071</v>
@@ -5104,7 +5134,7 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F77" t="s">
         <v>42</v>
@@ -5116,13 +5146,13 @@
         <v>45790</v>
       </c>
       <c r="I77" s="3">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="J77" t="s">
         <v>52</v>
       </c>
       <c r="K77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L77" s="2">
         <v>43964</v>
@@ -5147,53 +5177,40 @@
     </row>
     <row r="78" spans="1:22">
       <c r="A78" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B78" t="s">
+        <v>311</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46210</v>
+      </c>
+      <c r="D78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" t="s">
         <v>312</v>
       </c>
-      <c r="C78" s="2">
-        <v>45915</v>
-      </c>
-      <c r="D78" t="s">
-        <v>24</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" t="s">
         <v>313</v>
       </c>
-      <c r="F78" t="s">
-        <v>141</v>
-      </c>
-      <c r="G78" t="s">
-        <v>314</v>
-      </c>
       <c r="H78" s="2">
-        <v>46094</v>
+        <v>46216</v>
       </c>
       <c r="I78" s="3">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="J78" t="s">
-        <v>38</v>
-      </c>
-      <c r="K78" t="s">
-        <v>315</v>
-      </c>
-      <c r="L78" s="2">
-        <v>46086</v>
-      </c>
-      <c r="M78" s="3">
-        <v>171</v>
-      </c>
-      <c r="S78" s="2">
-        <v>47181</v>
-      </c>
-      <c r="T78" s="3">
-        <v>943</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="T78" s="3"/>
       <c r="U78" s="3"/>
       <c r="V78" s="4">
-        <v>71265.600000000006</v>
+        <v>67057.570000000007</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5201,54 +5218,50 @@
         <v>42</v>
       </c>
       <c r="B79" t="s">
+        <v>314</v>
+      </c>
+      <c r="C79" s="2">
+        <v>45915</v>
+      </c>
+      <c r="D79" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" t="s">
+        <v>315</v>
+      </c>
+      <c r="F79" t="s">
+        <v>141</v>
+      </c>
+      <c r="G79" t="s">
         <v>316</v>
       </c>
-      <c r="C79" s="2">
-        <v>45950</v>
-      </c>
-      <c r="D79" t="s">
-        <v>44</v>
-      </c>
-      <c r="E79" t="s">
-        <v>317</v>
-      </c>
-      <c r="F79" t="s">
-        <v>42</v>
-      </c>
-      <c r="G79" t="s">
-        <v>318</v>
-      </c>
       <c r="H79" s="2">
-        <v>45975</v>
+        <v>46094</v>
       </c>
       <c r="I79" s="3">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="J79" t="s">
         <v>38</v>
       </c>
       <c r="K79" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L79" s="2">
-        <v>45978</v>
+        <v>46086</v>
       </c>
       <c r="M79" s="3">
-        <v>28</v>
-      </c>
-      <c r="O79" t="s">
-        <v>59</v>
-      </c>
-      <c r="P79" s="2">
-        <v>46220</v>
+        <v>171</v>
       </c>
       <c r="S79" s="2">
-        <v>46220</v>
-      </c>
-      <c r="T79" s="3"/>
+        <v>47181</v>
+      </c>
+      <c r="T79" s="3">
+        <v>934</v>
+      </c>
       <c r="U79" s="3"/>
       <c r="V79" s="4">
-        <v>71722</v>
+        <v>71265.600000000006</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -5256,50 +5269,54 @@
         <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C80" s="2">
-        <v>45915</v>
+        <v>45950</v>
       </c>
       <c r="D80" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E80" t="s">
+        <v>319</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" t="s">
         <v>320</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" s="2">
+        <v>45975</v>
+      </c>
+      <c r="I80" s="3">
+        <v>272</v>
+      </c>
+      <c r="J80" t="s">
+        <v>38</v>
+      </c>
+      <c r="K80" t="s">
         <v>321</v>
       </c>
-      <c r="G80" t="s">
-        <v>322</v>
-      </c>
-      <c r="H80" s="2">
-        <v>46237</v>
-      </c>
-      <c r="I80" s="3">
-        <v>1</v>
-      </c>
-      <c r="J80" t="s">
-        <v>273</v>
-      </c>
-      <c r="K80" t="s">
-        <v>323</v>
-      </c>
       <c r="L80" s="2">
-        <v>46086</v>
+        <v>45978</v>
       </c>
       <c r="M80" s="3">
-        <v>171</v>
+        <v>28</v>
+      </c>
+      <c r="O80" t="s">
+        <v>59</v>
+      </c>
+      <c r="P80" s="2">
+        <v>46220</v>
       </c>
       <c r="S80" s="2">
-        <v>47181</v>
-      </c>
-      <c r="T80" s="3">
-        <v>943</v>
-      </c>
+        <v>46220</v>
+      </c>
+      <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="4">
-        <v>73620</v>
+        <v>71722</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -5307,7 +5324,7 @@
         <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C81" s="2">
         <v>45915</v>
@@ -5316,22 +5333,22 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
+        <v>322</v>
+      </c>
+      <c r="F81" t="s">
+        <v>323</v>
+      </c>
+      <c r="G81" t="s">
         <v>324</v>
       </c>
-      <c r="F81" t="s">
-        <v>141</v>
-      </c>
-      <c r="G81" t="s">
-        <v>314</v>
-      </c>
       <c r="H81" s="2">
-        <v>46094</v>
+        <v>46241</v>
       </c>
       <c r="I81" s="3">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="J81" t="s">
-        <v>38</v>
+        <v>269</v>
       </c>
       <c r="K81" t="s">
         <v>325</v>
@@ -5346,11 +5363,11 @@
         <v>47181</v>
       </c>
       <c r="T81" s="3">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
-        <v>104220</v>
+        <v>73620</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -5358,54 +5375,50 @@
         <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="C82" s="2">
-        <v>43902</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>61</v>
+        <v>326</v>
       </c>
       <c r="F82" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="G82" t="s">
-        <v>148</v>
+        <v>316</v>
       </c>
       <c r="H82" s="2">
-        <v>45790</v>
+        <v>46094</v>
       </c>
       <c r="I82" s="3">
-        <v>448</v>
+        <v>153</v>
       </c>
       <c r="J82" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K82" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L82" s="2">
-        <v>43964</v>
+        <v>46086</v>
       </c>
       <c r="M82" s="3">
-        <v>62</v>
-      </c>
-      <c r="O82" t="s">
-        <v>69</v>
-      </c>
-      <c r="P82" s="2">
-        <v>46160</v>
+        <v>171</v>
       </c>
       <c r="S82" s="2">
-        <v>44917</v>
-      </c>
-      <c r="T82" s="3"/>
+        <v>47181</v>
+      </c>
+      <c r="T82" s="3">
+        <v>934</v>
+      </c>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
-        <v>139755.72</v>
+        <v>104220</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -5413,50 +5426,54 @@
         <v>42</v>
       </c>
       <c r="B83" t="s">
-        <v>327</v>
+        <v>60</v>
       </c>
       <c r="C83" s="2">
-        <v>45819</v>
+        <v>43902</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>328</v>
+        <v>61</v>
       </c>
       <c r="F83" t="s">
         <v>42</v>
       </c>
       <c r="G83" t="s">
-        <v>329</v>
+        <v>148</v>
       </c>
       <c r="H83" s="2">
-        <v>46170</v>
+        <v>45790</v>
       </c>
       <c r="I83" s="3">
-        <v>68</v>
+        <v>457</v>
       </c>
       <c r="J83" t="s">
         <v>52</v>
       </c>
       <c r="K83" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L83" s="2">
-        <v>45904</v>
+        <v>43964</v>
       </c>
       <c r="M83" s="3">
-        <v>85</v>
+        <v>62</v>
+      </c>
+      <c r="O83" t="s">
+        <v>69</v>
+      </c>
+      <c r="P83" s="2">
+        <v>46160</v>
       </c>
       <c r="S83" s="2">
-        <v>46273</v>
-      </c>
-      <c r="T83" s="3">
-        <v>35</v>
-      </c>
+        <v>44917</v>
+      </c>
+      <c r="T83" s="3"/>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
-        <v>230000</v>
+        <v>139755.72</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -5464,50 +5481,37 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C84" s="2">
-        <v>45952</v>
+        <v>46245</v>
       </c>
       <c r="D84" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E84" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F84" t="s">
-        <v>333</v>
+        <v>26</v>
       </c>
       <c r="G84" t="s">
-        <v>334</v>
+        <v>264</v>
       </c>
       <c r="H84" s="2">
-        <v>46087</v>
+        <v>46246</v>
       </c>
       <c r="I84" s="3">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="J84" t="s">
-        <v>52</v>
-      </c>
-      <c r="K84" t="s">
-        <v>335</v>
-      </c>
-      <c r="L84" s="2">
-        <v>46086</v>
-      </c>
-      <c r="M84" s="3">
-        <v>134</v>
-      </c>
-      <c r="S84" s="2">
-        <v>47910</v>
-      </c>
-      <c r="T84" s="3">
-        <v>1672</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="4">
-        <v>250977.6</v>
+        <v>180600</v>
       </c>
     </row>
     <row r="85" spans="1:22">
@@ -5515,48 +5519,50 @@
         <v>42</v>
       </c>
       <c r="B85" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="C85" s="2">
-        <v>45775</v>
+        <v>45819</v>
       </c>
       <c r="D85" t="s">
         <v>44</v>
       </c>
       <c r="E85" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F85" t="s">
         <v>42</v>
       </c>
       <c r="G85" t="s">
-        <v>51</v>
+        <v>333</v>
       </c>
       <c r="H85" s="2">
-        <v>45861</v>
+        <v>46170</v>
       </c>
       <c r="I85" s="3">
-        <v>377</v>
+        <v>77</v>
       </c>
       <c r="J85" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K85" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="L85" s="2">
-        <v>45856</v>
+        <v>45904</v>
       </c>
       <c r="M85" s="3">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="S85" s="2">
-        <v>46225</v>
-      </c>
-      <c r="T85" s="3"/>
+        <v>46273</v>
+      </c>
+      <c r="T85" s="3">
+        <v>26</v>
+      </c>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
-        <v>288862</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -5564,37 +5570,50 @@
         <v>42</v>
       </c>
       <c r="B86" t="s">
+        <v>335</v>
+      </c>
+      <c r="C86" s="2">
+        <v>45952</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" t="s">
+        <v>336</v>
+      </c>
+      <c r="F86" t="s">
         <v>337</v>
       </c>
-      <c r="C86" s="2">
-        <v>45539</v>
-      </c>
-      <c r="D86" t="s">
-        <v>44</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="G86" t="s">
         <v>338</v>
       </c>
-      <c r="F86" t="s">
-        <v>339</v>
-      </c>
-      <c r="G86" t="s">
-        <v>340</v>
-      </c>
       <c r="H86" s="2">
-        <v>45607</v>
+        <v>46087</v>
       </c>
       <c r="I86" s="3">
-        <v>631</v>
+        <v>160</v>
       </c>
       <c r="J86" t="s">
         <v>52</v>
       </c>
-      <c r="M86" s="3"/>
-      <c r="T86" s="3"/>
+      <c r="K86" t="s">
+        <v>339</v>
+      </c>
+      <c r="L86" s="2">
+        <v>46086</v>
+      </c>
+      <c r="M86" s="3">
+        <v>134</v>
+      </c>
+      <c r="S86" s="2">
+        <v>47910</v>
+      </c>
+      <c r="T86" s="3">
+        <v>1663</v>
+      </c>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
-        <v>297600</v>
+        <v>250977.6</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -5602,50 +5621,48 @@
         <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="C87" s="2">
-        <v>45840</v>
+        <v>45775</v>
       </c>
       <c r="D87" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E87" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F87" t="s">
-        <v>343</v>
+        <v>42</v>
       </c>
       <c r="G87" t="s">
-        <v>344</v>
+        <v>51</v>
       </c>
       <c r="H87" s="2">
-        <v>46002</v>
+        <v>45861</v>
       </c>
       <c r="I87" s="3">
-        <v>236</v>
+        <v>386</v>
       </c>
       <c r="J87" t="s">
         <v>38</v>
       </c>
       <c r="K87" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="L87" s="2">
-        <v>46001</v>
+        <v>45856</v>
       </c>
       <c r="M87" s="3">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="S87" s="2">
-        <v>47097</v>
-      </c>
-      <c r="T87" s="3">
-        <v>859</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="T87" s="3"/>
       <c r="U87" s="3"/>
       <c r="V87" s="4">
-        <v>299821.5</v>
+        <v>288862</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -5653,50 +5670,37 @@
         <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C88" s="2">
-        <v>45868</v>
+        <v>45539</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F88" t="s">
-        <v>66</v>
+        <v>343</v>
       </c>
       <c r="G88" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="H88" s="2">
-        <v>46146</v>
+        <v>45607</v>
       </c>
       <c r="I88" s="3">
-        <v>92</v>
+        <v>640</v>
       </c>
       <c r="J88" t="s">
         <v>52</v>
       </c>
-      <c r="K88" t="s">
-        <v>349</v>
-      </c>
-      <c r="L88" s="2">
-        <v>46077</v>
-      </c>
-      <c r="M88" s="3">
-        <v>209</v>
-      </c>
-      <c r="S88" s="2">
-        <v>47905</v>
-      </c>
-      <c r="T88" s="3">
-        <v>1667</v>
-      </c>
+      <c r="M88" s="3"/>
+      <c r="T88" s="3"/>
       <c r="U88" s="3"/>
       <c r="V88" s="4">
-        <v>338580</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -5704,56 +5708,50 @@
         <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C89" s="2">
-        <v>44370</v>
+        <v>45840</v>
       </c>
       <c r="D89" t="s">
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F89" t="s">
-        <v>42</v>
+        <v>347</v>
       </c>
       <c r="G89" t="s">
-        <v>148</v>
+        <v>348</v>
       </c>
       <c r="H89" s="2">
-        <v>45881</v>
+        <v>46002</v>
       </c>
       <c r="I89" s="3">
-        <v>357</v>
+        <v>245</v>
       </c>
       <c r="J89" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K89" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="L89" s="2">
-        <v>44589</v>
+        <v>46001</v>
       </c>
       <c r="M89" s="3">
-        <v>219</v>
-      </c>
-      <c r="O89" t="s">
-        <v>353</v>
-      </c>
-      <c r="P89" s="2">
-        <v>46419</v>
+        <v>161</v>
       </c>
       <c r="S89" s="2">
-        <v>44593</v>
-      </c>
-      <c r="T89" s="3"/>
-      <c r="U89" s="3">
-        <v>181</v>
-      </c>
+        <v>47097</v>
+      </c>
+      <c r="T89" s="3">
+        <v>850</v>
+      </c>
+      <c r="U89" s="3"/>
       <c r="V89" s="4">
-        <v>374899.96</v>
+        <v>299821.5</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -5761,240 +5759,251 @@
         <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C90" s="2">
-        <v>45422</v>
+        <v>45868</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F90" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G90" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H90" s="2">
-        <v>45624</v>
+        <v>46146</v>
       </c>
       <c r="I90" s="3">
-        <v>614</v>
+        <v>101</v>
       </c>
       <c r="J90" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K90" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="L90" s="2">
-        <v>45544</v>
+        <v>46077</v>
       </c>
       <c r="M90" s="3">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="S90" s="2">
-        <v>45911</v>
-      </c>
-      <c r="T90" s="3"/>
+        <v>47905</v>
+      </c>
+      <c r="T90" s="3">
+        <v>1658</v>
+      </c>
       <c r="U90" s="3"/>
       <c r="V90" s="4">
-        <v>457600</v>
+        <v>338580</v>
       </c>
     </row>
     <row r="91" spans="1:22">
       <c r="A91" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C91" s="2">
-        <v>46038</v>
+        <v>44370</v>
       </c>
       <c r="D91" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F91" t="s">
         <v>42</v>
       </c>
       <c r="G91" t="s">
-        <v>360</v>
+        <v>148</v>
       </c>
       <c r="H91" s="2">
-        <v>46237</v>
+        <v>45881</v>
       </c>
       <c r="I91" s="3">
-        <v>1</v>
+        <v>366</v>
       </c>
       <c r="J91" t="s">
         <v>52</v>
       </c>
-      <c r="M91" s="3"/>
+      <c r="K91" t="s">
+        <v>356</v>
+      </c>
+      <c r="L91" s="2">
+        <v>44589</v>
+      </c>
+      <c r="M91" s="3">
+        <v>219</v>
+      </c>
+      <c r="O91" t="s">
+        <v>357</v>
+      </c>
+      <c r="P91" s="2">
+        <v>46419</v>
+      </c>
+      <c r="S91" s="2">
+        <v>44593</v>
+      </c>
       <c r="T91" s="3"/>
-      <c r="U91" s="3"/>
+      <c r="U91" s="3">
+        <v>172</v>
+      </c>
       <c r="V91" s="4">
-        <v>687500</v>
+        <v>374899.96</v>
       </c>
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B92" t="s">
+        <v>358</v>
+      </c>
+      <c r="C92" s="2">
+        <v>45422</v>
+      </c>
+      <c r="D92" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" t="s">
+        <v>359</v>
+      </c>
+      <c r="F92" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" t="s">
+        <v>360</v>
+      </c>
+      <c r="H92" s="2">
+        <v>45624</v>
+      </c>
+      <c r="I92" s="3">
+        <v>623</v>
+      </c>
+      <c r="J92" t="s">
+        <v>38</v>
+      </c>
+      <c r="K92" t="s">
         <v>361</v>
       </c>
-      <c r="C92" s="2">
-        <v>44939</v>
-      </c>
-      <c r="D92" t="s">
-        <v>362</v>
-      </c>
-      <c r="E92" t="s">
-        <v>363</v>
-      </c>
-      <c r="F92" t="s">
-        <v>29</v>
-      </c>
-      <c r="G92" t="s">
-        <v>364</v>
-      </c>
-      <c r="H92" s="2">
-        <v>45979</v>
-      </c>
-      <c r="I92" s="3">
-        <v>259</v>
-      </c>
-      <c r="J92" t="s">
-        <v>52</v>
-      </c>
-      <c r="K92" t="s">
-        <v>365</v>
-      </c>
       <c r="L92" s="2">
-        <v>45968</v>
+        <v>45544</v>
       </c>
       <c r="M92" s="3">
-        <v>1029</v>
-      </c>
-      <c r="O92" t="s">
-        <v>353</v>
-      </c>
-      <c r="P92" s="2">
-        <v>46426</v>
+        <v>122</v>
       </c>
       <c r="S92" s="2">
-        <v>45334</v>
+        <v>45911</v>
       </c>
       <c r="T92" s="3"/>
-      <c r="U92" s="3">
-        <v>188</v>
-      </c>
+      <c r="U92" s="3"/>
       <c r="V92" s="4">
-        <v>706431.6</v>
+        <v>457600</v>
       </c>
     </row>
     <row r="93" spans="1:22">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B93" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C93" s="2">
-        <v>45673</v>
+        <v>46038</v>
       </c>
       <c r="D93" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E93" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
       </c>
       <c r="G93" t="s">
-        <v>51</v>
+        <v>364</v>
       </c>
       <c r="H93" s="2">
-        <v>46140</v>
+        <v>46237</v>
       </c>
       <c r="I93" s="3">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="J93" t="s">
         <v>52</v>
       </c>
-      <c r="K93" t="s">
-        <v>368</v>
-      </c>
       <c r="M93" s="3"/>
-      <c r="S93" s="2">
-        <v>46598</v>
-      </c>
-      <c r="T93" s="3">
-        <v>360</v>
-      </c>
+      <c r="T93" s="3"/>
       <c r="U93" s="3"/>
       <c r="V93" s="4">
-        <v>890000</v>
+        <v>687500</v>
       </c>
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B94" t="s">
+        <v>365</v>
+      </c>
+      <c r="C94" s="2">
+        <v>44939</v>
+      </c>
+      <c r="D94" t="s">
+        <v>366</v>
+      </c>
+      <c r="E94" t="s">
+        <v>367</v>
+      </c>
+      <c r="F94" t="s">
+        <v>29</v>
+      </c>
+      <c r="G94" t="s">
+        <v>368</v>
+      </c>
+      <c r="H94" s="2">
+        <v>45979</v>
+      </c>
+      <c r="I94" s="3">
+        <v>268</v>
+      </c>
+      <c r="J94" t="s">
+        <v>52</v>
+      </c>
+      <c r="K94" t="s">
         <v>369</v>
       </c>
-      <c r="C94" s="2">
-        <v>45215</v>
-      </c>
-      <c r="D94" t="s">
-        <v>24</v>
-      </c>
-      <c r="E94" t="s">
-        <v>370</v>
-      </c>
-      <c r="F94" t="s">
-        <v>169</v>
-      </c>
-      <c r="G94" t="s">
-        <v>371</v>
-      </c>
-      <c r="H94" s="2">
-        <v>45687</v>
-      </c>
-      <c r="I94" s="3">
-        <v>551</v>
-      </c>
-      <c r="J94" t="s">
-        <v>38</v>
-      </c>
-      <c r="K94" t="s">
-        <v>372</v>
-      </c>
       <c r="L94" s="2">
-        <v>45685</v>
+        <v>45968</v>
       </c>
       <c r="M94" s="3">
-        <v>470</v>
+        <v>1029</v>
+      </c>
+      <c r="O94" t="s">
+        <v>357</v>
+      </c>
+      <c r="P94" s="2">
+        <v>46426</v>
       </c>
       <c r="S94" s="2">
-        <v>46780</v>
-      </c>
-      <c r="T94" s="3">
-        <v>542</v>
-      </c>
-      <c r="U94" s="3"/>
+        <v>45334</v>
+      </c>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3">
+        <v>179</v>
+      </c>
       <c r="V94" s="4">
-        <v>1220266.1399999999</v>
+        <v>706431.6</v>
       </c>
     </row>
     <row r="95" spans="1:22">
@@ -6002,99 +6011,96 @@
         <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C95" s="2">
-        <v>45366</v>
+        <v>45673</v>
       </c>
       <c r="D95" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
       </c>
       <c r="G95" t="s">
-        <v>375</v>
+        <v>51</v>
       </c>
       <c r="H95" s="2">
-        <v>45481</v>
+        <v>46140</v>
       </c>
       <c r="I95" s="3">
-        <v>757</v>
+        <v>107</v>
       </c>
       <c r="J95" t="s">
         <v>52</v>
       </c>
       <c r="K95" t="s">
-        <v>376</v>
-      </c>
-      <c r="L95" s="2">
-        <v>45471</v>
-      </c>
-      <c r="M95" s="3">
-        <v>105</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="M95" s="3"/>
       <c r="S95" s="2">
-        <v>47301</v>
+        <v>46598</v>
       </c>
       <c r="T95" s="3">
-        <v>1063</v>
+        <v>351</v>
       </c>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
-        <v>1245414.49</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C96" s="2">
-        <v>45152</v>
+        <v>45215</v>
       </c>
       <c r="D96" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F96" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="G96" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H96" s="2">
-        <v>45440</v>
+        <v>45687</v>
       </c>
       <c r="I96" s="3">
-        <v>798</v>
+        <v>560</v>
       </c>
       <c r="J96" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K96" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="L96" s="2">
-        <v>45303</v>
+        <v>45685</v>
       </c>
       <c r="M96" s="3">
-        <v>151</v>
+        <v>470</v>
       </c>
       <c r="S96" s="2">
-        <v>45992</v>
-      </c>
-      <c r="T96" s="3"/>
+        <v>46780</v>
+      </c>
+      <c r="T96" s="3">
+        <v>533</v>
+      </c>
       <c r="U96" s="3"/>
       <c r="V96" s="4">
-        <v>1298031.3600000001</v>
+        <v>1220266.1399999999</v>
       </c>
     </row>
     <row r="97" spans="1:22">
@@ -6102,105 +6108,99 @@
         <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C97" s="2">
-        <v>45373</v>
+        <v>45366</v>
       </c>
       <c r="D97" t="s">
         <v>44</v>
       </c>
       <c r="E97" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
       </c>
       <c r="G97" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H97" s="2">
-        <v>45492</v>
+        <v>45481</v>
       </c>
       <c r="I97" s="3">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="J97" t="s">
         <v>52</v>
       </c>
       <c r="K97" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="L97" s="2">
-        <v>45492</v>
+        <v>45471</v>
       </c>
       <c r="M97" s="3">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="S97" s="2">
-        <v>46587</v>
+        <v>47301</v>
       </c>
       <c r="T97" s="3">
-        <v>349</v>
+        <v>1054</v>
       </c>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
-        <v>1320176.8799999999</v>
+        <v>1245414.49</v>
       </c>
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C98" s="2">
-        <v>44663</v>
+        <v>45152</v>
       </c>
       <c r="D98" t="s">
-        <v>24</v>
+        <v>266</v>
       </c>
       <c r="E98" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F98" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="G98" t="s">
-        <v>200</v>
+        <v>383</v>
       </c>
       <c r="H98" s="2">
-        <v>45588</v>
+        <v>45440</v>
       </c>
       <c r="I98" s="3">
-        <v>650</v>
+        <v>807</v>
       </c>
       <c r="J98" t="s">
         <v>52</v>
       </c>
       <c r="K98" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L98" s="2">
-        <v>44893</v>
+        <v>45303</v>
       </c>
       <c r="M98" s="3">
-        <v>230</v>
-      </c>
-      <c r="O98" t="s">
-        <v>59</v>
-      </c>
-      <c r="P98" s="2">
-        <v>45996</v>
+        <v>151</v>
       </c>
       <c r="S98" s="2">
-        <v>45624</v>
+        <v>45992</v>
       </c>
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="4">
-        <v>1416380</v>
+        <v>1298031.3600000001</v>
       </c>
     </row>
     <row r="99" spans="1:22">
@@ -6208,88 +6208,105 @@
         <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C99" s="2">
-        <v>45826</v>
+        <v>45373</v>
       </c>
       <c r="D99" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E99" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F99" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="G99" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="H99" s="2">
-        <v>46079</v>
+        <v>45492</v>
       </c>
       <c r="I99" s="3">
-        <v>159</v>
+        <v>755</v>
       </c>
       <c r="J99" t="s">
         <v>52</v>
       </c>
       <c r="K99" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="L99" s="2">
-        <v>46076</v>
+        <v>45492</v>
       </c>
       <c r="M99" s="3">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="S99" s="2">
-        <v>47903</v>
+        <v>46587</v>
       </c>
       <c r="T99" s="3">
-        <v>1665</v>
+        <v>340</v>
       </c>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
-        <v>1435000</v>
+        <v>1320176.8799999999</v>
       </c>
     </row>
     <row r="100" spans="1:22">
       <c r="A100" t="s">
-        <v>391</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C100" s="2">
-        <v>46150</v>
+        <v>44663</v>
       </c>
       <c r="D100" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F100" t="s">
-        <v>391</v>
+        <v>128</v>
       </c>
       <c r="G100" t="s">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="H100" s="2">
-        <v>46206</v>
+        <v>45588</v>
       </c>
       <c r="I100" s="3">
-        <v>32</v>
+        <v>659</v>
       </c>
       <c r="J100" t="s">
         <v>52</v>
       </c>
-      <c r="M100" s="3"/>
+      <c r="K100" t="s">
+        <v>390</v>
+      </c>
+      <c r="L100" s="2">
+        <v>44893</v>
+      </c>
+      <c r="M100" s="3">
+        <v>230</v>
+      </c>
+      <c r="O100" t="s">
+        <v>59</v>
+      </c>
+      <c r="P100" s="2">
+        <v>45996</v>
+      </c>
+      <c r="S100" s="2">
+        <v>45624</v>
+      </c>
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="4">
-        <v>1719174</v>
+        <v>1416380</v>
       </c>
     </row>
     <row r="101" spans="1:22">
@@ -6297,88 +6314,88 @@
         <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C101" s="2">
-        <v>46094</v>
+        <v>45826</v>
       </c>
       <c r="D101" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F101" t="s">
-        <v>396</v>
+        <v>66</v>
       </c>
       <c r="G101" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="H101" s="2">
-        <v>46211</v>
+        <v>46079</v>
       </c>
       <c r="I101" s="3">
-        <v>27</v>
+        <v>168</v>
       </c>
       <c r="J101" t="s">
         <v>52</v>
       </c>
-      <c r="M101" s="3"/>
-      <c r="T101" s="3"/>
+      <c r="K101" t="s">
+        <v>394</v>
+      </c>
+      <c r="L101" s="2">
+        <v>46076</v>
+      </c>
+      <c r="M101" s="3">
+        <v>250</v>
+      </c>
+      <c r="S101" s="2">
+        <v>47903</v>
+      </c>
+      <c r="T101" s="3">
+        <v>1656</v>
+      </c>
       <c r="U101" s="3"/>
       <c r="V101" s="4">
-        <v>1828126.08</v>
+        <v>1435000</v>
       </c>
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
-        <v>42</v>
+        <v>395</v>
       </c>
       <c r="B102" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C102" s="2">
-        <v>45950</v>
+        <v>46150</v>
       </c>
       <c r="D102" t="s">
         <v>44</v>
       </c>
       <c r="E102" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F102" t="s">
-        <v>42</v>
+        <v>395</v>
       </c>
       <c r="G102" t="s">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="H102" s="2">
-        <v>45988</v>
+        <v>46206</v>
       </c>
       <c r="I102" s="3">
-        <v>250</v>
+        <v>41</v>
       </c>
       <c r="J102" t="s">
-        <v>38</v>
-      </c>
-      <c r="K102" t="s">
-        <v>401</v>
-      </c>
-      <c r="L102" s="2">
-        <v>45979</v>
-      </c>
-      <c r="M102" s="3">
-        <v>29</v>
-      </c>
-      <c r="S102" s="2">
-        <v>46343</v>
-      </c>
-      <c r="T102" s="3">
-        <v>105</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M102" s="3"/>
+      <c r="T102" s="3"/>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
-        <v>2075682</v>
+        <v>1719174</v>
       </c>
     </row>
     <row r="103" spans="1:22">
@@ -6386,487 +6403,452 @@
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C103" s="2">
-        <v>45511</v>
+        <v>46094</v>
       </c>
       <c r="D103" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E103" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F103" t="s">
-        <v>26</v>
+        <v>400</v>
       </c>
       <c r="G103" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H103" s="2">
-        <v>45786</v>
+        <v>46211</v>
       </c>
       <c r="I103" s="3">
-        <v>452</v>
+        <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>38</v>
-      </c>
-      <c r="K103" t="s">
-        <v>405</v>
-      </c>
-      <c r="L103" s="2">
-        <v>45794</v>
-      </c>
-      <c r="M103" s="3">
-        <v>283</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M103" s="3"/>
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
       <c r="V103" s="4">
-        <v>2594055</v>
+        <v>1828126.08</v>
       </c>
     </row>
     <row r="104" spans="1:22">
       <c r="A104" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C104" s="2">
-        <v>45848</v>
+        <v>45950</v>
       </c>
       <c r="D104" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E104" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F104" t="s">
-        <v>224</v>
+        <v>42</v>
       </c>
       <c r="G104" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="H104" s="2">
-        <v>46014</v>
+        <v>45988</v>
       </c>
       <c r="I104" s="3">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="J104" t="s">
         <v>38</v>
       </c>
       <c r="K104" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="L104" s="2">
-        <v>46008</v>
+        <v>45979</v>
       </c>
       <c r="M104" s="3">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="S104" s="2">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="T104" s="3">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
-        <v>2641069.35</v>
+        <v>2075682</v>
       </c>
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="2">
+        <v>45511</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" t="s">
+        <v>407</v>
+      </c>
+      <c r="F105" t="s">
         <v>26</v>
       </c>
-      <c r="B105" t="s">
-        <v>410</v>
-      </c>
-      <c r="C105" s="2">
-        <v>46030</v>
-      </c>
-      <c r="D105" t="s">
-        <v>270</v>
-      </c>
-      <c r="E105" t="s">
-        <v>411</v>
-      </c>
-      <c r="F105" t="s">
-        <v>29</v>
-      </c>
       <c r="G105" t="s">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="H105" s="2">
-        <v>46237</v>
+        <v>45786</v>
       </c>
       <c r="I105" s="3">
-        <v>1</v>
+        <v>461</v>
       </c>
       <c r="J105" t="s">
-        <v>52</v>
-      </c>
-      <c r="M105" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="K105" t="s">
+        <v>409</v>
+      </c>
+      <c r="L105" s="2">
+        <v>45794</v>
+      </c>
+      <c r="M105" s="3">
+        <v>283</v>
+      </c>
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
       <c r="V105" s="4">
-        <v>2652975.2799999998</v>
+        <v>2594055</v>
       </c>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B106" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C106" s="2">
-        <v>45365</v>
+        <v>45848</v>
       </c>
       <c r="D106" t="s">
         <v>35</v>
       </c>
       <c r="E106" t="s">
+        <v>411</v>
+      </c>
+      <c r="F106" t="s">
+        <v>224</v>
+      </c>
+      <c r="G106" t="s">
+        <v>412</v>
+      </c>
+      <c r="H106" s="2">
+        <v>46014</v>
+      </c>
+      <c r="I106" s="3">
+        <v>233</v>
+      </c>
+      <c r="J106" t="s">
+        <v>38</v>
+      </c>
+      <c r="K106" t="s">
         <v>413</v>
       </c>
-      <c r="F106" t="s">
-        <v>414</v>
-      </c>
-      <c r="G106" t="s">
-        <v>415</v>
-      </c>
-      <c r="H106" s="2">
-        <v>45568</v>
-      </c>
-      <c r="I106" s="3">
-        <v>670</v>
-      </c>
-      <c r="J106" t="s">
-        <v>52</v>
-      </c>
-      <c r="K106" t="s">
-        <v>416</v>
-      </c>
       <c r="L106" s="2">
-        <v>45567</v>
+        <v>46008</v>
       </c>
       <c r="M106" s="3">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="S106" s="2">
-        <v>46479</v>
+        <v>46373</v>
       </c>
       <c r="T106" s="3">
-        <v>241</v>
+        <v>126</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
-        <v>2780400.6</v>
+        <v>2641069.35</v>
       </c>
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C107" s="2">
-        <v>46232</v>
+        <v>46030</v>
       </c>
       <c r="D107" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
       <c r="E107" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F107" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G107" t="s">
-        <v>419</v>
+        <v>364</v>
       </c>
       <c r="H107" s="2">
         <v>46237</v>
       </c>
       <c r="I107" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J107" t="s">
-        <v>262</v>
+        <v>52</v>
       </c>
       <c r="M107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
-        <v>3446570</v>
+        <v>2652975.2799999998</v>
       </c>
     </row>
     <row r="108" spans="1:22">
       <c r="A108" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B108" t="s">
+        <v>416</v>
+      </c>
+      <c r="C108" s="2">
+        <v>45365</v>
+      </c>
+      <c r="D108" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" t="s">
+        <v>417</v>
+      </c>
+      <c r="F108" t="s">
+        <v>418</v>
+      </c>
+      <c r="G108" t="s">
+        <v>419</v>
+      </c>
+      <c r="H108" s="2">
+        <v>45568</v>
+      </c>
+      <c r="I108" s="3">
+        <v>679</v>
+      </c>
+      <c r="J108" t="s">
+        <v>52</v>
+      </c>
+      <c r="K108" t="s">
         <v>420</v>
       </c>
-      <c r="C108" s="2">
-        <v>45824</v>
-      </c>
-      <c r="D108" t="s">
-        <v>24</v>
-      </c>
-      <c r="E108" t="s">
-        <v>421</v>
-      </c>
-      <c r="F108" t="s">
-        <v>222</v>
-      </c>
-      <c r="G108" t="s">
-        <v>422</v>
-      </c>
-      <c r="H108" s="2">
-        <v>46237</v>
-      </c>
-      <c r="I108" s="3">
-        <v>1</v>
-      </c>
-      <c r="J108" t="s">
-        <v>273</v>
-      </c>
-      <c r="K108" t="s">
-        <v>423</v>
-      </c>
       <c r="L108" s="2">
-        <v>45951</v>
+        <v>45567</v>
       </c>
       <c r="M108" s="3">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="S108" s="2">
-        <v>46316</v>
+        <v>46479</v>
       </c>
       <c r="T108" s="3">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="U108" s="3"/>
       <c r="V108" s="4">
-        <v>4130258.58</v>
+        <v>2780400.6</v>
       </c>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
-        <v>424</v>
+        <v>42</v>
       </c>
       <c r="B109" t="s">
-        <v>425</v>
-      </c>
-      <c r="C109" s="2">
-        <v>45526</v>
+        <v>421</v>
       </c>
       <c r="D109" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E109" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F109" t="s">
-        <v>424</v>
+        <v>26</v>
       </c>
       <c r="G109" t="s">
-        <v>427</v>
+        <v>264</v>
       </c>
       <c r="H109" s="2">
-        <v>45932</v>
+        <v>46246</v>
       </c>
       <c r="I109" s="3">
-        <v>306</v>
+        <v>1</v>
       </c>
       <c r="J109" t="s">
-        <v>52</v>
-      </c>
-      <c r="K109" t="s">
-        <v>428</v>
+        <v>262</v>
       </c>
       <c r="M109" s="3"/>
-      <c r="S109" s="2">
-        <v>47748</v>
-      </c>
-      <c r="T109" s="3">
-        <v>1510</v>
-      </c>
+      <c r="T109" s="3"/>
       <c r="U109" s="3"/>
       <c r="V109" s="4">
-        <v>4440928.34</v>
+        <v>3446560</v>
       </c>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" t="s">
+        <v>423</v>
+      </c>
+      <c r="C110" s="2">
+        <v>46232</v>
+      </c>
+      <c r="D110" t="s">
+        <v>44</v>
+      </c>
+      <c r="E110" t="s">
+        <v>424</v>
+      </c>
+      <c r="F110" t="s">
         <v>26</v>
       </c>
-      <c r="B110" t="s">
-        <v>429</v>
-      </c>
-      <c r="C110" s="2">
-        <v>45560</v>
-      </c>
-      <c r="D110" t="s">
-        <v>24</v>
-      </c>
-      <c r="E110" t="s">
-        <v>430</v>
-      </c>
-      <c r="F110" t="s">
-        <v>431</v>
-      </c>
       <c r="G110" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="H110" s="2">
-        <v>45930</v>
+        <v>46237</v>
       </c>
       <c r="I110" s="3">
-        <v>308</v>
+        <v>10</v>
       </c>
       <c r="J110" t="s">
-        <v>38</v>
-      </c>
-      <c r="K110" t="s">
-        <v>433</v>
-      </c>
-      <c r="L110" s="2">
-        <v>45854</v>
-      </c>
-      <c r="M110" s="3">
-        <v>294</v>
-      </c>
-      <c r="S110" s="2">
-        <v>46950</v>
-      </c>
-      <c r="T110" s="3">
-        <v>712</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="M110" s="3"/>
+      <c r="T110" s="3"/>
       <c r="U110" s="3"/>
       <c r="V110" s="4">
-        <v>6210000</v>
+        <v>3446570</v>
       </c>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
-        <v>274</v>
+        <v>26</v>
       </c>
       <c r="B111" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C111" s="2">
-        <v>44607</v>
+        <v>45824</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="F111" t="s">
-        <v>274</v>
+        <v>428</v>
       </c>
       <c r="G111" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="H111" s="2">
-        <v>46196</v>
+        <v>46241</v>
       </c>
       <c r="I111" s="3">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="J111" t="s">
-        <v>52</v>
+        <v>269</v>
       </c>
       <c r="K111" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="L111" s="2">
-        <v>44747</v>
+        <v>45951</v>
       </c>
       <c r="M111" s="3">
-        <v>140</v>
-      </c>
-      <c r="O111" t="s">
-        <v>438</v>
-      </c>
-      <c r="P111" s="2">
-        <v>46573</v>
+        <v>127</v>
       </c>
       <c r="S111" s="2">
-        <v>45111</v>
-      </c>
-      <c r="T111" s="3"/>
-      <c r="U111" s="3">
-        <v>335</v>
-      </c>
+        <v>46316</v>
+      </c>
+      <c r="T111" s="3">
+        <v>69</v>
+      </c>
+      <c r="U111" s="3"/>
       <c r="V111" s="4">
-        <v>6571898.25</v>
+        <v>4130258.58</v>
       </c>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="B112" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C112" s="2">
-        <v>38661</v>
+        <v>45526</v>
       </c>
       <c r="D112" t="s">
         <v>35</v>
       </c>
       <c r="E112" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="F112" t="s">
-        <v>26</v>
+        <v>431</v>
       </c>
       <c r="G112" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="H112" s="2">
-        <v>45993</v>
+        <v>45932</v>
       </c>
       <c r="I112" s="3">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="J112" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K112" t="s">
-        <v>443</v>
-      </c>
-      <c r="L112" s="2">
-        <v>45993</v>
-      </c>
-      <c r="M112" s="3">
-        <v>7332</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="M112" s="3"/>
       <c r="S112" s="2">
-        <v>46540</v>
+        <v>47748</v>
       </c>
       <c r="T112" s="3">
-        <v>302</v>
+        <v>1501</v>
       </c>
       <c r="U112" s="3"/>
       <c r="V112" s="4">
-        <v>9032000</v>
+        <v>4440928.34</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>224</v>
+        <v>26</v>
       </c>
       <c r="B113" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C113" s="2">
         <v>45560</v>
@@ -6875,390 +6857,549 @@
         <v>24</v>
       </c>
       <c r="E113" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="F113" t="s">
-        <v>224</v>
+        <v>438</v>
       </c>
       <c r="G113" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="H113" s="2">
-        <v>45797</v>
+        <v>45930</v>
       </c>
       <c r="I113" s="3">
-        <v>441</v>
+        <v>317</v>
       </c>
       <c r="J113" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K113" t="s">
-        <v>447</v>
-      </c>
-      <c r="M113" s="3"/>
+        <v>440</v>
+      </c>
+      <c r="L113" s="2">
+        <v>45854</v>
+      </c>
+      <c r="M113" s="3">
+        <v>294</v>
+      </c>
       <c r="S113" s="2">
-        <v>46523</v>
+        <v>46950</v>
       </c>
       <c r="T113" s="3">
-        <v>285</v>
+        <v>703</v>
       </c>
       <c r="U113" s="3"/>
       <c r="V113" s="4">
-        <v>9152353</v>
+        <v>6210000</v>
       </c>
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="B114" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C114" s="2">
-        <v>44763</v>
+        <v>44607</v>
       </c>
       <c r="D114" t="s">
-        <v>24</v>
+        <v>366</v>
       </c>
       <c r="E114" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="F114" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="G114" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="H114" s="2">
-        <v>46237</v>
+        <v>46196</v>
       </c>
       <c r="I114" s="3">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="J114" t="s">
-        <v>273</v>
+        <v>52</v>
       </c>
       <c r="K114" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="L114" s="2">
-        <v>45574</v>
+        <v>44747</v>
       </c>
       <c r="M114" s="3">
-        <v>811</v>
+        <v>140</v>
       </c>
       <c r="O114" t="s">
-        <v>59</v>
+        <v>445</v>
       </c>
       <c r="P114" s="2">
-        <v>46313</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>451</v>
-      </c>
-      <c r="R114" s="2">
-        <v>45786</v>
+        <v>46573</v>
       </c>
       <c r="S114" s="2">
-        <v>45218</v>
+        <v>45111</v>
       </c>
       <c r="T114" s="3"/>
       <c r="U114" s="3">
-        <v>75</v>
+        <v>326</v>
       </c>
       <c r="V114" s="4">
-        <v>10934411.34</v>
+        <v>6571898.25</v>
       </c>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>26</v>
+        <v>446</v>
       </c>
       <c r="B115" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C115" s="2">
-        <v>45014</v>
+        <v>38661</v>
       </c>
       <c r="D115" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E115" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F115" t="s">
         <v>26</v>
       </c>
       <c r="G115" t="s">
-        <v>360</v>
+        <v>449</v>
       </c>
       <c r="H115" s="2">
-        <v>46219</v>
+        <v>45993</v>
       </c>
       <c r="I115" s="3">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="J115" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K115" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L115" s="2">
-        <v>45148</v>
+        <v>45993</v>
       </c>
       <c r="M115" s="3">
-        <v>134</v>
-      </c>
-      <c r="O115" t="s">
-        <v>353</v>
-      </c>
-      <c r="P115" s="2">
-        <v>46609</v>
+        <v>7332</v>
       </c>
       <c r="S115" s="2">
-        <v>45518</v>
-      </c>
-      <c r="T115" s="3"/>
-      <c r="U115" s="3">
-        <v>371</v>
-      </c>
+        <v>46540</v>
+      </c>
+      <c r="T115" s="3">
+        <v>293</v>
+      </c>
+      <c r="U115" s="3"/>
       <c r="V115" s="4">
-        <v>17946403.739999998</v>
+        <v>9032000</v>
       </c>
     </row>
     <row r="116" spans="1:22">
       <c r="A116" t="s">
-        <v>455</v>
+        <v>224</v>
       </c>
       <c r="B116" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C116" s="2">
-        <v>45666</v>
+        <v>45560</v>
       </c>
       <c r="D116" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F116" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="G116" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="H116" s="2">
-        <v>46174</v>
+        <v>45797</v>
       </c>
       <c r="I116" s="3">
-        <v>64</v>
+        <v>450</v>
       </c>
       <c r="J116" t="s">
         <v>52</v>
       </c>
+      <c r="K116" t="s">
+        <v>454</v>
+      </c>
       <c r="M116" s="3"/>
-      <c r="T116" s="3"/>
+      <c r="S116" s="2">
+        <v>46523</v>
+      </c>
+      <c r="T116" s="3">
+        <v>276</v>
+      </c>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
-        <v>31106553.600000001</v>
+        <v>9152353</v>
       </c>
     </row>
     <row r="117" spans="1:22">
       <c r="A117" t="s">
-        <v>424</v>
+        <v>42</v>
       </c>
       <c r="B117" t="s">
+        <v>455</v>
+      </c>
+      <c r="C117" s="2">
+        <v>44763</v>
+      </c>
+      <c r="D117" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117" t="s">
+        <v>456</v>
+      </c>
+      <c r="F117" t="s">
+        <v>457</v>
+      </c>
+      <c r="G117" t="s">
+        <v>458</v>
+      </c>
+      <c r="H117" s="2">
+        <v>46238</v>
+      </c>
+      <c r="I117" s="3">
+        <v>9</v>
+      </c>
+      <c r="J117" t="s">
+        <v>269</v>
+      </c>
+      <c r="K117" t="s">
         <v>459</v>
       </c>
-      <c r="C117" s="2">
-        <v>45250</v>
-      </c>
-      <c r="D117" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="L117" s="2">
+        <v>45574</v>
+      </c>
+      <c r="M117" s="3">
+        <v>811</v>
+      </c>
+      <c r="O117" t="s">
+        <v>59</v>
+      </c>
+      <c r="P117" s="2">
+        <v>46313</v>
+      </c>
+      <c r="Q117" t="s">
         <v>460</v>
       </c>
-      <c r="F117" t="s">
-        <v>424</v>
-      </c>
-      <c r="G117" t="s">
-        <v>461</v>
-      </c>
-      <c r="H117" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I117" s="3">
-        <v>838</v>
-      </c>
-      <c r="J117" t="s">
-        <v>52</v>
-      </c>
-      <c r="K117" t="s">
-        <v>462</v>
-      </c>
-      <c r="L117" s="2">
-        <v>45401</v>
-      </c>
-      <c r="M117" s="3">
-        <v>151</v>
+      <c r="R117" s="2">
+        <v>45786</v>
       </c>
       <c r="S117" s="2">
-        <v>47227</v>
-      </c>
-      <c r="T117" s="3">
-        <v>989</v>
-      </c>
-      <c r="U117" s="3"/>
+        <v>45218</v>
+      </c>
+      <c r="T117" s="3"/>
+      <c r="U117" s="3">
+        <v>66</v>
+      </c>
       <c r="V117" s="4">
-        <v>41522909.280000001</v>
+        <v>10934411.34</v>
       </c>
     </row>
     <row r="118" spans="1:22">
       <c r="A118" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B118" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C118" s="2">
-        <v>44238</v>
+        <v>45014</v>
       </c>
       <c r="D118" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E118" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F118" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G118" t="s">
-        <v>465</v>
+        <v>364</v>
       </c>
       <c r="H118" s="2">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="I118" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J118" t="s">
         <v>52</v>
       </c>
       <c r="K118" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="L118" s="2">
-        <v>44969</v>
+        <v>45148</v>
       </c>
       <c r="M118" s="3">
-        <v>731</v>
+        <v>134</v>
       </c>
       <c r="O118" t="s">
-        <v>467</v>
+        <v>357</v>
       </c>
       <c r="P118" s="2">
-        <v>46798</v>
+        <v>46609</v>
       </c>
       <c r="S118" s="2">
-        <v>45886</v>
+        <v>45518</v>
       </c>
       <c r="T118" s="3"/>
       <c r="U118" s="3">
-        <v>560</v>
+        <v>362</v>
       </c>
       <c r="V118" s="4">
-        <v>41936400</v>
+        <v>17946403.739999998</v>
       </c>
     </row>
     <row r="119" spans="1:22">
       <c r="A119" t="s">
-        <v>42</v>
+        <v>464</v>
       </c>
       <c r="B119" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C119" s="2">
-        <v>45607</v>
+        <v>45666</v>
       </c>
       <c r="D119" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E119" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F119" t="s">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="G119" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H119" s="2">
-        <v>45798</v>
+        <v>46174</v>
       </c>
       <c r="I119" s="3">
-        <v>440</v>
+        <v>73</v>
       </c>
       <c r="J119" t="s">
         <v>52</v>
       </c>
-      <c r="K119" t="s">
-        <v>472</v>
-      </c>
-      <c r="L119" s="2">
-        <v>45798</v>
-      </c>
-      <c r="M119" s="3">
-        <v>191</v>
-      </c>
-      <c r="S119" s="2">
-        <v>46712</v>
-      </c>
-      <c r="T119" s="3">
-        <v>474</v>
-      </c>
+      <c r="M119" s="3"/>
+      <c r="T119" s="3"/>
       <c r="U119" s="3"/>
       <c r="V119" s="4">
-        <v>50963796</v>
+        <v>31106553.600000001</v>
       </c>
     </row>
     <row r="120" spans="1:22">
       <c r="A120" t="s">
-        <v>42</v>
+        <v>431</v>
       </c>
       <c r="B120" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C120" s="2">
-        <v>45664</v>
+        <v>45250</v>
       </c>
       <c r="D120" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E120" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F120" t="s">
-        <v>224</v>
+        <v>431</v>
       </c>
       <c r="G120" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="H120" s="2">
-        <v>45958</v>
+        <v>45400</v>
       </c>
       <c r="I120" s="3">
-        <v>280</v>
+        <v>847</v>
       </c>
       <c r="J120" t="s">
-        <v>28</v>
-      </c>
-      <c r="M120" s="3"/>
-      <c r="T120" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="K120" t="s">
+        <v>471</v>
+      </c>
+      <c r="L120" s="2">
+        <v>45401</v>
+      </c>
+      <c r="M120" s="3">
+        <v>151</v>
+      </c>
+      <c r="S120" s="2">
+        <v>47227</v>
+      </c>
+      <c r="T120" s="3">
+        <v>980</v>
+      </c>
       <c r="U120" s="3"/>
       <c r="V120" s="4">
+        <v>41522909.280000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22">
+      <c r="A121" t="s">
+        <v>42</v>
+      </c>
+      <c r="B121" t="s">
+        <v>472</v>
+      </c>
+      <c r="C121" s="2">
+        <v>44238</v>
+      </c>
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121" t="s">
+        <v>473</v>
+      </c>
+      <c r="F121" t="s">
+        <v>66</v>
+      </c>
+      <c r="G121" t="s">
+        <v>474</v>
+      </c>
+      <c r="H121" s="2">
+        <v>46211</v>
+      </c>
+      <c r="I121" s="3">
+        <v>36</v>
+      </c>
+      <c r="J121" t="s">
+        <v>52</v>
+      </c>
+      <c r="K121" t="s">
+        <v>475</v>
+      </c>
+      <c r="L121" s="2">
+        <v>44969</v>
+      </c>
+      <c r="M121" s="3">
+        <v>731</v>
+      </c>
+      <c r="O121" t="s">
+        <v>476</v>
+      </c>
+      <c r="P121" s="2">
+        <v>46798</v>
+      </c>
+      <c r="S121" s="2">
+        <v>45886</v>
+      </c>
+      <c r="T121" s="3"/>
+      <c r="U121" s="3">
+        <v>551</v>
+      </c>
+      <c r="V121" s="4">
+        <v>41936400</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22">
+      <c r="A122" t="s">
+        <v>42</v>
+      </c>
+      <c r="B122" t="s">
+        <v>477</v>
+      </c>
+      <c r="C122" s="2">
+        <v>45607</v>
+      </c>
+      <c r="D122" t="s">
+        <v>24</v>
+      </c>
+      <c r="E122" t="s">
+        <v>478</v>
+      </c>
+      <c r="F122" t="s">
+        <v>479</v>
+      </c>
+      <c r="G122" t="s">
+        <v>480</v>
+      </c>
+      <c r="H122" s="2">
+        <v>45798</v>
+      </c>
+      <c r="I122" s="3">
+        <v>449</v>
+      </c>
+      <c r="J122" t="s">
+        <v>52</v>
+      </c>
+      <c r="K122" t="s">
+        <v>481</v>
+      </c>
+      <c r="L122" s="2">
+        <v>45798</v>
+      </c>
+      <c r="M122" s="3">
+        <v>191</v>
+      </c>
+      <c r="S122" s="2">
+        <v>46712</v>
+      </c>
+      <c r="T122" s="3">
+        <v>465</v>
+      </c>
+      <c r="U122" s="3"/>
+      <c r="V122" s="4">
+        <v>50963796</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22">
+      <c r="A123" t="s">
+        <v>42</v>
+      </c>
+      <c r="B123" t="s">
+        <v>482</v>
+      </c>
+      <c r="C123" s="2">
+        <v>45664</v>
+      </c>
+      <c r="D123" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123" t="s">
+        <v>483</v>
+      </c>
+      <c r="F123" t="s">
+        <v>224</v>
+      </c>
+      <c r="G123" t="s">
+        <v>484</v>
+      </c>
+      <c r="H123" s="2">
+        <v>45958</v>
+      </c>
+      <c r="I123" s="3">
+        <v>289</v>
+      </c>
+      <c r="J123" t="s">
+        <v>28</v>
+      </c>
+      <c r="M123" s="3"/>
+      <c r="T123" s="3"/>
+      <c r="U123" s="3"/>
+      <c r="V123" s="4">
         <v>253382919</v>
       </c>
     </row>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E91F9A-158D-40C9-8E04-B146FA219FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216C238E-AEED-4878-8B34-6C601AAF8CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="487">
   <si>
     <t>Departamento</t>
   </si>
@@ -837,15 +837,18 @@
     <t>SOLICITAR NOVOS ORÇAMENTOS</t>
   </si>
   <si>
+    <t>202600005026802</t>
+  </si>
+  <si>
+    <t>SISLOG 122001 - Aquisição de Workstations</t>
+  </si>
+  <si>
+    <t>MINUTA CONTRATO E TERMO DE HOMOLOGAÇÃO EM DIGITAÇÃO</t>
+  </si>
+  <si>
     <t>Aquisição</t>
   </si>
   <si>
-    <t>SISLOG 120357 - Aquisição de Workstations</t>
-  </si>
-  <si>
-    <t>ELABORAÇÃO DOD ETP</t>
-  </si>
-  <si>
     <t>202600010023321</t>
   </si>
   <si>
@@ -867,7 +870,10 @@
     <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
   </si>
   <si>
-    <t>TERMO DE REFERÊNCIA</t>
+    <t>GEFIN</t>
+  </si>
+  <si>
+    <t>PARA PROSSEGUIMENTO</t>
   </si>
   <si>
     <t>GEIN</t>
@@ -990,7 +996,7 @@
     <t>SISLOG 121388 GALERA APP</t>
   </si>
   <si>
-    <t>Documentos feitos para nova Contratação</t>
+    <t>Envio para elaboração da Portaria e do Termo de Referência</t>
   </si>
   <si>
     <t>202500005030582</t>
@@ -1042,6 +1048,9 @@
   </si>
   <si>
     <t>SISLOG 121994- Aquisição Webcam e Headset</t>
+  </si>
+  <si>
+    <t>PORTARIA E TERMO DE REFERÊNCIA</t>
   </si>
   <si>
     <t>202500010044120</t>
@@ -1325,7 +1334,7 @@
     <t>202600010062463</t>
   </si>
   <si>
-    <t>Ata de Registro de Preços nº 001/2026, gerenciada por esse Egrégio Tribunal de Justiça do Estado de Goiás, cujo objeto contempla o fornecimento de microcomputadores e acessórios.</t>
+    <t>SISLOG Ata de Registro de Preços nº 001/2026, gerenciada por esse Egrégio Tribunal de Justiça do Estado de Goiás, cujo objeto contempla o fornecimento de microcomputadores e acessórios.</t>
   </si>
   <si>
     <t>AGUARDANDO RETORNO DE OFICIOS DE SOLICITAÇÃO DE AUTORIZAÇÃO A ADESÃO</t>
@@ -1337,10 +1346,7 @@
     <t>SISLOG 113930 -GLOBAL TI Contratação de solução de Inteligência Artificial (IA). Processo 202500010079078 paralelo CCONT</t>
   </si>
   <si>
-    <t>SUTIS GEFIN</t>
-  </si>
-  <si>
-    <t>ATENDER DILIGÊNCIA 14 DA CACTIC</t>
+    <t>Encaminhem-se a GCC para conhecimento do empenho e para devidas providencias quanto ao Apostilamento</t>
   </si>
   <si>
     <t>93/2025</t>
@@ -1425,10 +1431,10 @@
     <t>FORNECEDOR MEMORA. Contratação de mão de obra de infra e banco.</t>
   </si>
   <si>
-    <t>GEPO CACTIC SGI</t>
-  </si>
-  <si>
-    <t>ANEXO II E ATENDER DILIGÊNCIA 15 DA CACTIC SUGESTÃO DE ENVIO A CONTABILIDADE E PROCSET</t>
+    <t>CACTIC  GCC GECONT</t>
+  </si>
+  <si>
+    <t>ATENDER DILIGÊNCIA 21 DA CACTIC  CONTABILIDADE PARA ANÁLISE para cadastro da IPOF</t>
   </si>
   <si>
     <t>83/2023</t>
@@ -1874,6 +1880,7 @@
   <dimension ref="A1:V123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
@@ -1977,7 +1984,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -2013,7 +2020,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -2049,7 +2056,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>840</v>
+        <v>854</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -2085,7 +2092,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
@@ -2121,7 +2128,7 @@
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1106</v>
+        <v>1120</v>
       </c>
       <c r="J6" t="s">
         <v>38</v>
@@ -2169,7 +2176,7 @@
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1107</v>
+        <v>1121</v>
       </c>
       <c r="J7" t="s">
         <v>52</v>
@@ -2222,7 +2229,7 @@
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="J8" t="s">
         <v>52</v>
@@ -2275,7 +2282,7 @@
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="J9" t="s">
         <v>28</v>
@@ -2323,7 +2330,7 @@
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>875</v>
+        <v>889</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
@@ -2371,7 +2378,7 @@
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="J11" t="s">
         <v>28</v>
@@ -2419,7 +2426,7 @@
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1267</v>
+        <v>1281</v>
       </c>
       <c r="J12" t="s">
         <v>52</v>
@@ -2466,7 +2473,7 @@
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1140</v>
+        <v>1154</v>
       </c>
       <c r="J13" t="s">
         <v>52</v>
@@ -2513,7 +2520,7 @@
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1093</v>
+        <v>1107</v>
       </c>
       <c r="J14" t="s">
         <v>52</v>
@@ -2560,7 +2567,7 @@
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>1058</v>
+        <v>1072</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -2607,7 +2614,7 @@
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1102</v>
+        <v>1116</v>
       </c>
       <c r="J16" t="s">
         <v>52</v>
@@ -2654,7 +2661,7 @@
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1140</v>
+        <v>1154</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -2701,7 +2708,7 @@
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>1039</v>
+        <v>1053</v>
       </c>
       <c r="J18" t="s">
         <v>52</v>
@@ -2748,7 +2755,7 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1140</v>
+        <v>1154</v>
       </c>
       <c r="J19" t="s">
         <v>52</v>
@@ -2795,7 +2802,7 @@
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1213</v>
+        <v>1227</v>
       </c>
       <c r="J20" t="s">
         <v>28</v>
@@ -2831,7 +2838,7 @@
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1095</v>
+        <v>1109</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
@@ -2878,7 +2885,7 @@
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1339</v>
+        <v>1353</v>
       </c>
       <c r="J22" t="s">
         <v>52</v>
@@ -2925,7 +2932,7 @@
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1240</v>
+        <v>1254</v>
       </c>
       <c r="J23" t="s">
         <v>38</v>
@@ -2970,7 +2977,7 @@
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="J24" t="s">
         <v>28</v>
@@ -3006,7 +3013,7 @@
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>1021</v>
+        <v>1035</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
@@ -3053,7 +3060,7 @@
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>1023</v>
+        <v>1037</v>
       </c>
       <c r="J26" t="s">
         <v>52</v>
@@ -3100,7 +3107,7 @@
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
@@ -3142,7 +3149,7 @@
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1113</v>
+        <v>1127</v>
       </c>
       <c r="J28" t="s">
         <v>52</v>
@@ -3189,7 +3196,7 @@
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1204</v>
+        <v>1218</v>
       </c>
       <c r="J29" t="s">
         <v>28</v>
@@ -3225,7 +3232,7 @@
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="J30" t="s">
         <v>28</v>
@@ -3261,7 +3268,7 @@
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>996</v>
+        <v>1010</v>
       </c>
       <c r="J31" t="s">
         <v>28</v>
@@ -3297,7 +3304,7 @@
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1072</v>
+        <v>1086</v>
       </c>
       <c r="J32" t="s">
         <v>38</v>
@@ -3344,7 +3351,7 @@
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="J33" t="s">
         <v>38</v>
@@ -3391,7 +3398,7 @@
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>995</v>
+        <v>1009</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
@@ -3427,7 +3434,7 @@
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>980</v>
+        <v>994</v>
       </c>
       <c r="J35" t="s">
         <v>28</v>
@@ -3463,7 +3470,7 @@
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="J36" t="s">
         <v>28</v>
@@ -3499,7 +3506,7 @@
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>1011</v>
+        <v>1025</v>
       </c>
       <c r="J37" t="s">
         <v>38</v>
@@ -3546,7 +3553,7 @@
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>1038</v>
+        <v>1052</v>
       </c>
       <c r="J38" t="s">
         <v>28</v>
@@ -3582,7 +3589,7 @@
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
@@ -3632,7 +3639,7 @@
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="J40" t="s">
         <v>28</v>
@@ -3668,7 +3675,7 @@
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -3715,7 +3722,7 @@
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>821</v>
+        <v>835</v>
       </c>
       <c r="J42" t="s">
         <v>28</v>
@@ -3751,7 +3758,7 @@
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="J43" t="s">
         <v>28</v>
@@ -3787,7 +3794,7 @@
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="J44" t="s">
         <v>38</v>
@@ -3831,7 +3838,7 @@
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="J45" t="s">
         <v>38</v>
@@ -3873,7 +3880,7 @@
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>759</v>
+        <v>773</v>
       </c>
       <c r="J46" t="s">
         <v>38</v>
@@ -3915,7 +3922,7 @@
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="J47" t="s">
         <v>38</v>
@@ -3933,7 +3940,7 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1131</v>
+        <v>1117</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -3964,7 +3971,7 @@
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="J48" t="s">
         <v>38</v>
@@ -4014,7 +4021,7 @@
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="J49" t="s">
         <v>38</v>
@@ -4032,7 +4039,7 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1096</v>
+        <v>1082</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
@@ -4063,7 +4070,7 @@
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="J50" t="s">
         <v>28</v>
@@ -4107,7 +4114,7 @@
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="J51" t="s">
         <v>28</v>
@@ -4143,7 +4150,7 @@
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="J52" t="s">
         <v>28</v>
@@ -4179,7 +4186,7 @@
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="J53" t="s">
         <v>28</v>
@@ -4215,7 +4222,7 @@
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="J54" t="s">
         <v>52</v>
@@ -4262,7 +4269,7 @@
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="J55" t="s">
         <v>38</v>
@@ -4298,7 +4305,7 @@
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>1028</v>
+        <v>1042</v>
       </c>
       <c r="J56" t="s">
         <v>28</v>
@@ -4334,7 +4341,7 @@
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>932</v>
+        <v>946</v>
       </c>
       <c r="J57" t="s">
         <v>38</v>
@@ -4370,7 +4377,7 @@
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>948</v>
+        <v>962</v>
       </c>
       <c r="J58" t="s">
         <v>28</v>
@@ -4406,7 +4413,7 @@
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="J59" t="s">
         <v>38</v>
@@ -4442,7 +4449,7 @@
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>709</v>
+        <v>723</v>
       </c>
       <c r="J60" t="s">
         <v>52</v>
@@ -4460,7 +4467,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4491,7 +4498,7 @@
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="J61" t="s">
         <v>28</v>
@@ -4527,7 +4534,7 @@
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="J62" t="s">
         <v>28</v>
@@ -4563,10 +4570,10 @@
         <v>46246</v>
       </c>
       <c r="I63" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J63" t="s">
-        <v>262</v>
+        <v>28</v>
       </c>
       <c r="M63" s="3"/>
       <c r="T63" s="3"/>
@@ -4578,7 +4585,7 @@
         <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C64" s="2">
         <v>46245</v>
@@ -4590,19 +4597,19 @@
         <v>263</v>
       </c>
       <c r="F64" t="s">
-        <v>26</v>
+        <v>177</v>
       </c>
       <c r="G64" t="s">
         <v>264</v>
       </c>
       <c r="H64" s="2">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="I64" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M64" s="3"/>
       <c r="T64" s="3"/>
@@ -4614,31 +4621,31 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C65" s="2">
         <v>46126</v>
       </c>
       <c r="D65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F65" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="G65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H65" s="2">
         <v>46182</v>
       </c>
       <c r="I65" s="3">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="J65" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
@@ -4650,7 +4657,7 @@
         <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C66" s="2">
         <v>46211</v>
@@ -4659,22 +4666,22 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F66" t="s">
-        <v>177</v>
+        <v>273</v>
       </c>
       <c r="G66" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H66" s="2">
-        <v>46241</v>
+        <v>46259</v>
       </c>
       <c r="I66" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J66" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
@@ -4685,10 +4692,10 @@
     </row>
     <row r="67" spans="1:22">
       <c r="A67" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C67" s="2">
         <v>46136</v>
@@ -4697,19 +4704,19 @@
         <v>35</v>
       </c>
       <c r="E67" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F67" t="s">
         <v>169</v>
       </c>
       <c r="G67" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H67" s="2">
         <v>46156</v>
       </c>
       <c r="I67" s="3">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J67" t="s">
         <v>38</v>
@@ -4723,10 +4730,10 @@
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C68" s="2">
         <v>46135</v>
@@ -4735,19 +4742,19 @@
         <v>35</v>
       </c>
       <c r="E68" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H68" s="2">
         <v>46155</v>
       </c>
       <c r="I68" s="3">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="J68" t="s">
         <v>38</v>
@@ -4761,10 +4768,10 @@
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C69" s="2">
         <v>46136</v>
@@ -4773,19 +4780,19 @@
         <v>35</v>
       </c>
       <c r="E69" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H69" s="2">
         <v>46157</v>
       </c>
       <c r="I69" s="3">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -4802,7 +4809,7 @@
         <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C70" s="2">
         <v>45804</v>
@@ -4811,19 +4818,19 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H70" s="2">
         <v>45943</v>
       </c>
       <c r="I70" s="3">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="J70" t="s">
         <v>28</v>
@@ -4840,7 +4847,7 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C71" s="2">
         <v>45513</v>
@@ -4849,25 +4856,25 @@
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F71" t="s">
         <v>128</v>
       </c>
       <c r="G71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H71" s="2">
         <v>45715</v>
       </c>
       <c r="I71" s="3">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="J71" t="s">
         <v>52</v>
       </c>
       <c r="K71" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L71" s="2">
         <v>45712</v>
@@ -4889,7 +4896,7 @@
         <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C72" s="2">
         <v>45659</v>
@@ -4898,25 +4905,25 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F72" t="s">
         <v>66</v>
       </c>
       <c r="G72" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H72" s="2">
         <v>45817</v>
       </c>
       <c r="I72" s="3">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="J72" t="s">
         <v>52</v>
       </c>
       <c r="K72" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L72" s="2">
         <v>45812</v>
@@ -4928,7 +4935,7 @@
         <v>46909</v>
       </c>
       <c r="T72" s="3">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="U72" s="3"/>
       <c r="V72" s="4">
@@ -4940,7 +4947,7 @@
         <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2">
         <v>45492</v>
@@ -4949,7 +4956,7 @@
         <v>44</v>
       </c>
       <c r="E73" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F73" t="s">
         <v>42</v>
@@ -4961,13 +4968,13 @@
         <v>45911</v>
       </c>
       <c r="I73" s="3">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="J73" t="s">
         <v>52</v>
       </c>
       <c r="K73" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L73" s="2">
         <v>45546</v>
@@ -4992,7 +4999,7 @@
         <v>26</v>
       </c>
       <c r="B74" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C74" s="2">
         <v>45786</v>
@@ -5001,19 +5008,19 @@
         <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F74" t="s">
         <v>141</v>
       </c>
       <c r="G74" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H74" s="2">
         <v>45895</v>
       </c>
       <c r="I74" s="3">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="J74" t="s">
         <v>38</v>
@@ -5030,7 +5037,7 @@
         <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C75" s="2">
         <v>45946</v>
@@ -5039,19 +5046,19 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F75" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G75" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H75" s="2">
         <v>46196</v>
       </c>
       <c r="I75" s="3">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J75" t="s">
         <v>28</v>
@@ -5065,10 +5072,10 @@
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B76" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C76" s="2">
         <v>45665</v>
@@ -5077,25 +5084,25 @@
         <v>35</v>
       </c>
       <c r="E76" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H76" s="2">
         <v>46198</v>
       </c>
       <c r="I76" s="3">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J76" t="s">
         <v>38</v>
       </c>
       <c r="K76" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L76" s="2">
         <v>46071</v>
@@ -5104,7 +5111,7 @@
         <v>406</v>
       </c>
       <c r="O76" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P76" s="2">
         <v>46294</v>
@@ -5114,7 +5121,7 @@
       </c>
       <c r="T76" s="3"/>
       <c r="U76" s="3">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="V76" s="4">
         <v>51071</v>
@@ -5134,7 +5141,7 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F77" t="s">
         <v>42</v>
@@ -5146,13 +5153,13 @@
         <v>45790</v>
       </c>
       <c r="I77" s="3">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="J77" t="s">
         <v>52</v>
       </c>
       <c r="K77" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L77" s="2">
         <v>43964</v>
@@ -5180,7 +5187,7 @@
         <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C78" s="2">
         <v>46210</v>
@@ -5189,22 +5196,22 @@
         <v>35</v>
       </c>
       <c r="E78" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>177</v>
       </c>
       <c r="G78" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H78" s="2">
-        <v>46216</v>
+        <v>46259</v>
       </c>
       <c r="I78" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="J78" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M78" s="3"/>
       <c r="T78" s="3"/>
@@ -5218,7 +5225,7 @@
         <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C79" s="2">
         <v>45915</v>
@@ -5227,25 +5234,25 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F79" t="s">
         <v>141</v>
       </c>
       <c r="G79" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H79" s="2">
         <v>46094</v>
       </c>
       <c r="I79" s="3">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="J79" t="s">
         <v>38</v>
       </c>
       <c r="K79" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L79" s="2">
         <v>46086</v>
@@ -5257,7 +5264,7 @@
         <v>47181</v>
       </c>
       <c r="T79" s="3">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="U79" s="3"/>
       <c r="V79" s="4">
@@ -5269,7 +5276,7 @@
         <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C80" s="2">
         <v>45950</v>
@@ -5278,25 +5285,25 @@
         <v>44</v>
       </c>
       <c r="E80" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F80" t="s">
         <v>42</v>
       </c>
       <c r="G80" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H80" s="2">
         <v>45975</v>
       </c>
       <c r="I80" s="3">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="J80" t="s">
         <v>38</v>
       </c>
       <c r="K80" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L80" s="2">
         <v>45978</v>
@@ -5324,7 +5331,7 @@
         <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C81" s="2">
         <v>45915</v>
@@ -5333,25 +5340,25 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F81" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G81" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H81" s="2">
         <v>46241</v>
       </c>
       <c r="I81" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J81" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K81" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L81" s="2">
         <v>46086</v>
@@ -5363,7 +5370,7 @@
         <v>47181</v>
       </c>
       <c r="T81" s="3">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
@@ -5375,7 +5382,7 @@
         <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C82" s="2">
         <v>45915</v>
@@ -5384,25 +5391,25 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F82" t="s">
         <v>141</v>
       </c>
       <c r="G82" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H82" s="2">
         <v>46094</v>
       </c>
       <c r="I82" s="3">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="J82" t="s">
         <v>38</v>
       </c>
       <c r="K82" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L82" s="2">
         <v>46086</v>
@@ -5414,7 +5421,7 @@
         <v>47181</v>
       </c>
       <c r="T82" s="3">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
@@ -5447,13 +5454,13 @@
         <v>45790</v>
       </c>
       <c r="I83" s="3">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="J83" t="s">
         <v>52</v>
       </c>
       <c r="K83" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L83" s="2">
         <v>43964</v>
@@ -5481,7 +5488,7 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C84" s="2">
         <v>46245</v>
@@ -5490,22 +5497,22 @@
         <v>44</v>
       </c>
       <c r="E84" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F84" t="s">
-        <v>26</v>
+        <v>177</v>
       </c>
       <c r="G84" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="H84" s="2">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="I84" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M84" s="3"/>
       <c r="T84" s="3"/>
@@ -5519,7 +5526,7 @@
         <v>42</v>
       </c>
       <c r="B85" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C85" s="2">
         <v>45819</v>
@@ -5528,25 +5535,25 @@
         <v>44</v>
       </c>
       <c r="E85" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F85" t="s">
         <v>42</v>
       </c>
       <c r="G85" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H85" s="2">
         <v>46170</v>
       </c>
       <c r="I85" s="3">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J85" t="s">
         <v>52</v>
       </c>
       <c r="K85" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L85" s="2">
         <v>45904</v>
@@ -5558,7 +5565,7 @@
         <v>46273</v>
       </c>
       <c r="T85" s="3">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
@@ -5570,7 +5577,7 @@
         <v>42</v>
       </c>
       <c r="B86" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C86" s="2">
         <v>45952</v>
@@ -5579,25 +5586,25 @@
         <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F86" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G86" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H86" s="2">
         <v>46087</v>
       </c>
       <c r="I86" s="3">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="J86" t="s">
         <v>52</v>
       </c>
       <c r="K86" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L86" s="2">
         <v>46086</v>
@@ -5609,7 +5616,7 @@
         <v>47910</v>
       </c>
       <c r="T86" s="3">
-        <v>1663</v>
+        <v>1649</v>
       </c>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
@@ -5621,7 +5628,7 @@
         <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C87" s="2">
         <v>45775</v>
@@ -5630,7 +5637,7 @@
         <v>44</v>
       </c>
       <c r="E87" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F87" t="s">
         <v>42</v>
@@ -5642,13 +5649,13 @@
         <v>45861</v>
       </c>
       <c r="I87" s="3">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="J87" t="s">
         <v>38</v>
       </c>
       <c r="K87" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L87" s="2">
         <v>45856</v>
@@ -5670,7 +5677,7 @@
         <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C88" s="2">
         <v>45539</v>
@@ -5679,19 +5686,19 @@
         <v>44</v>
       </c>
       <c r="E88" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F88" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G88" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H88" s="2">
         <v>45607</v>
       </c>
       <c r="I88" s="3">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="J88" t="s">
         <v>52</v>
@@ -5708,7 +5715,7 @@
         <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C89" s="2">
         <v>45840</v>
@@ -5717,25 +5724,25 @@
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F89" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G89" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H89" s="2">
         <v>46002</v>
       </c>
       <c r="I89" s="3">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J89" t="s">
         <v>38</v>
       </c>
       <c r="K89" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L89" s="2">
         <v>46001</v>
@@ -5747,7 +5754,7 @@
         <v>47097</v>
       </c>
       <c r="T89" s="3">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="U89" s="3"/>
       <c r="V89" s="4">
@@ -5759,7 +5766,7 @@
         <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C90" s="2">
         <v>45868</v>
@@ -5768,25 +5775,25 @@
         <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F90" t="s">
         <v>66</v>
       </c>
       <c r="G90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H90" s="2">
         <v>46146</v>
       </c>
       <c r="I90" s="3">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="J90" t="s">
         <v>52</v>
       </c>
       <c r="K90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L90" s="2">
         <v>46077</v>
@@ -5798,7 +5805,7 @@
         <v>47905</v>
       </c>
       <c r="T90" s="3">
-        <v>1658</v>
+        <v>1644</v>
       </c>
       <c r="U90" s="3"/>
       <c r="V90" s="4">
@@ -5810,7 +5817,7 @@
         <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C91" s="2">
         <v>44370</v>
@@ -5819,7 +5826,7 @@
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F91" t="s">
         <v>42</v>
@@ -5831,13 +5838,13 @@
         <v>45881</v>
       </c>
       <c r="I91" s="3">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="J91" t="s">
         <v>52</v>
       </c>
       <c r="K91" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L91" s="2">
         <v>44589</v>
@@ -5846,7 +5853,7 @@
         <v>219</v>
       </c>
       <c r="O91" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P91" s="2">
         <v>46419</v>
@@ -5856,7 +5863,7 @@
       </c>
       <c r="T91" s="3"/>
       <c r="U91" s="3">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="V91" s="4">
         <v>374899.96</v>
@@ -5867,7 +5874,7 @@
         <v>42</v>
       </c>
       <c r="B92" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C92" s="2">
         <v>45422</v>
@@ -5876,25 +5883,25 @@
         <v>44</v>
       </c>
       <c r="E92" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F92" t="s">
         <v>42</v>
       </c>
       <c r="G92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H92" s="2">
         <v>45624</v>
       </c>
       <c r="I92" s="3">
-        <v>623</v>
+        <v>637</v>
       </c>
       <c r="J92" t="s">
         <v>38</v>
       </c>
       <c r="K92" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L92" s="2">
         <v>45544</v>
@@ -5916,7 +5923,7 @@
         <v>26</v>
       </c>
       <c r="B93" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C93" s="2">
         <v>46038</v>
@@ -5925,19 +5932,19 @@
         <v>44</v>
       </c>
       <c r="E93" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
       </c>
       <c r="G93" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H93" s="2">
         <v>46237</v>
       </c>
       <c r="I93" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J93" t="s">
         <v>52</v>
@@ -5954,34 +5961,34 @@
         <v>29</v>
       </c>
       <c r="B94" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C94" s="2">
         <v>44939</v>
       </c>
       <c r="D94" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E94" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F94" t="s">
         <v>29</v>
       </c>
       <c r="G94" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H94" s="2">
         <v>45979</v>
       </c>
       <c r="I94" s="3">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="J94" t="s">
         <v>52</v>
       </c>
       <c r="K94" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L94" s="2">
         <v>45968</v>
@@ -5990,7 +5997,7 @@
         <v>1029</v>
       </c>
       <c r="O94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P94" s="2">
         <v>46426</v>
@@ -6000,7 +6007,7 @@
       </c>
       <c r="T94" s="3"/>
       <c r="U94" s="3">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="V94" s="4">
         <v>706431.6</v>
@@ -6011,7 +6018,7 @@
         <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C95" s="2">
         <v>45673</v>
@@ -6020,7 +6027,7 @@
         <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
@@ -6032,20 +6039,20 @@
         <v>46140</v>
       </c>
       <c r="I95" s="3">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="J95" t="s">
         <v>52</v>
       </c>
       <c r="K95" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M95" s="3"/>
       <c r="S95" s="2">
         <v>46598</v>
       </c>
       <c r="T95" s="3">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
@@ -6057,7 +6064,7 @@
         <v>42</v>
       </c>
       <c r="B96" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C96" s="2">
         <v>45215</v>
@@ -6066,25 +6073,25 @@
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F96" t="s">
         <v>169</v>
       </c>
       <c r="G96" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H96" s="2">
         <v>45687</v>
       </c>
       <c r="I96" s="3">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="J96" t="s">
         <v>38</v>
       </c>
       <c r="K96" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L96" s="2">
         <v>45685</v>
@@ -6096,7 +6103,7 @@
         <v>46780</v>
       </c>
       <c r="T96" s="3">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="U96" s="3"/>
       <c r="V96" s="4">
@@ -6108,7 +6115,7 @@
         <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C97" s="2">
         <v>45366</v>
@@ -6117,25 +6124,25 @@
         <v>44</v>
       </c>
       <c r="E97" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
       </c>
       <c r="G97" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H97" s="2">
         <v>45481</v>
       </c>
       <c r="I97" s="3">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="J97" t="s">
         <v>52</v>
       </c>
       <c r="K97" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L97" s="2">
         <v>45471</v>
@@ -6147,7 +6154,7 @@
         <v>47301</v>
       </c>
       <c r="T97" s="3">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
@@ -6159,34 +6166,34 @@
         <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C98" s="2">
         <v>45152</v>
       </c>
       <c r="D98" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E98" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F98" t="s">
         <v>29</v>
       </c>
       <c r="G98" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H98" s="2">
         <v>45440</v>
       </c>
       <c r="I98" s="3">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="J98" t="s">
         <v>52</v>
       </c>
       <c r="K98" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L98" s="2">
         <v>45303</v>
@@ -6208,7 +6215,7 @@
         <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C99" s="2">
         <v>45373</v>
@@ -6217,25 +6224,25 @@
         <v>44</v>
       </c>
       <c r="E99" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F99" t="s">
         <v>42</v>
       </c>
       <c r="G99" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H99" s="2">
         <v>45492</v>
       </c>
       <c r="I99" s="3">
-        <v>755</v>
+        <v>769</v>
       </c>
       <c r="J99" t="s">
         <v>52</v>
       </c>
       <c r="K99" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L99" s="2">
         <v>45492</v>
@@ -6247,7 +6254,7 @@
         <v>46587</v>
       </c>
       <c r="T99" s="3">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
@@ -6259,7 +6266,7 @@
         <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C100" s="2">
         <v>44663</v>
@@ -6268,7 +6275,7 @@
         <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F100" t="s">
         <v>128</v>
@@ -6280,13 +6287,13 @@
         <v>45588</v>
       </c>
       <c r="I100" s="3">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="J100" t="s">
         <v>52</v>
       </c>
       <c r="K100" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L100" s="2">
         <v>44893</v>
@@ -6314,7 +6321,7 @@
         <v>42</v>
       </c>
       <c r="B101" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C101" s="2">
         <v>45826</v>
@@ -6323,25 +6330,25 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F101" t="s">
         <v>66</v>
       </c>
       <c r="G101" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H101" s="2">
         <v>46079</v>
       </c>
       <c r="I101" s="3">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="J101" t="s">
         <v>52</v>
       </c>
       <c r="K101" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L101" s="2">
         <v>46076</v>
@@ -6353,7 +6360,7 @@
         <v>47903</v>
       </c>
       <c r="T101" s="3">
-        <v>1656</v>
+        <v>1642</v>
       </c>
       <c r="U101" s="3"/>
       <c r="V101" s="4">
@@ -6362,10 +6369,10 @@
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B102" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C102" s="2">
         <v>46150</v>
@@ -6374,19 +6381,19 @@
         <v>44</v>
       </c>
       <c r="E102" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F102" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H102" s="2">
         <v>46206</v>
       </c>
       <c r="I102" s="3">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="J102" t="s">
         <v>52</v>
@@ -6403,7 +6410,7 @@
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C103" s="2">
         <v>46094</v>
@@ -6412,19 +6419,19 @@
         <v>44</v>
       </c>
       <c r="E103" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F103" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G103" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H103" s="2">
         <v>46211</v>
       </c>
       <c r="I103" s="3">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="J103" t="s">
         <v>52</v>
@@ -6441,7 +6448,7 @@
         <v>42</v>
       </c>
       <c r="B104" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C104" s="2">
         <v>45950</v>
@@ -6450,25 +6457,25 @@
         <v>44</v>
       </c>
       <c r="E104" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F104" t="s">
         <v>42</v>
       </c>
       <c r="G104" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H104" s="2">
         <v>45988</v>
       </c>
       <c r="I104" s="3">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="J104" t="s">
         <v>38</v>
       </c>
       <c r="K104" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L104" s="2">
         <v>45979</v>
@@ -6480,7 +6487,7 @@
         <v>46343</v>
       </c>
       <c r="T104" s="3">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
@@ -6492,7 +6499,7 @@
         <v>42</v>
       </c>
       <c r="B105" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C105" s="2">
         <v>45511</v>
@@ -6501,25 +6508,25 @@
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F105" t="s">
         <v>26</v>
       </c>
       <c r="G105" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H105" s="2">
         <v>45786</v>
       </c>
       <c r="I105" s="3">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="J105" t="s">
         <v>38</v>
       </c>
       <c r="K105" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L105" s="2">
         <v>45794</v>
@@ -6538,7 +6545,7 @@
         <v>26</v>
       </c>
       <c r="B106" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C106" s="2">
         <v>45848</v>
@@ -6547,25 +6554,25 @@
         <v>35</v>
       </c>
       <c r="E106" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F106" t="s">
         <v>224</v>
       </c>
       <c r="G106" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H106" s="2">
         <v>46014</v>
       </c>
       <c r="I106" s="3">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="J106" t="s">
         <v>38</v>
       </c>
       <c r="K106" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L106" s="2">
         <v>46008</v>
@@ -6577,7 +6584,7 @@
         <v>46373</v>
       </c>
       <c r="T106" s="3">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
@@ -6589,28 +6596,28 @@
         <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C107" s="2">
         <v>46030</v>
       </c>
       <c r="D107" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E107" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F107" t="s">
         <v>29</v>
       </c>
       <c r="G107" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H107" s="2">
         <v>46237</v>
       </c>
       <c r="I107" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J107" t="s">
         <v>52</v>
@@ -6627,7 +6634,7 @@
         <v>42</v>
       </c>
       <c r="B108" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C108" s="2">
         <v>45365</v>
@@ -6636,25 +6643,25 @@
         <v>35</v>
       </c>
       <c r="E108" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F108" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G108" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H108" s="2">
         <v>45568</v>
       </c>
       <c r="I108" s="3">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="J108" t="s">
         <v>52</v>
       </c>
       <c r="K108" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="L108" s="2">
         <v>45567</v>
@@ -6666,7 +6673,7 @@
         <v>46479</v>
       </c>
       <c r="T108" s="3">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="U108" s="3"/>
       <c r="V108" s="4">
@@ -6678,13 +6685,16 @@
         <v>42</v>
       </c>
       <c r="B109" t="s">
-        <v>421</v>
+        <v>424</v>
+      </c>
+      <c r="C109" s="2">
+        <v>46245</v>
       </c>
       <c r="D109" t="s">
         <v>44</v>
       </c>
       <c r="E109" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F109" t="s">
         <v>26</v>
@@ -6693,13 +6703,13 @@
         <v>264</v>
       </c>
       <c r="H109" s="2">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="I109" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J109" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M109" s="3"/>
       <c r="T109" s="3"/>
@@ -6713,7 +6723,7 @@
         <v>42</v>
       </c>
       <c r="B110" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C110" s="2">
         <v>46232</v>
@@ -6722,22 +6732,22 @@
         <v>44</v>
       </c>
       <c r="E110" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F110" t="s">
         <v>26</v>
       </c>
       <c r="G110" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="H110" s="2">
         <v>46237</v>
       </c>
       <c r="I110" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J110" t="s">
-        <v>262</v>
+        <v>28</v>
       </c>
       <c r="M110" s="3"/>
       <c r="T110" s="3"/>
@@ -6751,7 +6761,7 @@
         <v>26</v>
       </c>
       <c r="B111" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C111" s="2">
         <v>45824</v>
@@ -6760,25 +6770,25 @@
         <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F111" t="s">
-        <v>428</v>
+        <v>128</v>
       </c>
       <c r="G111" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H111" s="2">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="I111" s="3">
         <v>6</v>
       </c>
       <c r="J111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K111" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L111" s="2">
         <v>45951</v>
@@ -6790,7 +6800,7 @@
         <v>46316</v>
       </c>
       <c r="T111" s="3">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="U111" s="3"/>
       <c r="V111" s="4">
@@ -6799,10 +6809,10 @@
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B112" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C112" s="2">
         <v>45526</v>
@@ -6811,32 +6821,32 @@
         <v>35</v>
       </c>
       <c r="E112" t="s">
+        <v>435</v>
+      </c>
+      <c r="F112" t="s">
         <v>433</v>
       </c>
-      <c r="F112" t="s">
-        <v>431</v>
-      </c>
       <c r="G112" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H112" s="2">
         <v>45932</v>
       </c>
       <c r="I112" s="3">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="J112" t="s">
         <v>52</v>
       </c>
       <c r="K112" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M112" s="3"/>
       <c r="S112" s="2">
         <v>47748</v>
       </c>
       <c r="T112" s="3">
-        <v>1501</v>
+        <v>1487</v>
       </c>
       <c r="U112" s="3"/>
       <c r="V112" s="4">
@@ -6848,7 +6858,7 @@
         <v>26</v>
       </c>
       <c r="B113" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C113" s="2">
         <v>45560</v>
@@ -6857,25 +6867,25 @@
         <v>24</v>
       </c>
       <c r="E113" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F113" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G113" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H113" s="2">
         <v>45930</v>
       </c>
       <c r="I113" s="3">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="J113" t="s">
         <v>38</v>
       </c>
       <c r="K113" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L113" s="2">
         <v>45854</v>
@@ -6887,7 +6897,7 @@
         <v>46950</v>
       </c>
       <c r="T113" s="3">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="U113" s="3"/>
       <c r="V113" s="4">
@@ -6896,37 +6906,37 @@
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B114" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C114" s="2">
         <v>44607</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E114" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F114" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G114" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H114" s="2">
         <v>46196</v>
       </c>
       <c r="I114" s="3">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J114" t="s">
         <v>52</v>
       </c>
       <c r="K114" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L114" s="2">
         <v>44747</v>
@@ -6935,7 +6945,7 @@
         <v>140</v>
       </c>
       <c r="O114" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P114" s="2">
         <v>46573</v>
@@ -6945,7 +6955,7 @@
       </c>
       <c r="T114" s="3"/>
       <c r="U114" s="3">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="V114" s="4">
         <v>6571898.25</v>
@@ -6953,10 +6963,10 @@
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B115" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C115" s="2">
         <v>38661</v>
@@ -6965,25 +6975,25 @@
         <v>35</v>
       </c>
       <c r="E115" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F115" t="s">
         <v>26</v>
       </c>
       <c r="G115" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H115" s="2">
         <v>45993</v>
       </c>
       <c r="I115" s="3">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="J115" t="s">
         <v>38</v>
       </c>
       <c r="K115" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L115" s="2">
         <v>45993</v>
@@ -6995,7 +7005,7 @@
         <v>46540</v>
       </c>
       <c r="T115" s="3">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="U115" s="3"/>
       <c r="V115" s="4">
@@ -7007,7 +7017,7 @@
         <v>224</v>
       </c>
       <c r="B116" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C116" s="2">
         <v>45560</v>
@@ -7016,32 +7026,32 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F116" t="s">
         <v>224</v>
       </c>
       <c r="G116" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H116" s="2">
         <v>45797</v>
       </c>
       <c r="I116" s="3">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="J116" t="s">
         <v>52</v>
       </c>
       <c r="K116" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M116" s="3"/>
       <c r="S116" s="2">
         <v>46523</v>
       </c>
       <c r="T116" s="3">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
@@ -7053,7 +7063,7 @@
         <v>42</v>
       </c>
       <c r="B117" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C117" s="2">
         <v>44763</v>
@@ -7062,25 +7072,25 @@
         <v>24</v>
       </c>
       <c r="E117" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F117" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G117" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H117" s="2">
-        <v>46238</v>
+        <v>46259</v>
       </c>
       <c r="I117" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J117" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K117" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L117" s="2">
         <v>45574</v>
@@ -7095,7 +7105,7 @@
         <v>46313</v>
       </c>
       <c r="Q117" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="R117" s="2">
         <v>45786</v>
@@ -7105,7 +7115,7 @@
       </c>
       <c r="T117" s="3"/>
       <c r="U117" s="3">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="V117" s="4">
         <v>10934411.34</v>
@@ -7116,7 +7126,7 @@
         <v>26</v>
       </c>
       <c r="B118" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C118" s="2">
         <v>45014</v>
@@ -7125,25 +7135,25 @@
         <v>44</v>
       </c>
       <c r="E118" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F118" t="s">
         <v>26</v>
       </c>
       <c r="G118" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H118" s="2">
         <v>46219</v>
       </c>
       <c r="I118" s="3">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J118" t="s">
         <v>52</v>
       </c>
       <c r="K118" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L118" s="2">
         <v>45148</v>
@@ -7152,7 +7162,7 @@
         <v>134</v>
       </c>
       <c r="O118" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P118" s="2">
         <v>46609</v>
@@ -7162,7 +7172,7 @@
       </c>
       <c r="T118" s="3"/>
       <c r="U118" s="3">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="V118" s="4">
         <v>17946403.739999998</v>
@@ -7170,10 +7180,10 @@
     </row>
     <row r="119" spans="1:22">
       <c r="A119" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B119" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C119" s="2">
         <v>45666</v>
@@ -7182,19 +7192,19 @@
         <v>44</v>
       </c>
       <c r="E119" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F119" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G119" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="H119" s="2">
         <v>46174</v>
       </c>
       <c r="I119" s="3">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="J119" t="s">
         <v>52</v>
@@ -7208,10 +7218,10 @@
     </row>
     <row r="120" spans="1:22">
       <c r="A120" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B120" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C120" s="2">
         <v>45250</v>
@@ -7220,25 +7230,25 @@
         <v>35</v>
       </c>
       <c r="E120" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F120" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G120" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H120" s="2">
         <v>45400</v>
       </c>
       <c r="I120" s="3">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="J120" t="s">
         <v>52</v>
       </c>
       <c r="K120" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L120" s="2">
         <v>45401</v>
@@ -7250,7 +7260,7 @@
         <v>47227</v>
       </c>
       <c r="T120" s="3">
-        <v>980</v>
+        <v>966</v>
       </c>
       <c r="U120" s="3"/>
       <c r="V120" s="4">
@@ -7262,7 +7272,7 @@
         <v>42</v>
       </c>
       <c r="B121" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C121" s="2">
         <v>44238</v>
@@ -7271,25 +7281,25 @@
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F121" t="s">
         <v>66</v>
       </c>
       <c r="G121" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H121" s="2">
         <v>46211</v>
       </c>
       <c r="I121" s="3">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="J121" t="s">
         <v>52</v>
       </c>
       <c r="K121" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L121" s="2">
         <v>44969</v>
@@ -7298,7 +7308,7 @@
         <v>731</v>
       </c>
       <c r="O121" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="P121" s="2">
         <v>46798</v>
@@ -7308,7 +7318,7 @@
       </c>
       <c r="T121" s="3"/>
       <c r="U121" s="3">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="V121" s="4">
         <v>41936400</v>
@@ -7319,7 +7329,7 @@
         <v>42</v>
       </c>
       <c r="B122" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C122" s="2">
         <v>45607</v>
@@ -7328,25 +7338,25 @@
         <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F122" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G122" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H122" s="2">
         <v>45798</v>
       </c>
       <c r="I122" s="3">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="J122" t="s">
         <v>52</v>
       </c>
       <c r="K122" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L122" s="2">
         <v>45798</v>
@@ -7358,7 +7368,7 @@
         <v>46712</v>
       </c>
       <c r="T122" s="3">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="U122" s="3"/>
       <c r="V122" s="4">
@@ -7370,7 +7380,7 @@
         <v>42</v>
       </c>
       <c r="B123" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C123" s="2">
         <v>45664</v>
@@ -7379,19 +7389,19 @@
         <v>24</v>
       </c>
       <c r="E123" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F123" t="s">
         <v>224</v>
       </c>
       <c r="G123" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H123" s="2">
         <v>45958</v>
       </c>
       <c r="I123" s="3">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="J123" t="s">
         <v>28</v>
